--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,8 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0&quot; pcm&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -79,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,8 +101,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1439,74 +1443,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>290000</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Stubbin Close, Rawmarsh, Rotherham</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>S62</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>250000</v>
-      </c>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n">
-        <v>1368</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>William H. Brown, Rotherham</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>garden, garage</t>
-        </is>
-      </c>
-      <c r="T12" s="12" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Norstead Crescent, Bramley, Rotherham, S66 2SH</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>S66</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="5" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>181500</v>
+      </c>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n">
+        <v>1556</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Carly Wilson Estates, Wickersley</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>garden, garage, no chain</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -1517,9 +1519,9 @@
         </is>
       </c>
       <c r="V12" s="7" t="inlineStr"/>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>70e024b9c5299a9be193ba55fe0fa0df9050a18a</t>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>5c20f40f2c8055db4a59c041c47c0ac6f70b4c70</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1589,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T13" s="12" t="inlineStr">
+      <c r="T13" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -1643,7 +1645,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="12" t="n">
         <v>26.9</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -1672,7 +1674,7 @@
           <t>garden, no chain</t>
         </is>
       </c>
-      <c r="T14" s="12" t="inlineStr">
+      <c r="T14" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -1753,7 +1755,7 @@
           <t>garden, off-street parking</t>
         </is>
       </c>
-      <c r="T15" s="12" t="inlineStr">
+      <c r="T15" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -1836,7 +1838,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T16" s="12" t="inlineStr">
+      <c r="T16" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -1892,7 +1894,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -1921,7 +1923,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T17" s="12" t="inlineStr">
+      <c r="T17" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -1977,7 +1979,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <v>-8.1</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -2006,7 +2008,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T18" s="12" t="inlineStr">
+      <c r="T18" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2062,7 +2064,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <v>12.4</v>
       </c>
       <c r="L19" s="10" t="n">
@@ -2091,7 +2093,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T19" s="12" t="inlineStr">
+      <c r="T19" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2147,7 +2149,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K20" s="12" t="n">
         <v>20.9</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -2176,7 +2178,7 @@
           <t>garden, off-street parking</t>
         </is>
       </c>
-      <c r="T20" s="12" t="inlineStr">
+      <c r="T20" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2232,7 +2234,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="L21" s="10" t="n">
@@ -2261,7 +2263,7 @@
           <t>garden, south facing garden</t>
         </is>
       </c>
-      <c r="T21" s="12" t="inlineStr">
+      <c r="T21" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2319,7 +2321,7 @@
           <t>leasehold</t>
         </is>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="L22" s="10" t="n">
@@ -2348,7 +2350,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T22" s="12" t="inlineStr">
+      <c r="T22" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2404,7 +2406,7 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="12" t="n">
         <v>29.8</v>
       </c>
       <c r="L23" s="10" t="n">
@@ -2433,7 +2435,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T23" s="12" t="inlineStr">
+      <c r="T23" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2514,7 +2516,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T24" s="12" t="inlineStr">
+      <c r="T24" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2593,7 +2595,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T25" s="12" t="inlineStr">
+      <c r="T25" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2674,7 +2676,7 @@
           <t>garden, no chain</t>
         </is>
       </c>
-      <c r="T26" s="12" t="inlineStr">
+      <c r="T26" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2753,7 +2755,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T27" s="12" t="inlineStr">
+      <c r="T27" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2828,7 +2830,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T28" s="12" t="inlineStr">
+      <c r="T28" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2907,7 +2909,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T29" s="12" t="inlineStr">
+      <c r="T29" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -2988,7 +2990,7 @@
           <t>garden, no chain</t>
         </is>
       </c>
-      <c r="T30" s="12" t="inlineStr">
+      <c r="T30" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3067,7 +3069,7 @@
           <t>garden, garage</t>
         </is>
       </c>
-      <c r="T31" s="12" t="inlineStr">
+      <c r="T31" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3086,7 +3088,7 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -3094,27 +3096,27 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>185000</v>
+        <v>240000</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Derbyshire Lane, Norton Lees, S8 8SF</t>
+          <t>Whernside Avenue, Chapeltown</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -3123,36 +3125,30 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K32" s="11" t="n">
-        <v>-33.7</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>279000</v>
-      </c>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n">
-        <v>1960</v>
-      </c>
+      <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Staves Estate Agents, Sheffield</t>
+          <t>Haybrook, Chapeltown</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
-        </is>
-      </c>
-      <c r="T32" s="12" t="inlineStr">
+          <t>garden, garage</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3165,13 +3161,13 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>e76026472cdfa7dddeee8ac961216d4bbd6593c7</t>
+          <t>805e6123e2cbfbc89c539ee6d856e87b0dbb5a9a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
@@ -3179,27 +3175,27 @@
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>170000</v>
+        <v>290000</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Cairns Road, Beighton, Sheffield, S20 1BH</t>
+          <t>Stubbin Close, Rawmarsh, Rotherham</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -3208,15 +3204,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K33" s="11" t="n">
-        <v>11.8</v>
+      <c r="K33" s="12" t="n">
+        <v>16</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>152000</v>
+        <v>250000</v>
       </c>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n">
-        <v>2132</v>
+        <v>1368</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>0</v>
@@ -3224,20 +3220,20 @@
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>2Roost, Sheffield</t>
+          <t>William H. Brown, Rotherham</t>
         </is>
       </c>
       <c r="S33" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
-        </is>
-      </c>
-      <c r="T33" s="12" t="inlineStr">
+          <t>garden, garage</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3250,7 +3246,7 @@
       <c r="V33" s="7" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>45942ffccb4344b76e41a7e0a798ca3007819428</t>
+          <t>70e024b9c5299a9be193ba55fe0fa0df9050a18a</t>
         </is>
       </c>
     </row>
@@ -3264,22 +3260,22 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>300000</v>
+        <v>185000</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Cawthorne Grove, Millhouses, Sheffield</t>
+          <t>Derbyshire Lane, Norton Lees, S8 8SF</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -3287,23 +3283,21 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="I34" s="8" t="n">
-        <v>863</v>
-      </c>
+      <c r="I34" s="8" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K34" s="11" t="n">
-        <v>5.6</v>
+      <c r="K34" s="12" t="n">
+        <v>-33.7</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>284000</v>
+        <v>279000</v>
       </c>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n">
-        <v>2212</v>
+        <v>1960</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>0</v>
@@ -3311,12 +3305,12 @@
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>Saxton Mee, Sheffield</t>
+          <t>Staves Estate Agents, Sheffield</t>
         </is>
       </c>
       <c r="S34" s="9" t="inlineStr">
@@ -3324,7 +3318,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T34" s="12" t="inlineStr">
+      <c r="T34" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3337,7 +3331,7 @@
       <c r="V34" s="7" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>be6bd4a32c9a3b4c16fc2895f85834db3e4b60fc</t>
+          <t>e76026472cdfa7dddeee8ac961216d4bbd6593c7</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3345,7 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>200000</v>
+        <v>170000</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>3</v>
@@ -3366,12 +3360,12 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Hackthorn Road, Woodseats, S8 8TB</t>
+          <t>Cairns Road, Beighton, Sheffield, S20 1BH</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -3380,15 +3374,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K35" s="11" t="n">
-        <v>2.2</v>
+      <c r="K35" s="12" t="n">
+        <v>11.8</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>195600</v>
+        <v>152000</v>
       </c>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n">
-        <v>2152</v>
+        <v>2132</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>0</v>
@@ -3401,7 +3395,7 @@
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>Staves Estate Agents, Sheffield</t>
+          <t>2Roost, Sheffield</t>
         </is>
       </c>
       <c r="S35" s="9" t="inlineStr">
@@ -3409,7 +3403,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T35" s="12" t="inlineStr">
+      <c r="T35" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3422,7 +3416,7 @@
       <c r="V35" s="7" t="inlineStr"/>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>735fdffb5106fb5fd33d2b4fc23974bec92f8168</t>
+          <t>45942ffccb4344b76e41a7e0a798ca3007819428</t>
         </is>
       </c>
     </row>
@@ -3436,44 +3430,46 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>175000</v>
+        <v>300000</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Grasscroft Close, Loundsley Green, Chesterfield</t>
+          <t>Cawthorne Grove, Millhouses, Sheffield</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>S40</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="n"/>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>863</v>
+      </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K36" s="11" t="n">
-        <v>16.7</v>
+      <c r="K36" s="12" t="n">
+        <v>5.6</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>150000</v>
+        <v>284000</v>
       </c>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n">
-        <v>2712</v>
+        <v>2212</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>0</v>
@@ -3486,7 +3482,7 @@
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>Haus, Chesterfield</t>
+          <t>Saxton Mee, Sheffield</t>
         </is>
       </c>
       <c r="S36" s="9" t="inlineStr">
@@ -3494,7 +3490,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T36" s="12" t="inlineStr">
+      <c r="T36" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3507,7 +3503,7 @@
       <c r="V36" s="7" t="inlineStr"/>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>88ba07877f10ce8123d91f97b5b8085ed03be06a</t>
+          <t>be6bd4a32c9a3b4c16fc2895f85834db3e4b60fc</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3517,7 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>175000</v>
+        <v>200000</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>3</v>
@@ -3536,31 +3532,29 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Parkfield Place, Sheffield</t>
+          <t>Hackthorn Road, Woodseats, S8 8TB</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>1179</v>
-      </c>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="n"/>
       <c r="J37" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K37" s="11" t="n">
-        <v>-7.2</v>
+      <c r="K37" s="12" t="n">
+        <v>2.2</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>188500</v>
+        <v>195600</v>
       </c>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n">
-        <v>8900</v>
+        <v>2152</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>0</v>
@@ -3573,7 +3567,7 @@
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>Highgates, Sheffield</t>
+          <t>Staves Estate Agents, Sheffield</t>
         </is>
       </c>
       <c r="S37" s="9" t="inlineStr">
@@ -3581,7 +3575,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T37" s="12" t="inlineStr">
+      <c r="T37" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3594,7 +3588,7 @@
       <c r="V37" s="7" t="inlineStr"/>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>74a245b52c34a93f4e5d15135c82cdedfa732893</t>
+          <t>735fdffb5106fb5fd33d2b4fc23974bec92f8168</t>
         </is>
       </c>
     </row>
@@ -3608,27 +3602,27 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>280000</v>
+        <v>175000</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Wheatsheaf Way, Clowne, Chesterfield</t>
+          <t>Grasscroft Close, Loundsley Green, Chesterfield</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S40</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -3637,15 +3631,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K38" s="11" t="n">
-        <v>-12.5</v>
+      <c r="K38" s="12" t="n">
+        <v>16.7</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>320000</v>
+        <v>150000</v>
       </c>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n">
-        <v>708</v>
+        <v>2712</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>0</v>
@@ -3658,7 +3652,7 @@
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>William H. Brown, Chesterfield</t>
+          <t>Haus, Chesterfield</t>
         </is>
       </c>
       <c r="S38" s="9" t="inlineStr">
@@ -3666,7 +3660,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T38" s="12" t="inlineStr">
+      <c r="T38" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3679,7 +3673,7 @@
       <c r="V38" s="7" t="inlineStr"/>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>d6aff905b3a0eb99bc78c72f511393bb10ba6dc0</t>
+          <t>88ba07877f10ce8123d91f97b5b8085ed03be06a</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3687,7 @@
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>270000</v>
+        <v>175000</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>3</v>
@@ -3703,36 +3697,36 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Newbold Road, Newbold, Chesterfield, S41 7AF</t>
+          <t>Parkfield Place, Sheffield</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="I39" s="8" t="n">
-        <v>903</v>
+        <v>1179</v>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K39" s="11" t="n">
-        <v>54.3</v>
+      <c r="K39" s="12" t="n">
+        <v>-7.2</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>175000</v>
+        <v>188500</v>
       </c>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n">
-        <v>3880</v>
+        <v>8900</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>0</v>
@@ -3745,7 +3739,7 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Dales &amp; Peaks, Chesterfield</t>
+          <t>Highgates, Sheffield</t>
         </is>
       </c>
       <c r="S39" s="9" t="inlineStr">
@@ -3753,7 +3747,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T39" s="12" t="inlineStr">
+      <c r="T39" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3766,7 +3760,7 @@
       <c r="V39" s="7" t="inlineStr"/>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>be1db2a98a6155194944e15aec95d6a428dfe17a</t>
+          <t>74a245b52c34a93f4e5d15135c82cdedfa732893</t>
         </is>
       </c>
     </row>
@@ -3780,27 +3774,27 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>290000</v>
+        <v>280000</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>High Street, Rotherham, S66</t>
+          <t>Wheatsheaf Way, Clowne, Chesterfield</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -3809,15 +3803,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K40" s="11" t="n">
-        <v>7.4</v>
+      <c r="K40" s="12" t="n">
+        <v>-12.5</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>270000</v>
+        <v>320000</v>
       </c>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n">
-        <v>132</v>
+        <v>708</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>0</v>
@@ -3830,7 +3824,7 @@
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>Yopa, East Midlands &amp; Yorkshire</t>
+          <t>William H. Brown, Chesterfield</t>
         </is>
       </c>
       <c r="S40" s="9" t="inlineStr">
@@ -3838,7 +3832,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T40" s="12" t="inlineStr">
+      <c r="T40" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3851,7 +3845,7 @@
       <c r="V40" s="7" t="inlineStr"/>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>2835eb04b7af4f84564b0b2690d5d7338edbca86</t>
+          <t>d6aff905b3a0eb99bc78c72f511393bb10ba6dc0</t>
         </is>
       </c>
     </row>
@@ -3865,44 +3859,46 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>290000</v>
+        <v>270000</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Marlcliffe Road, Sheffield, S6</t>
+          <t>Newbold Road, Newbold, Chesterfield, S41 7AF</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="n"/>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>903</v>
+      </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K41" s="11" t="n">
-        <v>26.1</v>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>54.3</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>230000</v>
+        <v>175000</v>
       </c>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n">
-        <v>2852</v>
+        <v>3880</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>0</v>
@@ -3910,12 +3906,12 @@
       <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Purplebricks, covering Sheffield</t>
+          <t>Dales &amp; Peaks, Chesterfield</t>
         </is>
       </c>
       <c r="S41" s="9" t="inlineStr">
@@ -3923,7 +3919,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T41" s="12" t="inlineStr">
+      <c r="T41" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -3936,7 +3932,7 @@
       <c r="V41" s="7" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>a513e9f9e9d78b0d957e99c30f81d76bd9a89b94</t>
+          <t>be1db2a98a6155194944e15aec95d6a428dfe17a</t>
         </is>
       </c>
     </row>
@@ -3950,27 +3946,27 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>190000</v>
+        <v>290000</v>
       </c>
       <c r="D42" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>bungalow</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Elder Court, Killamarsh, Sheffield, S21</t>
+          <t>High Street, Rotherham, S66</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -3979,15 +3975,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K42" s="11" t="n">
-        <v>-0.8</v>
+      <c r="K42" s="12" t="n">
+        <v>7.4</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>191500</v>
+        <v>270000</v>
       </c>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n">
-        <v>696</v>
+        <v>132</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>0</v>
@@ -4000,7 +3996,7 @@
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>Key2go Estate &amp; Letting Agents Ltd, Sheffield</t>
+          <t>Yopa, East Midlands &amp; Yorkshire</t>
         </is>
       </c>
       <c r="S42" s="9" t="inlineStr">
@@ -4008,7 +4004,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T42" s="12" t="inlineStr">
+      <c r="T42" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4021,7 +4017,7 @@
       <c r="V42" s="7" t="inlineStr"/>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>e3c1fbb65691a71fdeea3ddb793e33f75b7b5e3e</t>
+          <t>2835eb04b7af4f84564b0b2690d5d7338edbca86</t>
         </is>
       </c>
     </row>
@@ -4035,46 +4031,44 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>190000</v>
+        <v>290000</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>bungalow</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>Hoades Avenue, Woodsetts</t>
+          <t>Marlcliffe Road, Sheffield, S6</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>655</v>
-      </c>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>14.8</v>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>26.1</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>165500</v>
+        <v>230000</v>
       </c>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n">
-        <v>112</v>
+        <v>2852</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>0</v>
@@ -4082,12 +4076,12 @@
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Worksop</t>
+          <t>Purplebricks, covering Sheffield</t>
         </is>
       </c>
       <c r="S43" s="9" t="inlineStr">
@@ -4095,7 +4089,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T43" s="12" t="inlineStr">
+      <c r="T43" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4108,7 +4102,7 @@
       <c r="V43" s="7" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>575fc562fbe68efef385f12b125759da675dca82</t>
+          <t>a513e9f9e9d78b0d957e99c30f81d76bd9a89b94</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4116,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>285000</v>
+        <v>190000</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -4137,29 +4131,29 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Firthwood Close, Coal Aston, Dronfield, Derbyshire, S18</t>
+          <t>Elder Court, Killamarsh, Sheffield, S21</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K44" s="11" t="n">
-        <v>-9.9</v>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>-0.8</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>316250</v>
+        <v>191500</v>
       </c>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n">
-        <v>460</v>
+        <v>696</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>0</v>
@@ -4167,12 +4161,12 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>Whitegates, Dronfield</t>
+          <t>Key2go Estate &amp; Letting Agents Ltd, Sheffield</t>
         </is>
       </c>
       <c r="S44" s="9" t="inlineStr">
@@ -4180,7 +4174,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T44" s="12" t="inlineStr">
+      <c r="T44" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4193,7 +4187,7 @@
       <c r="V44" s="7" t="inlineStr"/>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>00fff627c08a1bc1b69944e44da58363027902c9</t>
+          <t>e3c1fbb65691a71fdeea3ddb793e33f75b7b5e3e</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4201,7 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>2</v>
@@ -4217,34 +4211,36 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>bungalow</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Fountains Crescent, Parson Green, Sheffield</t>
+          <t>Hoades Avenue, Woodsetts</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="n"/>
+          <t>S81</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>655</v>
+      </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>-6</v>
+      <c r="K45" s="12" t="n">
+        <v>14.8</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>191500</v>
+        <v>165500</v>
       </c>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n">
-        <v>3496</v>
+        <v>112</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>0</v>
@@ -4257,7 +4253,7 @@
       </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>Hughes Family Estate Agents, Sheffield</t>
+          <t>Martin &amp; Co, Worksop</t>
         </is>
       </c>
       <c r="S45" s="9" t="inlineStr">
@@ -4265,7 +4261,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T45" s="12" t="inlineStr">
+      <c r="T45" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4278,7 +4274,7 @@
       <c r="V45" s="7" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>d0f10a7d5b13c55111f3206322f5e8f112ba7b52</t>
+          <t>575fc562fbe68efef385f12b125759da675dca82</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4288,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>190000</v>
+        <v>285000</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>2</v>
@@ -4302,30 +4298,34 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>bungalow</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>Holme Hall Crescent, Holme Hall, Chesterfield</t>
+          <t>Firthwood Close, Coal Aston, Dronfield, Derbyshire, S18</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="n"/>
-      <c r="L46" s="8" t="n"/>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>316250</v>
+      </c>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n">
-        <v>1572</v>
+        <v>460</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>0</v>
@@ -4333,12 +4333,12 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>Haus, Chesterfield</t>
+          <t>Whitegates, Dronfield</t>
         </is>
       </c>
       <c r="S46" s="9" t="inlineStr">
@@ -4346,7 +4346,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T46" s="12" t="inlineStr">
+      <c r="T46" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4359,7 +4359,7 @@
       <c r="V46" s="7" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>dc60ca39eed00ac7ffe98d78404e8f025d60ab08</t>
+          <t>00fff627c08a1bc1b69944e44da58363027902c9</t>
         </is>
       </c>
     </row>
@@ -4373,51 +4373,57 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>210000</v>
+        <v>180000</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Hoole Street, Sheffield</t>
+          <t>Fountains Crescent, Parson Green, Sheffield</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="n"/>
-      <c r="L47" s="8" t="n"/>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>191500</v>
+      </c>
       <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="N47" s="8" t="n">
+        <v>3496</v>
+      </c>
       <c r="O47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="8" t="n"/>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Crookes</t>
+          <t>Hughes Family Estate Agents, Sheffield</t>
         </is>
       </c>
       <c r="S47" s="9" t="inlineStr">
@@ -4425,7 +4431,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T47" s="12" t="inlineStr">
+      <c r="T47" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4438,7 +4444,7 @@
       <c r="V47" s="7" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>a2f4bf607ef53baf2362d1c968411591a5528485</t>
+          <t>d0f10a7d5b13c55111f3206322f5e8f112ba7b52</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4458,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>2</v>
@@ -4462,22 +4468,20 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Toyne Street, Crookes</t>
+          <t>Holme Hall Crescent, Holme Hall, Chesterfield</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>521</v>
-      </c>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="n"/>
       <c r="J48" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
@@ -4486,7 +4490,9 @@
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
+      <c r="N48" s="8" t="n">
+        <v>1572</v>
+      </c>
       <c r="O48" s="8" t="n">
         <v>0</v>
       </c>
@@ -4498,7 +4504,7 @@
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>Cocker and Carr Ltd, Sheffield</t>
+          <t>Haus, Chesterfield</t>
         </is>
       </c>
       <c r="S48" s="9" t="inlineStr">
@@ -4506,7 +4512,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T48" s="12" t="inlineStr">
+      <c r="T48" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4519,7 +4525,7 @@
       <c r="V48" s="7" t="inlineStr"/>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>7aa7aa43ff2c6f3ffcfe324b4eb926d7a1e39cd3</t>
+          <t>dc60ca39eed00ac7ffe98d78404e8f025d60ab08</t>
         </is>
       </c>
     </row>
@@ -4533,10 +4539,10 @@
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>180000</v>
+        <v>210000</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>1</v>
@@ -4548,18 +4554,18 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Olivet Road, Woodseats, S8 8QS</t>
+          <t>Hoole Street, Sheffield</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
+          <t>leasehold</t>
         </is>
       </c>
       <c r="K49" s="8" t="n"/>
@@ -4572,12 +4578,12 @@
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>Staves Estate Agents, Sheffield</t>
+          <t>Haybrook, Crookes</t>
         </is>
       </c>
       <c r="S49" s="9" t="inlineStr">
@@ -4585,7 +4591,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T49" s="12" t="inlineStr">
+      <c r="T49" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4598,7 +4604,7 @@
       <c r="V49" s="7" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>dab068fdbf0739111707ffa50e614ba36427d88d</t>
+          <t>a2f4bf607ef53baf2362d1c968411591a5528485</t>
         </is>
       </c>
     </row>
@@ -4612,33 +4618,35 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>160000</v>
+        <v>180000</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Monckton Road, Sheffield, S5</t>
+          <t>Toyne Street, Crookes</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n"/>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>521</v>
+      </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
+          <t>freehold</t>
         </is>
       </c>
       <c r="K50" s="8" t="n"/>
@@ -4651,12 +4659,12 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>Saxton Mee, Hillsborough</t>
+          <t>Cocker and Carr Ltd, Sheffield</t>
         </is>
       </c>
       <c r="S50" s="9" t="inlineStr">
@@ -4664,7 +4672,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T50" s="12" t="inlineStr">
+      <c r="T50" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4677,7 +4685,7 @@
       <c r="V50" s="7" t="inlineStr"/>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>f7d5d52c4aa6a6467649e7dd5fd275e154adc80d</t>
+          <t>7aa7aa43ff2c6f3ffcfe324b4eb926d7a1e39cd3</t>
         </is>
       </c>
     </row>
@@ -4694,24 +4702,24 @@
         <v>180000</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Rookery Road, Swinton</t>
+          <t>Olivet Road, Woodseats, S8 8QS</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -4730,12 +4738,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>Bsmart Homes, Swinton</t>
+          <t>Staves Estate Agents, Sheffield</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr">
@@ -4743,7 +4751,7 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="T51" s="12" t="inlineStr">
+      <c r="T51" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4756,13 +4764,13 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>962b68a60941b9948875fcc8b31ac774c742427c</t>
+          <t>dab068fdbf0739111707ffa50e614ba36427d88d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
@@ -4770,65 +4778,59 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Rockingham Gardens, Moorgate</t>
+          <t>Monckton Road, Sheffield, S5</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="L52" s="10" t="n">
-        <v>440000</v>
-      </c>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
-      <c r="N52" s="8" t="n">
-        <v>2104</v>
-      </c>
+      <c r="N52" s="8" t="n"/>
       <c r="O52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Swinton</t>
+          <t>Saxton Mee, Hillsborough</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr">
         <is>
-          <t>garage, no chain</t>
-        </is>
-      </c>
-      <c r="T52" s="12" t="inlineStr">
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T52" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4841,13 +4843,13 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>f9842c79c687b4b4150ecb28cd3dc083bba7e292</t>
+          <t>f7d5d52c4aa6a6467649e7dd5fd275e154adc80d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
@@ -4870,12 +4872,12 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Arthur Road, Sheffield</t>
+          <t>Rookery Road, Swinton</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -4899,15 +4901,15 @@
       </c>
       <c r="R53" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Hillsborough</t>
+          <t>Bsmart Homes, Swinton</t>
         </is>
       </c>
       <c r="S53" s="9" t="inlineStr">
         <is>
-          <t>garage, no chain</t>
-        </is>
-      </c>
-      <c r="T53" s="12" t="inlineStr">
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T53" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -4920,13 +4922,13 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>7efe8bc80748a11513136deee4024db39a8512c6</t>
+          <t>962b68a60941b9948875fcc8b31ac774c742427c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
@@ -4934,7 +4936,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>270000</v>
+        <v>210000</v>
       </c>
       <c r="D54" s="8" t="n">
         <v>3</v>
@@ -4949,29 +4951,31 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Moorland Place, Stannington, Sheffield, S6 6BU</t>
+          <t>Holme Close, Dronfield Woodhouse, Dronfield</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n"/>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>894</v>
+      </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="n">
-        <v>1.9</v>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>31.2</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>265000</v>
+        <v>160000</v>
       </c>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n">
-        <v>596</v>
+        <v>400</v>
       </c>
       <c r="O54" s="8" t="n">
         <v>0</v>
@@ -4984,15 +4988,15 @@
       </c>
       <c r="R54" s="8" t="inlineStr">
         <is>
-          <t>2Roost, Sheffield</t>
+          <t>Saxton Mee (Dronfield) Limited, Dronfield</t>
         </is>
       </c>
       <c r="S54" s="9" t="inlineStr">
         <is>
-          <t>garage</t>
-        </is>
-      </c>
-      <c r="T54" s="12" t="inlineStr">
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T54" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5005,13 +5009,13 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>a3f02107ce8a2b4de5aa130a7948a37ca59b055d</t>
+          <t>0f617541d712a4603b0fc9d2e5ab84ee173ca76a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
@@ -5019,46 +5023,44 @@
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Newbridge Lane, Old Whittington, Chesterfield, S41 9JQ</t>
+          <t>Cambridge Crescent, Rotherham, South Yorkshire, S65</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>S41</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>1338</v>
-      </c>
+          <t>S65</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K55" s="11" t="n">
-        <v>65.3</v>
+      <c r="K55" s="12" t="n">
+        <v>5.6</v>
       </c>
       <c r="L55" s="10" t="n">
-        <v>151250</v>
+        <v>142000</v>
       </c>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n">
-        <v>1720</v>
+        <v>6388</v>
       </c>
       <c r="O55" s="8" t="n">
         <v>0</v>
@@ -5066,20 +5068,20 @@
       <c r="P55" s="8" t="n"/>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R55" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Chesterfield</t>
+          <t>Lincoln Ralph, Rotherham</t>
         </is>
       </c>
       <c r="S55" s="9" t="inlineStr">
         <is>
-          <t>garage</t>
-        </is>
-      </c>
-      <c r="T55" s="12" t="inlineStr">
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T55" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5092,13 +5094,13 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>dc5f92a4890d15bad86cf311d68bba9a8c954bc3</t>
+          <t>12da6f1a6dc0106f9e5c6f1abf417b3642c86014</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
@@ -5106,7 +5108,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>170000</v>
+        <v>300000</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>3</v>
@@ -5116,55 +5118,49 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Queen Mary Road, Sheffield</t>
+          <t>Harvest Road, Wickersley, Rotherham, S66 2HX</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L56" s="10" t="n">
-        <v>155000</v>
-      </c>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
-      <c r="N56" s="8" t="n">
-        <v>4560</v>
-      </c>
+      <c r="N56" s="8" t="n"/>
       <c r="O56" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="8" t="n"/>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R56" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Gleadless</t>
+          <t>Carly Wilson Estates, Wickersley</t>
         </is>
       </c>
       <c r="S56" s="9" t="inlineStr">
         <is>
-          <t>no chain</t>
-        </is>
-      </c>
-      <c r="T56" s="12" t="inlineStr">
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T56" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5177,13 +5173,13 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>a87fd0b66cf9a04ec39cb98822832cd236810ca1</t>
+          <t>47ea15149e28f9b09bc7bd1919818b7a96a06453</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
@@ -5191,7 +5187,7 @@
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>210000</v>
+        <v>300000</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>4</v>
@@ -5201,32 +5197,34 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Danby Avenue, Old Whittington, Chesterfield, S41 9NH</t>
+          <t>Rockingham Gardens, Moorgate</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>S41</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>1779</v>
-      </c>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K57" s="8" t="n"/>
-      <c r="L57" s="8" t="n"/>
+      <c r="K57" s="12" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="L57" s="10" t="n">
+        <v>440000</v>
+      </c>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n">
-        <v>1676</v>
+        <v>2104</v>
       </c>
       <c r="O57" s="8" t="n">
         <v>0</v>
@@ -5239,15 +5237,15 @@
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Chesterfield</t>
+          <t>Haybrook, Swinton</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr">
         <is>
-          <t>garage</t>
-        </is>
-      </c>
-      <c r="T57" s="12" t="inlineStr">
+          <t>garage, no chain</t>
+        </is>
+      </c>
+      <c r="T57" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5260,13 +5258,13 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>18477e68019b85eabe4e795e7e01315f39e74635</t>
+          <t>f9842c79c687b4b4150ecb28cd3dc083bba7e292</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
@@ -5274,10 +5272,10 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>210000</v>
+        <v>180000</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" s="8" t="n">
         <v>1</v>
@@ -5289,12 +5287,12 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Joan Lane, Hooton Levitt, Rotherham</t>
+          <t>Arthur Road, Sheffield</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -5303,36 +5301,30 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K58" s="11" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="L58" s="10" t="n">
-        <v>157750</v>
-      </c>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
-      <c r="N58" s="8" t="n">
-        <v>1348</v>
-      </c>
+      <c r="N58" s="8" t="n"/>
       <c r="O58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="8" t="n"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>William H. Brown, Maltby</t>
+          <t>Haybrook, Hillsborough</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr">
         <is>
-          <t>garage</t>
-        </is>
-      </c>
-      <c r="T58" s="12" t="inlineStr">
+          <t>garage, no chain</t>
+        </is>
+      </c>
+      <c r="T58" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5345,7 +5337,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>4015027fded154718a20ed5dbf04f065a207a898</t>
+          <t>7efe8bc80748a11513136deee4024db39a8512c6</t>
         </is>
       </c>
     </row>
@@ -5359,10 +5351,10 @@
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>180000</v>
+        <v>270000</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>1</v>
@@ -5374,31 +5366,29 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Clarke Avenue, Dinnington, Sheffield</t>
+          <t>Moorland Place, Stannington, Sheffield, S6 6BU</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="I59" s="8" t="n">
-        <v>636</v>
-      </c>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="n"/>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>-14.3</v>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>1.9</v>
       </c>
       <c r="L59" s="10" t="n">
-        <v>210000</v>
+        <v>265000</v>
       </c>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n">
-        <v>904</v>
+        <v>596</v>
       </c>
       <c r="O59" s="8" t="n">
         <v>0</v>
@@ -5406,20 +5396,20 @@
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>Kendra Jacob, Bassetlaw</t>
+          <t>2Roost, Sheffield</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr">
         <is>
-          <t>no chain</t>
-        </is>
-      </c>
-      <c r="T59" s="12" t="inlineStr">
+          <t>garage</t>
+        </is>
+      </c>
+      <c r="T59" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5432,7 +5422,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>85491a32a3f7da450b97c9bc5b46882af22dbe2c</t>
+          <t>a3f02107ce8a2b4de5aa130a7948a37ca59b055d</t>
         </is>
       </c>
     </row>
@@ -5446,44 +5436,46 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>220000</v>
+        <v>250000</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Molloy Street, Sheffield, S8</t>
+          <t>Newbridge Lane, Old Whittington, Chesterfield, S41 9JQ</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="I60" s="8" t="n"/>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>1338</v>
+      </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K60" s="11" t="n">
-        <v>0.6</v>
+      <c r="K60" s="12" t="n">
+        <v>65.3</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>218750</v>
+        <v>151250</v>
       </c>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n">
-        <v>4304</v>
+        <v>1720</v>
       </c>
       <c r="O60" s="8" t="n">
         <v>0</v>
@@ -5491,20 +5483,20 @@
       <c r="P60" s="8" t="n"/>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Woodseats</t>
+          <t>Hunters, Chesterfield</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr">
         <is>
-          <t>no chain</t>
-        </is>
-      </c>
-      <c r="T60" s="12" t="inlineStr">
+          <t>garage</t>
+        </is>
+      </c>
+      <c r="T60" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5517,7 +5509,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>f367c5d301b8f5293d816c998737217b1bcea2d0</t>
+          <t>dc5f92a4890d15bad86cf311d68bba9a8c954bc3</t>
         </is>
       </c>
     </row>
@@ -5531,10 +5523,10 @@
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>225000</v>
+        <v>170000</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>1</v>
@@ -5546,29 +5538,29 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Mulehouse Road, Sheffield</t>
+          <t>Queen Mary Road, Sheffield</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>50.1</v>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="L61" s="10" t="n">
-        <v>149950</v>
+        <v>155000</v>
       </c>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>3364</v>
+        <v>4560</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -5576,12 +5568,12 @@
       <c r="P61" s="8" t="n"/>
       <c r="Q61" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>Evans Lee, Sheffield</t>
+          <t>Haybrook, Gleadless</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr">
@@ -5589,7 +5581,7 @@
           <t>no chain</t>
         </is>
       </c>
-      <c r="T61" s="12" t="inlineStr">
+      <c r="T61" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5602,7 +5594,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>7c5d1d355ceaf823fe89dd98e2e9f07102cf1c58</t>
+          <t>a87fd0b66cf9a04ec39cb98822832cd236810ca1</t>
         </is>
       </c>
     </row>
@@ -5616,44 +5608,42 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>265000</v>
+        <v>210000</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>detached</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Bridge Close, Whitwell, Worksop</t>
+          <t>Danby Avenue, Old Whittington, Chesterfield, S41 9NH</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>S80</t>
-        </is>
-      </c>
-      <c r="I62" s="8" t="n"/>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>1779</v>
+      </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K62" s="11" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="L62" s="10" t="n">
-        <v>143000</v>
-      </c>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>388</v>
+        <v>1676</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -5661,12 +5651,12 @@
       <c r="P62" s="8" t="n"/>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>Heywood Estates, Clowne</t>
+          <t>Hunters, Chesterfield</t>
         </is>
       </c>
       <c r="S62" s="9" t="inlineStr">
@@ -5674,7 +5664,7 @@
           <t>garage</t>
         </is>
       </c>
-      <c r="T62" s="12" t="inlineStr">
+      <c r="T62" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5687,7 +5677,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>ff67b9fae718fda40614dd3a00dcb91a0cd2cc44</t>
+          <t>18477e68019b85eabe4e795e7e01315f39e74635</t>
         </is>
       </c>
     </row>
@@ -5701,46 +5691,44 @@
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>290000</v>
+        <v>210000</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>detached</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Romeley Crescent, Clowne, Chesterfield, S43 4LB</t>
+          <t>Joan Lane, Hooton Levitt, Rotherham</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>S43</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>1395</v>
-      </c>
+          <t>S66</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K63" s="11" t="n">
-        <v>23.9</v>
+      <c r="K63" s="12" t="n">
+        <v>33.1</v>
       </c>
       <c r="L63" s="10" t="n">
-        <v>234000</v>
+        <v>157750</v>
       </c>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>836</v>
+        <v>1348</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -5753,7 +5741,7 @@
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Chesterfield</t>
+          <t>William H. Brown, Maltby</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr">
@@ -5761,7 +5749,7 @@
           <t>garage</t>
         </is>
       </c>
-      <c r="T63" s="12" t="inlineStr">
+      <c r="T63" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5774,7 +5762,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>3b69d10d80464c826830e386051d9078ef963b8c</t>
+          <t>4015027fded154718a20ed5dbf04f065a207a898</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5776,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>285000</v>
+        <v>180000</v>
       </c>
       <c r="D64" s="8" t="n">
         <v>2</v>
@@ -5798,34 +5786,36 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>bungalow</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Firthwood Close, Coal Aston, Dronfield</t>
+          <t>Clarke Avenue, Dinnington, Sheffield</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>S18</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="n"/>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>636</v>
+      </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="n">
-        <v>-9.9</v>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>-14.3</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>316250</v>
+        <v>210000</v>
       </c>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>460</v>
+        <v>904</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -5833,12 +5823,12 @@
       <c r="P64" s="8" t="n"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>Saxton Mee (Dronfield) Limited, Dronfield</t>
+          <t>Kendra Jacob, Bassetlaw</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr">
@@ -5846,7 +5836,7 @@
           <t>no chain</t>
         </is>
       </c>
-      <c r="T64" s="12" t="inlineStr">
+      <c r="T64" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5859,7 +5849,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>8b83a2cfaabe446070b5c9a0c2a83bdc1db10da7</t>
+          <t>85491a32a3f7da450b97c9bc5b46882af22dbe2c</t>
         </is>
       </c>
     </row>
@@ -5873,61 +5863,65 @@
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>180000</v>
+        <v>220000</v>
       </c>
       <c r="D65" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Southfield Lane, Whitwell, Worksop</t>
+          <t>Molloy Street, Sheffield, S8</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>S80</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="n">
-        <v>1026</v>
-      </c>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="n"/>
       <c r="J65" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K65" s="8" t="n"/>
-      <c r="L65" s="8" t="n"/>
+      <c r="K65" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L65" s="10" t="n">
+        <v>218750</v>
+      </c>
       <c r="M65" s="8" t="n"/>
-      <c r="N65" s="8" t="n"/>
+      <c r="N65" s="8" t="n">
+        <v>4304</v>
+      </c>
       <c r="O65" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="8" t="n"/>
       <c r="Q65" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>Kendra Jacob, Bassetlaw</t>
+          <t>Blundells, Woodseats</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr">
         <is>
-          <t>garage</t>
-        </is>
-      </c>
-      <c r="T65" s="12" t="inlineStr">
+          <t>no chain</t>
+        </is>
+      </c>
+      <c r="T65" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -5940,25 +5934,25 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>e4e29950c1e2d647f5ad0b1d856b67633ae2f5ff</t>
+          <t>f367c5d301b8f5293d816c998737217b1bcea2d0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>225000</v>
+      </c>
+      <c r="D66" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="E66" s="8" t="n">
         <v>1</v>
       </c>
@@ -5969,12 +5963,12 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Wood Lane, Treeton, Rotherham, S60 5QR</t>
+          <t>Mulehouse Road, Sheffield</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -5983,15 +5977,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K66" s="11" t="n">
-        <v>4</v>
+      <c r="K66" s="12" t="n">
+        <v>50.1</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>144250</v>
+        <v>149950</v>
       </c>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>252</v>
+        <v>3364</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -5999,16 +5993,20 @@
       <c r="P66" s="8" t="n"/>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>2Roost, Sheffield</t>
-        </is>
-      </c>
-      <c r="S66" s="9" t="inlineStr"/>
-      <c r="T66" s="12" t="inlineStr">
+          <t>Evans Lee, Sheffield</t>
+        </is>
+      </c>
+      <c r="S66" s="9" t="inlineStr">
+        <is>
+          <t>no chain</t>
+        </is>
+      </c>
+      <c r="T66" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6021,13 +6019,13 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>34eb2c94bb83d689a42f9c3a9afa5872ba3633ff</t>
+          <t>7c5d1d355ceaf823fe89dd98e2e9f07102cf1c58</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
@@ -6035,7 +6033,7 @@
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>230000</v>
+        <v>265000</v>
       </c>
       <c r="D67" s="8" t="n">
         <v>3</v>
@@ -6050,12 +6048,12 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Leadbeater Road, Sheffield, S12</t>
+          <t>Bridge Close, Whitwell, Worksop</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S80</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -6064,15 +6062,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K67" s="11" t="n">
-        <v>6</v>
+      <c r="K67" s="12" t="n">
+        <v>85.3</v>
       </c>
       <c r="L67" s="10" t="n">
-        <v>217000</v>
+        <v>143000</v>
       </c>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>4576</v>
+        <v>388</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -6080,16 +6078,20 @@
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Gleadless</t>
-        </is>
-      </c>
-      <c r="S67" s="9" t="inlineStr"/>
-      <c r="T67" s="12" t="inlineStr">
+          <t>Heywood Estates, Clowne</t>
+        </is>
+      </c>
+      <c r="S67" s="9" t="inlineStr">
+        <is>
+          <t>garage</t>
+        </is>
+      </c>
+      <c r="T67" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6102,54 +6104,60 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>451ee8e485b773d0e57e6fecc4c6da594e397608</t>
+          <t>ff67b9fae718fda40614dd3a00dcb91a0cd2cc44</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="n">
-        <v>175000</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Loxley Road, Sheffield</t>
+          <t>Romeley Crescent, Clowne, Chesterfield, S43 4LB</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="n"/>
+          <t>S43</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>1395</v>
+      </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K68" s="8" t="n"/>
-      <c r="L68" s="8" t="n"/>
+      <c r="K68" s="12" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L68" s="10" t="n">
+        <v>234000</v>
+      </c>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>2100</v>
+        <v>836</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -6162,11 +6170,15 @@
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Hillsborough</t>
-        </is>
-      </c>
-      <c r="S68" s="9" t="inlineStr"/>
-      <c r="T68" s="12" t="inlineStr">
+          <t>Hunters, Chesterfield</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr">
+        <is>
+          <t>garage</t>
+        </is>
+      </c>
+      <c r="T68" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6179,54 +6191,58 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>e32477294f4d7e8f93a36319f71b57c0a19fa65e</t>
+          <t>3b69d10d80464c826830e386051d9078ef963b8c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>285000</v>
+      </c>
+      <c r="D69" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="E69" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>bungalow</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Torksey Road, Sheffield, S5</t>
+          <t>Firthwood Close, Coal Aston, Dronfield</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="L69" s="10" t="n">
+        <v>316250</v>
+      </c>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>5092</v>
+        <v>460</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -6234,16 +6250,20 @@
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Reeds Rains, Hillsborough</t>
-        </is>
-      </c>
-      <c r="S69" s="9" t="inlineStr"/>
-      <c r="T69" s="12" t="inlineStr">
+          <t>Saxton Mee (Dronfield) Limited, Dronfield</t>
+        </is>
+      </c>
+      <c r="S69" s="9" t="inlineStr">
+        <is>
+          <t>no chain</t>
+        </is>
+      </c>
+      <c r="T69" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6256,28 +6276,28 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>096f95d41864f09a81c7abf297bc3baaad4dbad8</t>
+          <t>8b83a2cfaabe446070b5c9a0c2a83bdc1db10da7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
           <t>semi_detached</t>
@@ -6285,16 +6305,16 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>East Glade Avenue, Sheffield, S12</t>
+          <t>Southfield Lane, Whitwell, Worksop</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S80</t>
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>721</v>
+        <v>1026</v>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
@@ -6304,25 +6324,27 @@
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
-      <c r="N70" s="8" t="n">
-        <v>2016</v>
-      </c>
+      <c r="N70" s="8" t="n"/>
       <c r="O70" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>Whitehornes, Banner Cross</t>
-        </is>
-      </c>
-      <c r="S70" s="9" t="inlineStr"/>
-      <c r="T70" s="12" t="inlineStr">
+          <t>Kendra Jacob, Bassetlaw</t>
+        </is>
+      </c>
+      <c r="S70" s="9" t="inlineStr">
+        <is>
+          <t>garage</t>
+        </is>
+      </c>
+      <c r="T70" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6335,7 +6357,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>1b6718f74a1e01100d8bc7bc9afce0aa045c3020</t>
+          <t>e4e29950c1e2d647f5ad0b1d856b67633ae2f5ff</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6371,7 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>230000</v>
+        <v>150000</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>3</v>
@@ -6364,29 +6386,29 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Wath Road, Sheffield, S7</t>
+          <t>Wood Lane, Treeton, Rotherham, S60 5QR</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K71" s="11" t="n">
-        <v>-2.7</v>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="n">
+        <v>4</v>
       </c>
       <c r="L71" s="10" t="n">
-        <v>236400</v>
+        <v>144250</v>
       </c>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n">
-        <v>5024</v>
+        <v>252</v>
       </c>
       <c r="O71" s="8" t="n">
         <v>0</v>
@@ -6394,16 +6416,16 @@
       <c r="P71" s="8" t="n"/>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Banner Cross</t>
+          <t>2Roost, Sheffield</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
-      <c r="T71" s="12" t="inlineStr">
+      <c r="T71" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6416,7 +6438,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>0954d9ce43354314864ca9016b9a1d3d3534c844</t>
+          <t>34eb2c94bb83d689a42f9c3a9afa5872ba3633ff</t>
         </is>
       </c>
     </row>
@@ -6430,46 +6452,44 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>175000</v>
+        <v>230000</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Cramfit Road, North Anston, Sheffield</t>
+          <t>Leadbeater Road, Sheffield, S12</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>892</v>
-      </c>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="n"/>
       <c r="J72" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K72" s="11" t="n">
-        <v>26.1</v>
+      <c r="K72" s="12" t="n">
+        <v>6</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>138750</v>
+        <v>217000</v>
       </c>
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n">
-        <v>1024</v>
+        <v>4576</v>
       </c>
       <c r="O72" s="8" t="n">
         <v>0</v>
@@ -6482,11 +6502,11 @@
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Kendra Jacob, Bassetlaw</t>
+          <t>Blundells, Gleadless</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
-      <c r="T72" s="12" t="inlineStr">
+      <c r="T72" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6499,7 +6519,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>4e5fcd6754247bf886a7432d8127a6f4a84d4079</t>
+          <t>451ee8e485b773d0e57e6fecc4c6da594e397608</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6533,7 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>150000</v>
+        <v>175000</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>3</v>
@@ -6528,29 +6548,25 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Vickers Road, Sheffield</t>
+          <t>Loxley Road, Sheffield</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="L73" s="10" t="n">
-        <v>110000</v>
-      </c>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n">
-        <v>6236</v>
+        <v>2100</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0</v>
@@ -6558,16 +6574,16 @@
       <c r="P73" s="8" t="n"/>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Uflit, Rotherham</t>
+          <t>Haybrook, Hillsborough</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
-      <c r="T73" s="12" t="inlineStr">
+      <c r="T73" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6580,7 +6596,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>35481bb3d35ac9bc50ec43fac4b54268028de028</t>
+          <t>e32477294f4d7e8f93a36319f71b57c0a19fa65e</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6610,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>170000</v>
+        <v>160000</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>3</v>
@@ -6604,17 +6620,17 @@
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Becket Crescent, SHEFFIELD, South Yorkshire, S8</t>
+          <t>Torksey Road, Sheffield, S5</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -6623,15 +6639,11 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K74" s="11" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="L74" s="10" t="n">
-        <v>114500</v>
-      </c>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n">
-        <v>2036</v>
+        <v>5092</v>
       </c>
       <c r="O74" s="8" t="n">
         <v>0</v>
@@ -6644,11 +6656,11 @@
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Woodseats</t>
+          <t>Reeds Rains, Hillsborough</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
-      <c r="T74" s="12" t="inlineStr">
+      <c r="T74" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6661,7 +6673,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>f11758109e60a138c22547b023f46eabedb54408</t>
+          <t>096f95d41864f09a81c7abf297bc3baaad4dbad8</t>
         </is>
       </c>
     </row>
@@ -6675,46 +6687,42 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>180000</v>
+        <v>160000</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>Devonshire Avenue North, New Whittington, Chesterfield, S43 2DF</t>
+          <t>East Glade Avenue, Sheffield, S12</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I75" s="8" t="n">
-        <v>957</v>
+        <v>721</v>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K75" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="L75" s="10" t="n">
-        <v>135000</v>
-      </c>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="8" t="n">
-        <v>584</v>
+        <v>2016</v>
       </c>
       <c r="O75" s="8" t="n">
         <v>0</v>
@@ -6722,16 +6730,16 @@
       <c r="P75" s="8" t="n"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="R75" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Chesterfield</t>
+          <t>Whitehornes, Banner Cross</t>
         </is>
       </c>
       <c r="S75" s="9" t="inlineStr"/>
-      <c r="T75" s="12" t="inlineStr">
+      <c r="T75" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6744,7 +6752,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>6eccf1c48ce90136b808a7c8c0a8da52431be2d6</t>
+          <t>1b6718f74a1e01100d8bc7bc9afce0aa045c3020</t>
         </is>
       </c>
     </row>
@@ -6758,40 +6766,44 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>200000</v>
+        <v>230000</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Beaconsfield Road, Broom, Rotherham</t>
+          <t>Wath Road, Sheffield, S7</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="n"/>
-      <c r="L76" s="8" t="n"/>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L76" s="10" t="n">
+        <v>236400</v>
+      </c>
       <c r="M76" s="8" t="n"/>
       <c r="N76" s="8" t="n">
-        <v>3180</v>
+        <v>5024</v>
       </c>
       <c r="O76" s="8" t="n">
         <v>0</v>
@@ -6799,16 +6811,16 @@
       <c r="P76" s="8" t="n"/>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>William H. Brown, Rotherham</t>
+          <t>Blundells, Banner Cross</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
-      <c r="T76" s="12" t="inlineStr">
+      <c r="T76" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6821,7 +6833,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>c8698c0ccaacba10e336a1f1842066e620019a42</t>
+          <t>0954d9ce43354314864ca9016b9a1d3d3534c844</t>
         </is>
       </c>
     </row>
@@ -6835,44 +6847,46 @@
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>300000</v>
+        <v>175000</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Far Golden Smithies, Mexborough</t>
+          <t>Cramfit Road, North Anston, Sheffield</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>S64</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="n"/>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>892</v>
+      </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K77" s="11" t="n">
-        <v>9.9</v>
+      <c r="K77" s="12" t="n">
+        <v>26.1</v>
       </c>
       <c r="L77" s="10" t="n">
-        <v>273000</v>
+        <v>138750</v>
       </c>
       <c r="M77" s="8" t="n"/>
       <c r="N77" s="8" t="n">
-        <v>2248</v>
+        <v>1024</v>
       </c>
       <c r="O77" s="8" t="n">
         <v>0</v>
@@ -6885,11 +6899,11 @@
       </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Swinton</t>
+          <t>Kendra Jacob, Bassetlaw</t>
         </is>
       </c>
       <c r="S77" s="9" t="inlineStr"/>
-      <c r="T77" s="12" t="inlineStr">
+      <c r="T77" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6902,7 +6916,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>3c6cc8f37b4c95ddb313f26d9e030b0d5150e672</t>
+          <t>4e5fcd6754247bf886a7432d8127a6f4a84d4079</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6933,7 @@
         <v>150000</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" s="8" t="n">
         <v>1</v>
@@ -6931,12 +6945,12 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Newlands Grove, Sheffield, South Yorkshire, S12</t>
+          <t>Vickers Road, Sheffield</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -6945,15 +6959,15 @@
           <t>leasehold</t>
         </is>
       </c>
-      <c r="K78" s="11" t="n">
-        <v>-6.2</v>
+      <c r="K78" s="12" t="n">
+        <v>36.4</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>160000</v>
+        <v>110000</v>
       </c>
       <c r="M78" s="8" t="n"/>
       <c r="N78" s="8" t="n">
-        <v>4776</v>
+        <v>6236</v>
       </c>
       <c r="O78" s="8" t="n">
         <v>0</v>
@@ -6961,16 +6975,16 @@
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Gleadless</t>
+          <t>Uflit, Rotherham</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
-      <c r="T78" s="12" t="inlineStr">
+      <c r="T78" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -6983,7 +6997,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>906b73cce0cbd08fb322d066632d779c40f8a876</t>
+          <t>35481bb3d35ac9bc50ec43fac4b54268028de028</t>
         </is>
       </c>
     </row>
@@ -7000,24 +7014,24 @@
         <v>170000</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Motehall Drive, Sheffield, South Yorkshire, S2</t>
+          <t>Becket Crescent, SHEFFIELD, South Yorkshire, S8</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -7026,11 +7040,15 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K79" s="8" t="n"/>
-      <c r="L79" s="8" t="n"/>
+      <c r="K79" s="12" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="L79" s="10" t="n">
+        <v>114500</v>
+      </c>
       <c r="M79" s="8" t="n"/>
       <c r="N79" s="8" t="n">
-        <v>4160</v>
+        <v>2036</v>
       </c>
       <c r="O79" s="8" t="n">
         <v>0</v>
@@ -7038,16 +7056,16 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Gleadless</t>
+          <t>Blundells, Woodseats</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
-      <c r="T79" s="12" t="inlineStr">
+      <c r="T79" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7060,7 +7078,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>fcfdb066dc01a336796273ac36f5cc40d7afb1de</t>
+          <t>f11758109e60a138c22547b023f46eabedb54408</t>
         </is>
       </c>
     </row>
@@ -7074,57 +7092,63 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>225000</v>
+        <v>180000</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Gomersal Lane, Dronfield</t>
+          <t>Devonshire Avenue North, New Whittington, Chesterfield, S43 2DF</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>903</v>
+        <v>957</v>
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
         </is>
       </c>
-      <c r="K80" s="8" t="n"/>
-      <c r="L80" s="8" t="n"/>
+      <c r="K80" s="12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L80" s="10" t="n">
+        <v>135000</v>
+      </c>
       <c r="M80" s="8" t="n"/>
-      <c r="N80" s="8" t="n"/>
+      <c r="N80" s="8" t="n">
+        <v>584</v>
+      </c>
       <c r="O80" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
         <is>
-          <t>Saxton Mee (Dronfield) Limited, Dronfield</t>
+          <t>Hunters, Chesterfield</t>
         </is>
       </c>
       <c r="S80" s="9" t="inlineStr"/>
-      <c r="T80" s="12" t="inlineStr">
+      <c r="T80" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7137,7 +7161,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>875349b81a70cec85877ded5aa91a5390e3d2807</t>
+          <t>6eccf1c48ce90136b808a7c8c0a8da52431be2d6</t>
         </is>
       </c>
     </row>
@@ -7151,10 +7175,10 @@
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>240000</v>
+        <v>200000</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="8" t="n">
         <v>1</v>
@@ -7166,40 +7190,42 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Kirkdale Drive, Sheffield, South Yorkshire, S13</t>
+          <t>Beaconsfield Road, Broom, Rotherham</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="I81" s="8" t="n"/>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
+          <t>freehold</t>
         </is>
       </c>
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="8" t="n"/>
       <c r="M81" s="8" t="n"/>
-      <c r="N81" s="8" t="n"/>
+      <c r="N81" s="8" t="n">
+        <v>3180</v>
+      </c>
       <c r="O81" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="8" t="n"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Gleadless</t>
+          <t>William H. Brown, Rotherham</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
-      <c r="T81" s="12" t="inlineStr">
+      <c r="T81" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7212,7 +7238,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>869120b959b052bebe20552157a4cc9223dec368</t>
+          <t>c8698c0ccaacba10e336a1f1842066e620019a42</t>
         </is>
       </c>
     </row>
@@ -7236,17 +7262,17 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Brampton Road, West Melton</t>
+          <t>Far Golden Smithies, Mexborough</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="I82" s="8" t="n"/>
@@ -7255,17 +7281,23 @@
           <t>freehold</t>
         </is>
       </c>
-      <c r="K82" s="8" t="n"/>
-      <c r="L82" s="8" t="n"/>
+      <c r="K82" s="12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L82" s="10" t="n">
+        <v>273000</v>
+      </c>
       <c r="M82" s="8" t="n"/>
-      <c r="N82" s="8" t="n"/>
+      <c r="N82" s="8" t="n">
+        <v>2248</v>
+      </c>
       <c r="O82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
@@ -7274,7 +7306,7 @@
         </is>
       </c>
       <c r="S82" s="9" t="inlineStr"/>
-      <c r="T82" s="12" t="inlineStr">
+      <c r="T82" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7287,7 +7319,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>e7b1690ccad3e41e1363d8c3eac02f9a5991d30b</t>
+          <t>3c6cc8f37b4c95ddb313f26d9e030b0d5150e672</t>
         </is>
       </c>
     </row>
@@ -7301,13 +7333,13 @@
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>275000</v>
+        <v>150000</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
@@ -7316,12 +7348,12 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Malton Drive, Aston, Sheffield, South Yorkshire, S26</t>
+          <t>Newlands Grove, Sheffield, South Yorkshire, S12</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I83" s="8" t="n"/>
@@ -7330,26 +7362,32 @@
           <t>leasehold</t>
         </is>
       </c>
-      <c r="K83" s="8" t="n"/>
-      <c r="L83" s="8" t="n"/>
+      <c r="K83" s="12" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="L83" s="10" t="n">
+        <v>160000</v>
+      </c>
       <c r="M83" s="8" t="n"/>
-      <c r="N83" s="8" t="n"/>
+      <c r="N83" s="8" t="n">
+        <v>4776</v>
+      </c>
       <c r="O83" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="8" t="n"/>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R83" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Crystal Peaks</t>
+          <t>Blundells, Gleadless</t>
         </is>
       </c>
       <c r="S83" s="9" t="inlineStr"/>
-      <c r="T83" s="12" t="inlineStr">
+      <c r="T83" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7362,7 +7400,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>b88c243c39d595c75d9474d937873549d664ff6c</t>
+          <t>906b73cce0cbd08fb322d066632d779c40f8a876</t>
         </is>
       </c>
     </row>
@@ -7379,24 +7417,24 @@
         <v>170000</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>Watson Street, Hoyland, Barnsley</t>
+          <t>Motehall Drive, Sheffield, South Yorkshire, S2</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="I84" s="8" t="n"/>
@@ -7408,7 +7446,9 @@
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
-      <c r="N84" s="8" t="n"/>
+      <c r="N84" s="8" t="n">
+        <v>4160</v>
+      </c>
       <c r="O84" s="8" t="n">
         <v>0</v>
       </c>
@@ -7420,11 +7460,11 @@
       </c>
       <c r="R84" s="8" t="inlineStr">
         <is>
-          <t>William H. Brown, Barnsley</t>
+          <t>Blundells, Gleadless</t>
         </is>
       </c>
       <c r="S84" s="9" t="inlineStr"/>
-      <c r="T84" s="12" t="inlineStr">
+      <c r="T84" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7437,7 +7477,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>44fcc8581a6109aa5ebce130143d102430b7f558</t>
+          <t>fcfdb066dc01a336796273ac36f5cc40d7afb1de</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7491,7 @@
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>158000</v>
+        <v>225000</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>3</v>
@@ -7466,15 +7506,17 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Aughton Road, Aughton, Sheffield, South Yorkshire, S26</t>
+          <t>Gomersal Lane, Dronfield</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="I85" s="8" t="n"/>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>903</v>
+      </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
           <t>freehold</t>
@@ -7495,11 +7537,11 @@
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>Reeds Rains, Dinnington</t>
+          <t>Saxton Mee (Dronfield) Limited, Dronfield</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
-      <c r="T85" s="12" t="inlineStr">
+      <c r="T85" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7512,7 +7554,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>e9dbd1df751d3d74186c2f0d33b7999f6de03ceb</t>
+          <t>875349b81a70cec85877ded5aa91a5390e3d2807</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7568,7 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>170000</v>
+        <v>240000</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>3</v>
@@ -7536,23 +7578,23 @@
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Burncross Road, Burncross</t>
+          <t>Kirkdale Drive, Sheffield, South Yorkshire, S13</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="I86" s="8" t="n"/>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
+          <t>leasehold</t>
         </is>
       </c>
       <c r="K86" s="8" t="n"/>
@@ -7565,16 +7607,16 @@
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>Haybrook, Chapeltown</t>
+          <t>Blundells, Gleadless</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
-      <c r="T86" s="12" t="inlineStr">
+      <c r="T86" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7587,7 +7629,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>0e588b58ff84020226952bf76754d3fe90dd8c7b</t>
+          <t>869120b959b052bebe20552157a4cc9223dec368</t>
         </is>
       </c>
     </row>
@@ -7601,35 +7643,33 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>240000</v>
+        <v>300000</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>Wath Road, Nether Edge, S7</t>
+          <t>Brampton Road, West Melton</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="n">
-        <v>1158</v>
-      </c>
+          <t>S63</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="n"/>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>leasehold</t>
+          <t>freehold</t>
         </is>
       </c>
       <c r="K87" s="8" t="n"/>
@@ -7647,11 +7687,11 @@
       </c>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>Whitehornes, Banner Cross</t>
+          <t>Haybrook, Swinton</t>
         </is>
       </c>
       <c r="S87" s="9" t="inlineStr"/>
-      <c r="T87" s="12" t="inlineStr">
+      <c r="T87" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7664,7 +7704,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>06ff1a25f5180882cbaee3e10b4c3944513dc9cc</t>
+          <t>e7b1690ccad3e41e1363d8c3eac02f9a5991d30b</t>
         </is>
       </c>
     </row>
@@ -7678,33 +7718,33 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>180000</v>
+        <v>275000</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Knutton Crescent, Sheffield, S5</t>
+          <t>Malton Drive, Aston, Sheffield, South Yorkshire, S26</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="I88" s="8" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>freehold</t>
+          <t>leasehold</t>
         </is>
       </c>
       <c r="K88" s="8" t="n"/>
@@ -7722,11 +7762,11 @@
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>Blundells, Chapeltown</t>
+          <t>Blundells, Crystal Peaks</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
-      <c r="T88" s="12" t="inlineStr">
+      <c r="T88" s="11" t="inlineStr">
         <is>
           <t>View listing</t>
         </is>
@@ -7739,14 +7779,466 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
+          <t>b88c243c39d595c75d9474d937873549d664ff6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>Watson Street, Hoyland, Barnsley</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>S74</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="8" t="n"/>
+      <c r="O89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="8" t="n"/>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R89" s="8" t="inlineStr">
+        <is>
+          <t>William H. Brown, Barnsley</t>
+        </is>
+      </c>
+      <c r="S89" s="9" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V89" s="7" t="inlineStr"/>
+      <c r="W89" s="8" t="inlineStr">
+        <is>
+          <t>44fcc8581a6109aa5ebce130143d102430b7f558</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>158000</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Aughton Road, Aughton, Sheffield, South Yorkshire, S26</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="n"/>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
+      <c r="N90" s="8" t="n"/>
+      <c r="O90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="8" t="n"/>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R90" s="8" t="inlineStr">
+        <is>
+          <t>Reeds Rains, Dinnington</t>
+        </is>
+      </c>
+      <c r="S90" s="9" t="inlineStr"/>
+      <c r="T90" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V90" s="7" t="inlineStr"/>
+      <c r="W90" s="8" t="inlineStr">
+        <is>
+          <t>e9dbd1df751d3d74186c2f0d33b7999f6de03ceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>Burncross Road, Burncross</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+      <c r="N91" s="8" t="n"/>
+      <c r="O91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="8" t="n"/>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R91" s="8" t="inlineStr">
+        <is>
+          <t>Haybrook, Chapeltown</t>
+        </is>
+      </c>
+      <c r="S91" s="9" t="inlineStr"/>
+      <c r="T91" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V91" s="7" t="inlineStr"/>
+      <c r="W91" s="8" t="inlineStr">
+        <is>
+          <t>0e588b58ff84020226952bf76754d3fe90dd8c7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>Wath Road, Nether Edge, S7</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>1158</v>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
+      <c r="N92" s="8" t="n"/>
+      <c r="O92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="8" t="n"/>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R92" s="8" t="inlineStr">
+        <is>
+          <t>Whitehornes, Banner Cross</t>
+        </is>
+      </c>
+      <c r="S92" s="9" t="inlineStr"/>
+      <c r="T92" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V92" s="7" t="inlineStr"/>
+      <c r="W92" s="8" t="inlineStr">
+        <is>
+          <t>06ff1a25f5180882cbaee3e10b4c3944513dc9cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>Knutton Crescent, Sheffield, S5</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+      <c r="N93" s="8" t="n"/>
+      <c r="O93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="8" t="n"/>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R93" s="8" t="inlineStr">
+        <is>
+          <t>Blundells, Chapeltown</t>
+        </is>
+      </c>
+      <c r="S93" s="9" t="inlineStr"/>
+      <c r="T93" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V93" s="7" t="inlineStr"/>
+      <c r="W93" s="8" t="inlineStr">
+        <is>
           <t>aef3a0729dc3e2726e6a817dfc3fdbfb951c274b</t>
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Challiner Mews, Catcliffe, Rotherham, South Yorkshire, S60</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
+      <c r="N94" s="8" t="n"/>
+      <c r="O94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="8" t="n"/>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R94" s="8" t="inlineStr">
+        <is>
+          <t>Blundells, Rotherham</t>
+        </is>
+      </c>
+      <c r="S94" s="9" t="inlineStr"/>
+      <c r="T94" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V94" s="7" t="inlineStr"/>
+      <c r="W94" s="8" t="inlineStr">
+        <is>
+          <t>8371ec6162623474d14a0ff93108d019c8362557</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W88"/>
+  <autoFilter ref="A1:W94"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7838,6 +8330,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T94" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7849,7 +8347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7994,12 +8492,3121 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Redland, Bristol, BS6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n">
+        <v>16556</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>parking, bills included</t>
+        </is>
+      </c>
+      <c r="T2" s="6" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V2" s="7" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>e75c2ceb14a04ab80617fbb1becf403f0031cc3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>North Road, St. Andrews, BS6</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n">
+        <v>8012</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>Bristol Property Centre, Bristol</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T3" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr"/>
+      <c r="W3" s="8" t="inlineStr">
+        <is>
+          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Boot Lane - Bedminster</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n">
+        <v>15180</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="n"/>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>Ocean, Southville</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Church Road, Redfield, Bristol</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n">
+        <v>9192</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>House + Co Property, Bristol</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr"/>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n">
+        <v>4996</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>CJ Hole, Kingswood</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr"/>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Caslon Court, Somerset Street, BS1</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n">
+        <v>18424</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr"/>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t>f6187d8c2bb085d8ddb57c1f8b8dc96ceada86aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Butlers Close, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n">
+        <v>4996</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>Parks Estate Agents, Bristol</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr"/>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Manor Road, Bishopston, Bristol</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>BS7</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n">
+        <v>5396</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>Connells Lettings, Southville</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr"/>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Marlborough Street, Eastville, Bristol</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>366</v>
+      </c>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n">
+        <v>7920</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>Hopewell, Bristol</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr"/>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>975</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n">
+        <v>7804</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>Northwood, Bristol</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr"/>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>975</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n">
+        <v>8640</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>Nook Lettings, Bristol</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr"/>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Ravenswood Road, Bristol, BS6</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n">
+        <v>16556</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>bills included</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr"/>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>St Michaels Hill Ref 708</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n">
+        <v>19512</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>Jackson Property Management Ltd, Bristol</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr"/>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n">
+        <v>8636</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>Abode Property Management, Bristol</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr"/>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>BS13</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n">
+        <v>4936</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>CJ Hole, Southville</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Flat B, City Road, Bristol</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n">
+        <v>20108</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>Holbrook Moran, Redfield</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr"/>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>City Centre, Unity Street, BS1 5HH</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>20772</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Clifton</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr"/>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n">
+        <v>4160</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t>Morgan &amp; Sons, Bristol</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr"/>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>965</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Boulevard View, Whitchurch Lane</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n">
+        <v>5764</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr"/>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Braggs Lane, Bristol</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>409</v>
+      </c>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n">
+        <v>20360</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>House + Co Property, Bristol</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr"/>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Montague Court, Bristol</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n">
+        <v>21632</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>Connells Lettings, Southville</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr"/>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr"/>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>397</v>
+      </c>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n">
+        <v>15212</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>West Coast Properties, Bishopston</t>
+        </is>
+      </c>
+      <c r="S23" s="9" t="inlineStr"/>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr"/>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Talavera Close, Bristol</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n">
+        <v>19980</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr"/>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Barton Close, St. Annes Park, BS4</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>441</v>
+      </c>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="8" t="n">
+        <v>5212</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>Nook Lettings, Bristol</t>
+        </is>
+      </c>
+      <c r="S25" s="9" t="inlineStr"/>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr"/>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n">
+        <v>7112</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>Just Lets, Bristol</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr"/>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr"/>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Chapel Street, St Philips, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>549</v>
+      </c>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8" t="n">
+        <v>11732</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>Morgan &amp; Sons, Bristol</t>
+        </is>
+      </c>
+      <c r="S27" s="9" t="inlineStr"/>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr"/>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n">
+        <v>14596</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>Savills Lettings, Clifton</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr"/>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr"/>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Stapleton Road, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8" t="n">
+        <v>19576</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S29" s="9" t="inlineStr"/>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr"/>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>BS7</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n">
+        <v>5316</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>Holbrook Moran, Redfield</t>
+        </is>
+      </c>
+      <c r="S30" s="9" t="inlineStr"/>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr"/>
+      <c r="W30" s="8" t="inlineStr">
+        <is>
+          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8" t="n">
+        <v>7112</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>Just Lets, Bristol</t>
+        </is>
+      </c>
+      <c r="S31" s="9" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr"/>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Seymour Road, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>484</v>
+      </c>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n">
+        <v>17164</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>Bristol Property Centre, Bristol</t>
+        </is>
+      </c>
+      <c r="S32" s="9" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr"/>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Pinkhams Twist, Bristol</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="8" t="n">
+        <v>4276</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>Hunters, Whitchurch</t>
+        </is>
+      </c>
+      <c r="S33" s="9" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V33" s="7" t="inlineStr"/>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Alexandra Park, Redland, Bristol, BS6</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n">
+        <v>12812</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>Romans, Clifton</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V34" s="7" t="inlineStr"/>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="8" t="n">
+        <v>18020</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="8" t="n"/>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t>West Coast Properties, Bishopston</t>
+        </is>
+      </c>
+      <c r="S35" s="9" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="inlineStr"/>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Church Road, Bristol, BS5</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>3057</v>
+      </c>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n">
+        <v>11864</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>Lets Rent Bristol, Bristol</t>
+        </is>
+      </c>
+      <c r="S36" s="9" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V36" s="7" t="inlineStr"/>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="8" t="n">
+        <v>2652</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="inlineStr">
+        <is>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
+        </is>
+      </c>
+      <c r="S37" s="9" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V37" s="7" t="inlineStr"/>
+      <c r="W37" s="8" t="inlineStr">
+        <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S38" s="9" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V38" s="7" t="inlineStr"/>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>995</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Two Mile Hill Road, Kingswood, Bristol</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>BS15</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="8" t="n">
+        <v>5116</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t>TLS Estate Agents, Bristol</t>
+        </is>
+      </c>
+      <c r="S39" s="9" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V39" s="7" t="inlineStr"/>
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Robertson Drive, St Annes Park</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n">
+        <v>4252</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t>D W Smith &amp; Company, Hanham</t>
+        </is>
+      </c>
+      <c r="S40" s="9" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V40" s="7" t="inlineStr"/>
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="8" t="n">
+        <v>15212</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t>Accommodation Unlimited, Bristol</t>
+        </is>
+      </c>
+      <c r="S41" s="9" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V41" s="7" t="inlineStr"/>
+      <c r="W41" s="8" t="inlineStr">
+        <is>
+          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>527</v>
+      </c>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="8" t="n">
+        <v>5548</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="8" t="n"/>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t>Sheedy &amp; Co, Covering Bristol</t>
+        </is>
+      </c>
+      <c r="S42" s="9" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V42" s="7" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:W42"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8017,7 +11624,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>How to use this workbook</t>
         </is>
@@ -8044,7 +11651,7 @@
       <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Status - pick from the dropdown:</t>
         </is>
@@ -8117,7 +11724,7 @@
       <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Notes - anything you like. Survives every run.</t>
         </is>
@@ -8144,7 +11751,7 @@
       <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>vs Local % compares the asking price to what similar properties nearby</t>
         </is>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,8 +12,8 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -103,8 +103,12 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -471,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8235,10 +8239,6379 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="13" t="n">
+        <v>179950</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Church Road</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>972</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
+        </is>
+      </c>
+      <c r="S95" s="7" t="inlineStr"/>
+      <c r="T95" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V95" s="7" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>dd76366deca8981b30e1eaaa50ecb1e80c948a02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="13" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Wellington Road, Broughton, Flintshire, CH4</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>797</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K96" s="15" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="L96" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="N96" t="n">
+        <v>420</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Chester</t>
+        </is>
+      </c>
+      <c r="S96" s="7" t="inlineStr"/>
+      <c r="T96" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V96" s="7" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>87c708be93157d6e1b6b8b815c8af4cd24c73b73</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="13" t="n">
+        <v>239995</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Queensgate, Welsh Road, Deeside, Flintshire, CH5 2HJ</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K97" s="15" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="L97" s="13" t="n">
+        <v>141000</v>
+      </c>
+      <c r="N97" t="n">
+        <v>980</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Persimmon Homes</t>
+        </is>
+      </c>
+      <c r="S97" s="7" t="inlineStr"/>
+      <c r="T97" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V97" s="7" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>42cb5281529bc95b9e8bfa2992a1b86db9af4900</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="13" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Bro Brwynog, Treuddyn, CH7</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L98" s="13" t="n">
+        <v>202250</v>
+      </c>
+      <c r="N98" t="n">
+        <v>52</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Reades, Hawarden Sales</t>
+        </is>
+      </c>
+      <c r="S98" s="7" t="inlineStr"/>
+      <c r="T98" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V98" s="7" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>85866a09863f08c0095e1a3a3518fdd85b495848</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="13" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Lon Goed, Holywell</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L99" s="13" t="n">
+        <v>145000</v>
+      </c>
+      <c r="N99" t="n">
+        <v>572</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S99" s="7" t="inlineStr"/>
+      <c r="T99" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V99" s="7" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>18ad3059416dd76bc6b325dd6e8c6a724bfa566c</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="13" t="n">
+        <v>205000</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Llys Daniel Owen, Denbigh Road, Mold, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="L100" s="13" t="n">
+        <v>160000</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1244</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>J Bradburne Price &amp; Co, Mold</t>
+        </is>
+      </c>
+      <c r="S100" s="7" t="inlineStr"/>
+      <c r="T100" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V100" s="7" t="inlineStr"/>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>02b70f30b8761564f149da15e81112634a148f23</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Llys Daniel Owen, Denbigh Road, Mold, Flintshire</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L101" s="13" t="n">
+        <v>136250</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1240</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>J Bradburne Price &amp; Co, Mold</t>
+        </is>
+      </c>
+      <c r="S101" s="7" t="inlineStr"/>
+      <c r="T101" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V101" s="7" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>32c56704d29ce2088777c113f2a3482a4bf1cc57</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Lon Tywysog, Denbigh, LL16</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>846</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>436</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S102" s="7" t="inlineStr"/>
+      <c r="T102" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V102" s="7" t="inlineStr"/>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>7b59b8e212ab5a4b08f6c909239eeae6f2a0299f</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Maxwell Close, Buckley, CH7</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K103" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L103" s="13" t="n">
+        <v>192000</v>
+      </c>
+      <c r="N103" t="n">
+        <v>976</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Yopa, North West &amp; Midlands</t>
+        </is>
+      </c>
+      <c r="S103" s="7" t="inlineStr"/>
+      <c r="T103" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V103" s="7" t="inlineStr"/>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>d119416b239e906e2744705827a0ebf4d11d6ebd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Hillside Court, Holywell</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>936</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S104" s="7" t="inlineStr"/>
+      <c r="T104" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V104" s="7" t="inlineStr"/>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>6d5d0c1359a29c1d463ad4bb838862aaf9c45074</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Brookdale Avenue, Deeside, CH5</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K105" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L105" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="N105" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Yopa, North West &amp; Midlands</t>
+        </is>
+      </c>
+      <c r="S105" s="7" t="inlineStr"/>
+      <c r="T105" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V105" s="7" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>ddeb3891bec66957f508c0e3584f3c21d46030d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>Brunswick Road, Buckley, CH7</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>904</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K106" s="15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L106" s="13" t="n">
+        <v>145000</v>
+      </c>
+      <c r="N106" t="n">
+        <v>944</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Swain Hennessey Estate Agents, Covering North Wales, Cheshire and the Wirral</t>
+        </is>
+      </c>
+      <c r="S106" s="7" t="inlineStr"/>
+      <c r="T106" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V106" s="7" t="inlineStr"/>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>e51bd7e6a0acb6f311beced032f9a6865c0b4ae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="13" t="n">
+        <v>270000</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Maxwell Close, Buckley</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K107" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L107" s="13" t="n">
+        <v>192000</v>
+      </c>
+      <c r="N107" t="n">
+        <v>976</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Mold</t>
+        </is>
+      </c>
+      <c r="S107" s="7" t="inlineStr"/>
+      <c r="T107" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V107" s="7" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>b33d1aa3e6758485c42149c957c7d6e06ebb903b</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="n"/>
+      <c r="C108" s="13" t="n">
+        <v>235000</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Lluesty Gardens, Holywell, Flintshire, CH8</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="L108" s="13" t="n">
+        <v>202500</v>
+      </c>
+      <c r="N108" t="n">
+        <v>688</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Beresford Adams, Holywell</t>
+        </is>
+      </c>
+      <c r="S108" s="7" t="inlineStr"/>
+      <c r="T108" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V108" s="7" t="inlineStr"/>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>787a4188403b7874478c21f44f6c8307251f05ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Fulbrooke, Greenfield</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>468</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S109" s="7" t="inlineStr"/>
+      <c r="T109" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V109" s="7" t="inlineStr"/>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>640911bf95cc02cc9ff44787785aaa2d305be061</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="7" t="n"/>
+      <c r="C110" s="13" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>Queensway, Gwersyllt, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K110" s="15" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L110" s="13" t="n">
+        <v>180000</v>
+      </c>
+      <c r="N110" t="n">
+        <v>848</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Whitegates, Wrexham</t>
+        </is>
+      </c>
+      <c r="S110" s="7" t="inlineStr"/>
+      <c r="T110" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V110" s="7" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>386e6e0fc6ee0130c22eac73f1e4d0cc30fc403c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="13" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Chapel Street, Connah's Quay, CH5</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>1960</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>The Property Selling Company, Nationwide</t>
+        </is>
+      </c>
+      <c r="S111" s="7" t="inlineStr"/>
+      <c r="T111" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V111" s="7" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>8cc8a357e45089989242ed9eeb966a70f7d6006b</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="13" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Vale Avenue, Hawarden, CH5</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>840</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L112" s="13" t="n">
+        <v>217500</v>
+      </c>
+      <c r="N112" t="n">
+        <v>492</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Reades, Hawarden Sales</t>
+        </is>
+      </c>
+      <c r="S112" s="7" t="inlineStr"/>
+      <c r="T112" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V112" s="7" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>25750e72779cdc65e04d3415f833b2dd45a2fbc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="13" t="n">
+        <v>215000</v>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Clos Owain, Hope, LL12</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>753</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K113" s="15" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="L113" s="13" t="n">
+        <v>136500</v>
+      </c>
+      <c r="N113" t="n">
+        <v>220</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Monopoly Estate Agents, Rossett</t>
+        </is>
+      </c>
+      <c r="S113" s="7" t="inlineStr"/>
+      <c r="T113" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V113" s="7" t="inlineStr"/>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>431f133f7b5566b71f70bac6090339060015f051</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="13" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Maes Y Goron, Lixwm</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K114" s="15" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L114" s="13" t="n">
+        <v>185500</v>
+      </c>
+      <c r="N114" t="n">
+        <v>20</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S114" s="7" t="inlineStr"/>
+      <c r="T114" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V114" s="7" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>995ce12ebbae638e61a76f99d3ccc67034d2fd5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Cambrian Close, Connah's Quay, Deeside, Flintshire, CH5</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>2016</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>William Gleave, Deeside</t>
+        </is>
+      </c>
+      <c r="S115" s="7" t="inlineStr"/>
+      <c r="T115" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V115" s="7" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>74628e9bb9d0109791a5394b68aca721e0a3b217</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="13" t="n">
+        <v>299950</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Fferm Llidiart Werdd, Coedpoeth, Wrexham</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K116" s="15" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L116" s="13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="N116" t="n">
+        <v>456</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Wrexham</t>
+        </is>
+      </c>
+      <c r="S116" s="7" t="inlineStr"/>
+      <c r="T116" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V116" s="7" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>0013fa29e288e45988554c4218fc039a8ab17968</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="13" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Hawthorne Villas, Ewloe, Flintshire, CH5</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>947</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>440</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Deeside</t>
+        </is>
+      </c>
+      <c r="S117" s="7" t="inlineStr"/>
+      <c r="T117" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V117" s="7" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>69ea6569f37adfc483208a3d526fc663835447a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="13" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>Mill Terrace, Afonwen, CH7</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>534</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K118" s="15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L118" s="13" t="n">
+        <v>160500</v>
+      </c>
+      <c r="N118" t="n">
+        <v>28</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S118" s="7" t="inlineStr"/>
+      <c r="T118" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V118" s="7" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>87d6096cf329e9a0a7731fda6779c74ceeb1ca91</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="13" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>Penymynydd, Chester, CH4</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1033</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K119" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L119" s="13" t="n">
+        <v>271000</v>
+      </c>
+      <c r="N119" t="n">
+        <v>196</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Reades, Hawarden Sales</t>
+        </is>
+      </c>
+      <c r="S119" s="7" t="inlineStr"/>
+      <c r="T119" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V119" s="7" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>e0c87d709b41bfb9a391e5ef656405cd5d38e062</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="13" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Moelwyn Close, Bryn Y Baal</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K120" s="15" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L120" s="13" t="n">
+        <v>195000</v>
+      </c>
+      <c r="N120" t="n">
+        <v>500</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Cavendish Estate Agents, Mold</t>
+        </is>
+      </c>
+      <c r="S120" s="7" t="inlineStr"/>
+      <c r="T120" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V120" s="7" t="inlineStr"/>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>823ec76596107a8a01c542029f47b183656affe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="13" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>Wepre Lane, Deeside, CH5 4JU</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K121" s="15" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L121" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="N121" t="n">
+        <v>1256</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Keystone Estate Agents, Connah's Quay</t>
+        </is>
+      </c>
+      <c r="S121" s="7" t="inlineStr"/>
+      <c r="T121" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V121" s="7" t="inlineStr"/>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>e366f56033bfaf866c72e47f07499c5e4baf3b42</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="7" t="n"/>
+      <c r="C122" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>The Close, Greenfield, Holywell</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>508</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Holywell</t>
+        </is>
+      </c>
+      <c r="S122" s="7" t="inlineStr"/>
+      <c r="T122" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V122" s="7" t="inlineStr"/>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>263af044a93d33bf34f37196eb5c06a2136a2515</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="7" t="n"/>
+      <c r="C123" s="13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Royal Drive, Flint, Flintshire</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K123" s="15" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L123" s="13" t="n">
+        <v>206750</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1188</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S123" s="7" t="inlineStr"/>
+      <c r="T123" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V123" s="7" t="inlineStr"/>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>cc9c24e22688ee7d276c6b88fb15bd5b2034d719</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="7" t="n"/>
+      <c r="C124" s="13" t="n">
+        <v>185000</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Bryn Felin, Pentre Halkyn, Holywell</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K124" s="15" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="L124" s="13" t="n">
+        <v>248000</v>
+      </c>
+      <c r="N124" t="n">
+        <v>56</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Holywell</t>
+        </is>
+      </c>
+      <c r="S124" s="7" t="inlineStr"/>
+      <c r="T124" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V124" s="7" t="inlineStr"/>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>b4ffc54c1d83d36b2f50f1ec5987624120970e43</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="13" t="n">
+        <v>225000</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>Cherry Dale Road, Broughton, Chester, CH4</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>692</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K125" s="15" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L125" s="13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="N125" t="n">
+        <v>204</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Jordan &amp; Halstead, Chester</t>
+        </is>
+      </c>
+      <c r="S125" s="7" t="inlineStr"/>
+      <c r="T125" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V125" s="7" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>ae764d550271fdea89730b8b80b79f18e6760e1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="7" t="n"/>
+      <c r="C126" s="13" t="n">
+        <v>249950</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Castle Hill, Denbigh, LL16</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>1130</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>956</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S126" s="7" t="inlineStr"/>
+      <c r="T126" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V126" s="7" t="inlineStr"/>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>d2e4a62265341dbc976d43b288c1385e96ae03fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="7" t="n"/>
+      <c r="C127" s="13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Clos Lowri, Hope, Wrexham</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>851</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>leasehold</t>
+        </is>
+      </c>
+      <c r="K127" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L127" s="13" t="n">
+        <v>378915</v>
+      </c>
+      <c r="N127" t="n">
+        <v>220</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Rose Residential, Wrexham</t>
+        </is>
+      </c>
+      <c r="S127" s="7" t="inlineStr"/>
+      <c r="T127" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V127" s="7" t="inlineStr"/>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>d01f0c71207204105ba760e4666ba4d909663d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="7" t="n"/>
+      <c r="C128" s="13" t="n">
+        <v>270000</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>The Highway, Hawarden, CH5</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>915</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K128" s="15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L128" s="13" t="n">
+        <v>220000</v>
+      </c>
+      <c r="N128" t="n">
+        <v>348</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Tate &amp; Co, Hawarden</t>
+        </is>
+      </c>
+      <c r="S128" s="7" t="inlineStr"/>
+      <c r="T128" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V128" s="7" t="inlineStr"/>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>e4b7185df31c9118a66fb758ed853662041143b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="7" t="n"/>
+      <c r="C129" s="13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Llawr Y Dyffryn, Ruthin</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>LL15</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K129" s="15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L129" s="13" t="n">
+        <v>275000</v>
+      </c>
+      <c r="N129" t="n">
+        <v>512</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Cavendish Estate Agents, Ruthin</t>
+        </is>
+      </c>
+      <c r="S129" s="7" t="inlineStr"/>
+      <c r="T129" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V129" s="7" t="inlineStr"/>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>9b08ba5f760346aa7fc1c1cdcd8ee55512451314</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="7" t="n"/>
+      <c r="C130" s="13" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>Clayton Road, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K130" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L130" s="13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N130" t="n">
+        <v>700</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Northwood, Wrexham</t>
+        </is>
+      </c>
+      <c r="S130" s="7" t="inlineStr"/>
+      <c r="T130" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V130" s="7" t="inlineStr"/>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>efba6e232500c2612cbfbaf7bdbff08d99ad2e97</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="13" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Mayfield Mews, Mold Road, Buckley, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>912</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>William Gleave, Buckley</t>
+        </is>
+      </c>
+      <c r="S131" s="7" t="inlineStr"/>
+      <c r="T131" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V131" s="7" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>11b7bd43eb50a69cd90f0195b0e763b0e47e0e52</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="7" t="n"/>
+      <c r="C132" s="13" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Hillside Crescent, Mold</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K132" s="15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L132" s="13" t="n">
+        <v>192500</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1240</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Mold</t>
+        </is>
+      </c>
+      <c r="S132" s="7" t="inlineStr"/>
+      <c r="T132" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V132" s="7" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>aae1c4e128648ed9f427b8e8a5394e7ce3793d97</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="7" t="n"/>
+      <c r="C133" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Ffordd Corwen, Treuddyn, CH7</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>980</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>60</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Swain Hennessey Estate Agents, Covering North Wales, Cheshire and the Wirral</t>
+        </is>
+      </c>
+      <c r="S133" s="7" t="inlineStr"/>
+      <c r="T133" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V133" s="7" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>642181081bbd22bde29ea6dc75186553b7649a87</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="7" t="n"/>
+      <c r="C134" s="13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Llys Wylfa, Mynydd Isa, CH7</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>861</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K134" s="15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="L134" s="13" t="n">
+        <v>200500</v>
+      </c>
+      <c r="N134" t="n">
+        <v>544</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Currans, North Wales</t>
+        </is>
+      </c>
+      <c r="S134" s="7" t="inlineStr"/>
+      <c r="T134" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V134" s="7" t="inlineStr"/>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>ee0338d4db7fb9b133b94ff7ea133454264b57e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="7" t="n"/>
+      <c r="C135" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Stanley Place, Deeside, CH5</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>1992</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Yopa, North West &amp; Midlands</t>
+        </is>
+      </c>
+      <c r="S135" s="7" t="inlineStr"/>
+      <c r="T135" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V135" s="7" t="inlineStr"/>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>6c7176b0d83c1dfb70008820d831270624533f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="7" t="n"/>
+      <c r="C136" s="13" t="n">
+        <v>195000</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Wrexham Road, Cefn-Y-Bedd</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K136" s="15" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="L136" s="13" t="n">
+        <v>115000</v>
+      </c>
+      <c r="N136" t="n">
+        <v>240</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Rose Residential, Wrexham</t>
+        </is>
+      </c>
+      <c r="S136" s="7" t="inlineStr"/>
+      <c r="T136" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V136" s="7" t="inlineStr"/>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>3cc1cefb9a3630d96c67315f4a34ea99b2a88f7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="7" t="n"/>
+      <c r="C137" s="13" t="n">
+        <v>295000</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>The Ridgeway, Milwr, Holywell</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K137" s="15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L137" s="13" t="n">
+        <v>280000</v>
+      </c>
+      <c r="N137" t="n">
+        <v>496</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S137" s="7" t="inlineStr"/>
+      <c r="T137" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V137" s="7" t="inlineStr"/>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>688796514d7d57d1ec7ebd8f6040fb168f3fdb1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="7" t="n"/>
+      <c r="C138" s="13" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Forest Drive, Broughton, CH4</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>797</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K138" s="15" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="L138" s="13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="N138" t="n">
+        <v>416</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Reades, Hawarden Sales</t>
+        </is>
+      </c>
+      <c r="S138" s="7" t="inlineStr"/>
+      <c r="T138" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V138" s="7" t="inlineStr"/>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>202ae42a1a7113522081f49dd9119a1fd05cbd64</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="13" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Top Farm Road, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1066</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K139" s="15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L139" s="13" t="n">
+        <v>242500</v>
+      </c>
+      <c r="N139" t="n">
+        <v>1480</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Red Door, North Wales</t>
+        </is>
+      </c>
+      <c r="S139" s="7" t="inlineStr"/>
+      <c r="T139" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V139" s="7" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>37d8c8875260083b2b098c616beab11143493e55</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="7" t="n"/>
+      <c r="C140" s="13" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>Bro Deg, Ruthin, LL15</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>LL15</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>592</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K140" s="15" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="L140" s="13" t="n">
+        <v>205000</v>
+      </c>
+      <c r="N140" t="n">
+        <v>520</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Williams Estates, Ruthin</t>
+        </is>
+      </c>
+      <c r="S140" s="7" t="inlineStr"/>
+      <c r="T140" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V140" s="7" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>8df98f9da751b2051181f73b7ee01465d52c0dd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="13" t="n">
+        <v>254740</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Cedar Close, Bradley, LL11</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>728</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Monopoly Estate Agents, Rossett</t>
+        </is>
+      </c>
+      <c r="S141" s="7" t="inlineStr"/>
+      <c r="T141" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V141" s="7" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>6f4ce2887e5ab5c6e14caf6cf680945a72551427</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="7" t="n"/>
+      <c r="C142" s="13" t="n">
+        <v>269950</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>Yr Hendy, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>104</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Yopa, North West &amp; Midlands</t>
+        </is>
+      </c>
+      <c r="S142" s="7" t="inlineStr"/>
+      <c r="T142" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V142" s="7" t="inlineStr"/>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>336bc515316cfe0797271055d2714e90f3a56f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Stryd Yr Wylan, Ruthin, LL15</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>LL15</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>947</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K143" s="15" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L143" s="13" t="n">
+        <v>192995</v>
+      </c>
+      <c r="N143" t="n">
+        <v>556</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Williams Estates, Ruthin</t>
+        </is>
+      </c>
+      <c r="S143" s="7" t="inlineStr"/>
+      <c r="T143" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V143" s="7" t="inlineStr"/>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>df553d0d5d13a95f7a2d8637cabbfe3e2bfaaad3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="7" t="n"/>
+      <c r="C144" s="13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D144" t="n">
+        <v>4</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Welsh Road, Garden City, Deeside, CH5 2RA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K144" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L144" s="13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N144" t="n">
+        <v>996</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Keepmoat</t>
+        </is>
+      </c>
+      <c r="S144" s="7" t="inlineStr"/>
+      <c r="T144" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V144" s="7" t="inlineStr"/>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>4b0f95697473cf8d5f033a0dcb7e463680f65ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="13" t="n">
+        <v>225000</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Tan Y Coed, Carmel</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K145" s="15" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="L145" s="13" t="n">
+        <v>159000</v>
+      </c>
+      <c r="N145" t="n">
+        <v>176</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S145" s="7" t="inlineStr"/>
+      <c r="T145" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V145" s="7" t="inlineStr"/>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>bcb49191b928ae4e3fd1b9fa6362989ed59c19ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="7" t="n"/>
+      <c r="C146" s="13" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Manor Park, Sychdyn</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K146" s="15" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L146" s="13" t="n">
+        <v>205000</v>
+      </c>
+      <c r="N146" t="n">
+        <v>72</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S146" s="7" t="inlineStr"/>
+      <c r="T146" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V146" s="7" t="inlineStr"/>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>044aa1a66ba50a163b85c8011858c77b504705b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="7" t="n"/>
+      <c r="C147" s="13" t="n">
+        <v>265000</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Highland Avenue, Aston, Deeside</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>1868</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Molyneux, Shotton</t>
+        </is>
+      </c>
+      <c r="S147" s="7" t="inlineStr"/>
+      <c r="T147" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V147" s="7" t="inlineStr"/>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>86c49a100f46c357878deeba86303b41c6c8fd09</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="7" t="n"/>
+      <c r="C148" s="13" t="n">
+        <v>235000</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>Walnut Grove, Llay, LL12</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K148" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L148" s="13" t="n">
+        <v>232500</v>
+      </c>
+      <c r="N148" t="n">
+        <v>444</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Changing-Home, Chester</t>
+        </is>
+      </c>
+      <c r="S148" s="7" t="inlineStr"/>
+      <c r="T148" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V148" s="7" t="inlineStr"/>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>ec82398176ac47addfa46f4fe1d74d88f02b0c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="7" t="n"/>
+      <c r="C149" s="13" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Machynlleth Way, Connah's Quay, Deeside, Flintshire, CH5 4UG</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K149" s="15" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L149" s="13" t="n">
+        <v>177000</v>
+      </c>
+      <c r="N149" t="n">
+        <v>1444</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Keystone Estate Agents, Connah's Quay</t>
+        </is>
+      </c>
+      <c r="S149" s="7" t="inlineStr"/>
+      <c r="T149" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V149" s="7" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>2a0a2588941b9edb4b5f8c8c4e7e1d1137c6ee23</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="7" t="n"/>
+      <c r="C150" s="13" t="n">
+        <v>295000</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Hulleys Close, Penymynydd, CH4</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1023</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>196</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Williams Estates, Mold</t>
+        </is>
+      </c>
+      <c r="S150" s="7" t="inlineStr"/>
+      <c r="T150" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V150" s="7" t="inlineStr"/>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>1d7948c7804f45cb3ddbe588cd668654628b4633</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="7" t="n"/>
+      <c r="C151" s="13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Bryn Hilyn Lane, Mold, CH7</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>584</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K151" s="15" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="L151" s="13" t="n">
+        <v>195000</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1356</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Monopoly Estate Agents, Rossett</t>
+        </is>
+      </c>
+      <c r="S151" s="7" t="inlineStr"/>
+      <c r="T151" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V151" s="7" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>30827afa3df69614f4945180ec710f248869f528</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="7" t="n"/>
+      <c r="C152" s="13" t="n">
+        <v>245000</v>
+      </c>
+      <c r="D152" t="n">
+        <v>4</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Bryn Mawr Road, Holywell, Flintshire, CH8</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K152" s="15" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="L152" s="13" t="n">
+        <v>141000</v>
+      </c>
+      <c r="N152" t="n">
+        <v>1056</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Beresford Adams, Holywell</t>
+        </is>
+      </c>
+      <c r="S152" s="7" t="inlineStr"/>
+      <c r="T152" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V152" s="7" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>47635802ade358968c95bea63db649af16e59bda</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="7" t="n"/>
+      <c r="C153" s="13" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D153" t="n">
+        <v>3</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>St. Davids Drive, Connah's Quay, Deeside, CH5 4SR</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K153" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L153" s="13" t="n">
+        <v>178000</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1892</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Keystone Estate Agents, Connah's Quay</t>
+        </is>
+      </c>
+      <c r="S153" s="7" t="inlineStr"/>
+      <c r="T153" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V153" s="7" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>c635f6d96cdad1409914f0372102a0288dd31d45</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="7" t="n"/>
+      <c r="C154" s="13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Bryn Siriol, Coedpoeth, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="K154" s="15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L154" s="13" t="n">
+        <v>225000</v>
+      </c>
+      <c r="N154" t="n">
+        <v>464</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Whitegates, Wrexham</t>
+        </is>
+      </c>
+      <c r="S154" s="7" t="inlineStr"/>
+      <c r="T154" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V154" s="7" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>f2dec6dd731325162e22059b4cfd961b9b1422e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="7" t="n"/>
+      <c r="C155" s="13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Cae Glas, Coedpoeth, Wrexham</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>980</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Wingetts, Wrexham</t>
+        </is>
+      </c>
+      <c r="S155" s="7" t="inlineStr"/>
+      <c r="T155" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V155" s="7" t="inlineStr"/>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>3a77b1fab6c6853aaa7cb05193a4b58554b41494</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="7" t="n"/>
+      <c r="C156" s="13" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D156" t="n">
+        <v>3</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>Grosvenor Drive, Buckley, CH7</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>861</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Currans, North Wales</t>
+        </is>
+      </c>
+      <c r="S156" s="7" t="inlineStr"/>
+      <c r="T156" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V156" s="7" t="inlineStr"/>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>58df60f9767d565fcbf74a36b91fb52b7a746542</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="7" t="n"/>
+      <c r="C157" s="13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>Willow Crescent, Connah's Quay, Deeside, Flintshire, CH5 4XP</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Keystone Estate Agents, Connah's Quay</t>
+        </is>
+      </c>
+      <c r="S157" s="7" t="inlineStr"/>
+      <c r="T157" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V157" s="7" t="inlineStr"/>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>ff01738079cb5e93653592e3b572a6d70eb4a154</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="7" t="n"/>
+      <c r="C158" s="13" t="n">
+        <v>252995</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>Ffordd Bayley/ Bayley Road, Deeside, Flintshire, CH5 2GH</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>885</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Anwyl Homes</t>
+        </is>
+      </c>
+      <c r="S158" s="7" t="inlineStr"/>
+      <c r="T158" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V158" s="7" t="inlineStr"/>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>55474b6b8a175f100ba4d5f87347f15a6654c1b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="7" t="n"/>
+      <c r="C159" s="13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Cwrt Melangell, Oakenholt, Flint, Flintshire, CH6</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>William Gleave, Deeside</t>
+        </is>
+      </c>
+      <c r="S159" s="7" t="inlineStr"/>
+      <c r="T159" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V159" s="7" t="inlineStr"/>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>4a023f8f2873244ea1203d3085ac53a20cfdb206</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="7" t="n"/>
+      <c r="C160" s="13" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>Llannerch Park, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1410</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Idris Estates, North Wales</t>
+        </is>
+      </c>
+      <c r="S160" s="7" t="inlineStr"/>
+      <c r="T160" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V160" s="7" t="inlineStr"/>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>5b1981c082f45e212bb601475090d9d4fb85e404</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="7" t="n"/>
+      <c r="C161" s="13" t="n">
+        <v>225000</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Marlow Terrace, Mold</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Cavendish Estate Agents, Mold</t>
+        </is>
+      </c>
+      <c r="S161" s="7" t="inlineStr"/>
+      <c r="T161" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V161" s="7" t="inlineStr"/>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>9faeac7b02f18d5ea6aeff0f9ec94cd2ba3d715f</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="7" t="n"/>
+      <c r="C162" s="13" t="n">
+        <v>159950</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Bryn Y Gwynt, Pen Y Maes</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Newsome Homes, Holywell</t>
+        </is>
+      </c>
+      <c r="S162" s="7" t="inlineStr"/>
+      <c r="T162" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V162" s="7" t="inlineStr"/>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>658f5be8b21ef9279c1bad7cc812f79ca57b9f21</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="7" t="n"/>
+      <c r="C163" s="13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>Parkfield Road, Broughton, CH4</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Reades, Hawarden Sales</t>
+        </is>
+      </c>
+      <c r="S163" s="7" t="inlineStr"/>
+      <c r="T163" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V163" s="7" t="inlineStr"/>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>c08cc35a7f381f0903374406398ccbf444e7fca3</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="7" t="n"/>
+      <c r="C164" s="13" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>Woodland View, Little Mountain Road, Buckley, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>William Gleave, Buckley</t>
+        </is>
+      </c>
+      <c r="S164" s="7" t="inlineStr"/>
+      <c r="T164" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V164" s="7" t="inlineStr"/>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>5529aa427a416641601094d681a13158727af6ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="7" t="n"/>
+      <c r="C165" s="13" t="n">
+        <v>179950</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>Bentley Avenue, Gwersyllt, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Reeds Rains, Wrexham</t>
+        </is>
+      </c>
+      <c r="S165" s="7" t="inlineStr"/>
+      <c r="T165" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V165" s="7" t="inlineStr"/>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>048bceb8e66e6a263dd50ab86ae7953999f85025</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="7" t="n"/>
+      <c r="C166" s="13" t="n">
+        <v>159950</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>St. Albans Road, Tanyfron, LL11</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>905</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Monopoly Estate Agents, Rossett</t>
+        </is>
+      </c>
+      <c r="S166" s="7" t="inlineStr"/>
+      <c r="T166" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V166" s="7" t="inlineStr"/>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>2ce45be9df0056cc1ec89582103ad374cb1c7df7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="7" t="n"/>
+      <c r="C167" s="13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D167" t="n">
+        <v>4</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>Queen Street, Queensferry, Deeside, Flintshire, CH5</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>William Gleave, Deeside</t>
+        </is>
+      </c>
+      <c r="S167" s="7" t="inlineStr"/>
+      <c r="T167" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V167" s="7" t="inlineStr"/>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>903ea305fca974b47a8fc696fb0a55911f5ad456</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="7" t="n"/>
+      <c r="C168" s="13" t="n">
+        <v>245000</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>Lon Wynne, Denbigh, LL16</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>711</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S168" s="7" t="inlineStr"/>
+      <c r="T168" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V168" s="7" t="inlineStr"/>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>ce587699dd06c99a94881aee82c2969fb0fb2673</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="7" t="n"/>
+      <c r="C169" s="13" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Rhodfa Clawdd Offa, Denbigh, LL16</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>1044</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S169" s="7" t="inlineStr"/>
+      <c r="T169" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V169" s="7" t="inlineStr"/>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>13f9756086d944c0bc41dd3d41f06ddd6d777753</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="7" t="n"/>
+      <c r="C170" s="13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>Cae Bryn, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>515</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S170" s="7" t="inlineStr"/>
+      <c r="T170" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V170" s="7" t="inlineStr"/>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>ffcbdb3cc5f2934a7152efcfbf432635ae478a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="13" t="n">
+        <v>195000</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>Brookes Avenue, Broughton, Flintshire, CH4</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1012</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Chester</t>
+        </is>
+      </c>
+      <c r="S171" s="7" t="inlineStr"/>
+      <c r="T171" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V171" s="7" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>7b9390d88548f7473a2c3741dececfddb799c02a</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="7" t="n"/>
+      <c r="C172" s="13" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Cymau Lane, Caergwrle</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Molyneux, Wrexham</t>
+        </is>
+      </c>
+      <c r="S172" s="7" t="inlineStr"/>
+      <c r="T172" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V172" s="7" t="inlineStr"/>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>a90b9fed04495894c56433bf074cd470f49755c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="13" t="n">
+        <v>270000</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>Llys Dedwydd, Mynydd Isa, Mold, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Beresford Adams, Mold</t>
+        </is>
+      </c>
+      <c r="S173" s="7" t="inlineStr"/>
+      <c r="T173" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V173" s="7" t="inlineStr"/>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>a73924a118cb29c57d95ceddb851bd521ad5c9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="7" t="n"/>
+      <c r="C174" s="13" t="n">
+        <v>199995</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>Llys Ambrose, Mold, CH7 1GU</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Berry and George, Mold</t>
+        </is>
+      </c>
+      <c r="S174" s="7" t="inlineStr"/>
+      <c r="T174" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V174" s="7" t="inlineStr"/>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>68166ed8a0be18848f708b8eab606832c4881ff8</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="7" t="n"/>
+      <c r="C175" s="13" t="n">
+        <v>215000</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>Llys Derwen, Higher Kinnerton, Chester, Flintshire, CH4</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Beresford Adams, Chester</t>
+        </is>
+      </c>
+      <c r="S175" s="7" t="inlineStr"/>
+      <c r="T175" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V175" s="7" t="inlineStr"/>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>1479445706a10234a1b063ac6d3e33ccdc903e3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="7" t="n"/>
+      <c r="C176" s="13" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>Long Road, Broughton, Flintshire, CH4</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>1109</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Chester</t>
+        </is>
+      </c>
+      <c r="S176" s="7" t="inlineStr"/>
+      <c r="T176" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V176" s="7" t="inlineStr"/>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>e45ec5c288d7c255deef1d26997407386cdc3b24</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="7" t="n"/>
+      <c r="C177" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Allt Celyn, Bagillt, CH6</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>829</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Currans, North Wales</t>
+        </is>
+      </c>
+      <c r="S177" s="7" t="inlineStr"/>
+      <c r="T177" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V177" s="7" t="inlineStr"/>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>7a7f6cd085269c38809dc4bf6f67697747bbb18d</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="7" t="n"/>
+      <c r="C178" s="13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D178" t="n">
+        <v>4</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Bod Offa Drive, Buckley, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Beresford Adams, Mold</t>
+        </is>
+      </c>
+      <c r="S178" s="7" t="inlineStr"/>
+      <c r="T178" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V178" s="7" t="inlineStr"/>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>cf0332043c240d7f8419dd7c3efbffb13767e8ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Ffordd Madog, Oakenholt, Flintshire, CH6</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>958</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Deeside</t>
+        </is>
+      </c>
+      <c r="S179" s="7" t="inlineStr"/>
+      <c r="T179" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V179" s="7" t="inlineStr"/>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>05cc202ccfca08ce9b430329dc0f4b0013c5fc5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="7" t="n"/>
+      <c r="C180" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>Cedar Grove, Mold, CH7</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>969</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Currans, North Wales</t>
+        </is>
+      </c>
+      <c r="S180" s="7" t="inlineStr"/>
+      <c r="T180" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V180" s="7" t="inlineStr"/>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>15224c1ec0b4c4bb7399fcf6edd01319b22623e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="7" t="n"/>
+      <c r="C181" s="13" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>Bryn Y Wern, Coedpoeth, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Beresford Adams, Wrexham</t>
+        </is>
+      </c>
+      <c r="S181" s="7" t="inlineStr"/>
+      <c r="T181" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V181" s="7" t="inlineStr"/>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>4c65be3eda3276e5af3a86ca963df4d96cf2624a</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="7" t="n"/>
+      <c r="C182" s="13" t="n">
+        <v>159950</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>Cae Bryn, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>555</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S182" s="7" t="inlineStr"/>
+      <c r="T182" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V182" s="7" t="inlineStr"/>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>ed97dc405158406d7b9f3daeec601a958e363220</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="7" t="n"/>
+      <c r="C183" s="13" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>Clywedog Close, Summerhill</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S183" s="7" t="inlineStr"/>
+      <c r="T183" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V183" s="7" t="inlineStr"/>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>b50325b8bcadea6e99b66e9fd19e7d933b059281</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="7" t="n"/>
+      <c r="C184" s="13" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>Holywell Road, Ewloe, Flintshire, CH5</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1087</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Deeside</t>
+        </is>
+      </c>
+      <c r="S184" s="7" t="inlineStr"/>
+      <c r="T184" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V184" s="7" t="inlineStr"/>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>fe1422c6c77ec9ac8db120dc26b45b5763eee68a</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="13" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>Ruthin Road, Denbigh, LL16</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>727</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S185" s="7" t="inlineStr"/>
+      <c r="T185" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V185" s="7" t="inlineStr"/>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>5949217d6e7549a9453ad081b5875ad040c52777</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="7" t="n"/>
+      <c r="C186" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Brunswick Road, Buckley, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>William Gleave, Buckley</t>
+        </is>
+      </c>
+      <c r="S186" s="7" t="inlineStr"/>
+      <c r="T186" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V186" s="7" t="inlineStr"/>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>2edd2088aafdb6cf560cd8363a6afcd159c3a291</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="13" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>bungalow</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Marcellas Court, Denbigh, LL16</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>706</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S187" s="7" t="inlineStr"/>
+      <c r="T187" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V187" s="7" t="inlineStr"/>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>da5caa122b03d907956f924ac493ae98a6a78339</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="7" t="n"/>
+      <c r="C188" s="13" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Plough Lane, Shotton, Deeside, Flintshire, CH5 1XS</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>freehold</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Keystone Estate Agents, Connah's Quay</t>
+        </is>
+      </c>
+      <c r="S188" s="7" t="inlineStr"/>
+      <c r="T188" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V188" s="7" t="inlineStr"/>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>413a961ef8bc1a16ebc7d9accb83c73c068600f9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W94"/>
+  <autoFilter ref="A1:W188"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8336,6 +14709,100 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8347,7 +14814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8501,7 +14968,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="16" t="n">
         <v>1200</v>
       </c>
       <c r="D2" s="2" t="n">
@@ -8578,7 +15045,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D3" s="8" t="n">
@@ -8657,7 +15124,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D4" s="8" t="n">
@@ -8734,7 +15201,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D5" s="8" t="n">
@@ -8811,7 +15278,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D6" s="8" t="n">
@@ -8888,7 +15355,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D7" s="8" t="n">
@@ -8965,7 +15432,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D8" s="8" t="n">
@@ -9042,7 +15509,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D9" s="8" t="n">
@@ -9119,7 +15586,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D10" s="8" t="n">
@@ -9198,7 +15665,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="17" t="n">
         <v>975</v>
       </c>
       <c r="D11" s="8" t="n">
@@ -9275,7 +15742,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>975</v>
       </c>
       <c r="D12" s="8" t="n">
@@ -9352,7 +15819,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D13" s="8" t="n">
@@ -9429,7 +15896,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D14" s="8" t="n">
@@ -9502,7 +15969,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D15" s="8" t="n">
@@ -9575,7 +16042,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D16" s="8" t="n">
@@ -9648,7 +16115,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D17" s="8" t="n">
@@ -9721,7 +16188,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -9796,7 +16263,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -9869,7 +16336,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>965</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -9942,7 +16409,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -10017,7 +16484,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -10090,7 +16557,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -10165,7 +16632,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -10238,7 +16705,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -10313,7 +16780,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -10386,7 +16853,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D27" s="8" t="n">
@@ -10461,7 +16928,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D28" s="8" t="n">
@@ -10536,7 +17003,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D29" s="8" t="n">
@@ -10609,7 +17076,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D30" s="8" t="n">
@@ -10682,7 +17149,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -10755,7 +17222,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D32" s="8" t="n">
@@ -10830,7 +17297,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D33" s="8" t="n">
@@ -10903,7 +17370,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D34" s="8" t="n">
@@ -10976,7 +17443,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C35" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D35" s="8" t="n">
@@ -11049,7 +17516,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C36" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D36" s="8" t="n">
@@ -11124,7 +17591,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="17" t="n">
         <v>1095</v>
       </c>
       <c r="D37" s="8" t="n">
@@ -11197,7 +17664,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n">
+      <c r="C38" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="D38" s="8" t="n">
@@ -11272,7 +17739,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="17" t="n">
         <v>995</v>
       </c>
       <c r="D39" s="8" t="n">
@@ -11345,7 +17812,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="D40" s="8" t="n">
@@ -11418,7 +17885,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C41" s="14" t="n">
+      <c r="C41" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D41" s="8" t="n">
@@ -11491,7 +17958,7 @@
           <t>Keyword match only (no API key configured for full scoring).</t>
         </is>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C42" s="17" t="n">
         <v>1150</v>
       </c>
       <c r="D42" s="8" t="n">
@@ -11557,10 +18024,1951 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>448</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr"/>
+      <c r="T43" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V43" s="7" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Newmarket Road, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>328</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr"/>
+      <c r="T44" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V44" s="7" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="18" t="n">
+        <v>625</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>824</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Habodel Property Services Ltd, Doncaster</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr"/>
+      <c r="T45" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V45" s="7" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Cilcain, The Square, CH7</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Williams Estates, Rhuddlan</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr"/>
+      <c r="T46" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V46" s="7" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>56</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>William Gleave, Deeside</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr"/>
+      <c r="T47" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V47" s="7" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="18" t="n">
+        <v>925</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Hill Top Close, Ewloe, CH5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>721</v>
+      </c>
+      <c r="N48" t="n">
+        <v>472</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Reades, Hawarden Lettings</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr"/>
+      <c r="T48" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V48" s="7" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="18" t="n">
+        <v>650</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Chester Road East, Shotton, Deeside</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>474</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2016</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Thomas Property Group, Chester</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr"/>
+      <c r="T49" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V49" s="7" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="18" t="n">
+        <v>750</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LL11</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1300</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr"/>
+      <c r="T50" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V50" s="7" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>936</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>William Gleave, Deeside</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr"/>
+      <c r="T51" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V51" s="7" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>9 Park Road, Ruthin</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LL15</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>576</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr"/>
+      <c r="T52" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V52" s="7" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Gladstone Street, Mold</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>905</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1356</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Mold</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr"/>
+      <c r="T53" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V53" s="7" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>710</v>
+      </c>
+      <c r="N54" t="n">
+        <v>248</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Thomas Property Group, Chester</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr"/>
+      <c r="T54" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V54" s="7" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Central Drive, Shotton, Deeside</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>636</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1924</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Mold</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr"/>
+      <c r="T55" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V55" s="7" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="18" t="n">
+        <v>850</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Llys Y Ddol, Mold</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1368</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Cavendish Rentals Ltd, Mold</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr"/>
+      <c r="T56" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V56" s="7" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Mill View Road, Shotton, CH5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1087</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2236</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Deeside</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr"/>
+      <c r="T57" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V57" s="7" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="18" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Chestnut Way, Penyffordd, Chester</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>765</v>
+      </c>
+      <c r="N58" t="n">
+        <v>144</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Reid and Roberts, Mold</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr"/>
+      <c r="T58" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V58" s="7" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>32</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr"/>
+      <c r="T59" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V59" s="7" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="18" t="n">
+        <v>875</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>540</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Visum, Nationwide</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr"/>
+      <c r="T60" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V60" s="7" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="18" t="n">
+        <v>725</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>High Street, Connah's Quay, CH5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1904</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Pinewood Estate Agency, Deeside</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr"/>
+      <c r="T61" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V61" s="7" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="18" t="n">
+        <v>625</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Well Street, Holywell</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>904</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Cavendish Rentals Ltd, Mold</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr"/>
+      <c r="T62" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V62" s="7" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>200</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>William Gleave, Deeside</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr"/>
+      <c r="T63" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V63" s="7" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>semi_detached</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>657</v>
+      </c>
+      <c r="N64" t="n">
+        <v>876</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Currans, North Wales</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V64" s="7" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="18" t="n">
+        <v>750</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>29 Tai Maes, Mold</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1356</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Cavendish Rentals Ltd, Mold</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr"/>
+      <c r="T65" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V65" s="7" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="18" t="n">
+        <v>600</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>St Marys Mews, Mold</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1372</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Cavendish Rentals Ltd, Mold</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr"/>
+      <c r="T66" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V66" s="7" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="18" t="n">
+        <v>875</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Castle Street, Caergwrle</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>264</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr"/>
+      <c r="T67" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V67" s="7" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Fagl Lane, Hope, LL12</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>244</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Belvoir, Wrexham</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr"/>
+      <c r="T68" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V68" s="7" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="18" t="n">
+        <v>595</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Ryeland Street, Deeside</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2152</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr"/>
+      <c r="T69" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V69" s="7" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="18" t="n">
+        <v>750</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>High Street, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>232</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S70" s="7" t="inlineStr"/>
+      <c r="T70" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V70" s="7" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Newmarket Road, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>328</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S71" s="7" t="inlineStr"/>
+      <c r="T71" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V71" s="7" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>940</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr"/>
+      <c r="T72" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V72" s="7" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Derby Road, Caergwrle, Wrexham</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>252</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S73" s="7" t="inlineStr"/>
+      <c r="T73" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V73" s="7" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>268</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S74" s="7" t="inlineStr"/>
+      <c r="T74" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V74" s="7" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W42"/>
+  <autoFilter ref="A1:W74"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11606,6 +20014,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11624,7 +20064,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>How to use this workbook</t>
         </is>
@@ -11651,7 +20091,7 @@
       <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Status - pick from the dropdown:</t>
         </is>
@@ -11724,7 +20164,7 @@
       <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Notes - anything you like. Survives every run.</t>
         </is>
@@ -11751,7 +20191,7 @@
       <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>vs Local % compares the asking price to what similar properties nearby</t>
         </is>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W169"/>
+  <dimension ref="A1:W174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -26888,7 +26888,7 @@
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>1100</v>
+        <v>1540</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>1</v>
@@ -26903,21 +26903,23 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>St Michaels Hill Ref 708</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I135" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="n">
+        <v>451</v>
+      </c>
       <c r="J135" s="8" t="n"/>
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n">
-        <v>19512</v>
+        <v>20820</v>
       </c>
       <c r="O135" s="8" t="n">
         <v>0</v>
@@ -26925,12 +26927,12 @@
       <c r="P135" s="8" t="n"/>
       <c r="Q135" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R135" s="8" t="inlineStr">
         <is>
-          <t>Jackson Property Management Ltd, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S135" s="9" t="inlineStr"/>
@@ -26947,7 +26949,7 @@
       <c r="V135" s="7" t="inlineStr"/>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
         </is>
       </c>
     </row>
@@ -26961,13 +26963,13 @@
         </is>
       </c>
       <c r="C136" s="17" t="n">
-        <v>1095</v>
+        <v>2095</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
@@ -26976,21 +26978,23 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n">
-        <v>2652</v>
+        <v>20820</v>
       </c>
       <c r="O136" s="8" t="n">
         <v>0</v>
@@ -26998,12 +27002,12 @@
       <c r="P136" s="8" t="n"/>
       <c r="Q136" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R136" s="8" t="inlineStr">
         <is>
-          <t>Millennium Lettings &amp; Management, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S136" s="9" t="inlineStr"/>
@@ -27020,7 +27024,7 @@
       <c r="V136" s="7" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
         </is>
       </c>
     </row>
@@ -27034,7 +27038,7 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1200</v>
+        <v>1660</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>1</v>
@@ -27049,23 +27053,23 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Old Market, Verdigris, BS2 0AF</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I137" s="8" t="n">
-        <v>388</v>
+        <v>486</v>
       </c>
       <c r="J137" s="8" t="n"/>
       <c r="K137" s="8" t="n"/>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n">
-        <v>21220</v>
+        <v>21504</v>
       </c>
       <c r="O137" s="8" t="n">
         <v>0</v>
@@ -27073,12 +27077,12 @@
       <c r="P137" s="8" t="n"/>
       <c r="Q137" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R137" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S137" s="9" t="inlineStr"/>
@@ -27095,314 +27099,383 @@
       <c r="V137" s="7" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="n">
+        <v>2175</v>
+      </c>
+      <c r="D138" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="n">
+        <v>814</v>
+      </c>
+      <c r="J138" s="8" t="n"/>
+      <c r="K138" s="8" t="n"/>
+      <c r="L138" s="8" t="n"/>
+      <c r="M138" s="8" t="n"/>
+      <c r="N138" s="8" t="n">
+        <v>21504</v>
+      </c>
+      <c r="O138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="8" t="n"/>
+      <c r="Q138" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="R138" s="8" t="inlineStr">
+        <is>
+          <t>Grainger, Hawkins &amp; George</t>
+        </is>
+      </c>
+      <c r="S138" s="9" t="inlineStr"/>
+      <c r="T138" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V138" s="7" t="inlineStr"/>
+      <c r="W138" s="8" t="inlineStr">
+        <is>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>Small Street - City Centre</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="n"/>
+      <c r="J139" s="8" t="n"/>
+      <c r="K139" s="8" t="n"/>
+      <c r="L139" s="8" t="n"/>
+      <c r="M139" s="8" t="n"/>
+      <c r="N139" s="8" t="n">
+        <v>21816</v>
+      </c>
+      <c r="O139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="8" t="n"/>
+      <c r="Q139" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="R139" s="8" t="inlineStr">
+        <is>
+          <t>Ocean, Clifton</t>
+        </is>
+      </c>
+      <c r="S139" s="9" t="inlineStr"/>
+      <c r="T139" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V139" s="7" t="inlineStr"/>
+      <c r="W139" s="8" t="inlineStr">
+        <is>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>St Michaels Hill Ref 708</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="n"/>
+      <c r="J140" s="8" t="n"/>
+      <c r="K140" s="8" t="n"/>
+      <c r="L140" s="8" t="n"/>
+      <c r="M140" s="8" t="n"/>
+      <c r="N140" s="8" t="n">
+        <v>19512</v>
+      </c>
+      <c r="O140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="8" t="n"/>
+      <c r="Q140" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R140" s="8" t="inlineStr">
+        <is>
+          <t>Jackson Property Management Ltd, Bristol</t>
+        </is>
+      </c>
+      <c r="S140" s="9" t="inlineStr"/>
+      <c r="T140" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V140" s="7" t="inlineStr"/>
+      <c r="W140" s="8" t="inlineStr">
+        <is>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="n"/>
+      <c r="J141" s="8" t="n"/>
+      <c r="K141" s="8" t="n"/>
+      <c r="L141" s="8" t="n"/>
+      <c r="M141" s="8" t="n"/>
+      <c r="N141" s="8" t="n">
+        <v>2652</v>
+      </c>
+      <c r="O141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="8" t="n"/>
+      <c r="Q141" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R141" s="8" t="inlineStr">
+        <is>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
+        </is>
+      </c>
+      <c r="S141" s="9" t="inlineStr"/>
+      <c r="T141" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V141" s="7" t="inlineStr"/>
+      <c r="W141" s="8" t="inlineStr">
+        <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J142" s="8" t="n"/>
+      <c r="K142" s="8" t="n"/>
+      <c r="L142" s="8" t="n"/>
+      <c r="M142" s="8" t="n"/>
+      <c r="N142" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="8" t="n"/>
+      <c r="Q142" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R142" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S142" s="9" t="inlineStr"/>
+      <c r="T142" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V142" s="7" t="inlineStr"/>
+      <c r="W142" s="8" t="inlineStr">
+        <is>
           <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="7" t="n"/>
-      <c r="C138" s="18" t="n">
-        <v>800</v>
-      </c>
-      <c r="D138" t="n">
-        <v>2</v>
-      </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>LL11</t>
-        </is>
-      </c>
-      <c r="N138" t="n">
-        <v>448</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S138" s="7" t="inlineStr"/>
-      <c r="T138" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V138" s="7" t="inlineStr"/>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="7" t="n"/>
-      <c r="C139" s="18" t="n">
-        <v>900</v>
-      </c>
-      <c r="D139" t="n">
-        <v>2</v>
-      </c>
-      <c r="E139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>LL18</t>
-        </is>
-      </c>
-      <c r="N139" t="n">
-        <v>328</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>Fifty North West, Chester</t>
-        </is>
-      </c>
-      <c r="S139" s="7" t="inlineStr"/>
-      <c r="T139" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V139" s="7" t="inlineStr"/>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="7" t="n"/>
-      <c r="C140" s="18" t="n">
-        <v>625</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>Field View, Mancot, Deeside, CH5 2EY</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="N140" t="n">
-        <v>824</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>Habodel Property Services Ltd, Doncaster</t>
-        </is>
-      </c>
-      <c r="S140" s="7" t="inlineStr"/>
-      <c r="T140" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V140" s="7" t="inlineStr"/>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="7" t="n"/>
-      <c r="C141" s="18" t="n">
-        <v>795</v>
-      </c>
-      <c r="D141" t="n">
-        <v>2</v>
-      </c>
-      <c r="E141" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>semi_detached</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>Cilcain, The Square, CH7</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>CH7</t>
-        </is>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>Williams Estates, Rhuddlan</t>
-        </is>
-      </c>
-      <c r="S141" s="7" t="inlineStr"/>
-      <c r="T141" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V141" s="7" t="inlineStr"/>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="7" t="n"/>
-      <c r="C142" s="18" t="n">
-        <v>950</v>
-      </c>
-      <c r="D142" t="n">
-        <v>2</v>
-      </c>
-      <c r="E142" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>semi_detached</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>CH8</t>
-        </is>
-      </c>
-      <c r="N142" t="n">
-        <v>56</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>William Gleave, Deeside</t>
-        </is>
-      </c>
-      <c r="S142" s="7" t="inlineStr"/>
-      <c r="T142" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V142" s="7" t="inlineStr"/>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="7" t="n"/>
       <c r="C143" s="18" t="n">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="D143" t="n">
         <v>2</v>
@@ -27412,36 +27485,33 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Hill Top Close, Ewloe, CH5</t>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I143" t="n">
-        <v>721</v>
+          <t>LL11</t>
+        </is>
       </c>
       <c r="N143" t="n">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Reades, Hawarden Lettings</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S143" s="7" t="inlineStr"/>
@@ -27458,17 +27528,17 @@
       <c r="V143" s="7" t="inlineStr"/>
       <c r="W143" t="inlineStr">
         <is>
-          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="7" t="n"/>
       <c r="C144" s="18" t="n">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -27480,31 +27550,28 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Chester Road East, Shotton, Deeside</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I144" t="n">
-        <v>474</v>
+          <t>LL18</t>
+        </is>
       </c>
       <c r="N144" t="n">
-        <v>2016</v>
+        <v>328</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S144" s="7" t="inlineStr"/>
@@ -27521,50 +27588,50 @@
       <c r="V144" s="7" t="inlineStr"/>
       <c r="W144" t="inlineStr">
         <is>
-          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="7" t="n"/>
       <c r="C145" s="18" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>LL11</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1300</v>
+        <v>824</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Habodel Property Services Ltd, Doncaster</t>
         </is>
       </c>
       <c r="S145" s="7" t="inlineStr"/>
@@ -27581,14 +27648,14 @@
       <c r="V145" s="7" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>40274ada7dfa710e5054184216178477a704016c</t>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="7" t="n"/>
       <c r="C146" s="18" t="n">
-        <v>900</v>
+        <v>795</v>
       </c>
       <c r="D146" t="n">
         <v>2</v>
@@ -27603,7 +27670,7 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+          <t>Cilcain, The Square, CH7</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -27612,19 +27679,19 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>936</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Williams Estates, Rhuddlan</t>
         </is>
       </c>
       <c r="S146" s="7" t="inlineStr"/>
@@ -27641,14 +27708,14 @@
       <c r="V146" s="7" t="inlineStr"/>
       <c r="W146" t="inlineStr">
         <is>
-          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="7" t="n"/>
       <c r="C147" s="18" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="D147" t="n">
         <v>2</v>
@@ -27658,33 +27725,33 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>9 Park Road, Ruthin</t>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>LL15</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N147" t="n">
-        <v>576</v>
+        <v>56</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Ruthin</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S147" s="7" t="inlineStr"/>
@@ -27701,14 +27768,14 @@
       <c r="V147" s="7" t="inlineStr"/>
       <c r="W147" t="inlineStr">
         <is>
-          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="7" t="n"/>
       <c r="C148" s="18" t="n">
-        <v>795</v>
+        <v>925</v>
       </c>
       <c r="D148" t="n">
         <v>2</v>
@@ -27723,31 +27790,31 @@
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Gladstone Street, Mold</t>
+          <t>Hill Top Close, Ewloe, CH5</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>905</v>
+        <v>721</v>
       </c>
       <c r="N148" t="n">
-        <v>1356</v>
+        <v>472</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Reades, Hawarden Lettings</t>
         </is>
       </c>
       <c r="S148" s="7" t="inlineStr"/>
@@ -27764,48 +27831,48 @@
       <c r="V148" s="7" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
-          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="7" t="n"/>
       <c r="C149" s="18" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>1</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Llwyn Dinas Fechan, St. Asaph</t>
+          <t>Chester Road East, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>710</v>
+        <v>474</v>
       </c>
       <c r="N149" t="n">
-        <v>248</v>
+        <v>2016</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -27827,14 +27894,14 @@
       <c r="V149" s="7" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
-          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="7" t="n"/>
       <c r="C150" s="18" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="D150" t="n">
         <v>2</v>
@@ -27844,36 +27911,33 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Central Drive, Shotton, Deeside</t>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
-        <v>636</v>
+          <t>LL11</t>
+        </is>
       </c>
       <c r="N150" t="n">
-        <v>1924</v>
+        <v>1300</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S150" s="7" t="inlineStr"/>
@@ -27890,29 +27954,29 @@
       <c r="V150" s="7" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
-          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="7" t="n"/>
       <c r="C151" s="18" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D151" t="n">
         <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Llys Y Ddol, Mold</t>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -27921,19 +27985,19 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1368</v>
+        <v>936</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S151" s="7" t="inlineStr"/>
@@ -27950,53 +28014,50 @@
       <c r="V151" s="7" t="inlineStr"/>
       <c r="W151" t="inlineStr">
         <is>
-          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="7" t="n"/>
       <c r="C152" s="18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Mill View Road, Shotton, CH5</t>
+          <t>9 Park Road, Ruthin</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I152" t="n">
-        <v>1087</v>
+          <t>LL15</t>
+        </is>
       </c>
       <c r="N152" t="n">
-        <v>2236</v>
+        <v>576</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
         </is>
       </c>
       <c r="S152" s="7" t="inlineStr"/>
@@ -28013,48 +28074,48 @@
       <c r="V152" s="7" t="inlineStr"/>
       <c r="W152" t="inlineStr">
         <is>
-          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="7" t="n"/>
       <c r="C153" s="18" t="n">
-        <v>1100</v>
+        <v>795</v>
       </c>
       <c r="D153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Chestnut Way, Penyffordd, Chester</t>
+          <t>Gladstone Street, Mold</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>CH4</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>765</v>
+        <v>905</v>
       </c>
       <c r="N153" t="n">
-        <v>144</v>
+        <v>1356</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -28076,17 +28137,17 @@
       <c r="V153" s="7" t="inlineStr"/>
       <c r="W153" t="inlineStr">
         <is>
-          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="7" t="n"/>
       <c r="C154" s="18" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
@@ -28098,28 +28159,31 @@
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>LL18</t>
-        </is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>710</v>
       </c>
       <c r="N154" t="n">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S154" s="7" t="inlineStr"/>
@@ -28136,50 +28200,53 @@
       <c r="V154" s="7" t="inlineStr"/>
       <c r="W154" t="inlineStr">
         <is>
-          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7" t="n"/>
       <c r="C155" s="18" t="n">
-        <v>875</v>
+        <v>700</v>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+          <t>Central Drive, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>636</v>
       </c>
       <c r="N155" t="n">
-        <v>540</v>
+        <v>1924</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S155" s="7" t="inlineStr"/>
@@ -28196,17 +28263,20 @@
       <c r="V155" s="7" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
-          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="18" t="n">
-        <v>725</v>
+        <v>850</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -28215,28 +28285,28 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>High Street, Connah's Quay, CH5</t>
+          <t>Llys Y Ddol, Mold</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>1904</v>
+        <v>1368</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S156" s="7" t="inlineStr"/>
@@ -28253,50 +28323,53 @@
       <c r="V156" s="7" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
-          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7" t="n"/>
       <c r="C157" s="18" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Well Street, Holywell</t>
+          <t>Mill View Road, Shotton, CH5</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1087</v>
       </c>
       <c r="N157" t="n">
-        <v>904</v>
+        <v>2236</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S157" s="7" t="inlineStr"/>
@@ -28313,50 +28386,53 @@
       <c r="V157" s="7" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
-          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="18" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+          <t>Chestnut Way, Penyffordd, Chester</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>CH6</t>
-        </is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>765</v>
       </c>
       <c r="N158" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S158" s="7" t="inlineStr"/>
@@ -28373,20 +28449,20 @@
       <c r="V158" s="7" t="inlineStr"/>
       <c r="W158" t="inlineStr">
         <is>
-          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7" t="n"/>
       <c r="C159" s="18" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -28395,31 +28471,28 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Rue St. Gregoire, Holywell, CH8</t>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>657</v>
+          <t>LL18</t>
+        </is>
       </c>
       <c r="N159" t="n">
-        <v>876</v>
+        <v>32</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Currans, North Wales</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S159" s="7" t="inlineStr"/>
@@ -28436,50 +28509,50 @@
       <c r="V159" s="7" t="inlineStr"/>
       <c r="W159" t="inlineStr">
         <is>
-          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="18" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>29 Tai Maes, Mold</t>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>1356</v>
+        <v>540</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S160" s="7" t="inlineStr"/>
@@ -28496,21 +28569,18 @@
       <c r="V160" s="7" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
-          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7" t="n"/>
       <c r="C161" s="18" t="n">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>flat</t>
@@ -28518,28 +28588,28 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>St Marys Mews, Mold</t>
+          <t>High Street, Connah's Quay, CH5</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1372</v>
+        <v>1904</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S161" s="7" t="inlineStr"/>
@@ -28556,50 +28626,50 @@
       <c r="V161" s="7" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
-          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="18" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Castle Street, Caergwrle</t>
+          <t>Well Street, Holywell</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>264</v>
+        <v>904</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Town &amp; Country Estate Agents, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S162" s="7" t="inlineStr"/>
@@ -28616,14 +28686,14 @@
       <c r="V162" s="7" t="inlineStr"/>
       <c r="W162" t="inlineStr">
         <is>
-          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7" t="n"/>
       <c r="C163" s="18" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="D163" t="n">
         <v>2</v>
@@ -28633,33 +28703,33 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Fagl Lane, Hope, LL12</t>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH6</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Belvoir, Wrexham</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S163" s="7" t="inlineStr"/>
@@ -28676,50 +28746,53 @@
       <c r="V163" s="7" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
-          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="18" t="n">
-        <v>595</v>
+        <v>950</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Ryeland Street, Deeside</t>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>657</v>
       </c>
       <c r="N164" t="n">
-        <v>2152</v>
+        <v>876</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Currans, North Wales</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr"/>
@@ -28736,7 +28809,7 @@
       <c r="V164" s="7" t="inlineStr"/>
       <c r="W164" t="inlineStr">
         <is>
-          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
         </is>
       </c>
     </row>
@@ -28758,28 +28831,28 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>High Street, Dyserth, LL18</t>
+          <t>29 Tai Maes, Mold</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>232</v>
+        <v>1356</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S165" s="7" t="inlineStr"/>
@@ -28796,17 +28869,17 @@
       <c r="V165" s="7" t="inlineStr"/>
       <c r="W165" t="inlineStr">
         <is>
-          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="18" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
@@ -28818,28 +28891,28 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>St Marys Mews, Mold</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>328</v>
+        <v>1372</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr"/>
@@ -28856,20 +28929,20 @@
       <c r="V166" s="7" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
-          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7" t="n"/>
       <c r="C167" s="18" t="n">
-        <v>795</v>
+        <v>875</v>
       </c>
       <c r="D167" t="n">
         <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -28878,28 +28951,28 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+          <t>Castle Street, Caergwrle</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>LL16</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>940</v>
+        <v>264</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr"/>
@@ -28916,29 +28989,29 @@
       <c r="V167" s="7" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
-          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="18" t="n">
-        <v>975</v>
+        <v>800</v>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
         <v>1</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Derby Road, Caergwrle, Wrexham</t>
+          <t>Fagl Lane, Hope, LL12</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28947,19 +29020,19 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Belvoir, Wrexham</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr"/>
@@ -28976,20 +29049,20 @@
       <c r="V168" s="7" t="inlineStr"/>
       <c r="W168" t="inlineStr">
         <is>
-          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7" t="n"/>
       <c r="C169" s="18" t="n">
-        <v>985</v>
+        <v>595</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -28998,28 +29071,28 @@
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Livingstone Place, St. Asaph, LL17</t>
+          <t>Ryeland Street, Deeside</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N169" t="n">
-        <v>268</v>
+        <v>2152</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr"/>
@@ -29036,12 +29109,312 @@
       <c r="V169" s="7" t="inlineStr"/>
       <c r="W169" t="inlineStr">
         <is>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="7" t="n"/>
+      <c r="C170" s="18" t="n">
+        <v>750</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>High Street, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>232</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S170" s="7" t="inlineStr"/>
+      <c r="T170" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V170" s="7" t="inlineStr"/>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>Newmarket Road, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>328</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S171" s="7" t="inlineStr"/>
+      <c r="T171" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V171" s="7" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="7" t="n"/>
+      <c r="C172" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>940</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S172" s="7" t="inlineStr"/>
+      <c r="T172" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V172" s="7" t="inlineStr"/>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>Derby Road, Caergwrle, Wrexham</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>252</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S173" s="7" t="inlineStr"/>
+      <c r="T173" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V173" s="7" t="inlineStr"/>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="7" t="n"/>
+      <c r="C174" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>268</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S174" s="7" t="inlineStr"/>
+      <c r="T174" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V174" s="7" t="inlineStr"/>
+      <c r="W174" t="inlineStr">
+        <is>
           <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W169"/>
+  <autoFilter ref="A1:W174"/>
   <dataValidations count="1">
     <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
@@ -29216,6 +29589,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T174" r:id="rId173"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W175"/>
+  <dimension ref="A1:W179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17326,7 +17326,7 @@
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n">
-        <v>21660</v>
+        <v>21616</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>1200</v>
+        <v>1630</v>
       </c>
       <c r="D113" s="8" t="n">
         <v>1</v>
@@ -25287,21 +25287,23 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="n">
+        <v>560</v>
+      </c>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
       <c r="N113" s="8" t="n">
-        <v>8636</v>
+        <v>20820</v>
       </c>
       <c r="O113" s="8" t="n">
         <v>0</v>
@@ -25309,12 +25311,12 @@
       <c r="P113" s="8" t="n"/>
       <c r="Q113" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R113" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S113" s="9" t="inlineStr"/>
@@ -25331,7 +25333,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
+          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
         </is>
       </c>
     </row>
@@ -25345,13 +25347,13 @@
         </is>
       </c>
       <c r="C114" s="17" t="n">
-        <v>1100</v>
+        <v>2115</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
@@ -25360,21 +25362,23 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>BS13</t>
-        </is>
-      </c>
-      <c r="I114" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="n">
+        <v>823</v>
+      </c>
       <c r="J114" s="8" t="n"/>
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
       <c r="N114" s="8" t="n">
-        <v>4936</v>
+        <v>20820</v>
       </c>
       <c r="O114" s="8" t="n">
         <v>0</v>
@@ -25382,12 +25386,12 @@
       <c r="P114" s="8" t="n"/>
       <c r="Q114" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R114" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S114" s="9" t="inlineStr"/>
@@ -25404,7 +25408,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -25418,7 +25422,7 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1100</v>
+        <v>1660</v>
       </c>
       <c r="D115" s="8" t="n">
         <v>1</v>
@@ -25433,21 +25437,23 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>Flat B, City Road, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I115" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="n">
+        <v>486</v>
+      </c>
       <c r="J115" s="8" t="n"/>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
       <c r="N115" s="8" t="n">
-        <v>20108</v>
+        <v>21504</v>
       </c>
       <c r="O115" s="8" t="n">
         <v>0</v>
@@ -25455,12 +25461,12 @@
       <c r="P115" s="8" t="n"/>
       <c r="Q115" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R115" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S115" s="9" t="inlineStr"/>
@@ -25477,7 +25483,7 @@
       <c r="V115" s="7" t="inlineStr"/>
       <c r="W115" s="8" t="inlineStr">
         <is>
-          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -25491,13 +25497,13 @@
         </is>
       </c>
       <c r="C116" s="17" t="n">
-        <v>1200</v>
+        <v>1915</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
@@ -25506,7 +25512,7 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Unity Street, BS1 5HH</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
@@ -25515,14 +25521,14 @@
         </is>
       </c>
       <c r="I116" s="8" t="n">
-        <v>452</v>
+        <v>746</v>
       </c>
       <c r="J116" s="8" t="n"/>
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n">
-        <v>20772</v>
+        <v>21680</v>
       </c>
       <c r="O116" s="8" t="n">
         <v>0</v>
@@ -25530,12 +25536,12 @@
       <c r="P116" s="8" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R116" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S116" s="9" t="inlineStr"/>
@@ -25552,7 +25558,7 @@
       <c r="V116" s="7" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25575,7 @@
         <v>1200</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
         <v>1</v>
@@ -25581,12 +25587,12 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
+          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I117" s="8" t="n"/>
@@ -25595,7 +25601,7 @@
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
       <c r="N117" s="8" t="n">
-        <v>4160</v>
+        <v>8636</v>
       </c>
       <c r="O117" s="8" t="n">
         <v>0</v>
@@ -25603,12 +25609,12 @@
       <c r="P117" s="8" t="n"/>
       <c r="Q117" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R117" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S117" s="9" t="inlineStr"/>
@@ -25625,7 +25631,7 @@
       <c r="V117" s="7" t="inlineStr"/>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
+          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
         </is>
       </c>
     </row>
@@ -25639,7 +25645,7 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>965</v>
+        <v>1100</v>
       </c>
       <c r="D118" s="8" t="n">
         <v>1</v>
@@ -25654,12 +25660,12 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>Boulevard View, Whitchurch Lane</t>
+          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS13</t>
         </is>
       </c>
       <c r="I118" s="8" t="n"/>
@@ -25668,7 +25674,7 @@
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n">
-        <v>5764</v>
+        <v>4936</v>
       </c>
       <c r="O118" s="8" t="n">
         <v>0</v>
@@ -25676,12 +25682,12 @@
       <c r="P118" s="8" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R118" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S118" s="9" t="inlineStr"/>
@@ -25698,7 +25704,7 @@
       <c r="V118" s="7" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
+          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
         </is>
       </c>
     </row>
@@ -25712,7 +25718,7 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D119" s="8" t="n">
         <v>1</v>
@@ -25727,7 +25733,7 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>Braggs Lane, Bristol</t>
+          <t>Flat B, City Road, Bristol</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -25735,15 +25741,13 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I119" s="8" t="n">
-        <v>409</v>
-      </c>
+      <c r="I119" s="8" t="n"/>
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
       <c r="N119" s="8" t="n">
-        <v>20360</v>
+        <v>20108</v>
       </c>
       <c r="O119" s="8" t="n">
         <v>0</v>
@@ -25751,12 +25755,12 @@
       <c r="P119" s="8" t="n"/>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R119" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S119" s="9" t="inlineStr"/>
@@ -25773,7 +25777,7 @@
       <c r="V119" s="7" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
+          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
         </is>
       </c>
     </row>
@@ -25802,21 +25806,23 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>Montague Court, Bristol</t>
+          <t>City Centre, Unity Street, BS1 5HH</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I120" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="n">
+        <v>452</v>
+      </c>
       <c r="J120" s="8" t="n"/>
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n">
-        <v>21632</v>
+        <v>20772</v>
       </c>
       <c r="O120" s="8" t="n">
         <v>0</v>
@@ -25829,7 +25835,7 @@
       </c>
       <c r="R120" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S120" s="9" t="inlineStr"/>
@@ -25846,7 +25852,7 @@
       <c r="V120" s="7" t="inlineStr"/>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
+          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
         </is>
       </c>
     </row>
@@ -25860,10 +25866,10 @@
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="8" t="n">
         <v>1</v>
@@ -25875,23 +25881,21 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
+          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I121" s="8" t="n">
-        <v>397</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="n"/>
       <c r="J121" s="8" t="n"/>
       <c r="K121" s="8" t="n"/>
       <c r="L121" s="8" t="n"/>
       <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n">
-        <v>15212</v>
+        <v>4160</v>
       </c>
       <c r="O121" s="8" t="n">
         <v>0</v>
@@ -25899,12 +25903,12 @@
       <c r="P121" s="8" t="n"/>
       <c r="Q121" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R121" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S121" s="9" t="inlineStr"/>
@@ -25921,7 +25925,7 @@
       <c r="V121" s="7" t="inlineStr"/>
       <c r="W121" s="8" t="inlineStr">
         <is>
-          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
+          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
         </is>
       </c>
     </row>
@@ -25935,7 +25939,7 @@
         </is>
       </c>
       <c r="C122" s="17" t="n">
-        <v>1100</v>
+        <v>965</v>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
@@ -25950,23 +25954,21 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Barton Close, St. Annes Park, BS4</t>
+          <t>Boulevard View, Whitchurch Lane</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I122" s="8" t="n">
-        <v>441</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="n"/>
       <c r="J122" s="8" t="n"/>
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
       <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n">
-        <v>5212</v>
+        <v>5764</v>
       </c>
       <c r="O122" s="8" t="n">
         <v>0</v>
@@ -25974,12 +25976,12 @@
       <c r="P122" s="8" t="n"/>
       <c r="Q122" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R122" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S122" s="9" t="inlineStr"/>
@@ -25996,7 +25998,7 @@
       <c r="V122" s="7" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr">
         <is>
-          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
+          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
         </is>
       </c>
     </row>
@@ -26010,7 +26012,7 @@
         </is>
       </c>
       <c r="C123" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D123" s="8" t="n">
         <v>1</v>
@@ -26025,21 +26027,23 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Braggs Lane, Bristol</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I123" s="8" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="n">
+        <v>409</v>
+      </c>
       <c r="J123" s="8" t="n"/>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n">
-        <v>7112</v>
+        <v>20360</v>
       </c>
       <c r="O123" s="8" t="n">
         <v>0</v>
@@ -26047,12 +26051,12 @@
       <c r="P123" s="8" t="n"/>
       <c r="Q123" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R123" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S123" s="9" t="inlineStr"/>
@@ -26069,7 +26073,7 @@
       <c r="V123" s="7" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr">
         <is>
-          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
+          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
         </is>
       </c>
     </row>
@@ -26083,7 +26087,7 @@
         </is>
       </c>
       <c r="C124" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D124" s="8" t="n">
         <v>1</v>
@@ -26098,7 +26102,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>Chapel Street, St Philips, Bristol, BS2</t>
+          <t>Montague Court, Bristol</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
@@ -26106,15 +26110,13 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I124" s="8" t="n">
-        <v>549</v>
-      </c>
+      <c r="I124" s="8" t="n"/>
       <c r="J124" s="8" t="n"/>
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
       <c r="M124" s="8" t="n"/>
       <c r="N124" s="8" t="n">
-        <v>11732</v>
+        <v>21632</v>
       </c>
       <c r="O124" s="8" t="n">
         <v>0</v>
@@ -26122,12 +26124,12 @@
       <c r="P124" s="8" t="n"/>
       <c r="Q124" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R124" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S124" s="9" t="inlineStr"/>
@@ -26144,7 +26146,7 @@
       <c r="V124" s="7" t="inlineStr"/>
       <c r="W124" s="8" t="inlineStr">
         <is>
-          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
+          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
         </is>
       </c>
     </row>
@@ -26173,23 +26175,23 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
+          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I125" s="8" t="n">
-        <v>211</v>
+        <v>397</v>
       </c>
       <c r="J125" s="8" t="n"/>
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
       <c r="M125" s="8" t="n"/>
       <c r="N125" s="8" t="n">
-        <v>14596</v>
+        <v>15212</v>
       </c>
       <c r="O125" s="8" t="n">
         <v>0</v>
@@ -26197,12 +26199,12 @@
       <c r="P125" s="8" t="n"/>
       <c r="Q125" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R125" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S125" s="9" t="inlineStr"/>
@@ -26219,7 +26221,7 @@
       <c r="V125" s="7" t="inlineStr"/>
       <c r="W125" s="8" t="inlineStr">
         <is>
-          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
+          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
         </is>
       </c>
     </row>
@@ -26248,21 +26250,23 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
+          <t>Barton Close, St. Annes Park, BS4</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
-        </is>
-      </c>
-      <c r="I126" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="n">
+        <v>441</v>
+      </c>
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n">
-        <v>5316</v>
+        <v>5212</v>
       </c>
       <c r="O126" s="8" t="n">
         <v>0</v>
@@ -26270,12 +26274,12 @@
       <c r="P126" s="8" t="n"/>
       <c r="Q126" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R126" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S126" s="9" t="inlineStr"/>
@@ -26292,7 +26296,7 @@
       <c r="V126" s="7" t="inlineStr"/>
       <c r="W126" s="8" t="inlineStr">
         <is>
-          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
+          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
         </is>
       </c>
     </row>
@@ -26343,7 +26347,7 @@
       <c r="P127" s="8" t="n"/>
       <c r="Q127" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R127" s="8" t="inlineStr">
@@ -26365,7 +26369,7 @@
       <c r="V127" s="7" t="inlineStr"/>
       <c r="W127" s="8" t="inlineStr">
         <is>
-          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
+          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26383,7 @@
         </is>
       </c>
       <c r="C128" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D128" s="8" t="n">
         <v>1</v>
@@ -26394,23 +26398,23 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>Seymour Road, Bristol, BS5</t>
+          <t>Chapel Street, St Philips, Bristol, BS2</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>484</v>
+        <v>549</v>
       </c>
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="n"/>
       <c r="N128" s="8" t="n">
-        <v>17164</v>
+        <v>11732</v>
       </c>
       <c r="O128" s="8" t="n">
         <v>0</v>
@@ -26418,12 +26422,12 @@
       <c r="P128" s="8" t="n"/>
       <c r="Q128" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R128" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S128" s="9" t="inlineStr"/>
@@ -26440,7 +26444,7 @@
       <c r="V128" s="7" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
+          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
         </is>
       </c>
     </row>
@@ -26469,21 +26473,23 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>Pinkhams Twist, Bristol</t>
+          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I129" s="8" t="n"/>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="n">
+        <v>211</v>
+      </c>
       <c r="J129" s="8" t="n"/>
       <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n">
-        <v>4276</v>
+        <v>14596</v>
       </c>
       <c r="O129" s="8" t="n">
         <v>0</v>
@@ -26491,12 +26497,12 @@
       <c r="P129" s="8" t="n"/>
       <c r="Q129" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R129" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Whitchurch</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S129" s="9" t="inlineStr"/>
@@ -26513,7 +26519,7 @@
       <c r="V129" s="7" t="inlineStr"/>
       <c r="W129" s="8" t="inlineStr">
         <is>
-          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
+          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
         </is>
       </c>
     </row>
@@ -26527,7 +26533,7 @@
         </is>
       </c>
       <c r="C130" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D130" s="8" t="n">
         <v>1</v>
@@ -26537,17 +26543,17 @@
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>Alexandra Park, Redland, Bristol, BS6</t>
+          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I130" s="8" t="n"/>
@@ -26556,7 +26562,7 @@
       <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n">
-        <v>12812</v>
+        <v>5316</v>
       </c>
       <c r="O130" s="8" t="n">
         <v>0</v>
@@ -26564,12 +26570,12 @@
       <c r="P130" s="8" t="n"/>
       <c r="Q130" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R130" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S130" s="9" t="inlineStr"/>
@@ -26586,7 +26592,7 @@
       <c r="V130" s="7" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
+          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
         </is>
       </c>
     </row>
@@ -26615,12 +26621,12 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I131" s="8" t="n"/>
@@ -26629,7 +26635,7 @@
       <c r="L131" s="8" t="n"/>
       <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n">
-        <v>18020</v>
+        <v>7112</v>
       </c>
       <c r="O131" s="8" t="n">
         <v>0</v>
@@ -26637,12 +26643,12 @@
       <c r="P131" s="8" t="n"/>
       <c r="Q131" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R131" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S131" s="9" t="inlineStr"/>
@@ -26659,7 +26665,7 @@
       <c r="V131" s="7" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr">
         <is>
-          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
+          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
         </is>
       </c>
     </row>
@@ -26676,7 +26682,7 @@
         <v>1150</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="8" t="n">
         <v>1</v>
@@ -26688,7 +26694,7 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Bristol, BS5</t>
+          <t>Seymour Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
@@ -26697,14 +26703,14 @@
         </is>
       </c>
       <c r="I132" s="8" t="n">
-        <v>3057</v>
+        <v>484</v>
       </c>
       <c r="J132" s="8" t="n"/>
       <c r="K132" s="8" t="n"/>
       <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n">
-        <v>11864</v>
+        <v>17164</v>
       </c>
       <c r="O132" s="8" t="n">
         <v>0</v>
@@ -26712,12 +26718,12 @@
       <c r="P132" s="8" t="n"/>
       <c r="Q132" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R132" s="8" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S132" s="9" t="inlineStr"/>
@@ -26734,7 +26740,7 @@
       <c r="V132" s="7" t="inlineStr"/>
       <c r="W132" s="8" t="inlineStr">
         <is>
-          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
+          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
         </is>
       </c>
     </row>
@@ -26748,7 +26754,7 @@
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>995</v>
+        <v>1150</v>
       </c>
       <c r="D133" s="8" t="n">
         <v>1</v>
@@ -26763,12 +26769,12 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>Two Mile Hill Road, Kingswood, Bristol</t>
+          <t>Pinkhams Twist, Bristol</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>BS15</t>
+          <t>BS14</t>
         </is>
       </c>
       <c r="I133" s="8" t="n"/>
@@ -26777,7 +26783,7 @@
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n">
-        <v>5116</v>
+        <v>4276</v>
       </c>
       <c r="O133" s="8" t="n">
         <v>0</v>
@@ -26785,12 +26791,12 @@
       <c r="P133" s="8" t="n"/>
       <c r="Q133" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R133" s="8" t="inlineStr">
         <is>
-          <t>TLS Estate Agents, Bristol</t>
+          <t>Hunters, Whitchurch</t>
         </is>
       </c>
       <c r="S133" s="9" t="inlineStr"/>
@@ -26807,7 +26813,7 @@
       <c r="V133" s="7" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr">
         <is>
-          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
+          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
         </is>
       </c>
     </row>
@@ -26821,7 +26827,7 @@
         </is>
       </c>
       <c r="C134" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D134" s="8" t="n">
         <v>1</v>
@@ -26831,17 +26837,17 @@
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>Robertson Drive, St Annes Park</t>
+          <t>Alexandra Park, Redland, Bristol, BS6</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I134" s="8" t="n"/>
@@ -26850,7 +26856,7 @@
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n">
-        <v>4252</v>
+        <v>12812</v>
       </c>
       <c r="O134" s="8" t="n">
         <v>0</v>
@@ -26858,12 +26864,12 @@
       <c r="P134" s="8" t="n"/>
       <c r="Q134" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R134" s="8" t="inlineStr">
         <is>
-          <t>D W Smith &amp; Company, Hanham</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S134" s="9" t="inlineStr"/>
@@ -26880,7 +26886,7 @@
       <c r="V134" s="7" t="inlineStr"/>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
+          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
         </is>
       </c>
     </row>
@@ -26894,7 +26900,7 @@
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>1</v>
@@ -26909,23 +26915,21 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
+          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I135" s="8" t="n">
-        <v>527</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="n"/>
       <c r="J135" s="8" t="n"/>
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n">
-        <v>5548</v>
+        <v>18020</v>
       </c>
       <c r="O135" s="8" t="n">
         <v>0</v>
@@ -26933,12 +26937,12 @@
       <c r="P135" s="8" t="n"/>
       <c r="Q135" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R135" s="8" t="inlineStr">
         <is>
-          <t>Sheedy &amp; Co, Covering Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S135" s="9" t="inlineStr"/>
@@ -26955,7 +26959,7 @@
       <c r="V135" s="7" t="inlineStr"/>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
+          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
         </is>
       </c>
     </row>
@@ -26969,10 +26973,10 @@
         </is>
       </c>
       <c r="C136" s="17" t="n">
-        <v>1195</v>
+        <v>1150</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>1</v>
@@ -26984,7 +26988,7 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Church Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
@@ -26993,14 +26997,14 @@
         </is>
       </c>
       <c r="I136" s="8" t="n">
-        <v>409</v>
+        <v>3057</v>
       </c>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n">
-        <v>10420</v>
+        <v>11864</v>
       </c>
       <c r="O136" s="8" t="n">
         <v>0</v>
@@ -27008,12 +27012,12 @@
       <c r="P136" s="8" t="n"/>
       <c r="Q136" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R136" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S136" s="9" t="inlineStr"/>
@@ -27030,7 +27034,7 @@
       <c r="V136" s="7" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
+          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
         </is>
       </c>
     </row>
@@ -27044,7 +27048,7 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1200</v>
+        <v>995</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>1</v>
@@ -27059,12 +27063,12 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol, BS4</t>
+          <t>Two Mile Hill Road, Kingswood, Bristol</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS15</t>
         </is>
       </c>
       <c r="I137" s="8" t="n"/>
@@ -27073,7 +27077,7 @@
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n">
-        <v>6852</v>
+        <v>5116</v>
       </c>
       <c r="O137" s="8" t="n">
         <v>0</v>
@@ -27081,12 +27085,12 @@
       <c r="P137" s="8" t="n"/>
       <c r="Q137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R137" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>TLS Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S137" s="9" t="inlineStr"/>
@@ -27103,7 +27107,7 @@
       <c r="V137" s="7" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
+          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
         </is>
       </c>
     </row>
@@ -27117,7 +27121,7 @@
         </is>
       </c>
       <c r="C138" s="17" t="n">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="D138" s="8" t="n">
         <v>1</v>
@@ -27127,28 +27131,26 @@
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Robertson Drive, St Annes Park</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I138" s="8" t="n">
-        <v>248</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="n"/>
       <c r="J138" s="8" t="n"/>
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
       <c r="M138" s="8" t="n"/>
       <c r="N138" s="8" t="n">
-        <v>10420</v>
+        <v>4252</v>
       </c>
       <c r="O138" s="8" t="n">
         <v>0</v>
@@ -27156,12 +27158,12 @@
       <c r="P138" s="8" t="n"/>
       <c r="Q138" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R138" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>D W Smith &amp; Company, Hanham</t>
         </is>
       </c>
       <c r="S138" s="9" t="inlineStr"/>
@@ -27178,7 +27180,7 @@
       <c r="V138" s="7" t="inlineStr"/>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
+          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
         </is>
       </c>
     </row>
@@ -27192,13 +27194,13 @@
         </is>
       </c>
       <c r="C139" s="17" t="n">
-        <v>1600</v>
+        <v>1150</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
@@ -27207,21 +27209,23 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Central Quay North</t>
+          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I139" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="n">
+        <v>527</v>
+      </c>
       <c r="J139" s="8" t="n"/>
       <c r="K139" s="8" t="n"/>
       <c r="L139" s="8" t="n"/>
       <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n">
-        <v>20792</v>
+        <v>5548</v>
       </c>
       <c r="O139" s="8" t="n">
         <v>0</v>
@@ -27229,12 +27233,12 @@
       <c r="P139" s="8" t="n"/>
       <c r="Q139" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R139" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Sheedy &amp; Co, Covering Bristol</t>
         </is>
       </c>
       <c r="S139" s="9" t="inlineStr"/>
@@ -27251,7 +27255,7 @@
       <c r="V139" s="7" t="inlineStr"/>
       <c r="W139" s="8" t="inlineStr">
         <is>
-          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
         </is>
       </c>
     </row>
@@ -27265,13 +27269,13 @@
         </is>
       </c>
       <c r="C140" s="17" t="n">
-        <v>1600</v>
+        <v>1195</v>
       </c>
       <c r="D140" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
@@ -27280,32 +27284,36 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I140" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="n">
+        <v>409</v>
+      </c>
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
-      <c r="N140" s="8" t="n"/>
+      <c r="N140" s="8" t="n">
+        <v>10420</v>
+      </c>
       <c r="O140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="8" t="n"/>
       <c r="Q140" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R140" s="8" t="inlineStr">
         <is>
-          <t>Stonebridge Shaw, Portishead</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S140" s="9" t="inlineStr"/>
@@ -27322,7 +27330,7 @@
       <c r="V140" s="7" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27344,7 @@
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D141" s="8" t="n">
         <v>1</v>
@@ -27351,12 +27359,12 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>St Michaels Hill Ref 708</t>
+          <t>Knowle Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I141" s="8" t="n"/>
@@ -27365,7 +27373,7 @@
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n">
-        <v>19512</v>
+        <v>6852</v>
       </c>
       <c r="O141" s="8" t="n">
         <v>0</v>
@@ -27373,12 +27381,12 @@
       <c r="P141" s="8" t="n"/>
       <c r="Q141" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R141" s="8" t="inlineStr">
         <is>
-          <t>Jackson Property Management Ltd, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S141" s="9" t="inlineStr"/>
@@ -27395,7 +27403,7 @@
       <c r="V141" s="7" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
         </is>
       </c>
     </row>
@@ -27409,7 +27417,7 @@
         </is>
       </c>
       <c r="C142" s="17" t="n">
-        <v>1095</v>
+        <v>850</v>
       </c>
       <c r="D142" s="8" t="n">
         <v>1</v>
@@ -27424,21 +27432,23 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I142" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="n">
+        <v>248</v>
+      </c>
       <c r="J142" s="8" t="n"/>
       <c r="K142" s="8" t="n"/>
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n">
-        <v>2652</v>
+        <v>10420</v>
       </c>
       <c r="O142" s="8" t="n">
         <v>0</v>
@@ -27446,12 +27456,12 @@
       <c r="P142" s="8" t="n"/>
       <c r="Q142" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R142" s="8" t="inlineStr">
         <is>
-          <t>Millennium Lettings &amp; Management, Bristol</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S142" s="9" t="inlineStr"/>
@@ -27468,7 +27478,7 @@
       <c r="V142" s="7" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
         </is>
       </c>
     </row>
@@ -27482,13 +27492,13 @@
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
@@ -27497,23 +27507,21 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Old Market, Verdigris, BS2 0AF</t>
+          <t>Central Quay North</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I143" s="8" t="n">
-        <v>388</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="n"/>
       <c r="J143" s="8" t="n"/>
       <c r="K143" s="8" t="n"/>
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n">
-        <v>21220</v>
+        <v>20792</v>
       </c>
       <c r="O143" s="8" t="n">
         <v>0</v>
@@ -27521,12 +27529,12 @@
       <c r="P143" s="8" t="n"/>
       <c r="Q143" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R143" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S143" s="9" t="inlineStr"/>
@@ -27543,254 +27551,306 @@
       <c r="V143" s="7" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
+          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>Marsh Street, Bristol</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="n"/>
+      <c r="J144" s="8" t="n"/>
+      <c r="K144" s="8" t="n"/>
+      <c r="L144" s="8" t="n"/>
+      <c r="M144" s="8" t="n"/>
+      <c r="N144" s="8" t="n"/>
+      <c r="O144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="8" t="n"/>
+      <c r="Q144" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R144" s="8" t="inlineStr">
+        <is>
+          <t>Stonebridge Shaw, Portishead</t>
+        </is>
+      </c>
+      <c r="S144" s="9" t="inlineStr"/>
+      <c r="T144" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V144" s="7" t="inlineStr"/>
+      <c r="W144" s="8" t="inlineStr">
+        <is>
+          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>St Michaels Hill Ref 708</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="n"/>
+      <c r="J145" s="8" t="n"/>
+      <c r="K145" s="8" t="n"/>
+      <c r="L145" s="8" t="n"/>
+      <c r="M145" s="8" t="n"/>
+      <c r="N145" s="8" t="n">
+        <v>19512</v>
+      </c>
+      <c r="O145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="8" t="n"/>
+      <c r="Q145" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R145" s="8" t="inlineStr">
+        <is>
+          <t>Jackson Property Management Ltd, Bristol</t>
+        </is>
+      </c>
+      <c r="S145" s="9" t="inlineStr"/>
+      <c r="T145" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V145" s="7" t="inlineStr"/>
+      <c r="W145" s="8" t="inlineStr">
+        <is>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="n"/>
+      <c r="J146" s="8" t="n"/>
+      <c r="K146" s="8" t="n"/>
+      <c r="L146" s="8" t="n"/>
+      <c r="M146" s="8" t="n"/>
+      <c r="N146" s="8" t="n">
+        <v>2652</v>
+      </c>
+      <c r="O146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="8" t="n"/>
+      <c r="Q146" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R146" s="8" t="inlineStr">
+        <is>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
+        </is>
+      </c>
+      <c r="S146" s="9" t="inlineStr"/>
+      <c r="T146" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V146" s="7" t="inlineStr"/>
+      <c r="W146" s="8" t="inlineStr">
+        <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I147" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J147" s="8" t="n"/>
+      <c r="K147" s="8" t="n"/>
+      <c r="L147" s="8" t="n"/>
+      <c r="M147" s="8" t="n"/>
+      <c r="N147" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="8" t="n"/>
+      <c r="Q147" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R147" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S147" s="9" t="inlineStr"/>
+      <c r="T147" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V147" s="7" t="inlineStr"/>
+      <c r="W147" s="8" t="inlineStr">
+        <is>
           <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="7" t="n"/>
-      <c r="C144" s="18" t="n">
-        <v>800</v>
-      </c>
-      <c r="D144" t="n">
-        <v>2</v>
-      </c>
-      <c r="E144" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>LL11</t>
-        </is>
-      </c>
-      <c r="N144" t="n">
-        <v>448</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S144" s="7" t="inlineStr"/>
-      <c r="T144" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V144" s="7" t="inlineStr"/>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="7" t="n"/>
-      <c r="C145" s="18" t="n">
-        <v>900</v>
-      </c>
-      <c r="D145" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>LL18</t>
-        </is>
-      </c>
-      <c r="N145" t="n">
-        <v>328</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Fifty North West, Chester</t>
-        </is>
-      </c>
-      <c r="S145" s="7" t="inlineStr"/>
-      <c r="T145" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V145" s="7" t="inlineStr"/>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="7" t="n"/>
-      <c r="C146" s="18" t="n">
-        <v>625</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>Field View, Mancot, Deeside, CH5 2EY</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="N146" t="n">
-        <v>824</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Habodel Property Services Ltd, Doncaster</t>
-        </is>
-      </c>
-      <c r="S146" s="7" t="inlineStr"/>
-      <c r="T146" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V146" s="7" t="inlineStr"/>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="7" t="n"/>
-      <c r="C147" s="18" t="n">
-        <v>795</v>
-      </c>
-      <c r="D147" t="n">
-        <v>2</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>semi_detached</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>Cilcain, The Square, CH7</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>CH7</t>
-        </is>
-      </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>Williams Estates, Rhuddlan</t>
-        </is>
-      </c>
-      <c r="S147" s="7" t="inlineStr"/>
-      <c r="T147" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V147" s="7" t="inlineStr"/>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="7" t="n"/>
       <c r="C148" s="18" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="D148" t="n">
         <v>2</v>
@@ -27800,33 +27860,33 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>56</v>
+        <v>448</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S148" s="7" t="inlineStr"/>
@@ -27843,14 +27903,14 @@
       <c r="V148" s="7" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
-          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="7" t="n"/>
       <c r="C149" s="18" t="n">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="D149" t="n">
         <v>2</v>
@@ -27860,36 +27920,33 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Hill Top Close, Ewloe, CH5</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
-        <v>721</v>
+          <t>LL18</t>
+        </is>
       </c>
       <c r="N149" t="n">
-        <v>472</v>
+        <v>328</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Reades, Hawarden Lettings</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S149" s="7" t="inlineStr"/>
@@ -27906,14 +27963,14 @@
       <c r="V149" s="7" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
-          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="7" t="n"/>
       <c r="C150" s="18" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -27928,7 +27985,7 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Chester Road East, Shotton, Deeside</t>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -27936,23 +27993,20 @@
           <t>CH5</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>474</v>
-      </c>
       <c r="N150" t="n">
-        <v>2016</v>
+        <v>824</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Habodel Property Services Ltd, Doncaster</t>
         </is>
       </c>
       <c r="S150" s="7" t="inlineStr"/>
@@ -27969,14 +28023,14 @@
       <c r="V150" s="7" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
-          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="7" t="n"/>
       <c r="C151" s="18" t="n">
-        <v>750</v>
+        <v>795</v>
       </c>
       <c r="D151" t="n">
         <v>2</v>
@@ -27986,33 +28040,33 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+          <t>Cilcain, The Square, CH7</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>LL11</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Williams Estates, Rhuddlan</t>
         </is>
       </c>
       <c r="S151" s="7" t="inlineStr"/>
@@ -28029,14 +28083,14 @@
       <c r="V151" s="7" t="inlineStr"/>
       <c r="W151" t="inlineStr">
         <is>
-          <t>40274ada7dfa710e5054184216178477a704016c</t>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="7" t="n"/>
       <c r="C152" s="18" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="D152" t="n">
         <v>2</v>
@@ -28051,23 +28105,23 @@
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>936</v>
+        <v>56</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -28089,14 +28143,14 @@
       <c r="V152" s="7" t="inlineStr"/>
       <c r="W152" t="inlineStr">
         <is>
-          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="7" t="n"/>
       <c r="C153" s="18" t="n">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="D153" t="n">
         <v>2</v>
@@ -28111,28 +28165,31 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>9 Park Road, Ruthin</t>
+          <t>Hill Top Close, Ewloe, CH5</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>LL15</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>721</v>
       </c>
       <c r="N153" t="n">
-        <v>576</v>
+        <v>472</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Ruthin</t>
+          <t>Reades, Hawarden Lettings</t>
         </is>
       </c>
       <c r="S153" s="7" t="inlineStr"/>
@@ -28149,53 +28206,53 @@
       <c r="V153" s="7" t="inlineStr"/>
       <c r="W153" t="inlineStr">
         <is>
-          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="7" t="n"/>
       <c r="C154" s="18" t="n">
-        <v>795</v>
+        <v>650</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Gladstone Street, Mold</t>
+          <t>Chester Road East, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>905</v>
+        <v>474</v>
       </c>
       <c r="N154" t="n">
-        <v>1356</v>
+        <v>2016</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S154" s="7" t="inlineStr"/>
@@ -28212,14 +28269,14 @@
       <c r="V154" s="7" t="inlineStr"/>
       <c r="W154" t="inlineStr">
         <is>
-          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7" t="n"/>
       <c r="C155" s="18" t="n">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="D155" t="n">
         <v>2</v>
@@ -28229,36 +28286,33 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Llwyn Dinas Fechan, St. Asaph</t>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>LL17</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>710</v>
+          <t>LL11</t>
+        </is>
       </c>
       <c r="N155" t="n">
-        <v>248</v>
+        <v>1300</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S155" s="7" t="inlineStr"/>
@@ -28275,14 +28329,14 @@
       <c r="V155" s="7" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
-          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="18" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D156" t="n">
         <v>2</v>
@@ -28292,36 +28346,33 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Central Drive, Shotton, Deeside</t>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I156" t="n">
-        <v>636</v>
+          <t>CH7</t>
+        </is>
       </c>
       <c r="N156" t="n">
-        <v>1924</v>
+        <v>936</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S156" s="7" t="inlineStr"/>
@@ -28338,50 +28389,50 @@
       <c r="V156" s="7" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
-          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7" t="n"/>
       <c r="C157" s="18" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D157" t="n">
         <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Llys Y Ddol, Mold</t>
+          <t>9 Park Road, Ruthin</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>LL15</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1368</v>
+        <v>576</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
         </is>
       </c>
       <c r="S157" s="7" t="inlineStr"/>
@@ -28398,53 +28449,53 @@
       <c r="V157" s="7" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
-          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="18" t="n">
-        <v>1000</v>
+        <v>795</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Mill View Road, Shotton, CH5</t>
+          <t>Gladstone Street, Mold</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1087</v>
+        <v>905</v>
       </c>
       <c r="N158" t="n">
-        <v>2236</v>
+        <v>1356</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S158" s="7" t="inlineStr"/>
@@ -28461,20 +28512,20 @@
       <c r="V158" s="7" t="inlineStr"/>
       <c r="W158" t="inlineStr">
         <is>
-          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7" t="n"/>
       <c r="C159" s="18" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -28483,31 +28534,31 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Chestnut Way, Penyffordd, Chester</t>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CH4</t>
+          <t>LL17</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>765</v>
+        <v>710</v>
       </c>
       <c r="N159" t="n">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S159" s="7" t="inlineStr"/>
@@ -28524,50 +28575,53 @@
       <c r="V159" s="7" t="inlineStr"/>
       <c r="W159" t="inlineStr">
         <is>
-          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="18" t="n">
-        <v>975</v>
+        <v>700</v>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+          <t>Central Drive, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>LL18</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>636</v>
       </c>
       <c r="N160" t="n">
-        <v>32</v>
+        <v>1924</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S160" s="7" t="inlineStr"/>
@@ -28584,50 +28638,50 @@
       <c r="V160" s="7" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
-          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7" t="n"/>
       <c r="C161" s="18" t="n">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="D161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+          <t>Llys Y Ddol, Mold</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>540</v>
+        <v>1368</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S161" s="7" t="inlineStr"/>
@@ -28644,26 +28698,29 @@
       <c r="V161" s="7" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
-          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="18" t="n">
-        <v>725</v>
+        <v>1000</v>
       </c>
       <c r="D162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>High Street, Connah's Quay, CH5</t>
+          <t>Mill View Road, Shotton, CH5</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28671,15 +28728,18 @@
           <t>CH5</t>
         </is>
       </c>
+      <c r="I162" t="n">
+        <v>1087</v>
+      </c>
       <c r="N162" t="n">
-        <v>1904</v>
+        <v>2236</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -28701,50 +28761,53 @@
       <c r="V162" s="7" t="inlineStr"/>
       <c r="W162" t="inlineStr">
         <is>
-          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7" t="n"/>
       <c r="C163" s="18" t="n">
-        <v>625</v>
+        <v>1100</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Well Street, Holywell</t>
+          <t>Chestnut Way, Penyffordd, Chester</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>765</v>
       </c>
       <c r="N163" t="n">
-        <v>904</v>
+        <v>144</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S163" s="7" t="inlineStr"/>
@@ -28761,50 +28824,50 @@
       <c r="V163" s="7" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
-          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="18" t="n">
-        <v>900</v>
+        <v>975</v>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
         <v>1</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CH6</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr"/>
@@ -28821,20 +28884,20 @@
       <c r="V164" s="7" t="inlineStr"/>
       <c r="W164" t="inlineStr">
         <is>
-          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="7" t="n"/>
       <c r="C165" s="18" t="n">
-        <v>950</v>
+        <v>875</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -28843,7 +28906,7 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Rue St. Gregoire, Holywell, CH8</t>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28851,23 +28914,20 @@
           <t>CH8</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>657</v>
-      </c>
       <c r="N165" t="n">
-        <v>876</v>
+        <v>540</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Currans, North Wales</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S165" s="7" t="inlineStr"/>
@@ -28884,19 +28944,16 @@
       <c r="V165" s="7" t="inlineStr"/>
       <c r="W165" t="inlineStr">
         <is>
-          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="18" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
-      </c>
-      <c r="E166" t="n">
         <v>1</v>
       </c>
       <c r="F166" t="inlineStr">
@@ -28906,28 +28963,28 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>29 Tai Maes, Mold</t>
+          <t>High Street, Connah's Quay, CH5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1356</v>
+        <v>1904</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr"/>
@@ -28944,14 +29001,14 @@
       <c r="V166" s="7" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
-          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7" t="n"/>
       <c r="C167" s="18" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -28966,23 +29023,23 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>St Marys Mews, Mold</t>
+          <t>Well Street, Holywell</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1372</v>
+        <v>904</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -29004,20 +29061,20 @@
       <c r="V167" s="7" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
-          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="18" t="n">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="D168" t="n">
         <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -29026,28 +29083,28 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Castle Street, Caergwrle</t>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH6</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Town &amp; Country Estate Agents, Wrexham</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr"/>
@@ -29064,50 +29121,53 @@
       <c r="V168" s="7" t="inlineStr"/>
       <c r="W168" t="inlineStr">
         <is>
-          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7" t="n"/>
       <c r="C169" s="18" t="n">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="D169" t="n">
         <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Fagl Lane, Hope, LL12</t>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>LL12</t>
-        </is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>657</v>
       </c>
       <c r="N169" t="n">
-        <v>244</v>
+        <v>876</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Belvoir, Wrexham</t>
+          <t>Currans, North Wales</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr"/>
@@ -29124,17 +29184,17 @@
       <c r="V169" s="7" t="inlineStr"/>
       <c r="W169" t="inlineStr">
         <is>
-          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="18" t="n">
-        <v>595</v>
+        <v>750</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
@@ -29146,28 +29206,28 @@
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>Ryeland Street, Deeside</t>
+          <t>29 Tai Maes, Mold</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>2152</v>
+        <v>1356</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr"/>
@@ -29184,17 +29244,17 @@
       <c r="V170" s="7" t="inlineStr"/>
       <c r="W170" t="inlineStr">
         <is>
-          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7" t="n"/>
       <c r="C171" s="18" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>1</v>
@@ -29206,28 +29266,28 @@
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>High Street, Dyserth, LL18</t>
+          <t>St Marys Mews, Mold</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N171" t="n">
-        <v>232</v>
+        <v>1372</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr"/>
@@ -29244,50 +29304,50 @@
       <c r="V171" s="7" t="inlineStr"/>
       <c r="W171" t="inlineStr">
         <is>
-          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="18" t="n">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="D172" t="n">
         <v>2</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>Castle Street, Caergwrle</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>328</v>
+        <v>264</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
         </is>
       </c>
       <c r="S172" s="7" t="inlineStr"/>
@@ -29304,14 +29364,14 @@
       <c r="V172" s="7" t="inlineStr"/>
       <c r="W172" t="inlineStr">
         <is>
-          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7" t="n"/>
       <c r="C173" s="18" t="n">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="D173" t="n">
         <v>2</v>
@@ -29321,33 +29381,33 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+          <t>Fagl Lane, Hope, LL12</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>LL16</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>940</v>
+        <v>244</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Belvoir, Wrexham</t>
         </is>
       </c>
       <c r="S173" s="7" t="inlineStr"/>
@@ -29364,45 +29424,45 @@
       <c r="V173" s="7" t="inlineStr"/>
       <c r="W173" t="inlineStr">
         <is>
-          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="18" t="n">
-        <v>975</v>
+        <v>595</v>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>Derby Road, Caergwrle, Wrexham</t>
+          <t>Ryeland Street, Deeside</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>252</v>
+        <v>2152</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -29424,20 +29484,20 @@
       <c r="V174" s="7" t="inlineStr"/>
       <c r="W174" t="inlineStr">
         <is>
-          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7" t="n"/>
       <c r="C175" s="18" t="n">
-        <v>985</v>
+        <v>750</v>
       </c>
       <c r="D175" t="n">
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -29446,28 +29506,28 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Livingstone Place, St. Asaph, LL17</t>
+          <t>High Street, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr"/>
@@ -29484,12 +29544,252 @@
       <c r="V175" s="7" t="inlineStr"/>
       <c r="W175" t="inlineStr">
         <is>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="7" t="n"/>
+      <c r="C176" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>Newmarket Road, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>328</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S176" s="7" t="inlineStr"/>
+      <c r="T176" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V176" s="7" t="inlineStr"/>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="7" t="n"/>
+      <c r="C177" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>940</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S177" s="7" t="inlineStr"/>
+      <c r="T177" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V177" s="7" t="inlineStr"/>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="7" t="n"/>
+      <c r="C178" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Derby Road, Caergwrle, Wrexham</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>252</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S178" s="7" t="inlineStr"/>
+      <c r="T178" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V178" s="7" t="inlineStr"/>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>268</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S179" s="7" t="inlineStr"/>
+      <c r="T179" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V179" s="7" t="inlineStr"/>
+      <c r="W179" t="inlineStr">
+        <is>
           <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W175"/>
+  <autoFilter ref="A1:W179"/>
   <dataValidations count="1">
     <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
@@ -29670,6 +29970,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T174" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W179"/>
+  <dimension ref="A1:W181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17326,7 +17326,7 @@
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n">
-        <v>21616</v>
+        <v>21660</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>0</v>
@@ -18310,13 +18310,13 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>3200</v>
+        <v>1550</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
+          <t>Baldwin Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -18333,28 +18333,24 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I19" s="8" t="n">
-        <v>1033</v>
-      </c>
+      <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n">
-        <v>20348</v>
-      </c>
+      <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="8" t="n"/>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S19" s="9" t="inlineStr">
@@ -18375,7 +18371,7 @@
       <c r="V19" s="7" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
+          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18385,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>1550</v>
+        <v>1733</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>1</v>
@@ -18404,7 +18400,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, Somerset, BS1</t>
+          <t>Cheltenham House, Clare Street, Bristol</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -18412,7 +18408,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I20" s="8" t="n"/>
+      <c r="I20" s="8" t="n">
+        <v>455</v>
+      </c>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
@@ -18424,12 +18422,12 @@
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S20" s="9" t="inlineStr">
@@ -18450,7 +18448,7 @@
       <c r="V20" s="7" t="inlineStr"/>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
+          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
         </is>
       </c>
     </row>
@@ -18464,13 +18462,13 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1733</v>
+        <v>1850</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -18479,7 +18477,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Cheltenham House, Clare Street, Bristol</t>
+          <t>Park Row, Bristol, BS1</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -18488,7 +18486,7 @@
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>455</v>
+        <v>797</v>
       </c>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
@@ -18501,12 +18499,12 @@
       <c r="P21" s="8" t="n"/>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S21" s="9" t="inlineStr">
@@ -18527,7 +18525,7 @@
       <c r="V21" s="7" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
+          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18539,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>1850</v>
+        <v>2975</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -18556,34 +18554,36 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Park Row, Bristol, BS1</t>
+          <t>Capricorn Place, Hotwells</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>797</v>
+        <v>1615</v>
       </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
+      <c r="N22" s="8" t="n">
+        <v>15104</v>
+      </c>
       <c r="O22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S22" s="9" t="inlineStr">
@@ -18604,7 +18604,7 @@
       <c r="V22" s="7" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
+          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
         </is>
       </c>
     </row>
@@ -18618,7 +18618,7 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>2975</v>
+        <v>2000</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>2</v>
@@ -18633,23 +18633,21 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>1615</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n">
-        <v>15104</v>
+        <v>22020</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>0</v>
@@ -18657,17 +18655,17 @@
       <c r="P23" s="8" t="n"/>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S23" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -18683,7 +18681,7 @@
       <c r="V23" s="7" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -18697,13 +18695,13 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
@@ -18712,23 +18710,23 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>North Road, St. Andrews, BS6</t>
+          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I24" s="8" t="n">
-        <v>420</v>
+        <v>1033</v>
       </c>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n">
-        <v>8012</v>
+        <v>20348</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>0</v>
@@ -18736,12 +18734,12 @@
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S24" s="9" t="inlineStr">
@@ -18762,7 +18760,7 @@
       <c r="V24" s="7" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
+          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
         </is>
       </c>
     </row>
@@ -18791,21 +18789,23 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Boot Lane - Bedminster</t>
+          <t>North Road, St. Andrews, BS6</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="n"/>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>420</v>
+      </c>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n">
-        <v>15180</v>
+        <v>8012</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>0</v>
@@ -18813,12 +18813,12 @@
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S25" s="9" t="inlineStr">
@@ -18839,7 +18839,7 @@
       <c r="V25" s="7" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
+          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
         </is>
       </c>
     </row>
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>1</v>
@@ -18868,12 +18868,12 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Redfield, Bristol</t>
+          <t>Boot Lane - Bedminster</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -18882,7 +18882,7 @@
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n">
-        <v>9192</v>
+        <v>15180</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>0</v>
@@ -18895,12 +18895,12 @@
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S26" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T26" s="12" t="inlineStr">
@@ -18916,7 +18916,7 @@
       <c r="V26" s="7" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
+          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>1</v>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
+          <t>Church Road, Redfield, Bristol</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -18959,7 +18959,7 @@
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n">
-        <v>4996</v>
+        <v>9192</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>0</v>
@@ -18967,17 +18967,17 @@
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S27" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
@@ -18993,7 +18993,7 @@
       <c r="V27" s="7" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
+          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
         </is>
       </c>
     </row>
@@ -19007,7 +19007,7 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>1</v>
@@ -19022,7 +19022,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Bristol, BS5</t>
+          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -19044,12 +19044,12 @@
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S28" s="9" t="inlineStr">
@@ -19070,7 +19070,7 @@
       <c r="V28" s="7" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
+          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
         </is>
       </c>
     </row>
@@ -19099,12 +19099,12 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Manor Road, Bishopston, Bristol</t>
+          <t>Butlers Close, Bristol, BS5</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -19113,7 +19113,7 @@
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n">
-        <v>5396</v>
+        <v>4996</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>0</v>
@@ -19121,12 +19121,12 @@
       <c r="P29" s="8" t="n"/>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S29" s="9" t="inlineStr">
@@ -19147,7 +19147,7 @@
       <c r="V29" s="7" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
+          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19161,7 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>1</v>
@@ -19176,23 +19176,21 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Marlborough Street, Eastville, Bristol</t>
+          <t>Manor Road, Bishopston, Bristol</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>366</v>
-      </c>
+          <t>BS7</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n">
-        <v>7920</v>
+        <v>5396</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>0</v>
@@ -19200,17 +19198,17 @@
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S30" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T30" s="12" t="inlineStr">
@@ -19226,7 +19224,7 @@
       <c r="V30" s="7" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
+          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19238,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>1</v>
@@ -19255,7 +19253,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
+          <t>Marlborough Street, Eastville, Bristol</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -19263,13 +19261,15 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I31" s="8" t="n"/>
+      <c r="I31" s="8" t="n">
+        <v>366</v>
+      </c>
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n">
-        <v>7804</v>
+        <v>7920</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>0</v>
@@ -19282,12 +19282,12 @@
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Northwood, Bristol</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S31" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
@@ -19303,7 +19303,7 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
+          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
         </is>
       </c>
     </row>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
+          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -19346,7 +19346,7 @@
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n">
-        <v>8640</v>
+        <v>7804</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>0</v>
@@ -19354,17 +19354,17 @@
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Northwood, Bristol</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T32" s="12" t="inlineStr">
@@ -19380,7 +19380,7 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
+          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
         </is>
       </c>
     </row>
@@ -19394,7 +19394,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>1100</v>
+        <v>975</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>1</v>
@@ -19409,12 +19409,12 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Ravenswood Road, Bristol, BS6</t>
+          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -19423,7 +19423,7 @@
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n">
-        <v>16556</v>
+        <v>8640</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>0</v>
@@ -19431,17 +19431,17 @@
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S33" s="9" t="inlineStr">
         <is>
-          <t>bills included</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
@@ -19457,13 +19457,13 @@
       <c r="V33" s="7" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
+          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>1</v>
@@ -19486,12 +19486,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Ravenswood Road, Bristol, BS6</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -19500,7 +19500,7 @@
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n">
-        <v>19980</v>
+        <v>16556</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>0</v>
@@ -19508,15 +19508,19 @@
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
-        </is>
-      </c>
-      <c r="S34" s="9" t="inlineStr"/>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>bills included</t>
+        </is>
+      </c>
       <c r="T34" s="12" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -19530,7 +19534,7 @@
       <c r="V34" s="7" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
         </is>
       </c>
     </row>
@@ -19559,12 +19563,12 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -19573,7 +19577,7 @@
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n">
-        <v>19576</v>
+        <v>19980</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>0</v>
@@ -19581,12 +19585,12 @@
       <c r="P35" s="8" t="n"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S35" s="9" t="inlineStr"/>
@@ -19603,7 +19607,7 @@
       <c r="V35" s="7" t="inlineStr"/>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -19617,7 +19621,7 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>1</v>
@@ -19632,12 +19636,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -19646,7 +19650,7 @@
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n">
-        <v>15212</v>
+        <v>19576</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>0</v>
@@ -19654,12 +19658,12 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S36" s="9" t="inlineStr"/>
@@ -19676,7 +19680,7 @@
       <c r="V36" s="7" t="inlineStr"/>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
+          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
         </is>
       </c>
     </row>
@@ -19690,7 +19694,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1640</v>
+        <v>1150</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>1</v>
@@ -19705,23 +19709,21 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>484</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="n"/>
       <c r="J37" s="8" t="n"/>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n">
-        <v>21504</v>
+        <v>15212</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>0</v>
@@ -19729,12 +19731,12 @@
       <c r="P37" s="8" t="n"/>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S37" s="9" t="inlineStr"/>
@@ -19751,7 +19753,7 @@
       <c r="V37" s="7" t="inlineStr"/>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
+          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
         </is>
       </c>
     </row>
@@ -19765,7 +19767,7 @@
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>1</v>
@@ -19780,12 +19782,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf</t>
+          <t>Knowle Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -19794,7 +19796,7 @@
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n">
-        <v>16708</v>
+        <v>6852</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>0</v>
@@ -19807,7 +19809,7 @@
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S38" s="9" t="inlineStr"/>
@@ -19824,7 +19826,7 @@
       <c r="V38" s="7" t="inlineStr"/>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
+          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
         </is>
       </c>
     </row>
@@ -19838,7 +19840,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1200</v>
+        <v>1640</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>1</v>
@@ -19853,7 +19855,7 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Buchanans Wharf North, Ferry Street, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -19862,14 +19864,14 @@
         </is>
       </c>
       <c r="I39" s="8" t="n">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n">
-        <v>20896</v>
+        <v>21504</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>0</v>
@@ -19877,12 +19879,12 @@
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S39" s="9" t="inlineStr"/>
@@ -19899,7 +19901,7 @@
       <c r="V39" s="7" t="inlineStr"/>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
+          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19918,7 @@
         <v>1600</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>1</v>
@@ -19928,12 +19930,12 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Hope Quay, Wapping Wharf</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -19942,7 +19944,7 @@
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n">
-        <v>19576</v>
+        <v>16708</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>0</v>
@@ -19950,12 +19952,12 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S40" s="9" t="inlineStr"/>
@@ -19972,7 +19974,7 @@
       <c r="V40" s="7" t="inlineStr"/>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
+          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19988,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>1</v>
@@ -20001,21 +20003,23 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court - City Centre</t>
+          <t>Buchanans Wharf North, Ferry Street, BS1</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>431</v>
+      </c>
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n">
-        <v>21616</v>
+        <v>20896</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>0</v>
@@ -20023,12 +20027,12 @@
       <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S41" s="9" t="inlineStr"/>
@@ -20045,7 +20049,7 @@
       <c r="V41" s="7" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
+          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20063,7 @@
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>2</v>
@@ -20074,12 +20078,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -20088,7 +20092,7 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n">
-        <v>21984</v>
+        <v>19576</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>0</v>
@@ -20096,12 +20100,12 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S42" s="9" t="inlineStr"/>
@@ -20118,7 +20122,7 @@
       <c r="V42" s="7" t="inlineStr"/>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
+          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
         </is>
       </c>
     </row>
@@ -20132,13 +20136,13 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>2300</v>
+        <v>1300</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
@@ -20147,7 +20151,7 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Hamilton Court - City Centre</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -20161,7 +20165,7 @@
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n">
-        <v>21984</v>
+        <v>21616</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>0</v>
@@ -20169,12 +20173,12 @@
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S43" s="9" t="inlineStr"/>
@@ -20191,7 +20195,7 @@
       <c r="V43" s="7" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
+          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
         </is>
       </c>
     </row>
@@ -20205,13 +20209,13 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
@@ -20220,7 +20224,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -20264,7 +20268,7 @@
       <c r="V44" s="7" t="inlineStr"/>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
+          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
         </is>
       </c>
     </row>
@@ -20278,13 +20282,13 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>2095</v>
+        <v>2300</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
@@ -20293,7 +20297,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -20337,7 +20341,7 @@
       <c r="V45" s="7" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
+          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
         </is>
       </c>
     </row>
@@ -20351,13 +20355,13 @@
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
@@ -20366,12 +20370,12 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -20380,7 +20384,7 @@
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n">
-        <v>20908</v>
+        <v>21984</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>0</v>
@@ -20388,12 +20392,12 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S46" s="9" t="inlineStr"/>
@@ -20410,7 +20414,7 @@
       <c r="V46" s="7" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
         </is>
       </c>
     </row>
@@ -20424,7 +20428,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>1500</v>
+        <v>2095</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>2</v>
@@ -20439,7 +20443,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -20453,7 +20457,7 @@
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n">
-        <v>21600</v>
+        <v>21984</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>0</v>
@@ -20461,12 +20465,12 @@
       <c r="P47" s="8" t="n"/>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S47" s="9" t="inlineStr"/>
@@ -20483,7 +20487,7 @@
       <c r="V47" s="7" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
         </is>
       </c>
     </row>
@@ -20497,7 +20501,7 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>1</v>
@@ -20512,12 +20516,12 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter - City Centre</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -20526,7 +20530,7 @@
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n">
-        <v>21812</v>
+        <v>20908</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>0</v>
@@ -20534,12 +20538,12 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S48" s="9" t="inlineStr"/>
@@ -20556,7 +20560,7 @@
       <c r="V48" s="7" t="inlineStr"/>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20574,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>2</v>
@@ -20585,7 +20589,7 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Waterloo Road, Midland Mews, BS2</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -20593,15 +20597,13 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I49" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n"/>
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n">
-        <v>20856</v>
+        <v>21600</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>0</v>
@@ -20609,12 +20611,12 @@
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S49" s="9" t="inlineStr"/>
@@ -20631,7 +20633,7 @@
       <c r="V49" s="7" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -20645,10 +20647,10 @@
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>1</v>
@@ -20660,21 +20662,23 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol</t>
+          <t>Waterloo Road, Midland Mews, BS2</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>721</v>
+      </c>
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n">
-        <v>22196</v>
+        <v>20856</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>0</v>
@@ -20682,12 +20686,12 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S50" s="9" t="inlineStr"/>
@@ -20704,7 +20708,7 @@
       <c r="V50" s="7" t="inlineStr"/>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
+          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
         </is>
       </c>
     </row>
@@ -20718,13 +20722,13 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>2150</v>
+        <v>1500</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
@@ -20733,7 +20737,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Eclipse, Bristol</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -20741,15 +20745,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I51" s="8" t="n">
-        <v>796</v>
-      </c>
+      <c r="I51" s="8" t="n"/>
       <c r="J51" s="8" t="n"/>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n">
-        <v>20820</v>
+        <v>22196</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>0</v>
@@ -20757,12 +20759,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr"/>
@@ -20779,7 +20781,7 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
+          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20795,7 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>2085</v>
+        <v>2150</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>2</v>
@@ -20808,7 +20810,7 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -20817,14 +20819,14 @@
         </is>
       </c>
       <c r="I52" s="8" t="n">
-        <v>722</v>
+        <v>796</v>
       </c>
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>0</v>
@@ -20837,7 +20839,7 @@
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr"/>
@@ -20854,7 +20856,7 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
         </is>
       </c>
     </row>
@@ -20868,13 +20870,13 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1640</v>
+        <v>2085</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
@@ -20883,7 +20885,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -20892,14 +20894,14 @@
         </is>
       </c>
       <c r="I53" s="8" t="n">
-        <v>570</v>
+        <v>722</v>
       </c>
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O53" s="8" t="n">
         <v>0</v>
@@ -20912,7 +20914,7 @@
       </c>
       <c r="R53" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S53" s="9" t="inlineStr"/>
@@ -20929,7 +20931,7 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -20943,10 +20945,10 @@
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="8" t="n">
         <v>1</v>
@@ -20958,21 +20960,23 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>570</v>
+      </c>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O54" s="8" t="n">
         <v>0</v>
@@ -20985,7 +20989,7 @@
       </c>
       <c r="R54" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S54" s="9" t="inlineStr"/>
@@ -21002,7 +21006,7 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -21016,10 +21020,10 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>1395</v>
+        <v>1500</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>1</v>
@@ -21031,12 +21035,12 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Hall Floor Flat, Queens Parade</t>
+          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -21045,7 +21049,7 @@
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n">
-        <v>18020</v>
+        <v>20856</v>
       </c>
       <c r="O55" s="8" t="n">
         <v>0</v>
@@ -21053,12 +21057,12 @@
       <c r="P55" s="8" t="n"/>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R55" s="8" t="inlineStr">
         <is>
-          <t>Flatline Letting and Property Management, Clifton</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S55" s="9" t="inlineStr"/>
@@ -21075,7 +21079,7 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
+          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
         </is>
       </c>
     </row>
@@ -21089,7 +21093,7 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>1300</v>
+        <v>1395</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>1</v>
@@ -21104,7 +21108,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Hall Floor Flat, Queens Parade</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -21112,15 +21116,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n">
-        <v>405</v>
-      </c>
+      <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n">
-        <v>20316</v>
+        <v>18020</v>
       </c>
       <c r="O56" s="8" t="n">
         <v>0</v>
@@ -21128,12 +21130,12 @@
       <c r="P56" s="8" t="n"/>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R56" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Flatline Letting and Property Management, Clifton</t>
         </is>
       </c>
       <c r="S56" s="9" t="inlineStr"/>
@@ -21150,7 +21152,7 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
         </is>
       </c>
     </row>
@@ -21164,13 +21166,13 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>2020</v>
+        <v>1300</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
@@ -21179,7 +21181,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -21188,14 +21190,14 @@
         </is>
       </c>
       <c r="I57" s="8" t="n">
-        <v>764</v>
+        <v>405</v>
       </c>
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n">
-        <v>20856</v>
+        <v>20316</v>
       </c>
       <c r="O57" s="8" t="n">
         <v>0</v>
@@ -21203,12 +21205,12 @@
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr"/>
@@ -21225,7 +21227,7 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -21239,7 +21241,7 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>2145</v>
+        <v>2020</v>
       </c>
       <c r="D58" s="8" t="n">
         <v>2</v>
@@ -21254,7 +21256,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -21263,14 +21265,14 @@
         </is>
       </c>
       <c r="I58" s="8" t="n">
-        <v>815</v>
+        <v>764</v>
       </c>
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O58" s="8" t="n">
         <v>0</v>
@@ -21283,7 +21285,7 @@
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr"/>
@@ -21300,7 +21302,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21314,13 +21316,13 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>1635</v>
+        <v>2145</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
@@ -21329,7 +21331,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -21338,7 +21340,7 @@
         </is>
       </c>
       <c r="I59" s="8" t="n">
-        <v>486</v>
+        <v>815</v>
       </c>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
@@ -21358,7 +21360,7 @@
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr"/>
@@ -21375,7 +21377,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21389,7 +21391,7 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D60" s="8" t="n">
         <v>1</v>
@@ -21404,7 +21406,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -21413,14 +21415,14 @@
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O60" s="8" t="n">
         <v>0</v>
@@ -21433,7 +21435,7 @@
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr"/>
@@ -21450,7 +21452,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -21464,13 +21466,13 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>1750</v>
+        <v>1640</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
@@ -21479,23 +21481,23 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>731</v>
+        <v>494</v>
       </c>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>4680</v>
+        <v>20820</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -21508,7 +21510,7 @@
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr"/>
@@ -21525,7 +21527,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
         </is>
       </c>
     </row>
@@ -21539,13 +21541,13 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>2100</v>
+        <v>1750</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
@@ -21554,21 +21556,23 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I62" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>731</v>
+      </c>
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>21148</v>
+        <v>4680</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -21576,12 +21580,12 @@
       <c r="P62" s="8" t="n"/>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S62" s="9" t="inlineStr"/>
@@ -21598,7 +21602,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21616,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1250</v>
+        <v>2100</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>1</v>
@@ -21627,7 +21631,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -21641,7 +21645,7 @@
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>21160</v>
+        <v>21148</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21654,7 +21658,7 @@
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21671,7 +21675,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -21685,7 +21689,7 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1640</v>
+        <v>1250</v>
       </c>
       <c r="D64" s="8" t="n">
         <v>1</v>
@@ -21700,7 +21704,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -21708,15 +21712,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I64" s="8" t="n">
-        <v>495</v>
-      </c>
+      <c r="I64" s="8" t="n"/>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>20820</v>
+        <v>21160</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21729,7 +21731,7 @@
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21746,7 +21748,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
+          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
         </is>
       </c>
     </row>
@@ -21760,13 +21762,13 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>2220</v>
+        <v>1640</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
@@ -21784,7 +21786,7 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>697</v>
+        <v>495</v>
       </c>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
@@ -21821,7 +21823,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
         </is>
       </c>
     </row>
@@ -21835,7 +21837,7 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>1890</v>
+        <v>2220</v>
       </c>
       <c r="D66" s="8" t="n">
         <v>2</v>
@@ -21850,7 +21852,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -21859,14 +21861,14 @@
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -21879,7 +21881,7 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21896,7 +21898,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -21910,13 +21912,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1300</v>
+        <v>1890</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21925,7 +21927,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -21933,13 +21935,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I67" s="8" t="n"/>
+      <c r="I67" s="8" t="n">
+        <v>702</v>
+      </c>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>21428</v>
+        <v>21680</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -21947,12 +21951,12 @@
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S67" s="9" t="inlineStr"/>
@@ -21969,7 +21973,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21987,7 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>1635</v>
+        <v>1300</v>
       </c>
       <c r="D68" s="8" t="n">
         <v>1</v>
@@ -21998,7 +22002,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -22006,15 +22010,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I68" s="8" t="n">
-        <v>517</v>
-      </c>
+      <c r="I68" s="8" t="n"/>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>20820</v>
+        <v>21428</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22022,12 +22024,12 @@
       <c r="P68" s="8" t="n"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22044,7 +22046,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>acf18902969821dd75405f7916c6929252fb214a</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -22058,13 +22060,13 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>1855</v>
+        <v>1635</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -22073,7 +22075,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22082,14 +22084,14 @@
         </is>
       </c>
       <c r="I69" s="8" t="n">
-        <v>607</v>
+        <v>517</v>
       </c>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -22102,7 +22104,7 @@
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22119,7 +22121,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
+          <t>acf18902969821dd75405f7916c6929252fb214a</t>
         </is>
       </c>
     </row>
@@ -22133,13 +22135,13 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1500</v>
+        <v>1855</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
@@ -22157,7 +22159,7 @@
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>548</v>
+        <v>607</v>
       </c>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
@@ -22194,7 +22196,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22210,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1615</v>
+        <v>1500</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>1</v>
@@ -22223,7 +22225,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22232,7 +22234,7 @@
         </is>
       </c>
       <c r="I71" s="8" t="n">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
@@ -22252,7 +22254,7 @@
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22269,7 +22271,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -22283,13 +22285,13 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>2180</v>
+        <v>1615</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
@@ -22298,7 +22300,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22307,14 +22309,14 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>767</v>
+        <v>486</v>
       </c>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O72" s="8" t="n">
         <v>0</v>
@@ -22327,7 +22329,7 @@
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22344,7 +22346,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -22358,7 +22360,7 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1750</v>
+        <v>2180</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>2</v>
@@ -22373,7 +22375,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -22381,13 +22383,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I73" s="8" t="n"/>
+      <c r="I73" s="8" t="n">
+        <v>767</v>
+      </c>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n">
-        <v>17744</v>
+        <v>20820</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0</v>
@@ -22400,7 +22404,7 @@
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
@@ -22417,7 +22421,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
         </is>
       </c>
     </row>
@@ -23234,7 +23238,7 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1375</v>
+        <v>1615</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>1</v>
@@ -23249,7 +23253,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -23257,7 +23261,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I85" s="8" t="n"/>
+      <c r="I85" s="8" t="n">
+        <v>487</v>
+      </c>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
@@ -23274,7 +23280,7 @@
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
@@ -23291,7 +23297,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -23305,13 +23311,13 @@
         </is>
       </c>
       <c r="C86" s="17" t="n">
-        <v>1615</v>
+        <v>2065</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
@@ -23320,7 +23326,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -23329,7 +23335,7 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>487</v>
+        <v>641</v>
       </c>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
@@ -23342,12 +23348,12 @@
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
@@ -23364,7 +23370,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -23378,13 +23384,13 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>2065</v>
+        <v>1545</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
@@ -23402,7 +23408,7 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>641</v>
+        <v>484</v>
       </c>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
@@ -23437,7 +23443,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
         </is>
       </c>
     </row>
@@ -23451,13 +23457,13 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>1545</v>
+        <v>2185</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
@@ -23466,7 +23472,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -23475,7 +23481,7 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>484</v>
+        <v>721</v>
       </c>
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
@@ -23493,7 +23499,7 @@
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
@@ -23510,7 +23516,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -23524,13 +23530,13 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>2185</v>
+        <v>1565</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
@@ -23548,7 +23554,7 @@
         </is>
       </c>
       <c r="I89" s="8" t="n">
-        <v>721</v>
+        <v>484</v>
       </c>
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
@@ -23583,7 +23589,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -23597,13 +23603,13 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>1565</v>
+        <v>2280</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
@@ -23612,7 +23618,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -23621,7 +23627,7 @@
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>484</v>
+        <v>885</v>
       </c>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
@@ -23639,7 +23645,7 @@
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23656,7 +23662,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
         </is>
       </c>
     </row>
@@ -23670,13 +23676,13 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>2280</v>
+        <v>1630</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
@@ -23694,7 +23700,7 @@
         </is>
       </c>
       <c r="I91" s="8" t="n">
-        <v>885</v>
+        <v>546</v>
       </c>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
@@ -23729,7 +23735,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
+          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
         </is>
       </c>
     </row>
@@ -23743,7 +23749,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>1630</v>
+        <v>1650</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>1</v>
@@ -23758,7 +23764,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -23766,9 +23772,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I92" s="8" t="n">
-        <v>546</v>
-      </c>
+      <c r="I92" s="8" t="n"/>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
@@ -23780,12 +23784,12 @@
       <c r="P92" s="8" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S92" s="9" t="inlineStr"/>
@@ -23802,7 +23806,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -23816,7 +23820,7 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>1</v>
@@ -23831,7 +23835,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Broad Weir, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -23839,7 +23843,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I93" s="8" t="n"/>
+      <c r="I93" s="8" t="n">
+        <v>485</v>
+      </c>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
@@ -23856,7 +23862,7 @@
       </c>
       <c r="R93" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S93" s="9" t="inlineStr"/>
@@ -23873,7 +23879,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -23887,7 +23893,7 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>1</v>
@@ -23902,7 +23908,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -23911,7 +23917,7 @@
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
@@ -23929,7 +23935,7 @@
       </c>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S94" s="9" t="inlineStr"/>
@@ -23946,7 +23952,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
         </is>
       </c>
     </row>
@@ -23960,13 +23966,13 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>1630</v>
+        <v>2145</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
@@ -23984,7 +23990,7 @@
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>517</v>
+        <v>713</v>
       </c>
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
@@ -23997,7 +24003,7 @@
       <c r="P95" s="8" t="n"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
@@ -24019,7 +24025,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
+          <t>6e6f162488026493723e3419801548c31fd0e534</t>
         </is>
       </c>
     </row>
@@ -24033,7 +24039,7 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>2145</v>
+        <v>2175</v>
       </c>
       <c r="D96" s="8" t="n">
         <v>2</v>
@@ -24048,7 +24054,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -24057,7 +24063,7 @@
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
@@ -24075,7 +24081,7 @@
       </c>
       <c r="R96" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S96" s="9" t="inlineStr"/>
@@ -24092,7 +24098,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>6e6f162488026493723e3419801548c31fd0e534</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -24106,13 +24112,13 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>2175</v>
+        <v>1500</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
@@ -24121,7 +24127,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Baldwin Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -24130,7 +24136,7 @@
         </is>
       </c>
       <c r="I97" s="8" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
@@ -24148,7 +24154,7 @@
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24165,7 +24171,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
         </is>
       </c>
     </row>
@@ -24179,13 +24185,13 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>1500</v>
+        <v>2155</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
@@ -24194,7 +24200,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -24203,7 +24209,7 @@
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>721</v>
+        <v>697</v>
       </c>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
@@ -24216,12 +24222,12 @@
       <c r="P98" s="8" t="n"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R98" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S98" s="9" t="inlineStr"/>
@@ -24238,7 +24244,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
+          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
         </is>
       </c>
     </row>
@@ -24252,13 +24258,13 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>2155</v>
+        <v>1500</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
@@ -24267,17 +24273,15 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Kings Quarter Apts, Bristol, BS2</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="n">
-        <v>697</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
@@ -24289,12 +24293,12 @@
       <c r="P99" s="8" t="n"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24311,7 +24315,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
+          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
         </is>
       </c>
     </row>
@@ -24325,10 +24329,10 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>1</v>
@@ -24340,12 +24344,12 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter Apts, Bristol, BS2</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I100" s="8" t="n"/>
@@ -24382,7 +24386,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -24396,13 +24400,13 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="D101" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -24411,7 +24415,7 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -24431,12 +24435,12 @@
       <c r="P101" s="8" t="n"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24453,7 +24457,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -24467,13 +24471,13 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
@@ -24482,7 +24486,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24495,19 +24499,21 @@
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
-      <c r="N102" s="8" t="n"/>
+      <c r="N102" s="8" t="n">
+        <v>21096</v>
+      </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="8" t="n"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24524,7 +24530,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
         </is>
       </c>
     </row>
@@ -24538,13 +24544,13 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1700</v>
+        <v>2500</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
@@ -24553,7 +24559,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Liberty Gardens, Caledonian Road, BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24561,26 +24567,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I103" s="8" t="n"/>
+      <c r="I103" s="8" t="n">
+        <v>1238</v>
+      </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
-      <c r="N103" s="8" t="n">
-        <v>21096</v>
-      </c>
+      <c r="N103" s="8" t="n"/>
       <c r="O103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="8" t="n"/>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24597,7 +24603,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
+          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
         </is>
       </c>
     </row>
@@ -24611,13 +24617,13 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
@@ -24626,17 +24632,15 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>Liberty Gardens, Caledonian Road, BS1</t>
+          <t>St Johns Lane, Bedminster</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I104" s="8" t="n">
-        <v>1238</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="n"/>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
@@ -24648,12 +24652,12 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24670,7 +24674,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
+          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
         </is>
       </c>
     </row>
@@ -24684,13 +24688,13 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -24699,15 +24703,17 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>St Johns Lane, Bedminster</t>
+          <t>Marsh House, Marsh Street, BS1</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I105" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I105" s="8" t="n">
+        <v>624</v>
+      </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
@@ -24724,7 +24730,7 @@
       </c>
       <c r="R105" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S105" s="9" t="inlineStr"/>
@@ -24741,7 +24747,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
+          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
         </is>
       </c>
     </row>
@@ -24755,13 +24761,13 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1600</v>
+        <v>1540</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
@@ -24770,7 +24776,7 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -24779,25 +24785,27 @@
         </is>
       </c>
       <c r="I106" s="8" t="n">
-        <v>624</v>
+        <v>451</v>
       </c>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n"/>
+      <c r="N106" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24814,7 +24822,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
+          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
         </is>
       </c>
     </row>
@@ -24828,13 +24836,13 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1540</v>
+        <v>2095</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -24852,7 +24860,7 @@
         </is>
       </c>
       <c r="I107" s="8" t="n">
-        <v>451</v>
+        <v>705</v>
       </c>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
@@ -24889,7 +24897,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
+          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
         </is>
       </c>
     </row>
@@ -24903,13 +24911,13 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>2095</v>
+        <v>1660</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
@@ -24918,7 +24926,7 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
@@ -24927,14 +24935,14 @@
         </is>
       </c>
       <c r="I108" s="8" t="n">
-        <v>705</v>
+        <v>486</v>
       </c>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -24947,7 +24955,7 @@
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -24964,7 +24972,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -24978,13 +24986,13 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>1660</v>
+        <v>2175</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
@@ -24993,7 +25001,7 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
@@ -25002,7 +25010,7 @@
         </is>
       </c>
       <c r="I109" s="8" t="n">
-        <v>486</v>
+        <v>814</v>
       </c>
       <c r="J109" s="8" t="n"/>
       <c r="K109" s="8" t="n"/>
@@ -25022,7 +25030,7 @@
       </c>
       <c r="R109" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S109" s="9" t="inlineStr"/>
@@ -25039,7 +25047,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -25053,7 +25061,7 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>2175</v>
+        <v>1500</v>
       </c>
       <c r="D110" s="8" t="n">
         <v>2</v>
@@ -25068,7 +25076,7 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -25076,15 +25084,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I110" s="8" t="n">
-        <v>814</v>
-      </c>
+      <c r="I110" s="8" t="n"/>
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
       <c r="N110" s="8" t="n">
-        <v>21504</v>
+        <v>21816</v>
       </c>
       <c r="O110" s="8" t="n">
         <v>0</v>
@@ -25097,7 +25103,7 @@
       </c>
       <c r="R110" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S110" s="9" t="inlineStr"/>
@@ -25114,7 +25120,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -25128,13 +25134,13 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
@@ -25143,12 +25149,12 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>The Old Drill Hall, Bristol, BS2</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I111" s="8" t="n"/>
@@ -25156,9 +25162,7 @@
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
-      <c r="N111" s="8" t="n">
-        <v>21816</v>
-      </c>
+      <c r="N111" s="8" t="n"/>
       <c r="O111" s="8" t="n">
         <v>0</v>
       </c>
@@ -25170,7 +25174,7 @@
       </c>
       <c r="R111" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S111" s="9" t="inlineStr"/>
@@ -25187,7 +25191,7 @@
       <c r="V111" s="7" t="inlineStr"/>
       <c r="W111" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>c847859d6a4555381482a51e75495800df35917d</t>
         </is>
       </c>
     </row>
@@ -25201,7 +25205,7 @@
         </is>
       </c>
       <c r="C112" s="17" t="n">
-        <v>1450</v>
+        <v>1630</v>
       </c>
       <c r="D112" s="8" t="n">
         <v>1</v>
@@ -25216,32 +25220,36 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>The Old Drill Hall, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I112" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="n">
+        <v>560</v>
+      </c>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
-      <c r="N112" s="8" t="n"/>
+      <c r="N112" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="8" t="n"/>
       <c r="Q112" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R112" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S112" s="9" t="inlineStr"/>
@@ -25258,7 +25266,7 @@
       <c r="V112" s="7" t="inlineStr"/>
       <c r="W112" s="8" t="inlineStr">
         <is>
-          <t>c847859d6a4555381482a51e75495800df35917d</t>
+          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
         </is>
       </c>
     </row>
@@ -25272,13 +25280,13 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>1630</v>
+        <v>2115</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
@@ -25296,7 +25304,7 @@
         </is>
       </c>
       <c r="I113" s="8" t="n">
-        <v>560</v>
+        <v>823</v>
       </c>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
@@ -25333,7 +25341,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -25347,13 +25355,13 @@
         </is>
       </c>
       <c r="C114" s="17" t="n">
-        <v>2115</v>
+        <v>1660</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
@@ -25362,7 +25370,7 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
@@ -25371,14 +25379,14 @@
         </is>
       </c>
       <c r="I114" s="8" t="n">
-        <v>823</v>
+        <v>486</v>
       </c>
       <c r="J114" s="8" t="n"/>
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
       <c r="N114" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O114" s="8" t="n">
         <v>0</v>
@@ -25391,7 +25399,7 @@
       </c>
       <c r="R114" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S114" s="9" t="inlineStr"/>
@@ -25408,7 +25416,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -25422,13 +25430,13 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1660</v>
+        <v>1915</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
@@ -25437,7 +25445,7 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
@@ -25446,14 +25454,14 @@
         </is>
       </c>
       <c r="I115" s="8" t="n">
-        <v>486</v>
+        <v>746</v>
       </c>
       <c r="J115" s="8" t="n"/>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
       <c r="N115" s="8" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O115" s="8" t="n">
         <v>0</v>
@@ -25466,7 +25474,7 @@
       </c>
       <c r="R115" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S115" s="9" t="inlineStr"/>
@@ -25483,7 +25491,7 @@
       <c r="V115" s="7" t="inlineStr"/>
       <c r="W115" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -25497,13 +25505,13 @@
         </is>
       </c>
       <c r="C116" s="17" t="n">
-        <v>1915</v>
+        <v>1150</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
@@ -25512,23 +25520,21 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I116" s="8" t="n">
-        <v>746</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="n"/>
       <c r="J116" s="8" t="n"/>
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n">
-        <v>21680</v>
+        <v>6872</v>
       </c>
       <c r="O116" s="8" t="n">
         <v>0</v>
@@ -25536,12 +25542,12 @@
       <c r="P116" s="8" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R116" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S116" s="9" t="inlineStr"/>
@@ -25558,7 +25564,7 @@
       <c r="V116" s="7" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25578,7 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D117" s="8" t="n">
         <v>1</v>
@@ -25587,12 +25593,12 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
+          <t>Kings Quarter - City Centre</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I117" s="8" t="n"/>
@@ -25601,7 +25607,7 @@
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
       <c r="N117" s="8" t="n">
-        <v>8636</v>
+        <v>21812</v>
       </c>
       <c r="O117" s="8" t="n">
         <v>0</v>
@@ -25609,12 +25615,12 @@
       <c r="P117" s="8" t="n"/>
       <c r="Q117" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R117" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S117" s="9" t="inlineStr"/>
@@ -25631,7 +25637,7 @@
       <c r="V117" s="7" t="inlineStr"/>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
+          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
         </is>
       </c>
     </row>
@@ -25645,13 +25651,13 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>1100</v>
+        <v>1750</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
@@ -25660,12 +25666,12 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
+          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>BS13</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I118" s="8" t="n"/>
@@ -25674,7 +25680,7 @@
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n">
-        <v>4936</v>
+        <v>17744</v>
       </c>
       <c r="O118" s="8" t="n">
         <v>0</v>
@@ -25682,12 +25688,12 @@
       <c r="P118" s="8" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R118" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S118" s="9" t="inlineStr"/>
@@ -25704,7 +25710,7 @@
       <c r="V118" s="7" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
+          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
         </is>
       </c>
     </row>
@@ -25718,7 +25724,7 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="D119" s="8" t="n">
         <v>1</v>
@@ -25733,12 +25739,12 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>Flat B, City Road, Bristol</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I119" s="8" t="n"/>
@@ -25746,21 +25752,19 @@
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
-      <c r="N119" s="8" t="n">
-        <v>20108</v>
-      </c>
+      <c r="N119" s="8" t="n"/>
       <c r="O119" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="8" t="n"/>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R119" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S119" s="9" t="inlineStr"/>
@@ -25777,7 +25781,7 @@
       <c r="V119" s="7" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
+          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
         </is>
       </c>
     </row>
@@ -25806,23 +25810,21 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Unity Street, BS1 5HH</t>
+          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I120" s="8" t="n">
-        <v>452</v>
-      </c>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="n"/>
       <c r="J120" s="8" t="n"/>
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n">
-        <v>20772</v>
+        <v>8636</v>
       </c>
       <c r="O120" s="8" t="n">
         <v>0</v>
@@ -25830,12 +25832,12 @@
       <c r="P120" s="8" t="n"/>
       <c r="Q120" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R120" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S120" s="9" t="inlineStr"/>
@@ -25852,7 +25854,7 @@
       <c r="V120" s="7" t="inlineStr"/>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
+          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
         </is>
       </c>
     </row>
@@ -25866,10 +25868,10 @@
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="8" t="n">
         <v>1</v>
@@ -25881,12 +25883,12 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
+          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS13</t>
         </is>
       </c>
       <c r="I121" s="8" t="n"/>
@@ -25895,7 +25897,7 @@
       <c r="L121" s="8" t="n"/>
       <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n">
-        <v>4160</v>
+        <v>4936</v>
       </c>
       <c r="O121" s="8" t="n">
         <v>0</v>
@@ -25903,12 +25905,12 @@
       <c r="P121" s="8" t="n"/>
       <c r="Q121" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R121" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S121" s="9" t="inlineStr"/>
@@ -25925,7 +25927,7 @@
       <c r="V121" s="7" t="inlineStr"/>
       <c r="W121" s="8" t="inlineStr">
         <is>
-          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
+          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
         </is>
       </c>
     </row>
@@ -25939,7 +25941,7 @@
         </is>
       </c>
       <c r="C122" s="17" t="n">
-        <v>965</v>
+        <v>1100</v>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
@@ -25954,12 +25956,12 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Boulevard View, Whitchurch Lane</t>
+          <t>Flat B, City Road, Bristol</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I122" s="8" t="n"/>
@@ -25968,7 +25970,7 @@
       <c r="L122" s="8" t="n"/>
       <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n">
-        <v>5764</v>
+        <v>20108</v>
       </c>
       <c r="O122" s="8" t="n">
         <v>0</v>
@@ -25976,12 +25978,12 @@
       <c r="P122" s="8" t="n"/>
       <c r="Q122" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R122" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S122" s="9" t="inlineStr"/>
@@ -25998,7 +26000,7 @@
       <c r="V122" s="7" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr">
         <is>
-          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
+          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
         </is>
       </c>
     </row>
@@ -26027,23 +26029,23 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>Braggs Lane, Bristol</t>
+          <t>City Centre, Unity Street, BS1 5HH</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I123" s="8" t="n">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="J123" s="8" t="n"/>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n">
-        <v>20360</v>
+        <v>20772</v>
       </c>
       <c r="O123" s="8" t="n">
         <v>0</v>
@@ -26056,7 +26058,7 @@
       </c>
       <c r="R123" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S123" s="9" t="inlineStr"/>
@@ -26073,7 +26075,7 @@
       <c r="V123" s="7" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr">
         <is>
-          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
+          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
         </is>
       </c>
     </row>
@@ -26090,7 +26092,7 @@
         <v>1200</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>1</v>
@@ -26102,12 +26104,12 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>Montague Court, Bristol</t>
+          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I124" s="8" t="n"/>
@@ -26116,7 +26118,7 @@
       <c r="L124" s="8" t="n"/>
       <c r="M124" s="8" t="n"/>
       <c r="N124" s="8" t="n">
-        <v>21632</v>
+        <v>4160</v>
       </c>
       <c r="O124" s="8" t="n">
         <v>0</v>
@@ -26129,7 +26131,7 @@
       </c>
       <c r="R124" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S124" s="9" t="inlineStr"/>
@@ -26146,7 +26148,7 @@
       <c r="V124" s="7" t="inlineStr"/>
       <c r="W124" s="8" t="inlineStr">
         <is>
-          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
+          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26162,7 @@
         </is>
       </c>
       <c r="C125" s="17" t="n">
-        <v>1150</v>
+        <v>965</v>
       </c>
       <c r="D125" s="8" t="n">
         <v>1</v>
@@ -26175,23 +26177,21 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
+          <t>Boulevard View, Whitchurch Lane</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I125" s="8" t="n">
-        <v>397</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I125" s="8" t="n"/>
       <c r="J125" s="8" t="n"/>
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
       <c r="M125" s="8" t="n"/>
       <c r="N125" s="8" t="n">
-        <v>15212</v>
+        <v>5764</v>
       </c>
       <c r="O125" s="8" t="n">
         <v>0</v>
@@ -26199,12 +26199,12 @@
       <c r="P125" s="8" t="n"/>
       <c r="Q125" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R125" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S125" s="9" t="inlineStr"/>
@@ -26221,7 +26221,7 @@
       <c r="V125" s="7" t="inlineStr"/>
       <c r="W125" s="8" t="inlineStr">
         <is>
-          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
+          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
         </is>
       </c>
     </row>
@@ -26235,7 +26235,7 @@
         </is>
       </c>
       <c r="C126" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D126" s="8" t="n">
         <v>1</v>
@@ -26250,23 +26250,23 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>Barton Close, St. Annes Park, BS4</t>
+          <t>Braggs Lane, Bristol</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I126" s="8" t="n">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n">
-        <v>5212</v>
+        <v>20360</v>
       </c>
       <c r="O126" s="8" t="n">
         <v>0</v>
@@ -26274,12 +26274,12 @@
       <c r="P126" s="8" t="n"/>
       <c r="Q126" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R126" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S126" s="9" t="inlineStr"/>
@@ -26296,7 +26296,7 @@
       <c r="V126" s="7" t="inlineStr"/>
       <c r="W126" s="8" t="inlineStr">
         <is>
-          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
+          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
         </is>
       </c>
       <c r="C127" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D127" s="8" t="n">
         <v>1</v>
@@ -26325,12 +26325,12 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Montague Court, Bristol</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I127" s="8" t="n"/>
@@ -26339,7 +26339,7 @@
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n">
-        <v>7112</v>
+        <v>21632</v>
       </c>
       <c r="O127" s="8" t="n">
         <v>0</v>
@@ -26347,12 +26347,12 @@
       <c r="P127" s="8" t="n"/>
       <c r="Q127" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R127" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S127" s="9" t="inlineStr"/>
@@ -26369,7 +26369,7 @@
       <c r="V127" s="7" t="inlineStr"/>
       <c r="W127" s="8" t="inlineStr">
         <is>
-          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
+          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
         </is>
       </c>
     </row>
@@ -26383,7 +26383,7 @@
         </is>
       </c>
       <c r="C128" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D128" s="8" t="n">
         <v>1</v>
@@ -26398,23 +26398,23 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>Chapel Street, St Philips, Bristol, BS2</t>
+          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>549</v>
+        <v>397</v>
       </c>
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="n"/>
       <c r="N128" s="8" t="n">
-        <v>11732</v>
+        <v>15212</v>
       </c>
       <c r="O128" s="8" t="n">
         <v>0</v>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="R128" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S128" s="9" t="inlineStr"/>
@@ -26444,7 +26444,7 @@
       <c r="V128" s="7" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
+          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
         </is>
       </c>
     </row>
@@ -26458,7 +26458,7 @@
         </is>
       </c>
       <c r="C129" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D129" s="8" t="n">
         <v>1</v>
@@ -26473,23 +26473,23 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
+          <t>Barton Close, St. Annes Park, BS4</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I129" s="8" t="n">
-        <v>211</v>
+        <v>441</v>
       </c>
       <c r="J129" s="8" t="n"/>
       <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n">
-        <v>14596</v>
+        <v>5212</v>
       </c>
       <c r="O129" s="8" t="n">
         <v>0</v>
@@ -26497,12 +26497,12 @@
       <c r="P129" s="8" t="n"/>
       <c r="Q129" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R129" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S129" s="9" t="inlineStr"/>
@@ -26519,7 +26519,7 @@
       <c r="V129" s="7" t="inlineStr"/>
       <c r="W129" s="8" t="inlineStr">
         <is>
-          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
+          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
         </is>
       </c>
     </row>
@@ -26548,12 +26548,12 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I130" s="8" t="n"/>
@@ -26562,7 +26562,7 @@
       <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n">
-        <v>5316</v>
+        <v>7112</v>
       </c>
       <c r="O130" s="8" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       <c r="P130" s="8" t="n"/>
       <c r="Q130" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R130" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S130" s="9" t="inlineStr"/>
@@ -26592,7 +26592,7 @@
       <c r="V130" s="7" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
+          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
         </is>
       </c>
     </row>
@@ -26621,21 +26621,23 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Chapel Street, St Philips, Bristol, BS2</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I131" s="8" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I131" s="8" t="n">
+        <v>549</v>
+      </c>
       <c r="J131" s="8" t="n"/>
       <c r="K131" s="8" t="n"/>
       <c r="L131" s="8" t="n"/>
       <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n">
-        <v>7112</v>
+        <v>11732</v>
       </c>
       <c r="O131" s="8" t="n">
         <v>0</v>
@@ -26643,12 +26645,12 @@
       <c r="P131" s="8" t="n"/>
       <c r="Q131" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R131" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S131" s="9" t="inlineStr"/>
@@ -26665,7 +26667,7 @@
       <c r="V131" s="7" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr">
         <is>
-          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
+          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
         </is>
       </c>
     </row>
@@ -26694,23 +26696,23 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>Seymour Road, Bristol, BS5</t>
+          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I132" s="8" t="n">
-        <v>484</v>
+        <v>211</v>
       </c>
       <c r="J132" s="8" t="n"/>
       <c r="K132" s="8" t="n"/>
       <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n">
-        <v>17164</v>
+        <v>14596</v>
       </c>
       <c r="O132" s="8" t="n">
         <v>0</v>
@@ -26718,12 +26720,12 @@
       <c r="P132" s="8" t="n"/>
       <c r="Q132" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R132" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S132" s="9" t="inlineStr"/>
@@ -26740,7 +26742,7 @@
       <c r="V132" s="7" t="inlineStr"/>
       <c r="W132" s="8" t="inlineStr">
         <is>
-          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
+          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
         </is>
       </c>
     </row>
@@ -26754,7 +26756,7 @@
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D133" s="8" t="n">
         <v>1</v>
@@ -26769,12 +26771,12 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>Pinkhams Twist, Bristol</t>
+          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I133" s="8" t="n"/>
@@ -26783,7 +26785,7 @@
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n">
-        <v>4276</v>
+        <v>5316</v>
       </c>
       <c r="O133" s="8" t="n">
         <v>0</v>
@@ -26791,12 +26793,12 @@
       <c r="P133" s="8" t="n"/>
       <c r="Q133" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R133" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Whitchurch</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S133" s="9" t="inlineStr"/>
@@ -26813,7 +26815,7 @@
       <c r="V133" s="7" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr">
         <is>
-          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
+          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
         </is>
       </c>
     </row>
@@ -26827,7 +26829,7 @@
         </is>
       </c>
       <c r="C134" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D134" s="8" t="n">
         <v>1</v>
@@ -26837,17 +26839,17 @@
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>Alexandra Park, Redland, Bristol, BS6</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I134" s="8" t="n"/>
@@ -26856,7 +26858,7 @@
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n">
-        <v>12812</v>
+        <v>7112</v>
       </c>
       <c r="O134" s="8" t="n">
         <v>0</v>
@@ -26864,12 +26866,12 @@
       <c r="P134" s="8" t="n"/>
       <c r="Q134" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R134" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S134" s="9" t="inlineStr"/>
@@ -26886,7 +26888,7 @@
       <c r="V134" s="7" t="inlineStr"/>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
+          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
         </is>
       </c>
     </row>
@@ -26900,7 +26902,7 @@
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>1</v>
@@ -26915,21 +26917,23 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
+          <t>Seymour Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I135" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J135" s="8" t="n"/>
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n">
-        <v>18020</v>
+        <v>17164</v>
       </c>
       <c r="O135" s="8" t="n">
         <v>0</v>
@@ -26937,12 +26941,12 @@
       <c r="P135" s="8" t="n"/>
       <c r="Q135" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R135" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S135" s="9" t="inlineStr"/>
@@ -26959,7 +26963,7 @@
       <c r="V135" s="7" t="inlineStr"/>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
+          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26980,7 @@
         <v>1150</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>1</v>
@@ -26988,23 +26992,21 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Bristol, BS5</t>
+          <t>Pinkhams Twist, Bristol</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="n">
-        <v>3057</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="n"/>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n">
-        <v>11864</v>
+        <v>4276</v>
       </c>
       <c r="O136" s="8" t="n">
         <v>0</v>
@@ -27012,12 +27014,12 @@
       <c r="P136" s="8" t="n"/>
       <c r="Q136" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R136" s="8" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>Hunters, Whitchurch</t>
         </is>
       </c>
       <c r="S136" s="9" t="inlineStr"/>
@@ -27034,7 +27036,7 @@
       <c r="V136" s="7" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
+          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
         </is>
       </c>
     </row>
@@ -27048,7 +27050,7 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>995</v>
+        <v>1200</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>1</v>
@@ -27058,17 +27060,17 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Two Mile Hill Road, Kingswood, Bristol</t>
+          <t>Alexandra Park, Redland, Bristol, BS6</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>BS15</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I137" s="8" t="n"/>
@@ -27077,7 +27079,7 @@
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n">
-        <v>5116</v>
+        <v>12812</v>
       </c>
       <c r="O137" s="8" t="n">
         <v>0</v>
@@ -27085,12 +27087,12 @@
       <c r="P137" s="8" t="n"/>
       <c r="Q137" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R137" s="8" t="inlineStr">
         <is>
-          <t>TLS Estate Agents, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S137" s="9" t="inlineStr"/>
@@ -27107,7 +27109,7 @@
       <c r="V137" s="7" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
+          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
         </is>
       </c>
     </row>
@@ -27131,17 +27133,17 @@
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Robertson Drive, St Annes Park</t>
+          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I138" s="8" t="n"/>
@@ -27150,7 +27152,7 @@
       <c r="L138" s="8" t="n"/>
       <c r="M138" s="8" t="n"/>
       <c r="N138" s="8" t="n">
-        <v>4252</v>
+        <v>18020</v>
       </c>
       <c r="O138" s="8" t="n">
         <v>0</v>
@@ -27158,12 +27160,12 @@
       <c r="P138" s="8" t="n"/>
       <c r="Q138" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R138" s="8" t="inlineStr">
         <is>
-          <t>D W Smith &amp; Company, Hanham</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S138" s="9" t="inlineStr"/>
@@ -27180,7 +27182,7 @@
       <c r="V138" s="7" t="inlineStr"/>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
+          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
         </is>
       </c>
     </row>
@@ -27197,7 +27199,7 @@
         <v>1150</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="8" t="n">
         <v>1</v>
@@ -27209,23 +27211,23 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
+          <t>Church Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I139" s="8" t="n">
-        <v>527</v>
+        <v>3057</v>
       </c>
       <c r="J139" s="8" t="n"/>
       <c r="K139" s="8" t="n"/>
       <c r="L139" s="8" t="n"/>
       <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n">
-        <v>5548</v>
+        <v>11864</v>
       </c>
       <c r="O139" s="8" t="n">
         <v>0</v>
@@ -27233,12 +27235,12 @@
       <c r="P139" s="8" t="n"/>
       <c r="Q139" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R139" s="8" t="inlineStr">
         <is>
-          <t>Sheedy &amp; Co, Covering Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S139" s="9" t="inlineStr"/>
@@ -27255,7 +27257,7 @@
       <c r="V139" s="7" t="inlineStr"/>
       <c r="W139" s="8" t="inlineStr">
         <is>
-          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
+          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
         </is>
       </c>
     </row>
@@ -27269,7 +27271,7 @@
         </is>
       </c>
       <c r="C140" s="17" t="n">
-        <v>1195</v>
+        <v>995</v>
       </c>
       <c r="D140" s="8" t="n">
         <v>1</v>
@@ -27284,23 +27286,21 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Two Mile Hill Road, Kingswood, Bristol</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I140" s="8" t="n">
-        <v>409</v>
-      </c>
+          <t>BS15</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="n"/>
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n">
-        <v>10420</v>
+        <v>5116</v>
       </c>
       <c r="O140" s="8" t="n">
         <v>0</v>
@@ -27308,12 +27308,12 @@
       <c r="P140" s="8" t="n"/>
       <c r="Q140" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R140" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>TLS Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S140" s="9" t="inlineStr"/>
@@ -27330,7 +27330,7 @@
       <c r="V140" s="7" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
+          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D141" s="8" t="n">
         <v>1</v>
@@ -27354,12 +27354,12 @@
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol, BS4</t>
+          <t>Robertson Drive, St Annes Park</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
@@ -27373,7 +27373,7 @@
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n">
-        <v>6852</v>
+        <v>4252</v>
       </c>
       <c r="O141" s="8" t="n">
         <v>0</v>
@@ -27381,12 +27381,12 @@
       <c r="P141" s="8" t="n"/>
       <c r="Q141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R141" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>D W Smith &amp; Company, Hanham</t>
         </is>
       </c>
       <c r="S141" s="9" t="inlineStr"/>
@@ -27403,7 +27403,7 @@
       <c r="V141" s="7" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
+          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="C142" s="17" t="n">
-        <v>850</v>
+        <v>1150</v>
       </c>
       <c r="D142" s="8" t="n">
         <v>1</v>
@@ -27432,23 +27432,23 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I142" s="8" t="n">
-        <v>248</v>
+        <v>527</v>
       </c>
       <c r="J142" s="8" t="n"/>
       <c r="K142" s="8" t="n"/>
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n">
-        <v>10420</v>
+        <v>5548</v>
       </c>
       <c r="O142" s="8" t="n">
         <v>0</v>
@@ -27456,12 +27456,12 @@
       <c r="P142" s="8" t="n"/>
       <c r="Q142" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R142" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>Sheedy &amp; Co, Covering Bristol</t>
         </is>
       </c>
       <c r="S142" s="9" t="inlineStr"/>
@@ -27478,7 +27478,7 @@
       <c r="V142" s="7" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
+          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
         </is>
       </c>
     </row>
@@ -27492,13 +27492,13 @@
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1600</v>
+        <v>1195</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
@@ -27507,21 +27507,23 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Central Quay North</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I143" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="n">
+        <v>409</v>
+      </c>
       <c r="J143" s="8" t="n"/>
       <c r="K143" s="8" t="n"/>
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n">
-        <v>20792</v>
+        <v>10420</v>
       </c>
       <c r="O143" s="8" t="n">
         <v>0</v>
@@ -27529,12 +27531,12 @@
       <c r="P143" s="8" t="n"/>
       <c r="Q143" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R143" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S143" s="9" t="inlineStr"/>
@@ -27551,7 +27553,7 @@
       <c r="V143" s="7" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
-          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
         </is>
       </c>
     </row>
@@ -27565,13 +27567,13 @@
         </is>
       </c>
       <c r="C144" s="17" t="n">
-        <v>1600</v>
+        <v>850</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
@@ -27580,32 +27582,36 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I144" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="n">
+        <v>248</v>
+      </c>
       <c r="J144" s="8" t="n"/>
       <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
       <c r="M144" s="8" t="n"/>
-      <c r="N144" s="8" t="n"/>
+      <c r="N144" s="8" t="n">
+        <v>10420</v>
+      </c>
       <c r="O144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="8" t="n"/>
       <c r="Q144" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R144" s="8" t="inlineStr">
         <is>
-          <t>Stonebridge Shaw, Portishead</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S144" s="9" t="inlineStr"/>
@@ -27622,7 +27628,7 @@
       <c r="V144" s="7" t="inlineStr"/>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
         </is>
       </c>
     </row>
@@ -27636,13 +27642,13 @@
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
@@ -27651,12 +27657,12 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>St Michaels Hill Ref 708</t>
+          <t>Central Quay North</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I145" s="8" t="n"/>
@@ -27665,7 +27671,7 @@
       <c r="L145" s="8" t="n"/>
       <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n">
-        <v>19512</v>
+        <v>20792</v>
       </c>
       <c r="O145" s="8" t="n">
         <v>0</v>
@@ -27673,12 +27679,12 @@
       <c r="P145" s="8" t="n"/>
       <c r="Q145" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R145" s="8" t="inlineStr">
         <is>
-          <t>Jackson Property Management Ltd, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S145" s="9" t="inlineStr"/>
@@ -27695,7 +27701,7 @@
       <c r="V145" s="7" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
         </is>
       </c>
     </row>
@@ -27709,13 +27715,13 @@
         </is>
       </c>
       <c r="C146" s="17" t="n">
-        <v>1095</v>
+        <v>1600</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
@@ -27724,12 +27730,12 @@
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+          <t>Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I146" s="8" t="n"/>
@@ -27737,21 +27743,19 @@
       <c r="K146" s="8" t="n"/>
       <c r="L146" s="8" t="n"/>
       <c r="M146" s="8" t="n"/>
-      <c r="N146" s="8" t="n">
-        <v>2652</v>
-      </c>
+      <c r="N146" s="8" t="n"/>
       <c r="O146" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="8" t="n"/>
       <c r="Q146" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R146" s="8" t="inlineStr">
         <is>
-          <t>Millennium Lettings &amp; Management, Bristol</t>
+          <t>Stonebridge Shaw, Portishead</t>
         </is>
       </c>
       <c r="S146" s="9" t="inlineStr"/>
@@ -27768,7 +27772,7 @@
       <c r="V146" s="7" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
         </is>
       </c>
     </row>
@@ -27782,7 +27786,7 @@
         </is>
       </c>
       <c r="C147" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D147" s="8" t="n">
         <v>1</v>
@@ -27797,7 +27801,7 @@
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>Old Market, Verdigris, BS2 0AF</t>
+          <t>St Michaels Hill Ref 708</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
@@ -27805,15 +27809,13 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I147" s="8" t="n">
-        <v>388</v>
-      </c>
+      <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n">
-        <v>21220</v>
+        <v>19512</v>
       </c>
       <c r="O147" s="8" t="n">
         <v>0</v>
@@ -27821,12 +27823,12 @@
       <c r="P147" s="8" t="n"/>
       <c r="Q147" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R147" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Jackson Property Management Ltd, Bristol</t>
         </is>
       </c>
       <c r="S147" s="9" t="inlineStr"/>
@@ -27843,137 +27845,165 @@
       <c r="V147" s="7" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="n"/>
+      <c r="J148" s="8" t="n"/>
+      <c r="K148" s="8" t="n"/>
+      <c r="L148" s="8" t="n"/>
+      <c r="M148" s="8" t="n"/>
+      <c r="N148" s="8" t="n">
+        <v>2652</v>
+      </c>
+      <c r="O148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="8" t="n"/>
+      <c r="Q148" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R148" s="8" t="inlineStr">
+        <is>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
+        </is>
+      </c>
+      <c r="S148" s="9" t="inlineStr"/>
+      <c r="T148" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V148" s="7" t="inlineStr"/>
+      <c r="W148" s="8" t="inlineStr">
+        <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I149" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J149" s="8" t="n"/>
+      <c r="K149" s="8" t="n"/>
+      <c r="L149" s="8" t="n"/>
+      <c r="M149" s="8" t="n"/>
+      <c r="N149" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="8" t="n"/>
+      <c r="Q149" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R149" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S149" s="9" t="inlineStr"/>
+      <c r="T149" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V149" s="7" t="inlineStr"/>
+      <c r="W149" s="8" t="inlineStr">
+        <is>
           <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="7" t="n"/>
-      <c r="C148" s="18" t="n">
-        <v>800</v>
-      </c>
-      <c r="D148" t="n">
-        <v>2</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G148" s="7" t="inlineStr">
-        <is>
-          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>LL11</t>
-        </is>
-      </c>
-      <c r="N148" t="n">
-        <v>448</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S148" s="7" t="inlineStr"/>
-      <c r="T148" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V148" s="7" t="inlineStr"/>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="7" t="n"/>
-      <c r="C149" s="18" t="n">
-        <v>900</v>
-      </c>
-      <c r="D149" t="n">
-        <v>2</v>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>LL18</t>
-        </is>
-      </c>
-      <c r="N149" t="n">
-        <v>328</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Fifty North West, Chester</t>
-        </is>
-      </c>
-      <c r="S149" s="7" t="inlineStr"/>
-      <c r="T149" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V149" s="7" t="inlineStr"/>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="7" t="n"/>
       <c r="C150" s="18" t="n">
-        <v>625</v>
+        <v>800</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
@@ -27985,28 +28015,28 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Field View, Mancot, Deeside, CH5 2EY</t>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>824</v>
+        <v>448</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Habodel Property Services Ltd, Doncaster</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S150" s="7" t="inlineStr"/>
@@ -28023,14 +28053,14 @@
       <c r="V150" s="7" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
-          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="7" t="n"/>
       <c r="C151" s="18" t="n">
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D151" t="n">
         <v>2</v>
@@ -28040,33 +28070,33 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Cilcain, The Square, CH7</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Williams Estates, Rhuddlan</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S151" s="7" t="inlineStr"/>
@@ -28083,50 +28113,50 @@
       <c r="V151" s="7" t="inlineStr"/>
       <c r="W151" t="inlineStr">
         <is>
-          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="7" t="n"/>
       <c r="C152" s="18" t="n">
-        <v>950</v>
+        <v>625</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>56</v>
+        <v>824</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Habodel Property Services Ltd, Doncaster</t>
         </is>
       </c>
       <c r="S152" s="7" t="inlineStr"/>
@@ -28143,14 +28173,14 @@
       <c r="V152" s="7" t="inlineStr"/>
       <c r="W152" t="inlineStr">
         <is>
-          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="7" t="n"/>
       <c r="C153" s="18" t="n">
-        <v>925</v>
+        <v>795</v>
       </c>
       <c r="D153" t="n">
         <v>2</v>
@@ -28160,36 +28190,33 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Hill Top Close, Ewloe, CH5</t>
+          <t>Cilcain, The Square, CH7</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I153" t="n">
-        <v>721</v>
+          <t>CH7</t>
+        </is>
       </c>
       <c r="N153" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Reades, Hawarden Lettings</t>
+          <t>Williams Estates, Rhuddlan</t>
         </is>
       </c>
       <c r="S153" s="7" t="inlineStr"/>
@@ -28206,53 +28233,50 @@
       <c r="V153" s="7" t="inlineStr"/>
       <c r="W153" t="inlineStr">
         <is>
-          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="7" t="n"/>
       <c r="C154" s="18" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Chester Road East, Shotton, Deeside</t>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>474</v>
+          <t>CH8</t>
+        </is>
       </c>
       <c r="N154" t="n">
-        <v>2016</v>
+        <v>56</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S154" s="7" t="inlineStr"/>
@@ -28269,14 +28293,14 @@
       <c r="V154" s="7" t="inlineStr"/>
       <c r="W154" t="inlineStr">
         <is>
-          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7" t="n"/>
       <c r="C155" s="18" t="n">
-        <v>750</v>
+        <v>925</v>
       </c>
       <c r="D155" t="n">
         <v>2</v>
@@ -28291,16 +28315,19 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+          <t>Hill Top Close, Ewloe, CH5</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>LL11</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>721</v>
       </c>
       <c r="N155" t="n">
-        <v>1300</v>
+        <v>472</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -28312,7 +28339,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Reades, Hawarden Lettings</t>
         </is>
       </c>
       <c r="S155" s="7" t="inlineStr"/>
@@ -28329,38 +28356,41 @@
       <c r="V155" s="7" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
-          <t>40274ada7dfa710e5054184216178477a704016c</t>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="18" t="n">
-        <v>900</v>
+        <v>650</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+          <t>Chester Road East, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>474</v>
       </c>
       <c r="N156" t="n">
-        <v>936</v>
+        <v>2016</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -28372,7 +28402,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S156" s="7" t="inlineStr"/>
@@ -28389,14 +28419,14 @@
       <c r="V156" s="7" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
-          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7" t="n"/>
       <c r="C157" s="18" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="D157" t="n">
         <v>2</v>
@@ -28411,28 +28441,28 @@
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>9 Park Road, Ruthin</t>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>LL15</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>576</v>
+        <v>1300</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Ruthin</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S157" s="7" t="inlineStr"/>
@@ -28449,14 +28479,14 @@
       <c r="V157" s="7" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
-          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="18" t="n">
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D158" t="n">
         <v>2</v>
@@ -28466,12 +28496,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Gladstone Street, Mold</t>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -28479,23 +28509,20 @@
           <t>CH7</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>905</v>
-      </c>
       <c r="N158" t="n">
-        <v>1356</v>
+        <v>936</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S158" s="7" t="inlineStr"/>
@@ -28512,14 +28539,14 @@
       <c r="V158" s="7" t="inlineStr"/>
       <c r="W158" t="inlineStr">
         <is>
-          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7" t="n"/>
       <c r="C159" s="18" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="D159" t="n">
         <v>2</v>
@@ -28529,24 +28556,21 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Llwyn Dinas Fechan, St. Asaph</t>
+          <t>9 Park Road, Ruthin</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>LL17</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>710</v>
+          <t>LL15</t>
+        </is>
       </c>
       <c r="N159" t="n">
-        <v>248</v>
+        <v>576</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -28558,7 +28582,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
         </is>
       </c>
       <c r="S159" s="7" t="inlineStr"/>
@@ -28575,14 +28599,14 @@
       <c r="V159" s="7" t="inlineStr"/>
       <c r="W159" t="inlineStr">
         <is>
-          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="18" t="n">
-        <v>700</v>
+        <v>795</v>
       </c>
       <c r="D160" t="n">
         <v>2</v>
@@ -28592,31 +28616,31 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Central Drive, Shotton, Deeside</t>
+          <t>Gladstone Street, Mold</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>636</v>
+        <v>905</v>
       </c>
       <c r="N160" t="n">
-        <v>1924</v>
+        <v>1356</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -28638,50 +28662,53 @@
       <c r="V160" s="7" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
-          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7" t="n"/>
       <c r="C161" s="18" t="n">
-        <v>850</v>
+        <v>1200</v>
       </c>
       <c r="D161" t="n">
         <v>2</v>
       </c>
       <c r="E161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Llys Y Ddol, Mold</t>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>710</v>
       </c>
       <c r="N161" t="n">
-        <v>1368</v>
+        <v>248</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S161" s="7" t="inlineStr"/>
@@ -28698,29 +28725,29 @@
       <c r="V161" s="7" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
-          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="18" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Mill View Road, Shotton, CH5</t>
+          <t>Central Drive, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28729,22 +28756,22 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1087</v>
+        <v>636</v>
       </c>
       <c r="N162" t="n">
-        <v>2236</v>
+        <v>1924</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S162" s="7" t="inlineStr"/>
@@ -28761,53 +28788,50 @@
       <c r="V162" s="7" t="inlineStr"/>
       <c r="W162" t="inlineStr">
         <is>
-          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7" t="n"/>
       <c r="C163" s="18" t="n">
-        <v>1100</v>
+        <v>850</v>
       </c>
       <c r="D163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
         <v>2</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Chestnut Way, Penyffordd, Chester</t>
+          <t>Llys Y Ddol, Mold</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CH4</t>
-        </is>
-      </c>
-      <c r="I163" t="n">
-        <v>765</v>
+          <t>CH7</t>
+        </is>
       </c>
       <c r="N163" t="n">
-        <v>144</v>
+        <v>1368</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S163" s="7" t="inlineStr"/>
@@ -28824,14 +28848,14 @@
       <c r="V163" s="7" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
-          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="18" t="n">
-        <v>975</v>
+        <v>1000</v>
       </c>
       <c r="D164" t="n">
         <v>3</v>
@@ -28846,16 +28870,19 @@
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+          <t>Mill View Road, Shotton, CH5</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>LL18</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1087</v>
       </c>
       <c r="N164" t="n">
-        <v>32</v>
+        <v>2236</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -28867,7 +28894,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr"/>
@@ -28884,20 +28911,20 @@
       <c r="V164" s="7" t="inlineStr"/>
       <c r="W164" t="inlineStr">
         <is>
-          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="7" t="n"/>
       <c r="C165" s="18" t="n">
-        <v>875</v>
+        <v>1100</v>
       </c>
       <c r="D165" t="n">
         <v>3</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -28906,28 +28933,31 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+          <t>Chestnut Way, Penyffordd, Chester</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>765</v>
       </c>
       <c r="N165" t="n">
-        <v>540</v>
+        <v>144</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S165" s="7" t="inlineStr"/>
@@ -28944,47 +28974,50 @@
       <c r="V165" s="7" t="inlineStr"/>
       <c r="W165" t="inlineStr">
         <is>
-          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="18" t="n">
-        <v>725</v>
+        <v>975</v>
       </c>
       <c r="D166" t="n">
+        <v>3</v>
+      </c>
+      <c r="E166" t="n">
         <v>1</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>High Street, Connah's Quay, CH5</t>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1904</v>
+        <v>32</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr"/>
@@ -29001,29 +29034,29 @@
       <c r="V166" s="7" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
-          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7" t="n"/>
       <c r="C167" s="18" t="n">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Well Street, Holywell</t>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29032,19 +29065,19 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>904</v>
+        <v>540</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr"/>
@@ -29061,50 +29094,47 @@
       <c r="V167" s="7" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
-          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="18" t="n">
-        <v>900</v>
+        <v>725</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
-      </c>
-      <c r="E168" t="n">
         <v>1</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+          <t>High Street, Connah's Quay, CH5</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CH6</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>200</v>
+        <v>1904</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr"/>
@@ -29121,29 +29151,29 @@
       <c r="V168" s="7" t="inlineStr"/>
       <c r="W168" t="inlineStr">
         <is>
-          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7" t="n"/>
       <c r="C169" s="18" t="n">
-        <v>950</v>
+        <v>625</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Rue St. Gregoire, Holywell, CH8</t>
+          <t>Well Street, Holywell</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -29151,23 +29181,20 @@
           <t>CH8</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>657</v>
-      </c>
       <c r="N169" t="n">
-        <v>876</v>
+        <v>904</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Currans, North Wales</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr"/>
@@ -29184,14 +29211,14 @@
       <c r="V169" s="7" t="inlineStr"/>
       <c r="W169" t="inlineStr">
         <is>
-          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="18" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="D170" t="n">
         <v>2</v>
@@ -29201,21 +29228,21 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>29 Tai Maes, Mold</t>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH6</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>1356</v>
+        <v>200</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -29227,7 +29254,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr"/>
@@ -29244,50 +29271,53 @@
       <c r="V170" s="7" t="inlineStr"/>
       <c r="W170" t="inlineStr">
         <is>
-          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7" t="n"/>
       <c r="C171" s="18" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>St Marys Mews, Mold</t>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>657</v>
       </c>
       <c r="N171" t="n">
-        <v>1372</v>
+        <v>876</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Currans, North Wales</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr"/>
@@ -29304,50 +29334,50 @@
       <c r="V171" s="7" t="inlineStr"/>
       <c r="W171" t="inlineStr">
         <is>
-          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="18" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="D172" t="n">
         <v>2</v>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Castle Street, Caergwrle</t>
+          <t>29 Tai Maes, Mold</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>264</v>
+        <v>1356</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Town &amp; Country Estate Agents, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S172" s="7" t="inlineStr"/>
@@ -29364,17 +29394,17 @@
       <c r="V172" s="7" t="inlineStr"/>
       <c r="W172" t="inlineStr">
         <is>
-          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7" t="n"/>
       <c r="C173" s="18" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>1</v>
@@ -29386,28 +29416,28 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>Fagl Lane, Hope, LL12</t>
+          <t>St Marys Mews, Mold</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>244</v>
+        <v>1372</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Belvoir, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S173" s="7" t="inlineStr"/>
@@ -29424,50 +29454,50 @@
       <c r="V173" s="7" t="inlineStr"/>
       <c r="W173" t="inlineStr">
         <is>
-          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="18" t="n">
-        <v>595</v>
+        <v>875</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>Ryeland Street, Deeside</t>
+          <t>Castle Street, Caergwrle</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2152</v>
+        <v>264</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
         </is>
       </c>
       <c r="S174" s="7" t="inlineStr"/>
@@ -29484,14 +29514,14 @@
       <c r="V174" s="7" t="inlineStr"/>
       <c r="W174" t="inlineStr">
         <is>
-          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7" t="n"/>
       <c r="C175" s="18" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="D175" t="n">
         <v>2</v>
@@ -29506,28 +29536,28 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>High Street, Dyserth, LL18</t>
+          <t>Fagl Lane, Hope, LL12</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Belvoir, Wrexham</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr"/>
@@ -29544,17 +29574,17 @@
       <c r="V175" s="7" t="inlineStr"/>
       <c r="W175" t="inlineStr">
         <is>
-          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="18" t="n">
-        <v>900</v>
+        <v>595</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -29566,28 +29596,28 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>Ryeland Street, Deeside</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>328</v>
+        <v>2152</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S176" s="7" t="inlineStr"/>
@@ -29604,14 +29634,14 @@
       <c r="V176" s="7" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
-          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="7" t="n"/>
       <c r="C177" s="18" t="n">
-        <v>795</v>
+        <v>750</v>
       </c>
       <c r="D177" t="n">
         <v>2</v>
@@ -29621,33 +29651,33 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+          <t>High Street, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>LL16</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>940</v>
+        <v>232</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S177" s="7" t="inlineStr"/>
@@ -29664,50 +29694,50 @@
       <c r="V177" s="7" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="18" t="n">
-        <v>975</v>
+        <v>900</v>
       </c>
       <c r="D178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>Derby Road, Caergwrle, Wrexham</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S178" s="7" t="inlineStr"/>
@@ -29724,50 +29754,50 @@
       <c r="V178" s="7" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
-          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7" t="n"/>
       <c r="C179" s="18" t="n">
-        <v>985</v>
+        <v>795</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Livingstone Place, St. Asaph, LL17</t>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>LL16</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>268</v>
+        <v>940</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S179" s="7" t="inlineStr"/>
@@ -29784,12 +29814,132 @@
       <c r="V179" s="7" t="inlineStr"/>
       <c r="W179" t="inlineStr">
         <is>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="7" t="n"/>
+      <c r="C180" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>Derby Road, Caergwrle, Wrexham</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>252</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S180" s="7" t="inlineStr"/>
+      <c r="T180" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V180" s="7" t="inlineStr"/>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="7" t="n"/>
+      <c r="C181" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>268</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S181" s="7" t="inlineStr"/>
+      <c r="T181" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V181" s="7" t="inlineStr"/>
+      <c r="W181" t="inlineStr">
+        <is>
           <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W179"/>
+  <autoFilter ref="A1:W181"/>
   <dataValidations count="1">
     <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
@@ -29974,6 +30124,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T181" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W181"/>
+  <dimension ref="A1:W186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -18310,7 +18310,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1550</v>
+        <v>1495</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>1</v>
@@ -18338,7 +18338,9 @@
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
+      <c r="N19" s="8" t="n">
+        <v>20848</v>
+      </c>
       <c r="O19" s="8" t="n">
         <v>0</v>
       </c>
@@ -18695,13 +18697,13 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>3200</v>
+        <v>1400</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
@@ -18710,7 +18712,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
+          <t>The Crescent, Harbourside, Bristol</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -18718,15 +18720,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I24" s="8" t="n">
-        <v>1033</v>
-      </c>
+      <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n">
-        <v>20348</v>
+        <v>16368</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>0</v>
@@ -18734,12 +18734,12 @@
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S24" s="9" t="inlineStr">
@@ -18760,7 +18760,7 @@
       <c r="V24" s="7" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -18774,13 +18774,13 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1200</v>
+        <v>1900</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -18789,23 +18789,21 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>North Road, St. Andrews, BS6</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>420</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n">
-        <v>8012</v>
+        <v>22132</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>0</v>
@@ -18813,12 +18811,12 @@
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S25" s="9" t="inlineStr">
@@ -18839,7 +18837,7 @@
       <c r="V25" s="7" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -18853,13 +18851,13 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
@@ -18868,21 +18866,23 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Boot Lane - Bedminster</t>
+          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>1033</v>
+      </c>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n">
-        <v>15180</v>
+        <v>20348</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>0</v>
@@ -18890,12 +18890,12 @@
       <c r="P26" s="8" t="n"/>
       <c r="Q26" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S26" s="9" t="inlineStr">
@@ -18916,7 +18916,7 @@
       <c r="V26" s="7" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
+          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>1</v>
@@ -18945,21 +18945,23 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Redfield, Bristol</t>
+          <t>North Road, St. Andrews, BS6</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="n"/>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>420</v>
+      </c>
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n">
-        <v>9192</v>
+        <v>8012</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>0</v>
@@ -18967,17 +18969,17 @@
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S27" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
@@ -18993,7 +18995,7 @@
       <c r="V27" s="7" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
+          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
         </is>
       </c>
     </row>
@@ -19022,12 +19024,12 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
+          <t>Boot Lane - Bedminster</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -19036,7 +19038,7 @@
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n">
-        <v>4996</v>
+        <v>15180</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>0</v>
@@ -19044,12 +19046,12 @@
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S28" s="9" t="inlineStr">
@@ -19070,7 +19072,7 @@
       <c r="V28" s="7" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
+          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19086,7 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>1</v>
@@ -19099,7 +19101,7 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Bristol, BS5</t>
+          <t>Church Road, Redfield, Bristol</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -19113,7 +19115,7 @@
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n">
-        <v>4996</v>
+        <v>9192</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>0</v>
@@ -19121,17 +19123,17 @@
       <c r="P29" s="8" t="n"/>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S29" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
@@ -19147,7 +19149,7 @@
       <c r="V29" s="7" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
+          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19163,7 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>1</v>
@@ -19176,12 +19178,12 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Manor Road, Bishopston, Bristol</t>
+          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -19190,7 +19192,7 @@
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n">
-        <v>5396</v>
+        <v>4996</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>0</v>
@@ -19198,12 +19200,12 @@
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S30" s="9" t="inlineStr">
@@ -19224,7 +19226,7 @@
       <c r="V30" s="7" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
+          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
         </is>
       </c>
     </row>
@@ -19238,7 +19240,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>1</v>
@@ -19253,7 +19255,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Marlborough Street, Eastville, Bristol</t>
+          <t>Butlers Close, Bristol, BS5</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -19261,15 +19263,13 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>366</v>
-      </c>
+      <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n">
-        <v>7920</v>
+        <v>4996</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>0</v>
@@ -19277,17 +19277,17 @@
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S31" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
@@ -19303,7 +19303,7 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
+          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
         </is>
       </c>
     </row>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>975</v>
+        <v>1100</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>1</v>
@@ -19332,12 +19332,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
+          <t>Manor Road, Bishopston, Bristol</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -19346,7 +19346,7 @@
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n">
-        <v>7804</v>
+        <v>5396</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>0</v>
@@ -19354,12 +19354,12 @@
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Northwood, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr">
@@ -19380,7 +19380,7 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
+          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
         </is>
       </c>
     </row>
@@ -19394,7 +19394,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>1</v>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
+          <t>Marlborough Street, Eastville, Bristol</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -19417,13 +19417,15 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I33" s="8" t="n"/>
+      <c r="I33" s="8" t="n">
+        <v>366</v>
+      </c>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n">
-        <v>8640</v>
+        <v>7920</v>
       </c>
       <c r="O33" s="8" t="n">
         <v>0</v>
@@ -19431,12 +19433,12 @@
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S33" s="9" t="inlineStr">
@@ -19457,7 +19459,7 @@
       <c r="V33" s="7" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
+          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
         </is>
       </c>
     </row>
@@ -19471,7 +19473,7 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>1100</v>
+        <v>975</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>1</v>
@@ -19486,12 +19488,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Ravenswood Road, Bristol, BS6</t>
+          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -19500,7 +19502,7 @@
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n">
-        <v>16556</v>
+        <v>7804</v>
       </c>
       <c r="O34" s="8" t="n">
         <v>0</v>
@@ -19508,17 +19510,17 @@
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Northwood, Bristol</t>
         </is>
       </c>
       <c r="S34" s="9" t="inlineStr">
         <is>
-          <t>bills included</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T34" s="12" t="inlineStr">
@@ -19534,13 +19536,13 @@
       <c r="V34" s="7" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
+          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
@@ -19548,7 +19550,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>1200</v>
+        <v>975</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>1</v>
@@ -19563,12 +19565,12 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -19577,7 +19579,7 @@
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n">
-        <v>19980</v>
+        <v>8640</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>0</v>
@@ -19585,15 +19587,19 @@
       <c r="P35" s="8" t="n"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
-        </is>
-      </c>
-      <c r="S35" s="9" t="inlineStr"/>
+          <t>Nook Lettings, Bristol</t>
+        </is>
+      </c>
+      <c r="S35" s="9" t="inlineStr">
+        <is>
+          <t>garden</t>
+        </is>
+      </c>
       <c r="T35" s="12" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -19607,13 +19613,13 @@
       <c r="V35" s="7" t="inlineStr"/>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
@@ -19621,7 +19627,7 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>1</v>
@@ -19636,12 +19642,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Ravenswood Road, Bristol, BS6</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -19650,7 +19656,7 @@
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n">
-        <v>19576</v>
+        <v>16556</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>0</v>
@@ -19658,7 +19664,7 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
@@ -19666,7 +19672,11 @@
           <t>OpenRent, London</t>
         </is>
       </c>
-      <c r="S36" s="9" t="inlineStr"/>
+      <c r="S36" s="9" t="inlineStr">
+        <is>
+          <t>bills included</t>
+        </is>
+      </c>
       <c r="T36" s="12" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -19680,7 +19690,7 @@
       <c r="V36" s="7" t="inlineStr"/>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
+          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19704,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>1</v>
@@ -19709,12 +19719,12 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -19723,7 +19733,7 @@
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n">
-        <v>15212</v>
+        <v>19980</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>0</v>
@@ -19731,12 +19741,12 @@
       <c r="P37" s="8" t="n"/>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S37" s="9" t="inlineStr"/>
@@ -19753,7 +19763,7 @@
       <c r="V37" s="7" t="inlineStr"/>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -19782,12 +19792,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol, BS4</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -19796,7 +19806,7 @@
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n">
-        <v>6852</v>
+        <v>19576</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>0</v>
@@ -19804,7 +19814,7 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
@@ -19826,7 +19836,7 @@
       <c r="V38" s="7" t="inlineStr"/>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
+          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
         </is>
       </c>
     </row>
@@ -19840,7 +19850,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1640</v>
+        <v>1150</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>1</v>
@@ -19855,23 +19865,21 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>484</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="n"/>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n">
-        <v>21504</v>
+        <v>15212</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>0</v>
@@ -19879,12 +19887,12 @@
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S39" s="9" t="inlineStr"/>
@@ -19901,7 +19909,7 @@
       <c r="V39" s="7" t="inlineStr"/>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
+          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
         </is>
       </c>
     </row>
@@ -19915,7 +19923,7 @@
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>1</v>
@@ -19930,12 +19938,12 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf</t>
+          <t>Knowle Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -19944,7 +19952,7 @@
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n">
-        <v>16708</v>
+        <v>6852</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>0</v>
@@ -19957,7 +19965,7 @@
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S40" s="9" t="inlineStr"/>
@@ -19974,7 +19982,7 @@
       <c r="V40" s="7" t="inlineStr"/>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
+          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19996,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1200</v>
+        <v>1640</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>1</v>
@@ -20003,7 +20011,7 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Buchanans Wharf North, Ferry Street, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -20012,14 +20020,14 @@
         </is>
       </c>
       <c r="I41" s="8" t="n">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n">
-        <v>20896</v>
+        <v>21504</v>
       </c>
       <c r="O41" s="8" t="n">
         <v>0</v>
@@ -20027,12 +20035,12 @@
       <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S41" s="9" t="inlineStr"/>
@@ -20049,7 +20057,7 @@
       <c r="V41" s="7" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
+          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
         </is>
       </c>
     </row>
@@ -20066,7 +20074,7 @@
         <v>1600</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="8" t="n">
         <v>1</v>
@@ -20078,12 +20086,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Hope Quay, Wapping Wharf</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -20092,7 +20100,7 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n">
-        <v>19576</v>
+        <v>16708</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>0</v>
@@ -20100,12 +20108,12 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S42" s="9" t="inlineStr"/>
@@ -20122,7 +20130,7 @@
       <c r="V42" s="7" t="inlineStr"/>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
+          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20144,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>1</v>
@@ -20151,21 +20159,23 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court - City Centre</t>
+          <t>Buchanans Wharf North, Ferry Street, BS1</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>431</v>
+      </c>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n">
-        <v>21616</v>
+        <v>20896</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>0</v>
@@ -20173,12 +20183,12 @@
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S43" s="9" t="inlineStr"/>
@@ -20195,7 +20205,7 @@
       <c r="V43" s="7" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
+          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20219,7 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -20224,12 +20234,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -20238,7 +20248,7 @@
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n">
-        <v>21984</v>
+        <v>19576</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>0</v>
@@ -20246,12 +20256,12 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S44" s="9" t="inlineStr"/>
@@ -20268,7 +20278,7 @@
       <c r="V44" s="7" t="inlineStr"/>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
+          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
         </is>
       </c>
     </row>
@@ -20282,13 +20292,13 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>2300</v>
+        <v>1300</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
@@ -20297,7 +20307,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Hamilton Court - City Centre</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -20311,7 +20321,7 @@
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n">
-        <v>21984</v>
+        <v>21616</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>0</v>
@@ -20319,12 +20329,12 @@
       <c r="P45" s="8" t="n"/>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S45" s="9" t="inlineStr"/>
@@ -20341,7 +20351,7 @@
       <c r="V45" s="7" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
+          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
         </is>
       </c>
     </row>
@@ -20355,13 +20365,13 @@
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
@@ -20370,7 +20380,7 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -20414,7 +20424,7 @@
       <c r="V46" s="7" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
+          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
         </is>
       </c>
     </row>
@@ -20428,13 +20438,13 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>2095</v>
+        <v>2300</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
@@ -20443,7 +20453,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -20487,7 +20497,7 @@
       <c r="V47" s="7" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
+          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
         </is>
       </c>
     </row>
@@ -20501,13 +20511,13 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
@@ -20516,12 +20526,12 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -20530,7 +20540,7 @@
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n">
-        <v>20908</v>
+        <v>21984</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>0</v>
@@ -20538,12 +20548,12 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S48" s="9" t="inlineStr"/>
@@ -20560,7 +20570,7 @@
       <c r="V48" s="7" t="inlineStr"/>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20584,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>1500</v>
+        <v>2095</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>2</v>
@@ -20589,7 +20599,7 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -20603,7 +20613,7 @@
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n">
-        <v>21600</v>
+        <v>21984</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>0</v>
@@ -20611,12 +20621,12 @@
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S49" s="9" t="inlineStr"/>
@@ -20633,7 +20643,7 @@
       <c r="V49" s="7" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
         </is>
       </c>
     </row>
@@ -20647,10 +20657,10 @@
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>1</v>
@@ -20662,23 +20672,21 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Waterloo Road, Midland Mews, BS2</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>721</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n">
-        <v>20856</v>
+        <v>20908</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>0</v>
@@ -20686,12 +20694,12 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S50" s="9" t="inlineStr"/>
@@ -20708,7 +20716,7 @@
       <c r="V50" s="7" t="inlineStr"/>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -20725,7 +20733,7 @@
         <v>1500</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>1</v>
@@ -20737,12 +20745,12 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -20751,7 +20759,7 @@
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n">
-        <v>22196</v>
+        <v>21600</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>0</v>
@@ -20759,12 +20767,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr"/>
@@ -20781,7 +20789,7 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -20795,13 +20803,13 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>2150</v>
+        <v>1600</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
@@ -20810,23 +20818,23 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Waterloo Road, Midland Mews, BS2</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I52" s="8" t="n">
-        <v>796</v>
+        <v>721</v>
       </c>
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>0</v>
@@ -20834,12 +20842,12 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr"/>
@@ -20856,7 +20864,7 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
+          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
         </is>
       </c>
     </row>
@@ -20870,13 +20878,13 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>2085</v>
+        <v>1500</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
@@ -20885,7 +20893,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Eclipse, Bristol</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -20893,15 +20901,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I53" s="8" t="n">
-        <v>722</v>
-      </c>
+      <c r="I53" s="8" t="n"/>
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n">
-        <v>21504</v>
+        <v>22196</v>
       </c>
       <c r="O53" s="8" t="n">
         <v>0</v>
@@ -20909,12 +20915,12 @@
       <c r="P53" s="8" t="n"/>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R53" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S53" s="9" t="inlineStr"/>
@@ -20931,7 +20937,7 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
         </is>
       </c>
     </row>
@@ -20945,13 +20951,13 @@
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>1640</v>
+        <v>2150</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -20960,7 +20966,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -20969,7 +20975,7 @@
         </is>
       </c>
       <c r="I54" s="8" t="n">
-        <v>570</v>
+        <v>796</v>
       </c>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
@@ -21006,7 +21012,7 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
         </is>
       </c>
     </row>
@@ -21020,13 +21026,13 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>1500</v>
+        <v>2085</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
@@ -21035,21 +21041,23 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>722</v>
+      </c>
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O55" s="8" t="n">
         <v>0</v>
@@ -21062,7 +21070,7 @@
       </c>
       <c r="R55" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S55" s="9" t="inlineStr"/>
@@ -21079,7 +21087,7 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -21093,7 +21101,7 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>1395</v>
+        <v>1640</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>1</v>
@@ -21108,7 +21116,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Hall Floor Flat, Queens Parade</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -21116,13 +21124,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n"/>
+      <c r="I56" s="8" t="n">
+        <v>570</v>
+      </c>
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n">
-        <v>18020</v>
+        <v>20820</v>
       </c>
       <c r="O56" s="8" t="n">
         <v>0</v>
@@ -21130,12 +21140,12 @@
       <c r="P56" s="8" t="n"/>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R56" s="8" t="inlineStr">
         <is>
-          <t>Flatline Letting and Property Management, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S56" s="9" t="inlineStr"/>
@@ -21152,7 +21162,7 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -21166,10 +21176,10 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>1</v>
@@ -21181,23 +21191,21 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>405</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n">
-        <v>20316</v>
+        <v>20856</v>
       </c>
       <c r="O57" s="8" t="n">
         <v>0</v>
@@ -21210,7 +21218,7 @@
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr"/>
@@ -21227,7 +21235,7 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
         </is>
       </c>
     </row>
@@ -21241,13 +21249,13 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>2020</v>
+        <v>1395</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
@@ -21256,7 +21264,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hall Floor Flat, Queens Parade</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -21264,15 +21272,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I58" s="8" t="n">
-        <v>764</v>
-      </c>
+      <c r="I58" s="8" t="n"/>
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n">
-        <v>20856</v>
+        <v>18020</v>
       </c>
       <c r="O58" s="8" t="n">
         <v>0</v>
@@ -21280,12 +21286,12 @@
       <c r="P58" s="8" t="n"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Flatline Letting and Property Management, Clifton</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr"/>
@@ -21302,7 +21308,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
         </is>
       </c>
     </row>
@@ -21316,13 +21322,13 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>2145</v>
+        <v>1300</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
@@ -21331,7 +21337,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -21340,14 +21346,14 @@
         </is>
       </c>
       <c r="I59" s="8" t="n">
-        <v>815</v>
+        <v>405</v>
       </c>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n">
-        <v>21504</v>
+        <v>20316</v>
       </c>
       <c r="O59" s="8" t="n">
         <v>0</v>
@@ -21355,12 +21361,12 @@
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr"/>
@@ -21377,7 +21383,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -21391,13 +21397,13 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>1635</v>
+        <v>2020</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
@@ -21406,7 +21412,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -21415,14 +21421,14 @@
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>486</v>
+        <v>764</v>
       </c>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O60" s="8" t="n">
         <v>0</v>
@@ -21435,7 +21441,7 @@
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr"/>
@@ -21452,7 +21458,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21466,13 +21472,13 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>1640</v>
+        <v>2145</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
@@ -21481,7 +21487,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -21490,14 +21496,14 @@
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>494</v>
+        <v>815</v>
       </c>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -21510,7 +21516,7 @@
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr"/>
@@ -21527,7 +21533,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21541,13 +21547,13 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>1750</v>
+        <v>1635</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
@@ -21556,23 +21562,23 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I62" s="8" t="n">
-        <v>731</v>
+        <v>486</v>
       </c>
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>4680</v>
+        <v>21504</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -21585,7 +21591,7 @@
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S62" s="9" t="inlineStr"/>
@@ -21602,7 +21608,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21622,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>2100</v>
+        <v>1640</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>1</v>
@@ -21631,7 +21637,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -21639,13 +21645,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I63" s="8" t="n"/>
+      <c r="I63" s="8" t="n">
+        <v>494</v>
+      </c>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>21148</v>
+        <v>20820</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21653,12 +21661,12 @@
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21675,7 +21683,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
         </is>
       </c>
     </row>
@@ -21689,13 +21697,13 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1250</v>
+        <v>1750</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
@@ -21704,21 +21712,23 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>731</v>
+      </c>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>21160</v>
+        <v>4680</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21726,12 +21736,12 @@
       <c r="P64" s="8" t="n"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21748,7 +21758,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -21762,7 +21772,7 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>1640</v>
+        <v>2100</v>
       </c>
       <c r="D65" s="8" t="n">
         <v>1</v>
@@ -21777,7 +21787,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -21785,15 +21795,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I65" s="8" t="n">
-        <v>495</v>
-      </c>
+      <c r="I65" s="8" t="n"/>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n">
-        <v>20820</v>
+        <v>21148</v>
       </c>
       <c r="O65" s="8" t="n">
         <v>0</v>
@@ -21806,7 +21814,7 @@
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr"/>
@@ -21823,7 +21831,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -21837,13 +21845,13 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>2220</v>
+        <v>1250</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
@@ -21852,7 +21860,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -21860,15 +21868,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I66" s="8" t="n">
-        <v>697</v>
-      </c>
+      <c r="I66" s="8" t="n"/>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>20820</v>
+        <v>21160</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -21881,7 +21887,7 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21898,7 +21904,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
         </is>
       </c>
     </row>
@@ -21912,13 +21918,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1890</v>
+        <v>1640</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21927,7 +21933,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -21936,14 +21942,14 @@
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -21956,7 +21962,7 @@
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S67" s="9" t="inlineStr"/>
@@ -21973,7 +21979,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
+          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
         </is>
       </c>
     </row>
@@ -21987,13 +21993,13 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>1300</v>
+        <v>2220</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -22002,7 +22008,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -22010,13 +22016,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I68" s="8" t="n"/>
+      <c r="I68" s="8" t="n">
+        <v>697</v>
+      </c>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>21428</v>
+        <v>20820</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22024,12 +22032,12 @@
       <c r="P68" s="8" t="n"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22046,7 +22054,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -22060,13 +22068,13 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>1635</v>
+        <v>1890</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -22075,7 +22083,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22084,14 +22092,14 @@
         </is>
       </c>
       <c r="I69" s="8" t="n">
-        <v>517</v>
+        <v>702</v>
       </c>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -22099,12 +22107,12 @@
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22121,7 +22129,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>acf18902969821dd75405f7916c6929252fb214a</t>
+          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
         </is>
       </c>
     </row>
@@ -22135,13 +22143,13 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1855</v>
+        <v>1300</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
@@ -22150,7 +22158,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -22158,15 +22166,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="8" t="n">
-        <v>607</v>
-      </c>
+      <c r="I70" s="8" t="n"/>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n">
-        <v>21504</v>
+        <v>21428</v>
       </c>
       <c r="O70" s="8" t="n">
         <v>0</v>
@@ -22174,12 +22180,12 @@
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S70" s="9" t="inlineStr"/>
@@ -22196,7 +22202,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -22210,7 +22216,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1500</v>
+        <v>1635</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>1</v>
@@ -22225,7 +22231,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22234,14 +22240,14 @@
         </is>
       </c>
       <c r="I71" s="8" t="n">
-        <v>548</v>
+        <v>517</v>
       </c>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O71" s="8" t="n">
         <v>0</v>
@@ -22254,7 +22260,7 @@
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22271,7 +22277,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>acf18902969821dd75405f7916c6929252fb214a</t>
         </is>
       </c>
     </row>
@@ -22285,13 +22291,13 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1615</v>
+        <v>1855</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
@@ -22300,7 +22306,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22309,7 +22315,7 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>486</v>
+        <v>607</v>
       </c>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
@@ -22329,7 +22335,7 @@
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22346,7 +22352,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
         </is>
       </c>
     </row>
@@ -22360,13 +22366,13 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>2180</v>
+        <v>1500</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
@@ -22375,7 +22381,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -22384,14 +22390,14 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>767</v>
+        <v>548</v>
       </c>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0</v>
@@ -22404,7 +22410,7 @@
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
@@ -22421,7 +22427,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -22435,10 +22441,10 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>1965</v>
+        <v>1615</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="8" t="n">
         <v>1</v>
@@ -22450,7 +22456,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -22459,7 +22465,7 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>655</v>
+        <v>486</v>
       </c>
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
@@ -22474,12 +22480,12 @@
       <c r="P74" s="8" t="n"/>
       <c r="Q74" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
@@ -22496,7 +22502,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -22510,7 +22516,7 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>2080</v>
+        <v>2180</v>
       </c>
       <c r="D75" s="8" t="n">
         <v>2</v>
@@ -22534,7 +22540,7 @@
         </is>
       </c>
       <c r="I75" s="8" t="n">
-        <v>705</v>
+        <v>767</v>
       </c>
       <c r="J75" s="8" t="n"/>
       <c r="K75" s="8" t="n"/>
@@ -22549,7 +22555,7 @@
       <c r="P75" s="8" t="n"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R75" s="8" t="inlineStr">
@@ -22571,7 +22577,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
+          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
         </is>
       </c>
     </row>
@@ -22585,10 +22591,10 @@
         </is>
       </c>
       <c r="C76" s="17" t="n">
-        <v>1400</v>
+        <v>1965</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="8" t="n">
         <v>1</v>
@@ -22600,7 +22606,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -22608,13 +22614,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I76" s="8" t="n"/>
+      <c r="I76" s="8" t="n">
+        <v>655</v>
+      </c>
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="n"/>
       <c r="N76" s="8" t="n">
-        <v>19484</v>
+        <v>21504</v>
       </c>
       <c r="O76" s="8" t="n">
         <v>0</v>
@@ -22627,7 +22635,7 @@
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
@@ -22644,7 +22652,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
         </is>
       </c>
     </row>
@@ -22658,13 +22666,13 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2000</v>
+        <v>2080</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
@@ -22673,7 +22681,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -22682,13 +22690,15 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>908</v>
+        <v>705</v>
       </c>
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
       <c r="M77" s="8" t="n"/>
-      <c r="N77" s="8" t="n"/>
+      <c r="N77" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O77" s="8" t="n">
         <v>0</v>
       </c>
@@ -22700,7 +22710,7 @@
       </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>Hello Neighbour, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S77" s="9" t="inlineStr"/>
@@ -22717,7 +22727,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
+          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
         </is>
       </c>
     </row>
@@ -22731,13 +22741,13 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>2020</v>
+        <v>1400</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
@@ -22746,7 +22756,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -22754,26 +22764,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I78" s="8" t="n">
-        <v>705</v>
-      </c>
+      <c r="I78" s="8" t="n"/>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="n"/>
-      <c r="N78" s="8" t="n"/>
+      <c r="N78" s="8" t="n">
+        <v>19484</v>
+      </c>
       <c r="O78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
@@ -22790,7 +22800,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -22804,14 +22814,14 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>2175</v>
+        <v>2000</v>
       </c>
       <c r="D79" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E79" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
           <t>flat</t>
@@ -22819,7 +22829,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Welsh Back, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -22827,7 +22837,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I79" s="8" t="n"/>
+      <c r="I79" s="8" t="n">
+        <v>908</v>
+      </c>
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
@@ -22839,12 +22851,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Hello Neighbour, London</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
@@ -22861,7 +22873,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>6a00f91534112c4504453102597619449da3a2c1</t>
+          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
         </is>
       </c>
     </row>
@@ -22875,7 +22887,7 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>2000</v>
+        <v>2020</v>
       </c>
       <c r="D80" s="8" t="n">
         <v>2</v>
@@ -22890,7 +22902,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Eclipse - City Centre</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -22898,7 +22910,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I80" s="8" t="n"/>
+      <c r="I80" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
       <c r="L80" s="8" t="n"/>
@@ -22910,12 +22924,12 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S80" s="9" t="inlineStr"/>
@@ -22932,7 +22946,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
+          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
         </is>
       </c>
     </row>
@@ -22946,10 +22960,10 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>1595</v>
+        <v>2175</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" s="8" t="n">
         <v>1</v>
@@ -22961,7 +22975,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -22969,9 +22983,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I81" s="8" t="n">
-        <v>499</v>
-      </c>
+      <c r="I81" s="8" t="n"/>
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="8" t="n"/>
@@ -22983,12 +22995,12 @@
       <c r="P81" s="8" t="n"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
@@ -23005,7 +23017,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
+          <t>6a00f91534112c4504453102597619449da3a2c1</t>
         </is>
       </c>
     </row>
@@ -23019,7 +23031,7 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>2090</v>
+        <v>2000</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>2</v>
@@ -23034,7 +23046,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Eclipse - City Centre</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -23042,9 +23054,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I82" s="8" t="n">
-        <v>705</v>
-      </c>
+      <c r="I82" s="8" t="n"/>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
@@ -23056,12 +23066,12 @@
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S82" s="9" t="inlineStr"/>
@@ -23078,7 +23088,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>f37bb95403b6c94c61951f944bce88c63865f963</t>
+          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
         </is>
       </c>
     </row>
@@ -23092,7 +23102,7 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>1635</v>
+        <v>1595</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>1</v>
@@ -23107,7 +23117,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -23116,7 +23126,7 @@
         </is>
       </c>
       <c r="I83" s="8" t="n">
-        <v>546</v>
+        <v>499</v>
       </c>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
@@ -23134,7 +23144,7 @@
       </c>
       <c r="R83" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S83" s="9" t="inlineStr"/>
@@ -23151,7 +23161,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>36d0812581d3df99e6949e941acc69f0f62aaaf1</t>
+          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
         </is>
       </c>
     </row>
@@ -23165,7 +23175,7 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>2085</v>
+        <v>2090</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>2</v>
@@ -23202,7 +23212,7 @@
       <c r="P84" s="8" t="n"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R84" s="8" t="inlineStr">
@@ -23224,7 +23234,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
+          <t>f37bb95403b6c94c61951f944bce88c63865f963</t>
         </is>
       </c>
     </row>
@@ -23238,7 +23248,7 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1615</v>
+        <v>1635</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>1</v>
@@ -23253,7 +23263,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -23262,7 +23272,7 @@
         </is>
       </c>
       <c r="I85" s="8" t="n">
-        <v>487</v>
+        <v>546</v>
       </c>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
@@ -23275,12 +23285,12 @@
       <c r="P85" s="8" t="n"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
@@ -23297,7 +23307,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>36d0812581d3df99e6949e941acc69f0f62aaaf1</t>
         </is>
       </c>
     </row>
@@ -23311,7 +23321,7 @@
         </is>
       </c>
       <c r="C86" s="17" t="n">
-        <v>2065</v>
+        <v>2085</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>2</v>
@@ -23326,7 +23336,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -23335,7 +23345,7 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>641</v>
+        <v>705</v>
       </c>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
@@ -23348,12 +23358,12 @@
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
@@ -23370,7 +23380,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23394,7 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>1545</v>
+        <v>1615</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>1</v>
@@ -23399,7 +23409,7 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -23408,7 +23418,7 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
@@ -23421,12 +23431,12 @@
       <c r="P87" s="8" t="n"/>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S87" s="9" t="inlineStr"/>
@@ -23443,7 +23453,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23467,7 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>2185</v>
+        <v>2065</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>2</v>
@@ -23472,7 +23482,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -23481,7 +23491,7 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>721</v>
+        <v>641</v>
       </c>
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
@@ -23499,7 +23509,7 @@
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
@@ -23516,7 +23526,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -23530,7 +23540,7 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>1565</v>
+        <v>1545</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>1</v>
@@ -23545,7 +23555,7 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -23572,7 +23582,7 @@
       </c>
       <c r="R89" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S89" s="9" t="inlineStr"/>
@@ -23589,7 +23599,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23613,7 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>2280</v>
+        <v>2185</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>2</v>
@@ -23618,7 +23628,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -23627,7 +23637,7 @@
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>885</v>
+        <v>721</v>
       </c>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
@@ -23645,7 +23655,7 @@
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23662,7 +23672,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -23676,7 +23686,7 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>1630</v>
+        <v>1565</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>1</v>
@@ -23691,7 +23701,7 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -23700,7 +23710,7 @@
         </is>
       </c>
       <c r="I91" s="8" t="n">
-        <v>546</v>
+        <v>484</v>
       </c>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
@@ -23718,7 +23728,7 @@
       </c>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr"/>
@@ -23735,7 +23745,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -23749,13 +23759,13 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>1650</v>
+        <v>2280</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
@@ -23764,7 +23774,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Broad Weir, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -23772,7 +23782,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I92" s="8" t="n"/>
+      <c r="I92" s="8" t="n">
+        <v>885</v>
+      </c>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
@@ -23784,12 +23796,12 @@
       <c r="P92" s="8" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S92" s="9" t="inlineStr"/>
@@ -23806,7 +23818,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
         </is>
       </c>
     </row>
@@ -23820,7 +23832,7 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>1</v>
@@ -23835,7 +23847,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -23844,7 +23856,7 @@
         </is>
       </c>
       <c r="I93" s="8" t="n">
-        <v>485</v>
+        <v>546</v>
       </c>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
@@ -23857,12 +23869,12 @@
       <c r="P93" s="8" t="n"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S93" s="9" t="inlineStr"/>
@@ -23879,7 +23891,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
         </is>
       </c>
     </row>
@@ -23893,7 +23905,7 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1630</v>
+        <v>1650</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>1</v>
@@ -23908,7 +23920,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -23916,9 +23928,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I94" s="8" t="n">
-        <v>517</v>
-      </c>
+      <c r="I94" s="8" t="n"/>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
@@ -23935,7 +23945,7 @@
       </c>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S94" s="9" t="inlineStr"/>
@@ -23952,7 +23962,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -23966,13 +23976,13 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>2145</v>
+        <v>1625</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
@@ -23981,7 +23991,7 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -23990,7 +24000,7 @@
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>713</v>
+        <v>485</v>
       </c>
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
@@ -24003,12 +24013,12 @@
       <c r="P95" s="8" t="n"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S95" s="9" t="inlineStr"/>
@@ -24025,7 +24035,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>6e6f162488026493723e3419801548c31fd0e534</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -24039,13 +24049,13 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>2175</v>
+        <v>1630</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
@@ -24054,7 +24064,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -24063,7 +24073,7 @@
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>722</v>
+        <v>517</v>
       </c>
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
@@ -24076,12 +24086,12 @@
       <c r="P96" s="8" t="n"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S96" s="9" t="inlineStr"/>
@@ -24098,7 +24108,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
         </is>
       </c>
     </row>
@@ -24112,13 +24122,13 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>1500</v>
+        <v>2145</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
@@ -24127,7 +24137,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -24136,7 +24146,7 @@
         </is>
       </c>
       <c r="I97" s="8" t="n">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
@@ -24154,7 +24164,7 @@
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24171,7 +24181,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
+          <t>6e6f162488026493723e3419801548c31fd0e534</t>
         </is>
       </c>
     </row>
@@ -24185,7 +24195,7 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>2155</v>
+        <v>2175</v>
       </c>
       <c r="D98" s="8" t="n">
         <v>2</v>
@@ -24200,7 +24210,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -24209,7 +24219,7 @@
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>697</v>
+        <v>722</v>
       </c>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
@@ -24222,12 +24232,12 @@
       <c r="P98" s="8" t="n"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R98" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S98" s="9" t="inlineStr"/>
@@ -24244,7 +24254,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -24273,15 +24283,17 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter Apts, Bristol, BS2</t>
+          <t>Baldwin Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>721</v>
+      </c>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
@@ -24293,12 +24305,12 @@
       <c r="P99" s="8" t="n"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24315,7 +24327,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
+          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
         </is>
       </c>
     </row>
@@ -24329,13 +24341,13 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>2100</v>
+        <v>2155</v>
       </c>
       <c r="D100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
@@ -24344,7 +24356,7 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -24352,7 +24364,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I100" s="8" t="n"/>
+      <c r="I100" s="8" t="n">
+        <v>697</v>
+      </c>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
@@ -24364,12 +24378,12 @@
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24386,7 +24400,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
         </is>
       </c>
     </row>
@@ -24400,13 +24414,13 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -24415,12 +24429,12 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>Kings Quarter Apts, Bristol, BS2</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I101" s="8" t="n"/>
@@ -24435,12 +24449,12 @@
       <c r="P101" s="8" t="n"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24457,7 +24471,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
         </is>
       </c>
     </row>
@@ -24471,7 +24485,7 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>2</v>
@@ -24486,7 +24500,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24499,16 +24513,14 @@
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
-      <c r="N102" s="8" t="n">
-        <v>21096</v>
-      </c>
+      <c r="N102" s="8" t="n"/>
       <c r="O102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="8" t="n"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R102" s="8" t="inlineStr">
@@ -24530,7 +24542,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -24544,7 +24556,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>2</v>
@@ -24559,7 +24571,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Liberty Gardens, Caledonian Road, BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24567,9 +24579,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I103" s="8" t="n">
-        <v>1238</v>
-      </c>
+      <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
@@ -24586,7 +24596,7 @@
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24603,7 +24613,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -24617,10 +24627,10 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1250</v>
+        <v>1700</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
         <v>1</v>
@@ -24632,12 +24642,12 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>St Johns Lane, Bedminster</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I104" s="8" t="n"/>
@@ -24645,19 +24655,21 @@
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
-      <c r="N104" s="8" t="n"/>
+      <c r="N104" s="8" t="n">
+        <v>21096</v>
+      </c>
       <c r="O104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24674,7 +24686,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
+          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24700,7 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="D105" s="8" t="n">
         <v>2</v>
@@ -24703,7 +24715,7 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, BS1</t>
+          <t>Liberty Gardens, Caledonian Road, BS1</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
@@ -24712,7 +24724,7 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>624</v>
+        <v>1238</v>
       </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
@@ -24725,7 +24737,7 @@
       <c r="P105" s="8" t="n"/>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr">
@@ -24747,7 +24759,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
+          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24773,7 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1540</v>
+        <v>1250</v>
       </c>
       <c r="D106" s="8" t="n">
         <v>1</v>
@@ -24776,36 +24788,32 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>St Johns Lane, Bedminster</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I106" s="8" t="n">
-        <v>451</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="n"/>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N106" s="8" t="n"/>
       <c r="O106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24822,7 +24830,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
+          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
         </is>
       </c>
     </row>
@@ -24836,7 +24844,7 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>2095</v>
+        <v>1600</v>
       </c>
       <c r="D107" s="8" t="n">
         <v>2</v>
@@ -24851,7 +24859,7 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Marsh House, Marsh Street, BS1</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
@@ -24860,27 +24868,25 @@
         </is>
       </c>
       <c r="I107" s="8" t="n">
-        <v>705</v>
+        <v>624</v>
       </c>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
-      <c r="N107" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N107" s="8" t="n"/>
       <c r="O107" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S107" s="9" t="inlineStr"/>
@@ -24897,7 +24903,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
+          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
         </is>
       </c>
     </row>
@@ -24911,7 +24917,7 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>1660</v>
+        <v>1540</v>
       </c>
       <c r="D108" s="8" t="n">
         <v>1</v>
@@ -24926,7 +24932,7 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
@@ -24935,14 +24941,14 @@
         </is>
       </c>
       <c r="I108" s="8" t="n">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -24955,7 +24961,7 @@
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -24972,7 +24978,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
         </is>
       </c>
     </row>
@@ -24986,7 +24992,7 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>2175</v>
+        <v>2095</v>
       </c>
       <c r="D109" s="8" t="n">
         <v>2</v>
@@ -25001,7 +25007,7 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
@@ -25010,14 +25016,14 @@
         </is>
       </c>
       <c r="I109" s="8" t="n">
-        <v>814</v>
+        <v>705</v>
       </c>
       <c r="J109" s="8" t="n"/>
       <c r="K109" s="8" t="n"/>
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
       <c r="N109" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O109" s="8" t="n">
         <v>0</v>
@@ -25030,7 +25036,7 @@
       </c>
       <c r="R109" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S109" s="9" t="inlineStr"/>
@@ -25047,7 +25053,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
         </is>
       </c>
     </row>
@@ -25061,13 +25067,13 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>1500</v>
+        <v>1660</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
@@ -25076,7 +25082,7 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -25084,13 +25090,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I110" s="8" t="n"/>
+      <c r="I110" s="8" t="n">
+        <v>486</v>
+      </c>
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
       <c r="N110" s="8" t="n">
-        <v>21816</v>
+        <v>21504</v>
       </c>
       <c r="O110" s="8" t="n">
         <v>0</v>
@@ -25103,7 +25111,7 @@
       </c>
       <c r="R110" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S110" s="9" t="inlineStr"/>
@@ -25120,7 +25128,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -25134,13 +25142,13 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>1450</v>
+        <v>2175</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
@@ -25149,20 +25157,24 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>The Old Drill Hall, Bristol, BS2</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I111" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I111" s="8" t="n">
+        <v>814</v>
+      </c>
       <c r="J111" s="8" t="n"/>
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
-      <c r="N111" s="8" t="n"/>
+      <c r="N111" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O111" s="8" t="n">
         <v>0</v>
       </c>
@@ -25174,7 +25186,7 @@
       </c>
       <c r="R111" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S111" s="9" t="inlineStr"/>
@@ -25191,7 +25203,7 @@
       <c r="V111" s="7" t="inlineStr"/>
       <c r="W111" s="8" t="inlineStr">
         <is>
-          <t>c847859d6a4555381482a51e75495800df35917d</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -25205,13 +25217,13 @@
         </is>
       </c>
       <c r="C112" s="17" t="n">
-        <v>1630</v>
+        <v>1500</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
@@ -25220,7 +25232,7 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
@@ -25228,15 +25240,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I112" s="8" t="n">
-        <v>560</v>
-      </c>
+      <c r="I112" s="8" t="n"/>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
       <c r="N112" s="8" t="n">
-        <v>20820</v>
+        <v>21816</v>
       </c>
       <c r="O112" s="8" t="n">
         <v>0</v>
@@ -25244,12 +25254,12 @@
       <c r="P112" s="8" t="n"/>
       <c r="Q112" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R112" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S112" s="9" t="inlineStr"/>
@@ -25266,7 +25276,7 @@
       <c r="V112" s="7" t="inlineStr"/>
       <c r="W112" s="8" t="inlineStr">
         <is>
-          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -25280,13 +25290,13 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>2115</v>
+        <v>1450</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
@@ -25295,36 +25305,32 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Old Drill Hall, Bristol, BS2</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="n">
-        <v>823</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="n"/>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
-      <c r="N113" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N113" s="8" t="n"/>
       <c r="O113" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="8" t="n"/>
       <c r="Q113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R113" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S113" s="9" t="inlineStr"/>
@@ -25341,7 +25347,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>c847859d6a4555381482a51e75495800df35917d</t>
         </is>
       </c>
     </row>
@@ -25355,7 +25361,7 @@
         </is>
       </c>
       <c r="C114" s="17" t="n">
-        <v>1660</v>
+        <v>1630</v>
       </c>
       <c r="D114" s="8" t="n">
         <v>1</v>
@@ -25370,7 +25376,7 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
@@ -25379,14 +25385,14 @@
         </is>
       </c>
       <c r="I114" s="8" t="n">
-        <v>486</v>
+        <v>560</v>
       </c>
       <c r="J114" s="8" t="n"/>
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
       <c r="N114" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O114" s="8" t="n">
         <v>0</v>
@@ -25399,7 +25405,7 @@
       </c>
       <c r="R114" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S114" s="9" t="inlineStr"/>
@@ -25416,7 +25422,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
         </is>
       </c>
     </row>
@@ -25430,7 +25436,7 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1915</v>
+        <v>2115</v>
       </c>
       <c r="D115" s="8" t="n">
         <v>2</v>
@@ -25445,7 +25451,7 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
@@ -25454,14 +25460,14 @@
         </is>
       </c>
       <c r="I115" s="8" t="n">
-        <v>746</v>
+        <v>823</v>
       </c>
       <c r="J115" s="8" t="n"/>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
       <c r="N115" s="8" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O115" s="8" t="n">
         <v>0</v>
@@ -25474,7 +25480,7 @@
       </c>
       <c r="R115" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S115" s="9" t="inlineStr"/>
@@ -25491,7 +25497,7 @@
       <c r="V115" s="7" t="inlineStr"/>
       <c r="W115" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25511,7 @@
         </is>
       </c>
       <c r="C116" s="17" t="n">
-        <v>1150</v>
+        <v>1660</v>
       </c>
       <c r="D116" s="8" t="n">
         <v>1</v>
@@ -25520,21 +25526,23 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I116" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="n">
+        <v>486</v>
+      </c>
       <c r="J116" s="8" t="n"/>
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n">
-        <v>6872</v>
+        <v>21504</v>
       </c>
       <c r="O116" s="8" t="n">
         <v>0</v>
@@ -25542,12 +25550,12 @@
       <c r="P116" s="8" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R116" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S116" s="9" t="inlineStr"/>
@@ -25564,7 +25572,7 @@
       <c r="V116" s="7" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -25578,13 +25586,13 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>1250</v>
+        <v>1915</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
@@ -25593,21 +25601,23 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter - City Centre</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="n">
+        <v>746</v>
+      </c>
       <c r="J117" s="8" t="n"/>
       <c r="K117" s="8" t="n"/>
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
       <c r="N117" s="8" t="n">
-        <v>21812</v>
+        <v>21680</v>
       </c>
       <c r="O117" s="8" t="n">
         <v>0</v>
@@ -25615,12 +25625,12 @@
       <c r="P117" s="8" t="n"/>
       <c r="Q117" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R117" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S117" s="9" t="inlineStr"/>
@@ -25637,7 +25647,7 @@
       <c r="V117" s="7" t="inlineStr"/>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -25651,13 +25661,13 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>1750</v>
+        <v>1150</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
@@ -25666,12 +25676,12 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I118" s="8" t="n"/>
@@ -25680,7 +25690,7 @@
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n">
-        <v>17744</v>
+        <v>6872</v>
       </c>
       <c r="O118" s="8" t="n">
         <v>0</v>
@@ -25688,12 +25698,12 @@
       <c r="P118" s="8" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R118" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S118" s="9" t="inlineStr"/>
@@ -25710,7 +25720,7 @@
       <c r="V118" s="7" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -25724,13 +25734,13 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>1375</v>
+        <v>2450</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
@@ -25739,7 +25749,7 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -25752,19 +25762,21 @@
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
-      <c r="N119" s="8" t="n"/>
+      <c r="N119" s="8" t="n">
+        <v>21788</v>
+      </c>
       <c r="O119" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="8" t="n"/>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R119" s="8" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S119" s="9" t="inlineStr"/>
@@ -25781,7 +25793,7 @@
       <c r="V119" s="7" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -25795,13 +25807,13 @@
         </is>
       </c>
       <c r="C120" s="17" t="n">
-        <v>1200</v>
+        <v>1700</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
@@ -25810,12 +25822,12 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
+          <t>The Crescent</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I120" s="8" t="n"/>
@@ -25824,7 +25836,7 @@
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n">
-        <v>8636</v>
+        <v>16368</v>
       </c>
       <c r="O120" s="8" t="n">
         <v>0</v>
@@ -25832,12 +25844,12 @@
       <c r="P120" s="8" t="n"/>
       <c r="Q120" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R120" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S120" s="9" t="inlineStr"/>
@@ -25854,7 +25866,7 @@
       <c r="V120" s="7" t="inlineStr"/>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
+          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
         </is>
       </c>
     </row>
@@ -25868,7 +25880,7 @@
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="D121" s="8" t="n">
         <v>1</v>
@@ -25883,12 +25895,12 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>BS13</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I121" s="8" t="n"/>
@@ -25897,7 +25909,7 @@
       <c r="L121" s="8" t="n"/>
       <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n">
-        <v>4936</v>
+        <v>21160</v>
       </c>
       <c r="O121" s="8" t="n">
         <v>0</v>
@@ -25905,12 +25917,12 @@
       <c r="P121" s="8" t="n"/>
       <c r="Q121" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R121" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S121" s="9" t="inlineStr"/>
@@ -25927,7 +25939,7 @@
       <c r="V121" s="7" t="inlineStr"/>
       <c r="W121" s="8" t="inlineStr">
         <is>
-          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25953,7 @@
         </is>
       </c>
       <c r="C122" s="17" t="n">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
@@ -25956,7 +25968,7 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Flat B, City Road, Bristol</t>
+          <t>Kings Quarter - City Centre</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
@@ -25970,7 +25982,7 @@
       <c r="L122" s="8" t="n"/>
       <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n">
-        <v>20108</v>
+        <v>21812</v>
       </c>
       <c r="O122" s="8" t="n">
         <v>0</v>
@@ -25978,12 +25990,12 @@
       <c r="P122" s="8" t="n"/>
       <c r="Q122" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R122" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S122" s="9" t="inlineStr"/>
@@ -26000,7 +26012,7 @@
       <c r="V122" s="7" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr">
         <is>
-          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
+          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
         </is>
       </c>
     </row>
@@ -26014,13 +26026,13 @@
         </is>
       </c>
       <c r="C123" s="17" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
@@ -26029,7 +26041,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Unity Street, BS1 5HH</t>
+          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
@@ -26037,15 +26049,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I123" s="8" t="n">
-        <v>452</v>
-      </c>
+      <c r="I123" s="8" t="n"/>
       <c r="J123" s="8" t="n"/>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n">
-        <v>20772</v>
+        <v>17744</v>
       </c>
       <c r="O123" s="8" t="n">
         <v>0</v>
@@ -26053,12 +26063,12 @@
       <c r="P123" s="8" t="n"/>
       <c r="Q123" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R123" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S123" s="9" t="inlineStr"/>
@@ -26075,7 +26085,7 @@
       <c r="V123" s="7" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr">
         <is>
-          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
+          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
         </is>
       </c>
     </row>
@@ -26089,10 +26099,10 @@
         </is>
       </c>
       <c r="C124" s="17" t="n">
-        <v>1200</v>
+        <v>1375</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>1</v>
@@ -26104,12 +26114,12 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I124" s="8" t="n"/>
@@ -26117,21 +26127,19 @@
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
       <c r="M124" s="8" t="n"/>
-      <c r="N124" s="8" t="n">
-        <v>4160</v>
-      </c>
+      <c r="N124" s="8" t="n"/>
       <c r="O124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="8" t="n"/>
       <c r="Q124" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R124" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S124" s="9" t="inlineStr"/>
@@ -26148,7 +26156,7 @@
       <c r="V124" s="7" t="inlineStr"/>
       <c r="W124" s="8" t="inlineStr">
         <is>
-          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
+          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
         </is>
       </c>
     </row>
@@ -26162,7 +26170,7 @@
         </is>
       </c>
       <c r="C125" s="17" t="n">
-        <v>965</v>
+        <v>1200</v>
       </c>
       <c r="D125" s="8" t="n">
         <v>1</v>
@@ -26177,12 +26185,12 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>Boulevard View, Whitchurch Lane</t>
+          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I125" s="8" t="n"/>
@@ -26191,7 +26199,7 @@
       <c r="L125" s="8" t="n"/>
       <c r="M125" s="8" t="n"/>
       <c r="N125" s="8" t="n">
-        <v>5764</v>
+        <v>8636</v>
       </c>
       <c r="O125" s="8" t="n">
         <v>0</v>
@@ -26199,12 +26207,12 @@
       <c r="P125" s="8" t="n"/>
       <c r="Q125" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R125" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S125" s="9" t="inlineStr"/>
@@ -26221,7 +26229,7 @@
       <c r="V125" s="7" t="inlineStr"/>
       <c r="W125" s="8" t="inlineStr">
         <is>
-          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
+          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
         </is>
       </c>
     </row>
@@ -26235,7 +26243,7 @@
         </is>
       </c>
       <c r="C126" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D126" s="8" t="n">
         <v>1</v>
@@ -26250,23 +26258,21 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>Braggs Lane, Bristol</t>
+          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I126" s="8" t="n">
-        <v>409</v>
-      </c>
+          <t>BS13</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="n"/>
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n">
-        <v>20360</v>
+        <v>4936</v>
       </c>
       <c r="O126" s="8" t="n">
         <v>0</v>
@@ -26274,12 +26280,12 @@
       <c r="P126" s="8" t="n"/>
       <c r="Q126" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R126" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S126" s="9" t="inlineStr"/>
@@ -26296,7 +26302,7 @@
       <c r="V126" s="7" t="inlineStr"/>
       <c r="W126" s="8" t="inlineStr">
         <is>
-          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
+          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26316,7 @@
         </is>
       </c>
       <c r="C127" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D127" s="8" t="n">
         <v>1</v>
@@ -26325,7 +26331,7 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>Montague Court, Bristol</t>
+          <t>Flat B, City Road, Bristol</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
@@ -26339,7 +26345,7 @@
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n">
-        <v>21632</v>
+        <v>20108</v>
       </c>
       <c r="O127" s="8" t="n">
         <v>0</v>
@@ -26347,12 +26353,12 @@
       <c r="P127" s="8" t="n"/>
       <c r="Q127" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R127" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S127" s="9" t="inlineStr"/>
@@ -26369,7 +26375,7 @@
       <c r="V127" s="7" t="inlineStr"/>
       <c r="W127" s="8" t="inlineStr">
         <is>
-          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
+          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
         </is>
       </c>
     </row>
@@ -26383,7 +26389,7 @@
         </is>
       </c>
       <c r="C128" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D128" s="8" t="n">
         <v>1</v>
@@ -26398,23 +26404,23 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
+          <t>City Centre, Unity Street, BS1 5HH</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="n"/>
       <c r="N128" s="8" t="n">
-        <v>15212</v>
+        <v>20772</v>
       </c>
       <c r="O128" s="8" t="n">
         <v>0</v>
@@ -26422,12 +26428,12 @@
       <c r="P128" s="8" t="n"/>
       <c r="Q128" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R128" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S128" s="9" t="inlineStr"/>
@@ -26444,7 +26450,7 @@
       <c r="V128" s="7" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
+          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
         </is>
       </c>
     </row>
@@ -26458,10 +26464,10 @@
         </is>
       </c>
       <c r="C129" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="8" t="n">
         <v>1</v>
@@ -26473,23 +26479,21 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>Barton Close, St. Annes Park, BS4</t>
+          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I129" s="8" t="n">
-        <v>441</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="n"/>
       <c r="J129" s="8" t="n"/>
       <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n">
-        <v>5212</v>
+        <v>4160</v>
       </c>
       <c r="O129" s="8" t="n">
         <v>0</v>
@@ -26497,12 +26501,12 @@
       <c r="P129" s="8" t="n"/>
       <c r="Q129" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R129" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S129" s="9" t="inlineStr"/>
@@ -26519,7 +26523,7 @@
       <c r="V129" s="7" t="inlineStr"/>
       <c r="W129" s="8" t="inlineStr">
         <is>
-          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
+          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
         </is>
       </c>
     </row>
@@ -26533,7 +26537,7 @@
         </is>
       </c>
       <c r="C130" s="17" t="n">
-        <v>1100</v>
+        <v>965</v>
       </c>
       <c r="D130" s="8" t="n">
         <v>1</v>
@@ -26548,12 +26552,12 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Boulevard View, Whitchurch Lane</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS14</t>
         </is>
       </c>
       <c r="I130" s="8" t="n"/>
@@ -26562,7 +26566,7 @@
       <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n">
-        <v>7112</v>
+        <v>5764</v>
       </c>
       <c r="O130" s="8" t="n">
         <v>0</v>
@@ -26570,12 +26574,12 @@
       <c r="P130" s="8" t="n"/>
       <c r="Q130" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R130" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S130" s="9" t="inlineStr"/>
@@ -26592,7 +26596,7 @@
       <c r="V130" s="7" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
+          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
         </is>
       </c>
     </row>
@@ -26606,7 +26610,7 @@
         </is>
       </c>
       <c r="C131" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D131" s="8" t="n">
         <v>1</v>
@@ -26621,7 +26625,7 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>Chapel Street, St Philips, Bristol, BS2</t>
+          <t>Braggs Lane, Bristol</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
@@ -26630,14 +26634,14 @@
         </is>
       </c>
       <c r="I131" s="8" t="n">
-        <v>549</v>
+        <v>409</v>
       </c>
       <c r="J131" s="8" t="n"/>
       <c r="K131" s="8" t="n"/>
       <c r="L131" s="8" t="n"/>
       <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n">
-        <v>11732</v>
+        <v>20360</v>
       </c>
       <c r="O131" s="8" t="n">
         <v>0</v>
@@ -26645,12 +26649,12 @@
       <c r="P131" s="8" t="n"/>
       <c r="Q131" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R131" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S131" s="9" t="inlineStr"/>
@@ -26667,7 +26671,7 @@
       <c r="V131" s="7" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr">
         <is>
-          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
+          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26685,7 @@
         </is>
       </c>
       <c r="C132" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D132" s="8" t="n">
         <v>1</v>
@@ -26696,23 +26700,21 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
+          <t>Montague Court, Bristol</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
-        </is>
-      </c>
-      <c r="I132" s="8" t="n">
-        <v>211</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="n"/>
       <c r="J132" s="8" t="n"/>
       <c r="K132" s="8" t="n"/>
       <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n">
-        <v>14596</v>
+        <v>21632</v>
       </c>
       <c r="O132" s="8" t="n">
         <v>0</v>
@@ -26720,12 +26722,12 @@
       <c r="P132" s="8" t="n"/>
       <c r="Q132" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R132" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S132" s="9" t="inlineStr"/>
@@ -26742,7 +26744,7 @@
       <c r="V132" s="7" t="inlineStr"/>
       <c r="W132" s="8" t="inlineStr">
         <is>
-          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
+          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
         </is>
       </c>
     </row>
@@ -26756,7 +26758,7 @@
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D133" s="8" t="n">
         <v>1</v>
@@ -26771,21 +26773,23 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
+          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
-        </is>
-      </c>
-      <c r="I133" s="8" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I133" s="8" t="n">
+        <v>397</v>
+      </c>
       <c r="J133" s="8" t="n"/>
       <c r="K133" s="8" t="n"/>
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n">
-        <v>5316</v>
+        <v>15212</v>
       </c>
       <c r="O133" s="8" t="n">
         <v>0</v>
@@ -26793,12 +26797,12 @@
       <c r="P133" s="8" t="n"/>
       <c r="Q133" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R133" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S133" s="9" t="inlineStr"/>
@@ -26815,7 +26819,7 @@
       <c r="V133" s="7" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr">
         <is>
-          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
+          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
         </is>
       </c>
     </row>
@@ -26844,21 +26848,23 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Barton Close, St. Annes Park, BS4</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I134" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="n">
+        <v>441</v>
+      </c>
       <c r="J134" s="8" t="n"/>
       <c r="K134" s="8" t="n"/>
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n">
-        <v>7112</v>
+        <v>5212</v>
       </c>
       <c r="O134" s="8" t="n">
         <v>0</v>
@@ -26866,12 +26872,12 @@
       <c r="P134" s="8" t="n"/>
       <c r="Q134" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R134" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S134" s="9" t="inlineStr"/>
@@ -26888,7 +26894,7 @@
       <c r="V134" s="7" t="inlineStr"/>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
+          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
         </is>
       </c>
     </row>
@@ -26902,7 +26908,7 @@
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>1</v>
@@ -26917,7 +26923,7 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Seymour Road, Bristol, BS5</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
@@ -26925,15 +26931,13 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I135" s="8" t="n">
-        <v>484</v>
-      </c>
+      <c r="I135" s="8" t="n"/>
       <c r="J135" s="8" t="n"/>
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n">
-        <v>17164</v>
+        <v>7112</v>
       </c>
       <c r="O135" s="8" t="n">
         <v>0</v>
@@ -26941,12 +26945,12 @@
       <c r="P135" s="8" t="n"/>
       <c r="Q135" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R135" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S135" s="9" t="inlineStr"/>
@@ -26963,7 +26967,7 @@
       <c r="V135" s="7" t="inlineStr"/>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
+          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
         </is>
       </c>
     </row>
@@ -26977,7 +26981,7 @@
         </is>
       </c>
       <c r="C136" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>1</v>
@@ -26992,21 +26996,23 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Pinkhams Twist, Bristol</t>
+          <t>Chapel Street, St Philips, Bristol, BS2</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="n">
+        <v>549</v>
+      </c>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n">
-        <v>4276</v>
+        <v>11732</v>
       </c>
       <c r="O136" s="8" t="n">
         <v>0</v>
@@ -27014,12 +27020,12 @@
       <c r="P136" s="8" t="n"/>
       <c r="Q136" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R136" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Whitchurch</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S136" s="9" t="inlineStr"/>
@@ -27036,7 +27042,7 @@
       <c r="V136" s="7" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
+          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
         </is>
       </c>
     </row>
@@ -27050,7 +27056,7 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>1</v>
@@ -27060,26 +27066,28 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Alexandra Park, Redland, Bristol, BS6</t>
+          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
-        </is>
-      </c>
-      <c r="I137" s="8" t="n"/>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="n">
+        <v>211</v>
+      </c>
       <c r="J137" s="8" t="n"/>
       <c r="K137" s="8" t="n"/>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n">
-        <v>12812</v>
+        <v>14596</v>
       </c>
       <c r="O137" s="8" t="n">
         <v>0</v>
@@ -27087,12 +27095,12 @@
       <c r="P137" s="8" t="n"/>
       <c r="Q137" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R137" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S137" s="9" t="inlineStr"/>
@@ -27109,7 +27117,7 @@
       <c r="V137" s="7" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
+          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
         </is>
       </c>
     </row>
@@ -27138,12 +27146,12 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
+          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I138" s="8" t="n"/>
@@ -27152,7 +27160,7 @@
       <c r="L138" s="8" t="n"/>
       <c r="M138" s="8" t="n"/>
       <c r="N138" s="8" t="n">
-        <v>18020</v>
+        <v>5316</v>
       </c>
       <c r="O138" s="8" t="n">
         <v>0</v>
@@ -27160,12 +27168,12 @@
       <c r="P138" s="8" t="n"/>
       <c r="Q138" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R138" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S138" s="9" t="inlineStr"/>
@@ -27182,7 +27190,7 @@
       <c r="V138" s="7" t="inlineStr"/>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
+          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
         </is>
       </c>
     </row>
@@ -27196,10 +27204,10 @@
         </is>
       </c>
       <c r="C139" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
         <v>1</v>
@@ -27211,7 +27219,7 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Bristol, BS5</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
@@ -27219,15 +27227,13 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I139" s="8" t="n">
-        <v>3057</v>
-      </c>
+      <c r="I139" s="8" t="n"/>
       <c r="J139" s="8" t="n"/>
       <c r="K139" s="8" t="n"/>
       <c r="L139" s="8" t="n"/>
       <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n">
-        <v>11864</v>
+        <v>7112</v>
       </c>
       <c r="O139" s="8" t="n">
         <v>0</v>
@@ -27235,12 +27241,12 @@
       <c r="P139" s="8" t="n"/>
       <c r="Q139" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R139" s="8" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S139" s="9" t="inlineStr"/>
@@ -27257,7 +27263,7 @@
       <c r="V139" s="7" t="inlineStr"/>
       <c r="W139" s="8" t="inlineStr">
         <is>
-          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
+          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
         </is>
       </c>
     </row>
@@ -27271,7 +27277,7 @@
         </is>
       </c>
       <c r="C140" s="17" t="n">
-        <v>995</v>
+        <v>1150</v>
       </c>
       <c r="D140" s="8" t="n">
         <v>1</v>
@@ -27286,21 +27292,23 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>Two Mile Hill Road, Kingswood, Bristol</t>
+          <t>Seymour Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>BS15</t>
-        </is>
-      </c>
-      <c r="I140" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n">
-        <v>5116</v>
+        <v>17164</v>
       </c>
       <c r="O140" s="8" t="n">
         <v>0</v>
@@ -27308,12 +27316,12 @@
       <c r="P140" s="8" t="n"/>
       <c r="Q140" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R140" s="8" t="inlineStr">
         <is>
-          <t>TLS Estate Agents, Bristol</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S140" s="9" t="inlineStr"/>
@@ -27330,7 +27338,7 @@
       <c r="V140" s="7" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
+          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27352,7 @@
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D141" s="8" t="n">
         <v>1</v>
@@ -27354,17 +27362,17 @@
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>Robertson Drive, St Annes Park</t>
+          <t>Pinkhams Twist, Bristol</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS14</t>
         </is>
       </c>
       <c r="I141" s="8" t="n"/>
@@ -27373,7 +27381,7 @@
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n">
-        <v>4252</v>
+        <v>4276</v>
       </c>
       <c r="O141" s="8" t="n">
         <v>0</v>
@@ -27381,12 +27389,12 @@
       <c r="P141" s="8" t="n"/>
       <c r="Q141" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R141" s="8" t="inlineStr">
         <is>
-          <t>D W Smith &amp; Company, Hanham</t>
+          <t>Hunters, Whitchurch</t>
         </is>
       </c>
       <c r="S141" s="9" t="inlineStr"/>
@@ -27403,7 +27411,7 @@
       <c r="V141" s="7" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
+          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27425,7 @@
         </is>
       </c>
       <c r="C142" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D142" s="8" t="n">
         <v>1</v>
@@ -27427,28 +27435,26 @@
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
+          <t>Alexandra Park, Redland, Bristol, BS6</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I142" s="8" t="n">
-        <v>527</v>
-      </c>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="n"/>
       <c r="J142" s="8" t="n"/>
       <c r="K142" s="8" t="n"/>
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n">
-        <v>5548</v>
+        <v>12812</v>
       </c>
       <c r="O142" s="8" t="n">
         <v>0</v>
@@ -27456,12 +27462,12 @@
       <c r="P142" s="8" t="n"/>
       <c r="Q142" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R142" s="8" t="inlineStr">
         <is>
-          <t>Sheedy &amp; Co, Covering Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S142" s="9" t="inlineStr"/>
@@ -27478,7 +27484,7 @@
       <c r="V142" s="7" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
+          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27498,7 @@
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1195</v>
+        <v>1100</v>
       </c>
       <c r="D143" s="8" t="n">
         <v>1</v>
@@ -27507,23 +27513,21 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I143" s="8" t="n">
-        <v>409</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="n"/>
       <c r="J143" s="8" t="n"/>
       <c r="K143" s="8" t="n"/>
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n">
-        <v>10420</v>
+        <v>18020</v>
       </c>
       <c r="O143" s="8" t="n">
         <v>0</v>
@@ -27531,12 +27535,12 @@
       <c r="P143" s="8" t="n"/>
       <c r="Q143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R143" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S143" s="9" t="inlineStr"/>
@@ -27553,7 +27557,7 @@
       <c r="V143" s="7" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
-          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
+          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
         </is>
       </c>
     </row>
@@ -27567,10 +27571,10 @@
         </is>
       </c>
       <c r="C144" s="17" t="n">
-        <v>850</v>
+        <v>1150</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" s="8" t="n">
         <v>1</v>
@@ -27582,7 +27586,7 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Church Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
@@ -27591,14 +27595,14 @@
         </is>
       </c>
       <c r="I144" s="8" t="n">
-        <v>248</v>
+        <v>3057</v>
       </c>
       <c r="J144" s="8" t="n"/>
       <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
       <c r="M144" s="8" t="n"/>
       <c r="N144" s="8" t="n">
-        <v>10420</v>
+        <v>11864</v>
       </c>
       <c r="O144" s="8" t="n">
         <v>0</v>
@@ -27606,12 +27610,12 @@
       <c r="P144" s="8" t="n"/>
       <c r="Q144" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R144" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S144" s="9" t="inlineStr"/>
@@ -27628,7 +27632,7 @@
       <c r="V144" s="7" t="inlineStr"/>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
+          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
         </is>
       </c>
     </row>
@@ -27642,13 +27646,13 @@
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>1600</v>
+        <v>995</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
@@ -27657,12 +27661,12 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>Central Quay North</t>
+          <t>Two Mile Hill Road, Kingswood, Bristol</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS15</t>
         </is>
       </c>
       <c r="I145" s="8" t="n"/>
@@ -27671,7 +27675,7 @@
       <c r="L145" s="8" t="n"/>
       <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n">
-        <v>20792</v>
+        <v>5116</v>
       </c>
       <c r="O145" s="8" t="n">
         <v>0</v>
@@ -27679,12 +27683,12 @@
       <c r="P145" s="8" t="n"/>
       <c r="Q145" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R145" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>TLS Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S145" s="9" t="inlineStr"/>
@@ -27701,7 +27705,7 @@
       <c r="V145" s="7" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
         </is>
       </c>
     </row>
@@ -27715,27 +27719,27 @@
         </is>
       </c>
       <c r="C146" s="17" t="n">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol</t>
+          <t>Robertson Drive, St Annes Park</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I146" s="8" t="n"/>
@@ -27743,19 +27747,21 @@
       <c r="K146" s="8" t="n"/>
       <c r="L146" s="8" t="n"/>
       <c r="M146" s="8" t="n"/>
-      <c r="N146" s="8" t="n"/>
+      <c r="N146" s="8" t="n">
+        <v>4252</v>
+      </c>
       <c r="O146" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="8" t="n"/>
       <c r="Q146" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R146" s="8" t="inlineStr">
         <is>
-          <t>Stonebridge Shaw, Portishead</t>
+          <t>D W Smith &amp; Company, Hanham</t>
         </is>
       </c>
       <c r="S146" s="9" t="inlineStr"/>
@@ -27772,7 +27778,7 @@
       <c r="V146" s="7" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
         </is>
       </c>
     </row>
@@ -27786,7 +27792,7 @@
         </is>
       </c>
       <c r="C147" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D147" s="8" t="n">
         <v>1</v>
@@ -27801,21 +27807,23 @@
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>St Michaels Hill Ref 708</t>
+          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I147" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I147" s="8" t="n">
+        <v>527</v>
+      </c>
       <c r="J147" s="8" t="n"/>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n">
-        <v>19512</v>
+        <v>5548</v>
       </c>
       <c r="O147" s="8" t="n">
         <v>0</v>
@@ -27823,12 +27831,12 @@
       <c r="P147" s="8" t="n"/>
       <c r="Q147" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R147" s="8" t="inlineStr">
         <is>
-          <t>Jackson Property Management Ltd, Bristol</t>
+          <t>Sheedy &amp; Co, Covering Bristol</t>
         </is>
       </c>
       <c r="S147" s="9" t="inlineStr"/>
@@ -27845,7 +27853,7 @@
       <c r="V147" s="7" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
         </is>
       </c>
     </row>
@@ -27859,7 +27867,7 @@
         </is>
       </c>
       <c r="C148" s="17" t="n">
-        <v>1095</v>
+        <v>1195</v>
       </c>
       <c r="D148" s="8" t="n">
         <v>1</v>
@@ -27874,21 +27882,23 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I148" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="n">
+        <v>409</v>
+      </c>
       <c r="J148" s="8" t="n"/>
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
       <c r="N148" s="8" t="n">
-        <v>2652</v>
+        <v>10420</v>
       </c>
       <c r="O148" s="8" t="n">
         <v>0</v>
@@ -27896,12 +27906,12 @@
       <c r="P148" s="8" t="n"/>
       <c r="Q148" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R148" s="8" t="inlineStr">
         <is>
-          <t>Millennium Lettings &amp; Management, Bristol</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S148" s="9" t="inlineStr"/>
@@ -27918,7 +27928,7 @@
       <c r="V148" s="7" t="inlineStr"/>
       <c r="W148" s="8" t="inlineStr">
         <is>
-          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
         </is>
       </c>
     </row>
@@ -27932,7 +27942,7 @@
         </is>
       </c>
       <c r="C149" s="17" t="n">
-        <v>1200</v>
+        <v>850</v>
       </c>
       <c r="D149" s="8" t="n">
         <v>1</v>
@@ -27947,23 +27957,23 @@
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>Old Market, Verdigris, BS2 0AF</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I149" s="8" t="n">
-        <v>388</v>
+        <v>248</v>
       </c>
       <c r="J149" s="8" t="n"/>
       <c r="K149" s="8" t="n"/>
       <c r="L149" s="8" t="n"/>
       <c r="M149" s="8" t="n"/>
       <c r="N149" s="8" t="n">
-        <v>21220</v>
+        <v>10420</v>
       </c>
       <c r="O149" s="8" t="n">
         <v>0</v>
@@ -27971,12 +27981,12 @@
       <c r="P149" s="8" t="n"/>
       <c r="Q149" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R149" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S149" s="9" t="inlineStr"/>
@@ -27993,314 +28003,379 @@
       <c r="V149" s="7" t="inlineStr"/>
       <c r="W149" s="8" t="inlineStr">
         <is>
+          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D150" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>Central Quay North</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="8" t="n"/>
+      <c r="L150" s="8" t="n"/>
+      <c r="M150" s="8" t="n"/>
+      <c r="N150" s="8" t="n">
+        <v>20792</v>
+      </c>
+      <c r="O150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="8" t="n"/>
+      <c r="Q150" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R150" s="8" t="inlineStr">
+        <is>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S150" s="9" t="inlineStr"/>
+      <c r="T150" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V150" s="7" t="inlineStr"/>
+      <c r="W150" s="8" t="inlineStr">
+        <is>
+          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>Marsh Street, Bristol</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I151" s="8" t="n"/>
+      <c r="J151" s="8" t="n"/>
+      <c r="K151" s="8" t="n"/>
+      <c r="L151" s="8" t="n"/>
+      <c r="M151" s="8" t="n"/>
+      <c r="N151" s="8" t="n"/>
+      <c r="O151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="8" t="n"/>
+      <c r="Q151" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R151" s="8" t="inlineStr">
+        <is>
+          <t>Stonebridge Shaw, Portishead</t>
+        </is>
+      </c>
+      <c r="S151" s="9" t="inlineStr"/>
+      <c r="T151" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V151" s="7" t="inlineStr"/>
+      <c r="W151" s="8" t="inlineStr">
+        <is>
+          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>St Michaels Hill Ref 708</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="n"/>
+      <c r="J152" s="8" t="n"/>
+      <c r="K152" s="8" t="n"/>
+      <c r="L152" s="8" t="n"/>
+      <c r="M152" s="8" t="n"/>
+      <c r="N152" s="8" t="n">
+        <v>19512</v>
+      </c>
+      <c r="O152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="8" t="n"/>
+      <c r="Q152" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="R152" s="8" t="inlineStr">
+        <is>
+          <t>Jackson Property Management Ltd, Bristol</t>
+        </is>
+      </c>
+      <c r="S152" s="9" t="inlineStr"/>
+      <c r="T152" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V152" s="7" t="inlineStr"/>
+      <c r="W152" s="8" t="inlineStr">
+        <is>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I153" s="8" t="n"/>
+      <c r="J153" s="8" t="n"/>
+      <c r="K153" s="8" t="n"/>
+      <c r="L153" s="8" t="n"/>
+      <c r="M153" s="8" t="n"/>
+      <c r="N153" s="8" t="n">
+        <v>2652</v>
+      </c>
+      <c r="O153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="8" t="n"/>
+      <c r="Q153" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R153" s="8" t="inlineStr">
+        <is>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
+        </is>
+      </c>
+      <c r="S153" s="9" t="inlineStr"/>
+      <c r="T153" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V153" s="7" t="inlineStr"/>
+      <c r="W153" s="8" t="inlineStr">
+        <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J154" s="8" t="n"/>
+      <c r="K154" s="8" t="n"/>
+      <c r="L154" s="8" t="n"/>
+      <c r="M154" s="8" t="n"/>
+      <c r="N154" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="8" t="n"/>
+      <c r="Q154" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R154" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S154" s="9" t="inlineStr"/>
+      <c r="T154" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V154" s="7" t="inlineStr"/>
+      <c r="W154" s="8" t="inlineStr">
+        <is>
           <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="7" t="n"/>
-      <c r="C150" s="18" t="n">
-        <v>800</v>
-      </c>
-      <c r="D150" t="n">
-        <v>2</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>LL11</t>
-        </is>
-      </c>
-      <c r="N150" t="n">
-        <v>448</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S150" s="7" t="inlineStr"/>
-      <c r="T150" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V150" s="7" t="inlineStr"/>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="7" t="n"/>
-      <c r="C151" s="18" t="n">
-        <v>900</v>
-      </c>
-      <c r="D151" t="n">
-        <v>2</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>LL18</t>
-        </is>
-      </c>
-      <c r="N151" t="n">
-        <v>328</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>Fifty North West, Chester</t>
-        </is>
-      </c>
-      <c r="S151" s="7" t="inlineStr"/>
-      <c r="T151" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V151" s="7" t="inlineStr"/>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="7" t="n"/>
-      <c r="C152" s="18" t="n">
-        <v>625</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Field View, Mancot, Deeside, CH5 2EY</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="N152" t="n">
-        <v>824</v>
-      </c>
-      <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>Habodel Property Services Ltd, Doncaster</t>
-        </is>
-      </c>
-      <c r="S152" s="7" t="inlineStr"/>
-      <c r="T152" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V152" s="7" t="inlineStr"/>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="B153" s="7" t="n"/>
-      <c r="C153" s="18" t="n">
-        <v>795</v>
-      </c>
-      <c r="D153" t="n">
-        <v>2</v>
-      </c>
-      <c r="E153" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>semi_detached</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Cilcain, The Square, CH7</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>CH7</t>
-        </is>
-      </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>Williams Estates, Rhuddlan</t>
-        </is>
-      </c>
-      <c r="S153" s="7" t="inlineStr"/>
-      <c r="T153" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V153" s="7" t="inlineStr"/>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="7" t="n"/>
-      <c r="C154" s="18" t="n">
-        <v>950</v>
-      </c>
-      <c r="D154" t="n">
-        <v>2</v>
-      </c>
-      <c r="E154" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>semi_detached</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>CH8</t>
-        </is>
-      </c>
-      <c r="N154" t="n">
-        <v>56</v>
-      </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>William Gleave, Deeside</t>
-        </is>
-      </c>
-      <c r="S154" s="7" t="inlineStr"/>
-      <c r="T154" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V154" s="7" t="inlineStr"/>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="7" t="n"/>
       <c r="C155" s="18" t="n">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="D155" t="n">
         <v>2</v>
@@ -28310,36 +28385,33 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Hill Top Close, Ewloe, CH5</t>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>721</v>
+          <t>LL11</t>
+        </is>
       </c>
       <c r="N155" t="n">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Reades, Hawarden Lettings</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S155" s="7" t="inlineStr"/>
@@ -28356,17 +28428,17 @@
       <c r="V155" s="7" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
-          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="18" t="n">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
@@ -28378,31 +28450,28 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Chester Road East, Shotton, Deeside</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I156" t="n">
-        <v>474</v>
+          <t>LL18</t>
+        </is>
       </c>
       <c r="N156" t="n">
-        <v>2016</v>
+        <v>328</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S156" s="7" t="inlineStr"/>
@@ -28419,50 +28488,50 @@
       <c r="V156" s="7" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
-          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7" t="n"/>
       <c r="C157" s="18" t="n">
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>LL11</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1300</v>
+        <v>824</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Habodel Property Services Ltd, Doncaster</t>
         </is>
       </c>
       <c r="S157" s="7" t="inlineStr"/>
@@ -28479,14 +28548,14 @@
       <c r="V157" s="7" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
-          <t>40274ada7dfa710e5054184216178477a704016c</t>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="18" t="n">
-        <v>900</v>
+        <v>795</v>
       </c>
       <c r="D158" t="n">
         <v>2</v>
@@ -28501,7 +28570,7 @@
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+          <t>Cilcain, The Square, CH7</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -28510,19 +28579,19 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>936</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Williams Estates, Rhuddlan</t>
         </is>
       </c>
       <c r="S158" s="7" t="inlineStr"/>
@@ -28539,14 +28608,14 @@
       <c r="V158" s="7" t="inlineStr"/>
       <c r="W158" t="inlineStr">
         <is>
-          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7" t="n"/>
       <c r="C159" s="18" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="D159" t="n">
         <v>2</v>
@@ -28556,33 +28625,33 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>9 Park Road, Ruthin</t>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>LL15</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>576</v>
+        <v>56</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Ruthin</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S159" s="7" t="inlineStr"/>
@@ -28599,14 +28668,14 @@
       <c r="V159" s="7" t="inlineStr"/>
       <c r="W159" t="inlineStr">
         <is>
-          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="18" t="n">
-        <v>795</v>
+        <v>925</v>
       </c>
       <c r="D160" t="n">
         <v>2</v>
@@ -28621,31 +28690,31 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Gladstone Street, Mold</t>
+          <t>Hill Top Close, Ewloe, CH5</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>905</v>
+        <v>721</v>
       </c>
       <c r="N160" t="n">
-        <v>1356</v>
+        <v>472</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Reades, Hawarden Lettings</t>
         </is>
       </c>
       <c r="S160" s="7" t="inlineStr"/>
@@ -28662,48 +28731,48 @@
       <c r="V160" s="7" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
-          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7" t="n"/>
       <c r="C161" s="18" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Llwyn Dinas Fechan, St. Asaph</t>
+          <t>Chester Road East, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>710</v>
+        <v>474</v>
       </c>
       <c r="N161" t="n">
-        <v>248</v>
+        <v>2016</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -28725,14 +28794,14 @@
       <c r="V161" s="7" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
-          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="18" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="D162" t="n">
         <v>2</v>
@@ -28742,36 +28811,33 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Central Drive, Shotton, Deeside</t>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I162" t="n">
-        <v>636</v>
+          <t>LL11</t>
+        </is>
       </c>
       <c r="N162" t="n">
-        <v>1924</v>
+        <v>1300</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S162" s="7" t="inlineStr"/>
@@ -28788,29 +28854,29 @@
       <c r="V162" s="7" t="inlineStr"/>
       <c r="W162" t="inlineStr">
         <is>
-          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7" t="n"/>
       <c r="C163" s="18" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D163" t="n">
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Llys Y Ddol, Mold</t>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28819,19 +28885,19 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1368</v>
+        <v>936</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S163" s="7" t="inlineStr"/>
@@ -28848,53 +28914,50 @@
       <c r="V163" s="7" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
-          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="7" t="n"/>
       <c r="C164" s="18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
         <v>1</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Mill View Road, Shotton, CH5</t>
+          <t>9 Park Road, Ruthin</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I164" t="n">
-        <v>1087</v>
+          <t>LL15</t>
+        </is>
       </c>
       <c r="N164" t="n">
-        <v>2236</v>
+        <v>576</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr"/>
@@ -28911,48 +28974,48 @@
       <c r="V164" s="7" t="inlineStr"/>
       <c r="W164" t="inlineStr">
         <is>
-          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="7" t="n"/>
       <c r="C165" s="18" t="n">
-        <v>1100</v>
+        <v>795</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Chestnut Way, Penyffordd, Chester</t>
+          <t>Gladstone Street, Mold</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CH4</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>765</v>
+        <v>905</v>
       </c>
       <c r="N165" t="n">
-        <v>144</v>
+        <v>1356</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -28974,17 +29037,17 @@
       <c r="V165" s="7" t="inlineStr"/>
       <c r="W165" t="inlineStr">
         <is>
-          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="18" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
@@ -28996,28 +29059,31 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>LL18</t>
-        </is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>710</v>
       </c>
       <c r="N166" t="n">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr"/>
@@ -29034,50 +29100,53 @@
       <c r="V166" s="7" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
-          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7" t="n"/>
       <c r="C167" s="18" t="n">
-        <v>875</v>
+        <v>700</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+          <t>Central Drive, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>636</v>
       </c>
       <c r="N167" t="n">
-        <v>540</v>
+        <v>1924</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr"/>
@@ -29094,17 +29163,20 @@
       <c r="V167" s="7" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
-          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="18" t="n">
-        <v>725</v>
+        <v>850</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -29113,28 +29185,28 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>High Street, Connah's Quay, CH5</t>
+          <t>Llys Y Ddol, Mold</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1904</v>
+        <v>1368</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr"/>
@@ -29151,50 +29223,53 @@
       <c r="V168" s="7" t="inlineStr"/>
       <c r="W168" t="inlineStr">
         <is>
-          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7" t="n"/>
       <c r="C169" s="18" t="n">
-        <v>625</v>
+        <v>1000</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" t="n">
         <v>1</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Well Street, Holywell</t>
+          <t>Mill View Road, Shotton, CH5</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>1087</v>
       </c>
       <c r="N169" t="n">
-        <v>904</v>
+        <v>2236</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr"/>
@@ -29211,50 +29286,53 @@
       <c r="V169" s="7" t="inlineStr"/>
       <c r="W169" t="inlineStr">
         <is>
-          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="18" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="D170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+          <t>Chestnut Way, Penyffordd, Chester</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CH6</t>
-        </is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>765</v>
       </c>
       <c r="N170" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr"/>
@@ -29271,20 +29349,20 @@
       <c r="V170" s="7" t="inlineStr"/>
       <c r="W170" t="inlineStr">
         <is>
-          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7" t="n"/>
       <c r="C171" s="18" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -29293,31 +29371,28 @@
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Rue St. Gregoire, Holywell, CH8</t>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
-      </c>
-      <c r="I171" t="n">
-        <v>657</v>
+          <t>LL18</t>
+        </is>
       </c>
       <c r="N171" t="n">
-        <v>876</v>
+        <v>32</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Currans, North Wales</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr"/>
@@ -29334,50 +29409,50 @@
       <c r="V171" s="7" t="inlineStr"/>
       <c r="W171" t="inlineStr">
         <is>
-          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="18" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>29 Tai Maes, Mold</t>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1356</v>
+        <v>540</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S172" s="7" t="inlineStr"/>
@@ -29394,21 +29469,18 @@
       <c r="V172" s="7" t="inlineStr"/>
       <c r="W172" t="inlineStr">
         <is>
-          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7" t="n"/>
       <c r="C173" s="18" t="n">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
       <c r="F173" t="inlineStr">
         <is>
           <t>flat</t>
@@ -29416,28 +29488,28 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>St Marys Mews, Mold</t>
+          <t>High Street, Connah's Quay, CH5</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1372</v>
+        <v>1904</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S173" s="7" t="inlineStr"/>
@@ -29454,50 +29526,50 @@
       <c r="V173" s="7" t="inlineStr"/>
       <c r="W173" t="inlineStr">
         <is>
-          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="18" t="n">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>Castle Street, Caergwrle</t>
+          <t>Well Street, Holywell</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>264</v>
+        <v>904</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Town &amp; Country Estate Agents, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S174" s="7" t="inlineStr"/>
@@ -29514,14 +29586,14 @@
       <c r="V174" s="7" t="inlineStr"/>
       <c r="W174" t="inlineStr">
         <is>
-          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7" t="n"/>
       <c r="C175" s="18" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="D175" t="n">
         <v>2</v>
@@ -29531,33 +29603,33 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Fagl Lane, Hope, LL12</t>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH6</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Belvoir, Wrexham</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr"/>
@@ -29574,50 +29646,53 @@
       <c r="V175" s="7" t="inlineStr"/>
       <c r="W175" t="inlineStr">
         <is>
-          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="18" t="n">
-        <v>595</v>
+        <v>950</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>Ryeland Street, Deeside</t>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>657</v>
       </c>
       <c r="N176" t="n">
-        <v>2152</v>
+        <v>876</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Currans, North Wales</t>
         </is>
       </c>
       <c r="S176" s="7" t="inlineStr"/>
@@ -29634,7 +29709,7 @@
       <c r="V176" s="7" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
-          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
         </is>
       </c>
     </row>
@@ -29656,28 +29731,28 @@
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>High Street, Dyserth, LL18</t>
+          <t>29 Tai Maes, Mold</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>232</v>
+        <v>1356</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S177" s="7" t="inlineStr"/>
@@ -29694,17 +29769,17 @@
       <c r="V177" s="7" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="18" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -29716,28 +29791,28 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>St Marys Mews, Mold</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>328</v>
+        <v>1372</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S178" s="7" t="inlineStr"/>
@@ -29754,20 +29829,20 @@
       <c r="V178" s="7" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
-          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7" t="n"/>
       <c r="C179" s="18" t="n">
-        <v>795</v>
+        <v>875</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -29776,28 +29851,28 @@
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+          <t>Castle Street, Caergwrle</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>LL16</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>940</v>
+        <v>264</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
         </is>
       </c>
       <c r="S179" s="7" t="inlineStr"/>
@@ -29814,29 +29889,29 @@
       <c r="V179" s="7" t="inlineStr"/>
       <c r="W179" t="inlineStr">
         <is>
-          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="7" t="n"/>
       <c r="C180" s="18" t="n">
-        <v>975</v>
+        <v>800</v>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
         <v>1</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Derby Road, Caergwrle, Wrexham</t>
+          <t>Fagl Lane, Hope, LL12</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29845,19 +29920,19 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Belvoir, Wrexham</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr"/>
@@ -29874,20 +29949,20 @@
       <c r="V180" s="7" t="inlineStr"/>
       <c r="W180" t="inlineStr">
         <is>
-          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="7" t="n"/>
       <c r="C181" s="18" t="n">
-        <v>985</v>
+        <v>595</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -29896,28 +29971,28 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Livingstone Place, St. Asaph, LL17</t>
+          <t>Ryeland Street, Deeside</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>268</v>
+        <v>2152</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr"/>
@@ -29934,12 +30009,312 @@
       <c r="V181" s="7" t="inlineStr"/>
       <c r="W181" t="inlineStr">
         <is>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="7" t="n"/>
+      <c r="C182" s="18" t="n">
+        <v>750</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>High Street, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>232</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S182" s="7" t="inlineStr"/>
+      <c r="T182" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V182" s="7" t="inlineStr"/>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="7" t="n"/>
+      <c r="C183" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>Newmarket Road, Dyserth, LL18</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>LL18</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>328</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Fifty North West, Chester</t>
+        </is>
+      </c>
+      <c r="S183" s="7" t="inlineStr"/>
+      <c r="T183" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V183" s="7" t="inlineStr"/>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="7" t="n"/>
+      <c r="C184" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>LL16</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>940</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Monopoly, Denbigh</t>
+        </is>
+      </c>
+      <c r="S184" s="7" t="inlineStr"/>
+      <c r="T184" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V184" s="7" t="inlineStr"/>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>terraced</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>Derby Road, Caergwrle, Wrexham</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>LL12</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>252</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Bowen, Wrexham</t>
+        </is>
+      </c>
+      <c r="S185" s="7" t="inlineStr"/>
+      <c r="T185" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V185" s="7" t="inlineStr"/>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="7" t="n"/>
+      <c r="C186" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>268</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S186" s="7" t="inlineStr"/>
+      <c r="T186" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V186" s="7" t="inlineStr"/>
+      <c r="W186" t="inlineStr">
+        <is>
           <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W181"/>
+  <autoFilter ref="A1:W186"/>
   <dataValidations count="1">
     <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
@@ -30126,6 +30501,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T179" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T180" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W186"/>
+  <dimension ref="A1:W187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17528,13 +17528,13 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
@@ -17543,23 +17543,23 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Number One Bristol, BS1 2NR</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>527</v>
+        <v>783</v>
       </c>
       <c r="J9" s="8" t="n"/>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n">
-        <v>21804</v>
+        <v>4680</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>0</v>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S9" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T9" s="12" t="inlineStr">
@@ -17593,7 +17593,7 @@
       <c r="V9" s="7" t="inlineStr"/>
       <c r="W9" s="8" t="inlineStr">
         <is>
-          <t>27b085b9bcbec967c008845a19f54e272fc12b87</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17607,7 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>1900</v>
+        <v>2170</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -17622,23 +17622,23 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>522 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n">
-        <v>4680</v>
+        <v>20800</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>0</v>
@@ -17646,12 +17646,12 @@
       <c r="P10" s="8" t="n"/>
       <c r="Q10" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S10" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
       <c r="V10" s="7" t="inlineStr"/>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>c0573087585d4e3e5716cf3f127e0ed418364345</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17686,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>2170</v>
+        <v>2195</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>2</v>
@@ -17701,7 +17701,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>522 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2 0GJ</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="I11" s="8" t="n">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
@@ -17751,7 +17751,7 @@
       <c r="V11" s="7" t="inlineStr"/>
       <c r="W11" s="8" t="inlineStr">
         <is>
-          <t>c0573087585d4e3e5716cf3f127e0ed418364345</t>
+          <t>ad6f591658988c13d13881686e197fa878817439</t>
         </is>
       </c>
     </row>
@@ -17765,7 +17765,7 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>2195</v>
+        <v>1995</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>2</v>
@@ -17780,23 +17780,21 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>802 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2 0GJ</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>809</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n">
-        <v>20800</v>
+        <v>18544</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>0</v>
@@ -17809,7 +17807,7 @@
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S12" s="9" t="inlineStr">
@@ -17830,7 +17828,7 @@
       <c r="V12" s="7" t="inlineStr"/>
       <c r="W12" s="8" t="inlineStr">
         <is>
-          <t>ad6f591658988c13d13881686e197fa878817439</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -17844,13 +17842,13 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1995</v>
+        <v>1450</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -17859,21 +17857,23 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Bedminster, Berkeley Place, BS3</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>7685</v>
+      </c>
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n">
-        <v>18544</v>
+        <v>7648</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>0</v>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S13" s="9" t="inlineStr">
@@ -17907,7 +17907,7 @@
       <c r="V13" s="7" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>4855da62cb452e8973968307d05f937e5ab76b6c</t>
         </is>
       </c>
     </row>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>1450</v>
+        <v>1655</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>1</v>
@@ -17936,23 +17936,23 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Bedminster, Berkeley Place, BS3</t>
+          <t>New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I14" s="8" t="n">
-        <v>7685</v>
+        <v>547</v>
       </c>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n">
-        <v>7648</v>
+        <v>20800</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>0</v>
@@ -17960,12 +17960,12 @@
       <c r="P14" s="8" t="n"/>
       <c r="Q14" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S14" s="9" t="inlineStr">
@@ -17986,7 +17986,7 @@
       <c r="V14" s="7" t="inlineStr"/>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>4855da62cb452e8973968307d05f937e5ab76b6c</t>
+          <t>1f8489d296d842011bdf7a2ca1f952e6b948c3d3</t>
         </is>
       </c>
     </row>
@@ -18000,13 +18000,13 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>1655</v>
+        <v>2500</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -18015,23 +18015,21 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>New Kingsley Road, Bristol, BS2</t>
+          <t>Electricity House, Colston Avenue, BS1</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>547</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n">
-        <v>20800</v>
+        <v>21876</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>0</v>
@@ -18044,7 +18042,7 @@
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S15" s="9" t="inlineStr">
@@ -18065,7 +18063,7 @@
       <c r="V15" s="7" t="inlineStr"/>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>1f8489d296d842011bdf7a2ca1f952e6b948c3d3</t>
+          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
         </is>
       </c>
     </row>
@@ -18079,13 +18077,13 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -18094,12 +18092,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Stillhouse lane</t>
+          <t>The Crescent, Hannover Quay, BS1</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -18108,7 +18106,7 @@
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>14304</v>
+        <v>16232</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>0</v>
@@ -18121,7 +18119,7 @@
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S16" s="9" t="inlineStr">
@@ -18142,7 +18140,7 @@
       <c r="V16" s="7" t="inlineStr"/>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>5cd63c65fc4cff6a9795b3661298e348456cd9ae</t>
+          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
         </is>
       </c>
     </row>
@@ -18156,13 +18154,13 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>2500</v>
+        <v>1495</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -18171,7 +18169,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Electricity House, Colston Avenue, BS1</t>
+          <t>Baldwin Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -18185,7 +18183,7 @@
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n">
-        <v>21876</v>
+        <v>20848</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>0</v>
@@ -18193,12 +18191,12 @@
       <c r="P17" s="8" t="n"/>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S17" s="9" t="inlineStr">
@@ -18219,7 +18217,7 @@
       <c r="V17" s="7" t="inlineStr"/>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
+          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18231,7 @@
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>1500</v>
+        <v>1733</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>1</v>
@@ -18248,7 +18246,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, BS1</t>
+          <t>Cheltenham House, Clare Street, Bristol</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -18256,26 +18254,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I18" s="8" t="n"/>
+      <c r="I18" s="8" t="n">
+        <v>455</v>
+      </c>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n">
-        <v>16232</v>
-      </c>
+      <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="8" t="n"/>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S18" s="9" t="inlineStr">
@@ -18296,7 +18294,7 @@
       <c r="V18" s="7" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
+          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
         </is>
       </c>
     </row>
@@ -18310,13 +18308,13 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1495</v>
+        <v>1850</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -18325,7 +18323,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, Somerset, BS1</t>
+          <t>Park Row, Bristol, BS1</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -18333,26 +18331,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I19" s="8" t="n"/>
+      <c r="I19" s="8" t="n">
+        <v>797</v>
+      </c>
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n">
-        <v>20848</v>
-      </c>
+      <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="8" t="n"/>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S19" s="9" t="inlineStr">
@@ -18373,7 +18371,7 @@
       <c r="V19" s="7" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
+          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
         </is>
       </c>
     </row>
@@ -18387,13 +18385,13 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>1733</v>
+        <v>2975</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
@@ -18402,34 +18400,36 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Cheltenham House, Clare Street, Bristol</t>
+          <t>Capricorn Place, Hotwells</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I20" s="8" t="n">
-        <v>455</v>
+        <v>1615</v>
       </c>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
+      <c r="N20" s="8" t="n">
+        <v>15104</v>
+      </c>
       <c r="O20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S20" s="9" t="inlineStr">
@@ -18450,7 +18450,7 @@
       <c r="V20" s="7" t="inlineStr"/>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
+          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18464,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1850</v>
+        <v>2000</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>2</v>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Park Row, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -18487,31 +18487,31 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I21" s="8" t="n">
-        <v>797</v>
-      </c>
+      <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
+      <c r="N21" s="8" t="n">
+        <v>22020</v>
+      </c>
       <c r="O21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="8" t="n"/>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S21" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
@@ -18527,7 +18527,7 @@
       <c r="V21" s="7" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -18541,13 +18541,13 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>2975</v>
+        <v>1400</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
@@ -18556,23 +18556,21 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells</t>
+          <t>The Crescent, Harbourside, Bristol</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>1615</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n">
-        <v>15104</v>
+        <v>16368</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>0</v>
@@ -18580,12 +18578,12 @@
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S22" s="9" t="inlineStr">
@@ -18606,7 +18604,7 @@
       <c r="V22" s="7" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18618,7 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>2</v>
@@ -18635,7 +18633,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -18649,7 +18647,7 @@
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>0</v>
@@ -18667,7 +18665,7 @@
       </c>
       <c r="S23" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
@@ -18683,7 +18681,7 @@
       <c r="V23" s="7" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -18712,7 +18710,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, Bristol</t>
+          <t>City Centre, Number One Bristol, BS1 2NR</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -18720,13 +18718,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I24" s="8" t="n"/>
+      <c r="I24" s="8" t="n">
+        <v>527</v>
+      </c>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n">
-        <v>16368</v>
+        <v>21804</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>0</v>
@@ -18734,17 +18734,17 @@
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S24" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T24" s="12" t="inlineStr">
@@ -18760,7 +18760,7 @@
       <c r="V24" s="7" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>27b085b9bcbec967c008845a19f54e272fc12b87</t>
         </is>
       </c>
     </row>
@@ -18774,10 +18774,10 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1900</v>
+        <v>2200</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>2</v>
@@ -18789,12 +18789,12 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Stillhouse lane</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -18803,7 +18803,7 @@
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n">
-        <v>22132</v>
+        <v>14304</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>0</v>
@@ -18811,12 +18811,12 @@
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S25" s="9" t="inlineStr">
@@ -18837,7 +18837,7 @@
       <c r="V25" s="7" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>5cd63c65fc4cff6a9795b3661298e348456cd9ae</t>
         </is>
       </c>
     </row>
@@ -20144,10 +20144,10 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>1</v>
@@ -20159,23 +20159,21 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>Buchanans Wharf North, Ferry Street, BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>431</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n">
-        <v>20896</v>
+        <v>19576</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>0</v>
@@ -20183,12 +20181,12 @@
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S43" s="9" t="inlineStr"/>
@@ -20205,7 +20203,7 @@
       <c r="V43" s="7" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
+          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
         </is>
       </c>
     </row>
@@ -20219,10 +20217,10 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="8" t="n">
         <v>1</v>
@@ -20234,12 +20232,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Hamilton Court - City Centre</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -20248,7 +20246,7 @@
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n">
-        <v>19576</v>
+        <v>21616</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>0</v>
@@ -20256,12 +20254,12 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S44" s="9" t="inlineStr"/>
@@ -20278,7 +20276,7 @@
       <c r="V44" s="7" t="inlineStr"/>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
+          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
         </is>
       </c>
     </row>
@@ -20292,10 +20290,10 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>1300</v>
+        <v>2200</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>1</v>
@@ -20307,7 +20305,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court - City Centre</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -20321,7 +20319,7 @@
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n">
-        <v>21616</v>
+        <v>21984</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>0</v>
@@ -20329,12 +20327,12 @@
       <c r="P45" s="8" t="n"/>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S45" s="9" t="inlineStr"/>
@@ -20351,7 +20349,7 @@
       <c r="V45" s="7" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
+          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
         </is>
       </c>
     </row>
@@ -20365,13 +20363,13 @@
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
@@ -20424,7 +20422,7 @@
       <c r="V46" s="7" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
+          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
         </is>
       </c>
     </row>
@@ -20453,7 +20451,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -20497,7 +20495,7 @@
       <c r="V47" s="7" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
+          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
         </is>
       </c>
     </row>
@@ -20511,13 +20509,13 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>2300</v>
+        <v>2095</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
@@ -20526,7 +20524,7 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
+          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -20570,7 +20568,7 @@
       <c r="V48" s="7" t="inlineStr"/>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
+          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
         </is>
       </c>
     </row>
@@ -20584,10 +20582,10 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>2095</v>
+        <v>1400</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>1</v>
@@ -20599,12 +20597,12 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -20613,7 +20611,7 @@
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n">
-        <v>21984</v>
+        <v>20908</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>0</v>
@@ -20621,12 +20619,12 @@
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S49" s="9" t="inlineStr"/>
@@ -20643,7 +20641,7 @@
       <c r="V49" s="7" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -20657,10 +20655,10 @@
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>1</v>
@@ -20672,12 +20670,12 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -20686,7 +20684,7 @@
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n">
-        <v>20908</v>
+        <v>21600</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>0</v>
@@ -20694,12 +20692,12 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S50" s="9" t="inlineStr"/>
@@ -20716,7 +20714,7 @@
       <c r="V50" s="7" t="inlineStr"/>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20728,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>2</v>
@@ -20745,7 +20743,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Waterloo Road, Midland Mews, BS2</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -20753,13 +20751,15 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I51" s="8" t="n"/>
+      <c r="I51" s="8" t="n">
+        <v>721</v>
+      </c>
       <c r="J51" s="8" t="n"/>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n">
-        <v>21600</v>
+        <v>20856</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>0</v>
@@ -20767,12 +20767,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr"/>
@@ -20789,7 +20789,7 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
         </is>
       </c>
     </row>
@@ -20803,13 +20803,13 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>1600</v>
+        <v>2085</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
@@ -20818,23 +20818,23 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Waterloo Road, Midland Mews, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I52" s="8" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>0</v>
@@ -20842,12 +20842,12 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr"/>
@@ -20864,7 +20864,7 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>1</v>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -20901,13 +20901,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I53" s="8" t="n"/>
+      <c r="I53" s="8" t="n">
+        <v>570</v>
+      </c>
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n">
-        <v>22196</v>
+        <v>20820</v>
       </c>
       <c r="O53" s="8" t="n">
         <v>0</v>
@@ -20915,12 +20917,12 @@
       <c r="P53" s="8" t="n"/>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R53" s="8" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S53" s="9" t="inlineStr"/>
@@ -20937,7 +20939,7 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -20951,13 +20953,13 @@
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>2150</v>
+        <v>1500</v>
       </c>
       <c r="D54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -20966,23 +20968,21 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>796</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O54" s="8" t="n">
         <v>0</v>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="R54" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S54" s="9" t="inlineStr"/>
@@ -21012,7 +21012,7 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
+          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
         </is>
       </c>
     </row>
@@ -21026,13 +21026,13 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>2085</v>
+        <v>1395</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hall Floor Flat, Queens Parade</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -21049,15 +21049,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I55" s="8" t="n">
-        <v>722</v>
-      </c>
+      <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n">
-        <v>21504</v>
+        <v>18020</v>
       </c>
       <c r="O55" s="8" t="n">
         <v>0</v>
@@ -21065,12 +21063,12 @@
       <c r="P55" s="8" t="n"/>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R55" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Flatline Letting and Property Management, Clifton</t>
         </is>
       </c>
       <c r="S55" s="9" t="inlineStr"/>
@@ -21087,7 +21085,7 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
         </is>
       </c>
     </row>
@@ -21101,7 +21099,7 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>1640</v>
+        <v>1300</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>1</v>
@@ -21116,7 +21114,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -21125,14 +21123,14 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>570</v>
+        <v>405</v>
       </c>
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n">
-        <v>20820</v>
+        <v>20316</v>
       </c>
       <c r="O56" s="8" t="n">
         <v>0</v>
@@ -21145,7 +21143,7 @@
       </c>
       <c r="R56" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S56" s="9" t="inlineStr"/>
@@ -21162,7 +21160,7 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -21176,13 +21174,13 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>1500</v>
+        <v>2020</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
@@ -21191,15 +21189,17 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>764</v>
+      </c>
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
@@ -21213,12 +21213,12 @@
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr"/>
@@ -21235,7 +21235,7 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21249,13 +21249,13 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>1395</v>
+        <v>2145</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Hall Floor Flat, Queens Parade</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -21272,13 +21272,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I58" s="8" t="n"/>
+      <c r="I58" s="8" t="n">
+        <v>815</v>
+      </c>
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n">
-        <v>18020</v>
+        <v>21504</v>
       </c>
       <c r="O58" s="8" t="n">
         <v>0</v>
@@ -21286,12 +21288,12 @@
       <c r="P58" s="8" t="n"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>Flatline Letting and Property Management, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr"/>
@@ -21308,7 +21310,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21322,7 +21324,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>1300</v>
+        <v>1635</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>1</v>
@@ -21337,7 +21339,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -21346,14 +21348,14 @@
         </is>
       </c>
       <c r="I59" s="8" t="n">
-        <v>405</v>
+        <v>486</v>
       </c>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n">
-        <v>20316</v>
+        <v>21504</v>
       </c>
       <c r="O59" s="8" t="n">
         <v>0</v>
@@ -21361,12 +21363,12 @@
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr"/>
@@ -21383,7 +21385,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -21397,7 +21399,7 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>2020</v>
+        <v>1750</v>
       </c>
       <c r="D60" s="8" t="n">
         <v>2</v>
@@ -21412,23 +21414,23 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n">
-        <v>20856</v>
+        <v>4680</v>
       </c>
       <c r="O60" s="8" t="n">
         <v>0</v>
@@ -21441,7 +21443,7 @@
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr"/>
@@ -21458,7 +21460,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -21472,13 +21474,13 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>2145</v>
+        <v>2100</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
@@ -21487,7 +21489,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -21495,15 +21497,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I61" s="8" t="n">
-        <v>815</v>
-      </c>
+      <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>21504</v>
+        <v>21148</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -21511,12 +21511,12 @@
       <c r="P61" s="8" t="n"/>
       <c r="Q61" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -21547,13 +21547,13 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>1635</v>
+        <v>2220</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -21571,14 +21571,14 @@
         </is>
       </c>
       <c r="I62" s="8" t="n">
-        <v>486</v>
+        <v>697</v>
       </c>
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -21586,12 +21586,12 @@
       <c r="P62" s="8" t="n"/>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S62" s="9" t="inlineStr"/>
@@ -21608,7 +21608,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1640</v>
+        <v>1300</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>1</v>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -21645,15 +21645,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I63" s="8" t="n">
-        <v>494</v>
-      </c>
+      <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>20820</v>
+        <v>21428</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21661,12 +21659,12 @@
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21683,7 +21681,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -21697,13 +21695,13 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1750</v>
+        <v>1500</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
@@ -21712,23 +21710,23 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>731</v>
+        <v>548</v>
       </c>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>4680</v>
+        <v>21504</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21736,12 +21734,12 @@
       <c r="P64" s="8" t="n"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21758,7 +21756,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -21772,7 +21770,7 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>2100</v>
+        <v>1615</v>
       </c>
       <c r="D65" s="8" t="n">
         <v>1</v>
@@ -21787,7 +21785,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -21795,13 +21793,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I65" s="8" t="n"/>
+      <c r="I65" s="8" t="n">
+        <v>486</v>
+      </c>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n">
-        <v>21148</v>
+        <v>21504</v>
       </c>
       <c r="O65" s="8" t="n">
         <v>0</v>
@@ -21809,12 +21809,12 @@
       <c r="P65" s="8" t="n"/>
       <c r="Q65" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr"/>
@@ -21831,7 +21831,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -21845,10 +21845,10 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>1250</v>
+        <v>1965</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="n">
         <v>1</v>
@@ -21860,7 +21860,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -21868,13 +21868,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I66" s="8" t="n"/>
+      <c r="I66" s="8" t="n">
+        <v>655</v>
+      </c>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>21160</v>
+        <v>21504</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -21882,12 +21884,12 @@
       <c r="P66" s="8" t="n"/>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21904,7 +21906,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
+          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
         </is>
       </c>
     </row>
@@ -21918,13 +21920,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1640</v>
+        <v>2080</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21942,7 +21944,7 @@
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>495</v>
+        <v>705</v>
       </c>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
@@ -21957,7 +21959,7 @@
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr">
@@ -21979,7 +21981,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
+          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
         </is>
       </c>
     </row>
@@ -21993,13 +21995,13 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>2220</v>
+        <v>1400</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -22008,7 +22010,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -22016,15 +22018,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I68" s="8" t="n">
-        <v>697</v>
-      </c>
+      <c r="I68" s="8" t="n"/>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>20820</v>
+        <v>19484</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22032,12 +22032,12 @@
       <c r="P68" s="8" t="n"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22054,7 +22054,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -22068,13 +22068,13 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>1890</v>
+        <v>2000</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Welsh Back, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22092,27 +22092,25 @@
         </is>
       </c>
       <c r="I69" s="8" t="n">
-        <v>702</v>
+        <v>908</v>
       </c>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
-      <c r="N69" s="8" t="n">
-        <v>21680</v>
-      </c>
+      <c r="N69" s="8" t="n"/>
       <c r="O69" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Hello Neighbour, London</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22129,7 +22127,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
+          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
         </is>
       </c>
     </row>
@@ -22143,13 +22141,13 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1300</v>
+        <v>2020</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
@@ -22158,7 +22156,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -22166,26 +22164,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="8" t="n"/>
+      <c r="I70" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
-      <c r="N70" s="8" t="n">
-        <v>21428</v>
-      </c>
+      <c r="N70" s="8" t="n"/>
       <c r="O70" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S70" s="9" t="inlineStr"/>
@@ -22202,7 +22200,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
         </is>
       </c>
     </row>
@@ -22216,10 +22214,10 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1635</v>
+        <v>2175</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" s="8" t="n">
         <v>1</v>
@@ -22231,7 +22229,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22239,28 +22237,24 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I71" s="8" t="n">
-        <v>517</v>
-      </c>
+      <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
-      <c r="N71" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N71" s="8" t="n"/>
       <c r="O71" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="8" t="n"/>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22277,7 +22271,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>acf18902969821dd75405f7916c6929252fb214a</t>
+          <t>6a00f91534112c4504453102597619449da3a2c1</t>
         </is>
       </c>
     </row>
@@ -22291,7 +22285,7 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1855</v>
+        <v>2000</v>
       </c>
       <c r="D72" s="8" t="n">
         <v>2</v>
@@ -22306,7 +22300,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Eclipse - City Centre</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22314,28 +22308,24 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I72" s="8" t="n">
-        <v>607</v>
-      </c>
+      <c r="I72" s="8" t="n"/>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="n"/>
-      <c r="N72" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N72" s="8" t="n"/>
       <c r="O72" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="8" t="n"/>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22352,7 +22342,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
+          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
         </is>
       </c>
     </row>
@@ -22366,7 +22356,7 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1500</v>
+        <v>1595</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>1</v>
@@ -22390,22 +22380,20 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>548</v>
+        <v>499</v>
       </c>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
-      <c r="N73" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N73" s="8" t="n"/>
       <c r="O73" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="8" t="n"/>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R73" s="8" t="inlineStr">
@@ -22427,7 +22415,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
         </is>
       </c>
     </row>
@@ -22441,13 +22429,13 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>1615</v>
+        <v>2085</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
@@ -22456,7 +22444,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -22465,27 +22453,25 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>486</v>
+        <v>705</v>
       </c>
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
-      <c r="N74" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N74" s="8" t="n"/>
       <c r="O74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="8" t="n"/>
       <c r="Q74" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
@@ -22502,7 +22488,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
         </is>
       </c>
     </row>
@@ -22516,13 +22502,13 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>2180</v>
+        <v>1615</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
@@ -22531,7 +22517,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -22540,27 +22526,25 @@
         </is>
       </c>
       <c r="I75" s="8" t="n">
-        <v>767</v>
+        <v>487</v>
       </c>
       <c r="J75" s="8" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
-      <c r="N75" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="8" t="n"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R75" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S75" s="9" t="inlineStr"/>
@@ -22577,7 +22561,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -22591,13 +22575,13 @@
         </is>
       </c>
       <c r="C76" s="17" t="n">
-        <v>1965</v>
+        <v>2065</v>
       </c>
       <c r="D76" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
@@ -22615,22 +22599,20 @@
         </is>
       </c>
       <c r="I76" s="8" t="n">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="n"/>
-      <c r="N76" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N76" s="8" t="n"/>
       <c r="O76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="8" t="n"/>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R76" s="8" t="inlineStr">
@@ -22652,7 +22634,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -22666,7 +22648,7 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2080</v>
+        <v>2185</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>2</v>
@@ -22681,7 +22663,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -22690,27 +22672,25 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
       <c r="M77" s="8" t="n"/>
-      <c r="N77" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N77" s="8" t="n"/>
       <c r="O77" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="8" t="n"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S77" s="9" t="inlineStr"/>
@@ -22727,7 +22707,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -22741,7 +22721,7 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>1400</v>
+        <v>1565</v>
       </c>
       <c r="D78" s="8" t="n">
         <v>1</v>
@@ -22756,7 +22736,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -22764,26 +22744,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I78" s="8" t="n"/>
+      <c r="I78" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="n"/>
-      <c r="N78" s="8" t="n">
-        <v>19484</v>
-      </c>
+      <c r="N78" s="8" t="n"/>
       <c r="O78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
@@ -22800,7 +22780,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -22814,13 +22794,13 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>2000</v>
+        <v>1650</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
@@ -22829,7 +22809,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol, BS1</t>
+          <t>Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -22837,9 +22817,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I79" s="8" t="n">
-        <v>908</v>
-      </c>
+      <c r="I79" s="8" t="n"/>
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
@@ -22851,12 +22829,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>Hello Neighbour, London</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
@@ -22873,7 +22851,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -22887,13 +22865,13 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>2020</v>
+        <v>1625</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
@@ -22902,7 +22880,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -22911,7 +22889,7 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>705</v>
+        <v>485</v>
       </c>
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
@@ -22924,12 +22902,12 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S80" s="9" t="inlineStr"/>
@@ -22946,7 +22924,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -22963,10 +22941,10 @@
         <v>2175</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
@@ -22975,7 +22953,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -22983,7 +22961,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I81" s="8" t="n"/>
+      <c r="I81" s="8" t="n">
+        <v>722</v>
+      </c>
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="8" t="n"/>
@@ -22995,12 +22975,12 @@
       <c r="P81" s="8" t="n"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
@@ -23017,7 +22997,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>6a00f91534112c4504453102597619449da3a2c1</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -23031,13 +23011,13 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
@@ -23046,7 +23026,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Eclipse - City Centre</t>
+          <t>Baldwin Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -23054,7 +23034,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I82" s="8" t="n"/>
+      <c r="I82" s="8" t="n">
+        <v>721</v>
+      </c>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
@@ -23071,7 +23053,7 @@
       </c>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S82" s="9" t="inlineStr"/>
@@ -23088,7 +23070,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
+          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
         </is>
       </c>
     </row>
@@ -23102,7 +23084,7 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>1595</v>
+        <v>1500</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>1</v>
@@ -23117,17 +23099,15 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Kings Quarter Apts, Bristol, BS2</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I83" s="8" t="n">
-        <v>499</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
@@ -23139,12 +23119,12 @@
       <c r="P83" s="8" t="n"/>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R83" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S83" s="9" t="inlineStr"/>
@@ -23161,7 +23141,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
+          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
         </is>
       </c>
     </row>
@@ -23175,13 +23155,13 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
@@ -23190,7 +23170,7 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -23198,9 +23178,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="8" t="n">
-        <v>705</v>
-      </c>
+      <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
@@ -23212,12 +23190,12 @@
       <c r="P84" s="8" t="n"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R84" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S84" s="9" t="inlineStr"/>
@@ -23234,7 +23212,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>f37bb95403b6c94c61951f944bce88c63865f963</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -23248,13 +23226,13 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1635</v>
+        <v>1900</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
@@ -23263,7 +23241,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -23271,9 +23249,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I85" s="8" t="n">
-        <v>546</v>
-      </c>
+      <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
@@ -23285,12 +23261,12 @@
       <c r="P85" s="8" t="n"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
@@ -23307,7 +23283,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>36d0812581d3df99e6949e941acc69f0f62aaaf1</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -23321,7 +23297,7 @@
         </is>
       </c>
       <c r="C86" s="17" t="n">
-        <v>2085</v>
+        <v>2500</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>2</v>
@@ -23336,7 +23312,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Liberty Gardens, Caledonian Road, BS1</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -23345,7 +23321,7 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>705</v>
+        <v>1238</v>
       </c>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
@@ -23358,12 +23334,12 @@
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
@@ -23380,7 +23356,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
+          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23370,7 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>1615</v>
+        <v>1250</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>1</v>
@@ -23409,17 +23385,15 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>St Johns Lane, Bedminster</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="n">
-        <v>487</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="n"/>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
@@ -23431,12 +23405,12 @@
       <c r="P87" s="8" t="n"/>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S87" s="9" t="inlineStr"/>
@@ -23453,7 +23427,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
         </is>
       </c>
     </row>
@@ -23467,13 +23441,13 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>2065</v>
+        <v>1660</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
@@ -23482,7 +23456,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -23491,25 +23465,27 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>641</v>
+        <v>486</v>
       </c>
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="n"/>
-      <c r="N88" s="8" t="n"/>
+      <c r="N88" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O88" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="8" t="n"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
@@ -23526,7 +23502,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -23540,13 +23516,13 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>1545</v>
+        <v>2175</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
@@ -23564,20 +23540,22 @@
         </is>
       </c>
       <c r="I89" s="8" t="n">
-        <v>484</v>
+        <v>814</v>
       </c>
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
+      <c r="N89" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O89" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="8" t="n"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr">
@@ -23599,7 +23577,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23591,7 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>2185</v>
+        <v>1500</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>2</v>
@@ -23628,7 +23606,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -23636,26 +23614,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I90" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
-      <c r="N90" s="8" t="n"/>
+      <c r="N90" s="8" t="n">
+        <v>21816</v>
+      </c>
       <c r="O90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="8" t="n"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23672,7 +23650,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -23686,7 +23664,7 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>1565</v>
+        <v>1450</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>1</v>
@@ -23701,17 +23679,15 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Old Drill Hall, Bristol, BS2</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I91" s="8" t="n">
-        <v>484</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
@@ -23723,12 +23699,12 @@
       <c r="P91" s="8" t="n"/>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr"/>
@@ -23745,7 +23721,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>c847859d6a4555381482a51e75495800df35917d</t>
         </is>
       </c>
     </row>
@@ -23759,7 +23735,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>2280</v>
+        <v>2115</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>2</v>
@@ -23783,20 +23759,22 @@
         </is>
       </c>
       <c r="I92" s="8" t="n">
-        <v>885</v>
+        <v>823</v>
       </c>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
-      <c r="N92" s="8" t="n"/>
+      <c r="N92" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="8" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R92" s="8" t="inlineStr">
@@ -23818,7 +23796,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -23832,7 +23810,7 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>1630</v>
+        <v>1660</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>1</v>
@@ -23847,7 +23825,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -23856,25 +23834,27 @@
         </is>
       </c>
       <c r="I93" s="8" t="n">
-        <v>546</v>
+        <v>486</v>
       </c>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
       <c r="M93" s="8" t="n"/>
-      <c r="N93" s="8" t="n"/>
+      <c r="N93" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O93" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="8" t="n"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S93" s="9" t="inlineStr"/>
@@ -23891,7 +23871,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -23905,13 +23885,13 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1650</v>
+        <v>1915</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
@@ -23920,7 +23900,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>Broad Weir, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -23928,24 +23908,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I94" s="8" t="n"/>
+      <c r="I94" s="8" t="n">
+        <v>746</v>
+      </c>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
-      <c r="N94" s="8" t="n"/>
+      <c r="N94" s="8" t="n">
+        <v>21680</v>
+      </c>
       <c r="O94" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="8" t="n"/>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S94" s="9" t="inlineStr"/>
@@ -23962,7 +23946,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -23976,7 +23960,7 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>1625</v>
+        <v>1150</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>1</v>
@@ -23991,34 +23975,34 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I95" s="8" t="n">
-        <v>485</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="n"/>
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
       <c r="M95" s="8" t="n"/>
-      <c r="N95" s="8" t="n"/>
+      <c r="N95" s="8" t="n">
+        <v>6872</v>
+      </c>
       <c r="O95" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="8" t="n"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S95" s="9" t="inlineStr"/>
@@ -24035,7 +24019,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -24049,13 +24033,13 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>1630</v>
+        <v>2450</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
@@ -24064,7 +24048,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -24072,26 +24056,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I96" s="8" t="n">
-        <v>517</v>
-      </c>
+      <c r="I96" s="8" t="n"/>
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
-      <c r="N96" s="8" t="n"/>
+      <c r="N96" s="8" t="n">
+        <v>21788</v>
+      </c>
       <c r="O96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="8" t="n"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S96" s="9" t="inlineStr"/>
@@ -24108,7 +24092,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -24122,7 +24106,7 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>2145</v>
+        <v>1700</v>
       </c>
       <c r="D97" s="8" t="n">
         <v>2</v>
@@ -24137,7 +24121,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Crescent</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -24145,26 +24129,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I97" s="8" t="n">
-        <v>713</v>
-      </c>
+      <c r="I97" s="8" t="n"/>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
-      <c r="N97" s="8" t="n"/>
+      <c r="N97" s="8" t="n">
+        <v>16368</v>
+      </c>
       <c r="O97" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="8" t="n"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24181,7 +24165,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>6e6f162488026493723e3419801548c31fd0e534</t>
+          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
         </is>
       </c>
     </row>
@@ -24195,13 +24179,13 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>2175</v>
+        <v>1250</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
@@ -24210,7 +24194,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -24218,26 +24202,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="8" t="n">
-        <v>722</v>
-      </c>
+      <c r="I98" s="8" t="n"/>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
-      <c r="N98" s="8" t="n"/>
+      <c r="N98" s="8" t="n">
+        <v>21160</v>
+      </c>
       <c r="O98" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="8" t="n"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R98" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S98" s="9" t="inlineStr"/>
@@ -24254,7 +24238,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -24268,13 +24252,13 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
@@ -24283,34 +24267,34 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, BS1</t>
+          <t>Ratcliffe Court, Bristol, BS2</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="n">
-        <v>721</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
-      <c r="N99" s="8" t="n"/>
+      <c r="N99" s="8" t="n">
+        <v>20124</v>
+      </c>
       <c r="O99" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="8" t="n"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24327,7 +24311,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
+          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
         </is>
       </c>
     </row>
@@ -24341,13 +24325,13 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>2155</v>
+        <v>1200</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
@@ -24356,7 +24340,7 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Buchanans Wharf North, Ferry Street, BS1</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -24365,25 +24349,27 @@
         </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>697</v>
+        <v>431</v>
       </c>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
-      <c r="N100" s="8" t="n"/>
+      <c r="N100" s="8" t="n">
+        <v>20896</v>
+      </c>
       <c r="O100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24400,7 +24386,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
+          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
         </is>
       </c>
     </row>
@@ -24429,12 +24415,12 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter Apts, Bristol, BS2</t>
+          <t>Eclipse, Bristol</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I101" s="8" t="n"/>
@@ -24442,19 +24428,21 @@
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
-      <c r="N101" s="8" t="n"/>
+      <c r="N101" s="8" t="n">
+        <v>22196</v>
+      </c>
       <c r="O101" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="8" t="n"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24471,7 +24459,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
+          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
         </is>
       </c>
     </row>
@@ -24485,13 +24473,13 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
@@ -24500,7 +24488,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24508,24 +24496,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="8" t="n"/>
+      <c r="I102" s="8" t="n">
+        <v>796</v>
+      </c>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
-      <c r="N102" s="8" t="n"/>
+      <c r="N102" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="8" t="n"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24542,7 +24534,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
         </is>
       </c>
     </row>
@@ -24556,13 +24548,13 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1900</v>
+        <v>1640</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
@@ -24571,7 +24563,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24579,24 +24571,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I103" s="8" t="n"/>
+      <c r="I103" s="8" t="n">
+        <v>494</v>
+      </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
-      <c r="N103" s="8" t="n"/>
+      <c r="N103" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="8" t="n"/>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24613,7 +24609,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
         </is>
       </c>
     </row>
@@ -24627,10 +24623,10 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1700</v>
+        <v>1250</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
         <v>1</v>
@@ -24642,7 +24638,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
@@ -24656,7 +24652,7 @@
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n">
-        <v>21096</v>
+        <v>21160</v>
       </c>
       <c r="O104" s="8" t="n">
         <v>0</v>
@@ -24664,12 +24660,12 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24686,7 +24682,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
+          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
         </is>
       </c>
     </row>
@@ -24700,13 +24696,13 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>2500</v>
+        <v>1640</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -24715,7 +24711,7 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>Liberty Gardens, Caledonian Road, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
@@ -24724,25 +24720,27 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>1238</v>
+        <v>495</v>
       </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
-      <c r="N105" s="8" t="n"/>
+      <c r="N105" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O105" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="8" t="n"/>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S105" s="9" t="inlineStr"/>
@@ -24759,7 +24757,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
+          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
         </is>
       </c>
     </row>
@@ -24773,13 +24771,13 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1250</v>
+        <v>1890</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
@@ -24788,32 +24786,36 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>St Johns Lane, Bedminster</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I106" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="n">
+        <v>702</v>
+      </c>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n"/>
+      <c r="N106" s="8" t="n">
+        <v>21680</v>
+      </c>
       <c r="O106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24830,7 +24832,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
+          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
         </is>
       </c>
     </row>
@@ -24844,13 +24846,13 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1600</v>
+        <v>1635</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -24859,7 +24861,7 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
@@ -24868,25 +24870,27 @@
         </is>
       </c>
       <c r="I107" s="8" t="n">
-        <v>624</v>
+        <v>517</v>
       </c>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
-      <c r="N107" s="8" t="n"/>
+      <c r="N107" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O107" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S107" s="9" t="inlineStr"/>
@@ -24903,7 +24907,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
+          <t>acf18902969821dd75405f7916c6929252fb214a</t>
         </is>
       </c>
     </row>
@@ -24917,13 +24921,13 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>1540</v>
+        <v>1855</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
@@ -24932,7 +24936,7 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
@@ -24941,14 +24945,14 @@
         </is>
       </c>
       <c r="I108" s="8" t="n">
-        <v>451</v>
+        <v>607</v>
       </c>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -24956,12 +24960,12 @@
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -24978,7 +24982,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
+          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
         </is>
       </c>
     </row>
@@ -24992,7 +24996,7 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>2095</v>
+        <v>2180</v>
       </c>
       <c r="D109" s="8" t="n">
         <v>2</v>
@@ -25016,7 +25020,7 @@
         </is>
       </c>
       <c r="I109" s="8" t="n">
-        <v>705</v>
+        <v>767</v>
       </c>
       <c r="J109" s="8" t="n"/>
       <c r="K109" s="8" t="n"/>
@@ -25031,7 +25035,7 @@
       <c r="P109" s="8" t="n"/>
       <c r="Q109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R109" s="8" t="inlineStr">
@@ -25053,7 +25057,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
+          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
         </is>
       </c>
     </row>
@@ -25067,13 +25071,13 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>1660</v>
+        <v>2090</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
@@ -25082,7 +25086,7 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -25091,27 +25095,25 @@
         </is>
       </c>
       <c r="I110" s="8" t="n">
-        <v>486</v>
+        <v>705</v>
       </c>
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
-      <c r="N110" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N110" s="8" t="n"/>
       <c r="O110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="8" t="n"/>
       <c r="Q110" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R110" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S110" s="9" t="inlineStr"/>
@@ -25128,7 +25130,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>f37bb95403b6c94c61951f944bce88c63865f963</t>
         </is>
       </c>
     </row>
@@ -25142,13 +25144,13 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>2175</v>
+        <v>1635</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
@@ -25157,7 +25159,7 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
@@ -25166,27 +25168,25 @@
         </is>
       </c>
       <c r="I111" s="8" t="n">
-        <v>814</v>
+        <v>546</v>
       </c>
       <c r="J111" s="8" t="n"/>
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
-      <c r="N111" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N111" s="8" t="n"/>
       <c r="O111" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="8" t="n"/>
       <c r="Q111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R111" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S111" s="9" t="inlineStr"/>
@@ -25203,7 +25203,7 @@
       <c r="V111" s="7" t="inlineStr"/>
       <c r="W111" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>36d0812581d3df99e6949e941acc69f0f62aaaf1</t>
         </is>
       </c>
     </row>
@@ -25217,13 +25217,13 @@
         </is>
       </c>
       <c r="C112" s="17" t="n">
-        <v>1500</v>
+        <v>1545</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
@@ -25240,26 +25240,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I112" s="8" t="n"/>
+      <c r="I112" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
-      <c r="N112" s="8" t="n">
-        <v>21816</v>
-      </c>
+      <c r="N112" s="8" t="n"/>
       <c r="O112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="8" t="n"/>
       <c r="Q112" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R112" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S112" s="9" t="inlineStr"/>
@@ -25276,7 +25276,7 @@
       <c r="V112" s="7" t="inlineStr"/>
       <c r="W112" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
         </is>
       </c>
     </row>
@@ -25290,13 +25290,13 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>1450</v>
+        <v>2280</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
@@ -25305,15 +25305,17 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>The Old Drill Hall, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="n">
+        <v>885</v>
+      </c>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
@@ -25325,12 +25327,12 @@
       <c r="P113" s="8" t="n"/>
       <c r="Q113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R113" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S113" s="9" t="inlineStr"/>
@@ -25347,7 +25349,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>c847859d6a4555381482a51e75495800df35917d</t>
+          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
         </is>
       </c>
     </row>
@@ -25385,22 +25387,20 @@
         </is>
       </c>
       <c r="I114" s="8" t="n">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="J114" s="8" t="n"/>
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
-      <c r="N114" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N114" s="8" t="n"/>
       <c r="O114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="8" t="n"/>
       <c r="Q114" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R114" s="8" t="inlineStr">
@@ -25422,7 +25422,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
+          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
         </is>
       </c>
     </row>
@@ -25436,13 +25436,13 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>2115</v>
+        <v>1630</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
@@ -25460,22 +25460,20 @@
         </is>
       </c>
       <c r="I115" s="8" t="n">
-        <v>823</v>
+        <v>517</v>
       </c>
       <c r="J115" s="8" t="n"/>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
-      <c r="N115" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N115" s="8" t="n"/>
       <c r="O115" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="8" t="n"/>
       <c r="Q115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R115" s="8" t="inlineStr">
@@ -25497,7 +25495,7 @@
       <c r="V115" s="7" t="inlineStr"/>
       <c r="W115" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
         </is>
       </c>
     </row>
@@ -25511,13 +25509,13 @@
         </is>
       </c>
       <c r="C116" s="17" t="n">
-        <v>1660</v>
+        <v>2145</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
@@ -25526,7 +25524,7 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
@@ -25535,27 +25533,25 @@
         </is>
       </c>
       <c r="I116" s="8" t="n">
-        <v>486</v>
+        <v>713</v>
       </c>
       <c r="J116" s="8" t="n"/>
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
-      <c r="N116" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N116" s="8" t="n"/>
       <c r="O116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="8" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R116" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S116" s="9" t="inlineStr"/>
@@ -25572,7 +25568,7 @@
       <c r="V116" s="7" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>6e6f162488026493723e3419801548c31fd0e534</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25582,7 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>1915</v>
+        <v>2155</v>
       </c>
       <c r="D117" s="8" t="n">
         <v>2</v>
@@ -25601,7 +25597,7 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
@@ -25610,27 +25606,25 @@
         </is>
       </c>
       <c r="I117" s="8" t="n">
-        <v>746</v>
+        <v>697</v>
       </c>
       <c r="J117" s="8" t="n"/>
       <c r="K117" s="8" t="n"/>
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
-      <c r="N117" s="8" t="n">
-        <v>21680</v>
-      </c>
+      <c r="N117" s="8" t="n"/>
       <c r="O117" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="8" t="n"/>
       <c r="Q117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R117" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S117" s="9" t="inlineStr"/>
@@ -25647,7 +25641,7 @@
       <c r="V117" s="7" t="inlineStr"/>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
         </is>
       </c>
     </row>
@@ -25661,10 +25655,10 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>1150</v>
+        <v>1700</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="8" t="n">
         <v>1</v>
@@ -25676,12 +25670,12 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I118" s="8" t="n"/>
@@ -25690,7 +25684,7 @@
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n">
-        <v>6872</v>
+        <v>21096</v>
       </c>
       <c r="O118" s="8" t="n">
         <v>0</v>
@@ -25698,12 +25692,12 @@
       <c r="P118" s="8" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R118" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S118" s="9" t="inlineStr"/>
@@ -25720,7 +25714,7 @@
       <c r="V118" s="7" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
         </is>
       </c>
     </row>
@@ -25734,10 +25728,10 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>2450</v>
+        <v>1600</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" s="8" t="n">
         <v>2</v>
@@ -25749,7 +25743,7 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Marsh House, Marsh Street, BS1</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -25757,26 +25751,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I119" s="8" t="n"/>
+      <c r="I119" s="8" t="n">
+        <v>624</v>
+      </c>
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
-      <c r="N119" s="8" t="n">
-        <v>21788</v>
-      </c>
+      <c r="N119" s="8" t="n"/>
       <c r="O119" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="8" t="n"/>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R119" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S119" s="9" t="inlineStr"/>
@@ -25793,7 +25787,7 @@
       <c r="V119" s="7" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
         </is>
       </c>
     </row>
@@ -25807,13 +25801,13 @@
         </is>
       </c>
       <c r="C120" s="17" t="n">
-        <v>1700</v>
+        <v>1540</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
@@ -25822,7 +25816,7 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>The Crescent</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
@@ -25830,13 +25824,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I120" s="8" t="n"/>
+      <c r="I120" s="8" t="n">
+        <v>451</v>
+      </c>
       <c r="J120" s="8" t="n"/>
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n">
-        <v>16368</v>
+        <v>20820</v>
       </c>
       <c r="O120" s="8" t="n">
         <v>0</v>
@@ -25844,12 +25840,12 @@
       <c r="P120" s="8" t="n"/>
       <c r="Q120" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R120" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S120" s="9" t="inlineStr"/>
@@ -25866,7 +25862,7 @@
       <c r="V120" s="7" t="inlineStr"/>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
+          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
         </is>
       </c>
     </row>
@@ -25880,13 +25876,13 @@
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1250</v>
+        <v>2095</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
@@ -25895,7 +25891,7 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
@@ -25903,13 +25899,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I121" s="8" t="n"/>
+      <c r="I121" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J121" s="8" t="n"/>
       <c r="K121" s="8" t="n"/>
       <c r="L121" s="8" t="n"/>
       <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n">
-        <v>21160</v>
+        <v>20820</v>
       </c>
       <c r="O121" s="8" t="n">
         <v>0</v>
@@ -25917,12 +25915,12 @@
       <c r="P121" s="8" t="n"/>
       <c r="Q121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R121" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S121" s="9" t="inlineStr"/>
@@ -25939,7 +25937,7 @@
       <c r="V121" s="7" t="inlineStr"/>
       <c r="W121" s="8" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
         </is>
       </c>
     </row>
@@ -25953,7 +25951,7 @@
         </is>
       </c>
       <c r="C122" s="17" t="n">
-        <v>1250</v>
+        <v>1630</v>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
@@ -25968,21 +25966,23 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter - City Centre</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I122" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="n">
+        <v>560</v>
+      </c>
       <c r="J122" s="8" t="n"/>
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
       <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n">
-        <v>21812</v>
+        <v>20820</v>
       </c>
       <c r="O122" s="8" t="n">
         <v>0</v>
@@ -25990,12 +25990,12 @@
       <c r="P122" s="8" t="n"/>
       <c r="Q122" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R122" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S122" s="9" t="inlineStr"/>
@@ -26012,7 +26012,7 @@
       <c r="V122" s="7" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr">
         <is>
-          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
+          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
         </is>
       </c>
     </row>
@@ -26026,13 +26026,13 @@
         </is>
       </c>
       <c r="C123" s="17" t="n">
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
@@ -26041,12 +26041,12 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+          <t>Kings Quarter - City Centre</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I123" s="8" t="n"/>
@@ -26055,7 +26055,7 @@
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n">
-        <v>17744</v>
+        <v>21812</v>
       </c>
       <c r="O123" s="8" t="n">
         <v>0</v>
@@ -26063,12 +26063,12 @@
       <c r="P123" s="8" t="n"/>
       <c r="Q123" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R123" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S123" s="9" t="inlineStr"/>
@@ -26085,7 +26085,7 @@
       <c r="V123" s="7" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr">
         <is>
-          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
         </is>
       </c>
     </row>
@@ -26099,13 +26099,13 @@
         </is>
       </c>
       <c r="C124" s="17" t="n">
-        <v>1375</v>
+        <v>1750</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
@@ -26127,19 +26127,21 @@
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
       <c r="M124" s="8" t="n"/>
-      <c r="N124" s="8" t="n"/>
+      <c r="N124" s="8" t="n">
+        <v>17744</v>
+      </c>
       <c r="O124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="8" t="n"/>
       <c r="Q124" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R124" s="8" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S124" s="9" t="inlineStr"/>
@@ -26156,7 +26158,7 @@
       <c r="V124" s="7" t="inlineStr"/>
       <c r="W124" s="8" t="inlineStr">
         <is>
-          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
+          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
         </is>
       </c>
     </row>
@@ -26170,7 +26172,7 @@
         </is>
       </c>
       <c r="C125" s="17" t="n">
-        <v>1200</v>
+        <v>1375</v>
       </c>
       <c r="D125" s="8" t="n">
         <v>1</v>
@@ -26185,12 +26187,12 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I125" s="8" t="n"/>
@@ -26198,21 +26200,19 @@
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
       <c r="M125" s="8" t="n"/>
-      <c r="N125" s="8" t="n">
-        <v>8636</v>
-      </c>
+      <c r="N125" s="8" t="n"/>
       <c r="O125" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="8" t="n"/>
       <c r="Q125" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R125" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S125" s="9" t="inlineStr"/>
@@ -26229,7 +26229,7 @@
       <c r="V125" s="7" t="inlineStr"/>
       <c r="W125" s="8" t="inlineStr">
         <is>
-          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
+          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
         </is>
       </c>
     </row>
@@ -26243,7 +26243,7 @@
         </is>
       </c>
       <c r="C126" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D126" s="8" t="n">
         <v>1</v>
@@ -26258,12 +26258,12 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
+          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>BS13</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I126" s="8" t="n"/>
@@ -26272,7 +26272,7 @@
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n">
-        <v>4936</v>
+        <v>8636</v>
       </c>
       <c r="O126" s="8" t="n">
         <v>0</v>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="R126" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S126" s="9" t="inlineStr"/>
@@ -26302,7 +26302,7 @@
       <c r="V126" s="7" t="inlineStr"/>
       <c r="W126" s="8" t="inlineStr">
         <is>
-          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
+          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
         </is>
       </c>
     </row>
@@ -26331,12 +26331,12 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>Flat B, City Road, Bristol</t>
+          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS13</t>
         </is>
       </c>
       <c r="I127" s="8" t="n"/>
@@ -26345,7 +26345,7 @@
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n">
-        <v>20108</v>
+        <v>4936</v>
       </c>
       <c r="O127" s="8" t="n">
         <v>0</v>
@@ -26358,7 +26358,7 @@
       </c>
       <c r="R127" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S127" s="9" t="inlineStr"/>
@@ -26375,7 +26375,7 @@
       <c r="V127" s="7" t="inlineStr"/>
       <c r="W127" s="8" t="inlineStr">
         <is>
-          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
+          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
         </is>
       </c>
     </row>
@@ -26389,7 +26389,7 @@
         </is>
       </c>
       <c r="C128" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D128" s="8" t="n">
         <v>1</v>
@@ -26404,23 +26404,21 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Unity Street, BS1 5HH</t>
+          <t>Flat B, City Road, Bristol</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I128" s="8" t="n">
-        <v>452</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="n"/>
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="n"/>
       <c r="N128" s="8" t="n">
-        <v>20772</v>
+        <v>20108</v>
       </c>
       <c r="O128" s="8" t="n">
         <v>0</v>
@@ -26428,12 +26426,12 @@
       <c r="P128" s="8" t="n"/>
       <c r="Q128" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R128" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S128" s="9" t="inlineStr"/>
@@ -26450,7 +26448,7 @@
       <c r="V128" s="7" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
+          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26465,7 @@
         <v>1200</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="8" t="n">
         <v>1</v>
@@ -26479,21 +26477,23 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
+          <t>City Centre, Unity Street, BS1 5HH</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I129" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="n">
+        <v>452</v>
+      </c>
       <c r="J129" s="8" t="n"/>
       <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n">
-        <v>4160</v>
+        <v>20772</v>
       </c>
       <c r="O129" s="8" t="n">
         <v>0</v>
@@ -26506,7 +26506,7 @@
       </c>
       <c r="R129" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S129" s="9" t="inlineStr"/>
@@ -26523,7 +26523,7 @@
       <c r="V129" s="7" t="inlineStr"/>
       <c r="W129" s="8" t="inlineStr">
         <is>
-          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
+          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
         </is>
       </c>
     </row>
@@ -26537,10 +26537,10 @@
         </is>
       </c>
       <c r="C130" s="17" t="n">
-        <v>965</v>
+        <v>1200</v>
       </c>
       <c r="D130" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="8" t="n">
         <v>1</v>
@@ -26552,12 +26552,12 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>Boulevard View, Whitchurch Lane</t>
+          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I130" s="8" t="n"/>
@@ -26566,7 +26566,7 @@
       <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n">
-        <v>5764</v>
+        <v>4160</v>
       </c>
       <c r="O130" s="8" t="n">
         <v>0</v>
@@ -26579,7 +26579,7 @@
       </c>
       <c r="R130" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S130" s="9" t="inlineStr"/>
@@ -26596,7 +26596,7 @@
       <c r="V130" s="7" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
+          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26610,7 @@
         </is>
       </c>
       <c r="C131" s="17" t="n">
-        <v>1200</v>
+        <v>965</v>
       </c>
       <c r="D131" s="8" t="n">
         <v>1</v>
@@ -26625,23 +26625,21 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>Braggs Lane, Bristol</t>
+          <t>Boulevard View, Whitchurch Lane</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I131" s="8" t="n">
-        <v>409</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I131" s="8" t="n"/>
       <c r="J131" s="8" t="n"/>
       <c r="K131" s="8" t="n"/>
       <c r="L131" s="8" t="n"/>
       <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n">
-        <v>20360</v>
+        <v>5764</v>
       </c>
       <c r="O131" s="8" t="n">
         <v>0</v>
@@ -26654,7 +26652,7 @@
       </c>
       <c r="R131" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S131" s="9" t="inlineStr"/>
@@ -26671,7 +26669,7 @@
       <c r="V131" s="7" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr">
         <is>
-          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
+          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
         </is>
       </c>
     </row>
@@ -26700,7 +26698,7 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>Montague Court, Bristol</t>
+          <t>Braggs Lane, Bristol</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
@@ -26708,13 +26706,15 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I132" s="8" t="n"/>
+      <c r="I132" s="8" t="n">
+        <v>409</v>
+      </c>
       <c r="J132" s="8" t="n"/>
       <c r="K132" s="8" t="n"/>
       <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n">
-        <v>21632</v>
+        <v>20360</v>
       </c>
       <c r="O132" s="8" t="n">
         <v>0</v>
@@ -26727,7 +26727,7 @@
       </c>
       <c r="R132" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S132" s="9" t="inlineStr"/>
@@ -26744,7 +26744,7 @@
       <c r="V132" s="7" t="inlineStr"/>
       <c r="W132" s="8" t="inlineStr">
         <is>
-          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
+          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
         </is>
       </c>
     </row>
@@ -26758,7 +26758,7 @@
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D133" s="8" t="n">
         <v>1</v>
@@ -26773,23 +26773,21 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
+          <t>Montague Court, Bristol</t>
         </is>
       </c>
       <c r="H133" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I133" s="8" t="n">
-        <v>397</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I133" s="8" t="n"/>
       <c r="J133" s="8" t="n"/>
       <c r="K133" s="8" t="n"/>
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n">
-        <v>15212</v>
+        <v>21632</v>
       </c>
       <c r="O133" s="8" t="n">
         <v>0</v>
@@ -26797,12 +26795,12 @@
       <c r="P133" s="8" t="n"/>
       <c r="Q133" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R133" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S133" s="9" t="inlineStr"/>
@@ -26819,7 +26817,7 @@
       <c r="V133" s="7" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr">
         <is>
-          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
+          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
         </is>
       </c>
     </row>
@@ -26833,7 +26831,7 @@
         </is>
       </c>
       <c r="C134" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D134" s="8" t="n">
         <v>1</v>
@@ -26848,23 +26846,23 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>Barton Close, St. Annes Park, BS4</t>
+          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I134" s="8" t="n">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="J134" s="8" t="n"/>
       <c r="K134" s="8" t="n"/>
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n">
-        <v>5212</v>
+        <v>15212</v>
       </c>
       <c r="O134" s="8" t="n">
         <v>0</v>
@@ -26877,7 +26875,7 @@
       </c>
       <c r="R134" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S134" s="9" t="inlineStr"/>
@@ -26894,7 +26892,7 @@
       <c r="V134" s="7" t="inlineStr"/>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
+          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
         </is>
       </c>
     </row>
@@ -26923,21 +26921,23 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Barton Close, St. Annes Park, BS4</t>
         </is>
       </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I135" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="n">
+        <v>441</v>
+      </c>
       <c r="J135" s="8" t="n"/>
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n">
-        <v>7112</v>
+        <v>5212</v>
       </c>
       <c r="O135" s="8" t="n">
         <v>0</v>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="R135" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S135" s="9" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       <c r="V135" s="7" t="inlineStr"/>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
+          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
         </is>
       </c>
     </row>
@@ -26996,23 +26996,21 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Chapel Street, St Philips, Bristol, BS2</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="n">
-        <v>549</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="n"/>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n">
-        <v>11732</v>
+        <v>7112</v>
       </c>
       <c r="O136" s="8" t="n">
         <v>0</v>
@@ -27025,7 +27023,7 @@
       </c>
       <c r="R136" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S136" s="9" t="inlineStr"/>
@@ -27042,7 +27040,7 @@
       <c r="V136" s="7" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
+          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
         </is>
       </c>
     </row>
@@ -27056,7 +27054,7 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>1</v>
@@ -27071,23 +27069,23 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
+          <t>Chapel Street, St Philips, Bristol, BS2</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I137" s="8" t="n">
-        <v>211</v>
+        <v>549</v>
       </c>
       <c r="J137" s="8" t="n"/>
       <c r="K137" s="8" t="n"/>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n">
-        <v>14596</v>
+        <v>11732</v>
       </c>
       <c r="O137" s="8" t="n">
         <v>0</v>
@@ -27095,12 +27093,12 @@
       <c r="P137" s="8" t="n"/>
       <c r="Q137" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R137" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S137" s="9" t="inlineStr"/>
@@ -27117,7 +27115,7 @@
       <c r="V137" s="7" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
+          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27129,7 @@
         </is>
       </c>
       <c r="C138" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D138" s="8" t="n">
         <v>1</v>
@@ -27146,21 +27144,23 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
+          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
-        </is>
-      </c>
-      <c r="I138" s="8" t="n"/>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="n">
+        <v>211</v>
+      </c>
       <c r="J138" s="8" t="n"/>
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
       <c r="M138" s="8" t="n"/>
       <c r="N138" s="8" t="n">
-        <v>5316</v>
+        <v>14596</v>
       </c>
       <c r="O138" s="8" t="n">
         <v>0</v>
@@ -27168,12 +27168,12 @@
       <c r="P138" s="8" t="n"/>
       <c r="Q138" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R138" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S138" s="9" t="inlineStr"/>
@@ -27190,7 +27190,7 @@
       <c r="V138" s="7" t="inlineStr"/>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
+          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
         </is>
       </c>
     </row>
@@ -27219,12 +27219,12 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I139" s="8" t="n"/>
@@ -27233,7 +27233,7 @@
       <c r="L139" s="8" t="n"/>
       <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n">
-        <v>7112</v>
+        <v>5316</v>
       </c>
       <c r="O139" s="8" t="n">
         <v>0</v>
@@ -27246,7 +27246,7 @@
       </c>
       <c r="R139" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S139" s="9" t="inlineStr"/>
@@ -27263,7 +27263,7 @@
       <c r="V139" s="7" t="inlineStr"/>
       <c r="W139" s="8" t="inlineStr">
         <is>
-          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
+          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
         </is>
       </c>
     </row>
@@ -27277,7 +27277,7 @@
         </is>
       </c>
       <c r="C140" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D140" s="8" t="n">
         <v>1</v>
@@ -27292,7 +27292,7 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>Seymour Road, Bristol, BS5</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
@@ -27300,15 +27300,13 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I140" s="8" t="n">
-        <v>484</v>
-      </c>
+      <c r="I140" s="8" t="n"/>
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n">
-        <v>17164</v>
+        <v>7112</v>
       </c>
       <c r="O140" s="8" t="n">
         <v>0</v>
@@ -27316,12 +27314,12 @@
       <c r="P140" s="8" t="n"/>
       <c r="Q140" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R140" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S140" s="9" t="inlineStr"/>
@@ -27338,7 +27336,7 @@
       <c r="V140" s="7" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
+          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
         </is>
       </c>
     </row>
@@ -27367,21 +27365,23 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>Pinkhams Twist, Bristol</t>
+          <t>Seymour Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I141" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J141" s="8" t="n"/>
       <c r="K141" s="8" t="n"/>
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n">
-        <v>4276</v>
+        <v>17164</v>
       </c>
       <c r="O141" s="8" t="n">
         <v>0</v>
@@ -27389,12 +27389,12 @@
       <c r="P141" s="8" t="n"/>
       <c r="Q141" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R141" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Whitchurch</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S141" s="9" t="inlineStr"/>
@@ -27411,7 +27411,7 @@
       <c r="V141" s="7" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
+          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
         </is>
       </c>
     </row>
@@ -27425,7 +27425,7 @@
         </is>
       </c>
       <c r="C142" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D142" s="8" t="n">
         <v>1</v>
@@ -27435,17 +27435,17 @@
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Alexandra Park, Redland, Bristol, BS6</t>
+          <t>Pinkhams Twist, Bristol</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS14</t>
         </is>
       </c>
       <c r="I142" s="8" t="n"/>
@@ -27454,7 +27454,7 @@
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n">
-        <v>12812</v>
+        <v>4276</v>
       </c>
       <c r="O142" s="8" t="n">
         <v>0</v>
@@ -27467,7 +27467,7 @@
       </c>
       <c r="R142" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Hunters, Whitchurch</t>
         </is>
       </c>
       <c r="S142" s="9" t="inlineStr"/>
@@ -27484,7 +27484,7 @@
       <c r="V142" s="7" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
+          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,7 @@
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D143" s="8" t="n">
         <v>1</v>
@@ -27508,17 +27508,17 @@
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
+          <t>Alexandra Park, Redland, Bristol, BS6</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I143" s="8" t="n"/>
@@ -27527,7 +27527,7 @@
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n">
-        <v>18020</v>
+        <v>12812</v>
       </c>
       <c r="O143" s="8" t="n">
         <v>0</v>
@@ -27540,7 +27540,7 @@
       </c>
       <c r="R143" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S143" s="9" t="inlineStr"/>
@@ -27557,7 +27557,7 @@
       <c r="V143" s="7" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
-          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
+          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
         </is>
       </c>
     </row>
@@ -27571,10 +27571,10 @@
         </is>
       </c>
       <c r="C144" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="8" t="n">
         <v>1</v>
@@ -27586,23 +27586,21 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Bristol, BS5</t>
+          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I144" s="8" t="n">
-        <v>3057</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="n"/>
       <c r="J144" s="8" t="n"/>
       <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
       <c r="M144" s="8" t="n"/>
       <c r="N144" s="8" t="n">
-        <v>11864</v>
+        <v>18020</v>
       </c>
       <c r="O144" s="8" t="n">
         <v>0</v>
@@ -27610,12 +27608,12 @@
       <c r="P144" s="8" t="n"/>
       <c r="Q144" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R144" s="8" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S144" s="9" t="inlineStr"/>
@@ -27632,7 +27630,7 @@
       <c r="V144" s="7" t="inlineStr"/>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
+          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
         </is>
       </c>
     </row>
@@ -27646,10 +27644,10 @@
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>995</v>
+        <v>1150</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="8" t="n">
         <v>1</v>
@@ -27661,21 +27659,23 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>Two Mile Hill Road, Kingswood, Bristol</t>
+          <t>Church Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>BS15</t>
-        </is>
-      </c>
-      <c r="I145" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="n">
+        <v>3057</v>
+      </c>
       <c r="J145" s="8" t="n"/>
       <c r="K145" s="8" t="n"/>
       <c r="L145" s="8" t="n"/>
       <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n">
-        <v>5116</v>
+        <v>11864</v>
       </c>
       <c r="O145" s="8" t="n">
         <v>0</v>
@@ -27683,12 +27683,12 @@
       <c r="P145" s="8" t="n"/>
       <c r="Q145" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R145" s="8" t="inlineStr">
         <is>
-          <t>TLS Estate Agents, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S145" s="9" t="inlineStr"/>
@@ -27705,7 +27705,7 @@
       <c r="V145" s="7" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
+          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
         </is>
       </c>
     </row>
@@ -27719,7 +27719,7 @@
         </is>
       </c>
       <c r="C146" s="17" t="n">
-        <v>1100</v>
+        <v>995</v>
       </c>
       <c r="D146" s="8" t="n">
         <v>1</v>
@@ -27729,17 +27729,17 @@
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>Robertson Drive, St Annes Park</t>
+          <t>Two Mile Hill Road, Kingswood, Bristol</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS15</t>
         </is>
       </c>
       <c r="I146" s="8" t="n"/>
@@ -27748,7 +27748,7 @@
       <c r="L146" s="8" t="n"/>
       <c r="M146" s="8" t="n"/>
       <c r="N146" s="8" t="n">
-        <v>4252</v>
+        <v>5116</v>
       </c>
       <c r="O146" s="8" t="n">
         <v>0</v>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="R146" s="8" t="inlineStr">
         <is>
-          <t>D W Smith &amp; Company, Hanham</t>
+          <t>TLS Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S146" s="9" t="inlineStr"/>
@@ -27778,7 +27778,7 @@
       <c r="V146" s="7" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
+          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
         </is>
       </c>
     </row>
@@ -27792,7 +27792,7 @@
         </is>
       </c>
       <c r="C147" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D147" s="8" t="n">
         <v>1</v>
@@ -27802,12 +27802,12 @@
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
+          <t>Robertson Drive, St Annes Park</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
@@ -27815,15 +27815,13 @@
           <t>BS4</t>
         </is>
       </c>
-      <c r="I147" s="8" t="n">
-        <v>527</v>
-      </c>
+      <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n">
-        <v>5548</v>
+        <v>4252</v>
       </c>
       <c r="O147" s="8" t="n">
         <v>0</v>
@@ -27831,12 +27829,12 @@
       <c r="P147" s="8" t="n"/>
       <c r="Q147" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R147" s="8" t="inlineStr">
         <is>
-          <t>Sheedy &amp; Co, Covering Bristol</t>
+          <t>D W Smith &amp; Company, Hanham</t>
         </is>
       </c>
       <c r="S147" s="9" t="inlineStr"/>
@@ -27853,7 +27851,7 @@
       <c r="V147" s="7" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
+          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
         </is>
       </c>
     </row>
@@ -27867,7 +27865,7 @@
         </is>
       </c>
       <c r="C148" s="17" t="n">
-        <v>1195</v>
+        <v>1150</v>
       </c>
       <c r="D148" s="8" t="n">
         <v>1</v>
@@ -27882,23 +27880,23 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I148" s="8" t="n">
-        <v>409</v>
+        <v>527</v>
       </c>
       <c r="J148" s="8" t="n"/>
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
       <c r="N148" s="8" t="n">
-        <v>10420</v>
+        <v>5548</v>
       </c>
       <c r="O148" s="8" t="n">
         <v>0</v>
@@ -27906,12 +27904,12 @@
       <c r="P148" s="8" t="n"/>
       <c r="Q148" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R148" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>Sheedy &amp; Co, Covering Bristol</t>
         </is>
       </c>
       <c r="S148" s="9" t="inlineStr"/>
@@ -27928,7 +27926,7 @@
       <c r="V148" s="7" t="inlineStr"/>
       <c r="W148" s="8" t="inlineStr">
         <is>
-          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
+          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
         </is>
       </c>
     </row>
@@ -27942,7 +27940,7 @@
         </is>
       </c>
       <c r="C149" s="17" t="n">
-        <v>850</v>
+        <v>1195</v>
       </c>
       <c r="D149" s="8" t="n">
         <v>1</v>
@@ -27966,7 +27964,7 @@
         </is>
       </c>
       <c r="I149" s="8" t="n">
-        <v>248</v>
+        <v>409</v>
       </c>
       <c r="J149" s="8" t="n"/>
       <c r="K149" s="8" t="n"/>
@@ -28003,7 +28001,7 @@
       <c r="V149" s="7" t="inlineStr"/>
       <c r="W149" s="8" t="inlineStr">
         <is>
-          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
+          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
         </is>
       </c>
     </row>
@@ -28017,13 +28015,13 @@
         </is>
       </c>
       <c r="C150" s="17" t="n">
-        <v>1600</v>
+        <v>850</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
@@ -28032,21 +28030,23 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>Central Quay North</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I150" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="n">
+        <v>248</v>
+      </c>
       <c r="J150" s="8" t="n"/>
       <c r="K150" s="8" t="n"/>
       <c r="L150" s="8" t="n"/>
       <c r="M150" s="8" t="n"/>
       <c r="N150" s="8" t="n">
-        <v>20792</v>
+        <v>10420</v>
       </c>
       <c r="O150" s="8" t="n">
         <v>0</v>
@@ -28054,12 +28054,12 @@
       <c r="P150" s="8" t="n"/>
       <c r="Q150" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R150" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S150" s="9" t="inlineStr"/>
@@ -28076,7 +28076,7 @@
       <c r="V150" s="7" t="inlineStr"/>
       <c r="W150" s="8" t="inlineStr">
         <is>
-          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
         </is>
       </c>
     </row>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol</t>
+          <t>Central Quay North</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
@@ -28118,7 +28118,9 @@
       <c r="K151" s="8" t="n"/>
       <c r="L151" s="8" t="n"/>
       <c r="M151" s="8" t="n"/>
-      <c r="N151" s="8" t="n"/>
+      <c r="N151" s="8" t="n">
+        <v>20792</v>
+      </c>
       <c r="O151" s="8" t="n">
         <v>0</v>
       </c>
@@ -28130,7 +28132,7 @@
       </c>
       <c r="R151" s="8" t="inlineStr">
         <is>
-          <t>Stonebridge Shaw, Portishead</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S151" s="9" t="inlineStr"/>
@@ -28147,7 +28149,7 @@
       <c r="V151" s="7" t="inlineStr"/>
       <c r="W151" s="8" t="inlineStr">
         <is>
-          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
         </is>
       </c>
     </row>
@@ -28161,13 +28163,13 @@
         </is>
       </c>
       <c r="C152" s="17" t="n">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="D152" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
@@ -28176,12 +28178,12 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>St Michaels Hill Ref 708</t>
+          <t>Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I152" s="8" t="n"/>
@@ -28189,21 +28191,19 @@
       <c r="K152" s="8" t="n"/>
       <c r="L152" s="8" t="n"/>
       <c r="M152" s="8" t="n"/>
-      <c r="N152" s="8" t="n">
-        <v>19512</v>
-      </c>
+      <c r="N152" s="8" t="n"/>
       <c r="O152" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="8" t="n"/>
       <c r="Q152" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R152" s="8" t="inlineStr">
         <is>
-          <t>Jackson Property Management Ltd, Bristol</t>
+          <t>Stonebridge Shaw, Portishead</t>
         </is>
       </c>
       <c r="S152" s="9" t="inlineStr"/>
@@ -28220,7 +28220,7 @@
       <c r="V152" s="7" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
         </is>
       </c>
     </row>
@@ -28234,7 +28234,7 @@
         </is>
       </c>
       <c r="C153" s="17" t="n">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="D153" s="8" t="n">
         <v>1</v>
@@ -28249,12 +28249,12 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+          <t>St Michaels Hill Ref 708</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I153" s="8" t="n"/>
@@ -28263,7 +28263,7 @@
       <c r="L153" s="8" t="n"/>
       <c r="M153" s="8" t="n"/>
       <c r="N153" s="8" t="n">
-        <v>2652</v>
+        <v>19512</v>
       </c>
       <c r="O153" s="8" t="n">
         <v>0</v>
@@ -28271,12 +28271,12 @@
       <c r="P153" s="8" t="n"/>
       <c r="Q153" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R153" s="8" t="inlineStr">
         <is>
-          <t>Millennium Lettings &amp; Management, Bristol</t>
+          <t>Jackson Property Management Ltd, Bristol</t>
         </is>
       </c>
       <c r="S153" s="9" t="inlineStr"/>
@@ -28293,7 +28293,7 @@
       <c r="V153" s="7" t="inlineStr"/>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
         </is>
       </c>
     </row>
@@ -28307,7 +28307,7 @@
         </is>
       </c>
       <c r="C154" s="17" t="n">
-        <v>1200</v>
+        <v>1095</v>
       </c>
       <c r="D154" s="8" t="n">
         <v>1</v>
@@ -28322,23 +28322,21 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>Old Market, Verdigris, BS2 0AF</t>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I154" s="8" t="n">
-        <v>388</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="n"/>
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
       <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n">
-        <v>21220</v>
+        <v>2652</v>
       </c>
       <c r="O154" s="8" t="n">
         <v>0</v>
@@ -28346,12 +28344,12 @@
       <c r="P154" s="8" t="n"/>
       <c r="Q154" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R154" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
         </is>
       </c>
       <c r="S154" s="9" t="inlineStr"/>
@@ -28368,74 +28366,89 @@
       <c r="V154" s="7" t="inlineStr"/>
       <c r="W154" s="8" t="inlineStr">
         <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I155" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J155" s="8" t="n"/>
+      <c r="K155" s="8" t="n"/>
+      <c r="L155" s="8" t="n"/>
+      <c r="M155" s="8" t="n"/>
+      <c r="N155" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="8" t="n"/>
+      <c r="Q155" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R155" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S155" s="9" t="inlineStr"/>
+      <c r="T155" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V155" s="7" t="inlineStr"/>
+      <c r="W155" s="8" t="inlineStr">
+        <is>
           <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="7" t="n"/>
-      <c r="C155" s="18" t="n">
-        <v>800</v>
-      </c>
-      <c r="D155" t="n">
-        <v>2</v>
-      </c>
-      <c r="E155" t="n">
-        <v>1</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>LL11</t>
-        </is>
-      </c>
-      <c r="N155" t="n">
-        <v>448</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S155" s="7" t="inlineStr"/>
-      <c r="T155" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V155" s="7" t="inlineStr"/>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="7" t="n"/>
       <c r="C156" s="18" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D156" t="n">
         <v>2</v>
@@ -28450,28 +28463,28 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>328</v>
+        <v>448</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S156" s="7" t="inlineStr"/>
@@ -28488,17 +28501,17 @@
       <c r="V156" s="7" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
-          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="7" t="n"/>
       <c r="C157" s="18" t="n">
-        <v>625</v>
+        <v>900</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -28510,28 +28523,28 @@
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Field View, Mancot, Deeside, CH5 2EY</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>824</v>
+        <v>328</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Habodel Property Services Ltd, Doncaster</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S157" s="7" t="inlineStr"/>
@@ -28548,50 +28561,50 @@
       <c r="V157" s="7" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
-          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="7" t="n"/>
       <c r="C158" s="18" t="n">
-        <v>795</v>
+        <v>625</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Cilcain, The Square, CH7</t>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Williams Estates, Rhuddlan</t>
+          <t>Habodel Property Services Ltd, Doncaster</t>
         </is>
       </c>
       <c r="S158" s="7" t="inlineStr"/>
@@ -28608,14 +28621,14 @@
       <c r="V158" s="7" t="inlineStr"/>
       <c r="W158" t="inlineStr">
         <is>
-          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7" t="n"/>
       <c r="C159" s="18" t="n">
-        <v>950</v>
+        <v>795</v>
       </c>
       <c r="D159" t="n">
         <v>2</v>
@@ -28630,28 +28643,28 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
+          <t>Cilcain, The Square, CH7</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Williams Estates, Rhuddlan</t>
         </is>
       </c>
       <c r="S159" s="7" t="inlineStr"/>
@@ -28668,14 +28681,14 @@
       <c r="V159" s="7" t="inlineStr"/>
       <c r="W159" t="inlineStr">
         <is>
-          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7" t="n"/>
       <c r="C160" s="18" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="D160" t="n">
         <v>2</v>
@@ -28685,36 +28698,33 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Hill Top Close, Ewloe, CH5</t>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>721</v>
+          <t>CH8</t>
+        </is>
       </c>
       <c r="N160" t="n">
-        <v>472</v>
+        <v>56</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Reades, Hawarden Lettings</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S160" s="7" t="inlineStr"/>
@@ -28731,29 +28741,29 @@
       <c r="V160" s="7" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
-          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7" t="n"/>
       <c r="C161" s="18" t="n">
-        <v>650</v>
+        <v>925</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
         <v>1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Chester Road East, Shotton, Deeside</t>
+          <t>Hill Top Close, Ewloe, CH5</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -28762,10 +28772,10 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>474</v>
+        <v>721</v>
       </c>
       <c r="N161" t="n">
-        <v>2016</v>
+        <v>472</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -28777,7 +28787,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Reades, Hawarden Lettings</t>
         </is>
       </c>
       <c r="S161" s="7" t="inlineStr"/>
@@ -28794,38 +28804,41 @@
       <c r="V161" s="7" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
-          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7" t="n"/>
       <c r="C162" s="18" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+          <t>Chester Road East, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>LL11</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>474</v>
       </c>
       <c r="N162" t="n">
-        <v>1300</v>
+        <v>2016</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -28837,7 +28850,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S162" s="7" t="inlineStr"/>
@@ -28854,14 +28867,14 @@
       <c r="V162" s="7" t="inlineStr"/>
       <c r="W162" t="inlineStr">
         <is>
-          <t>40274ada7dfa710e5054184216178477a704016c</t>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="7" t="n"/>
       <c r="C163" s="18" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="D163" t="n">
         <v>2</v>
@@ -28871,21 +28884,21 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>936</v>
+        <v>1300</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -28897,7 +28910,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S163" s="7" t="inlineStr"/>
@@ -28914,7 +28927,7 @@
       <c r="V163" s="7" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
-          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
         </is>
       </c>
     </row>
@@ -28931,33 +28944,33 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>9 Park Road, Ruthin</t>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>LL15</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>576</v>
+        <v>936</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Ruthin</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S164" s="7" t="inlineStr"/>
@@ -28974,14 +28987,14 @@
       <c r="V164" s="7" t="inlineStr"/>
       <c r="W164" t="inlineStr">
         <is>
-          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="7" t="n"/>
       <c r="C165" s="18" t="n">
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D165" t="n">
         <v>2</v>
@@ -28996,19 +29009,16 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Gladstone Street, Mold</t>
+          <t>9 Park Road, Ruthin</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
-      </c>
-      <c r="I165" t="n">
-        <v>905</v>
+          <t>LL15</t>
+        </is>
       </c>
       <c r="N165" t="n">
-        <v>1356</v>
+        <v>576</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -29020,7 +29030,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
         </is>
       </c>
       <c r="S165" s="7" t="inlineStr"/>
@@ -29037,14 +29047,14 @@
       <c r="V165" s="7" t="inlineStr"/>
       <c r="W165" t="inlineStr">
         <is>
-          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="7" t="n"/>
       <c r="C166" s="18" t="n">
-        <v>1200</v>
+        <v>795</v>
       </c>
       <c r="D166" t="n">
         <v>2</v>
@@ -29054,24 +29064,24 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>Llwyn Dinas Fechan, St. Asaph</t>
+          <t>Gladstone Street, Mold</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>710</v>
+        <v>905</v>
       </c>
       <c r="N166" t="n">
-        <v>248</v>
+        <v>1356</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -29083,7 +29093,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S166" s="7" t="inlineStr"/>
@@ -29100,14 +29110,14 @@
       <c r="V166" s="7" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
-          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="7" t="n"/>
       <c r="C167" s="18" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="D167" t="n">
         <v>2</v>
@@ -29117,36 +29127,36 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Central Drive, Shotton, Deeside</t>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL17</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>636</v>
+        <v>710</v>
       </c>
       <c r="N167" t="n">
-        <v>1924</v>
+        <v>248</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S167" s="7" t="inlineStr"/>
@@ -29163,20 +29173,20 @@
       <c r="V167" s="7" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
-          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="7" t="n"/>
       <c r="C168" s="18" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="D168" t="n">
         <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -29185,16 +29195,19 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Llys Y Ddol, Mold</t>
+          <t>Central Drive, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>636</v>
       </c>
       <c r="N168" t="n">
-        <v>1368</v>
+        <v>1924</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -29206,7 +29219,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S168" s="7" t="inlineStr"/>
@@ -29223,53 +29236,50 @@
       <c r="V168" s="7" t="inlineStr"/>
       <c r="W168" t="inlineStr">
         <is>
-          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="7" t="n"/>
       <c r="C169" s="18" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Mill View Road, Shotton, CH5</t>
+          <t>Llys Y Ddol, Mold</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I169" t="n">
-        <v>1087</v>
+          <t>CH7</t>
+        </is>
       </c>
       <c r="N169" t="n">
-        <v>2236</v>
+        <v>1368</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S169" s="7" t="inlineStr"/>
@@ -29286,20 +29296,20 @@
       <c r="V169" s="7" t="inlineStr"/>
       <c r="W169" t="inlineStr">
         <is>
-          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="7" t="n"/>
       <c r="C170" s="18" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="D170" t="n">
         <v>3</v>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -29308,19 +29318,19 @@
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>Chestnut Way, Penyffordd, Chester</t>
+          <t>Mill View Road, Shotton, CH5</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CH4</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>765</v>
+        <v>1087</v>
       </c>
       <c r="N170" t="n">
-        <v>144</v>
+        <v>2236</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -29332,7 +29342,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S170" s="7" t="inlineStr"/>
@@ -29349,20 +29359,20 @@
       <c r="V170" s="7" t="inlineStr"/>
       <c r="W170" t="inlineStr">
         <is>
-          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="7" t="n"/>
       <c r="C171" s="18" t="n">
-        <v>975</v>
+        <v>1100</v>
       </c>
       <c r="D171" t="n">
         <v>3</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -29371,16 +29381,19 @@
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+          <t>Chestnut Way, Penyffordd, Chester</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>LL18</t>
-        </is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>765</v>
       </c>
       <c r="N171" t="n">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -29392,7 +29405,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S171" s="7" t="inlineStr"/>
@@ -29409,14 +29422,14 @@
       <c r="V171" s="7" t="inlineStr"/>
       <c r="W171" t="inlineStr">
         <is>
-          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="7" t="n"/>
       <c r="C172" s="18" t="n">
-        <v>875</v>
+        <v>975</v>
       </c>
       <c r="D172" t="n">
         <v>3</v>
@@ -29431,28 +29444,28 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>540</v>
+        <v>32</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S172" s="7" t="inlineStr"/>
@@ -29469,47 +29482,50 @@
       <c r="V172" s="7" t="inlineStr"/>
       <c r="W172" t="inlineStr">
         <is>
-          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="7" t="n"/>
       <c r="C173" s="18" t="n">
-        <v>725</v>
+        <v>875</v>
       </c>
       <c r="D173" t="n">
+        <v>3</v>
+      </c>
+      <c r="E173" t="n">
         <v>1</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>High Street, Connah's Quay, CH5</t>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1904</v>
+        <v>540</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S173" s="7" t="inlineStr"/>
@@ -29526,21 +29542,18 @@
       <c r="V173" s="7" t="inlineStr"/>
       <c r="W173" t="inlineStr">
         <is>
-          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="7" t="n"/>
       <c r="C174" s="18" t="n">
-        <v>625</v>
+        <v>725</v>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>flat</t>
@@ -29548,28 +29561,28 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>Well Street, Holywell</t>
+          <t>High Street, Connah's Quay, CH5</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>904</v>
+        <v>1904</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S174" s="7" t="inlineStr"/>
@@ -29586,50 +29599,50 @@
       <c r="V174" s="7" t="inlineStr"/>
       <c r="W174" t="inlineStr">
         <is>
-          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7" t="n"/>
       <c r="C175" s="18" t="n">
-        <v>900</v>
+        <v>625</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="n">
         <v>1</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+          <t>Well Street, Holywell</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>CH6</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>200</v>
+        <v>904</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr"/>
@@ -29646,41 +29659,38 @@
       <c r="V175" s="7" t="inlineStr"/>
       <c r="W175" t="inlineStr">
         <is>
-          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="18" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="D176" t="n">
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>Rue St. Gregoire, Holywell, CH8</t>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
-      </c>
-      <c r="I176" t="n">
-        <v>657</v>
+          <t>CH6</t>
+        </is>
       </c>
       <c r="N176" t="n">
-        <v>876</v>
+        <v>200</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -29692,7 +29702,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Currans, North Wales</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S176" s="7" t="inlineStr"/>
@@ -29709,38 +29719,41 @@
       <c r="V176" s="7" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
-          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="7" t="n"/>
       <c r="C177" s="18" t="n">
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="D177" t="n">
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>29 Tai Maes, Mold</t>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>657</v>
       </c>
       <c r="N177" t="n">
-        <v>1356</v>
+        <v>876</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -29752,7 +29765,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Currans, North Wales</t>
         </is>
       </c>
       <c r="S177" s="7" t="inlineStr"/>
@@ -29769,17 +29782,17 @@
       <c r="V177" s="7" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="18" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -29791,7 +29804,7 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>St Marys Mews, Mold</t>
+          <t>29 Tai Maes, Mold</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29800,14 +29813,14 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>1372</v>
+        <v>1356</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -29829,38 +29842,38 @@
       <c r="V178" s="7" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
-          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7" t="n"/>
       <c r="C179" s="18" t="n">
-        <v>875</v>
+        <v>600</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Castle Street, Caergwrle</t>
+          <t>St Marys Mews, Mold</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>264</v>
+        <v>1372</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -29872,7 +29885,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Town &amp; Country Estate Agents, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S179" s="7" t="inlineStr"/>
@@ -29889,29 +29902,29 @@
       <c r="V179" s="7" t="inlineStr"/>
       <c r="W179" t="inlineStr">
         <is>
-          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="7" t="n"/>
       <c r="C180" s="18" t="n">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="D180" t="n">
         <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Fagl Lane, Hope, LL12</t>
+          <t>Castle Street, Caergwrle</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29920,19 +29933,19 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Belvoir, Wrexham</t>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr"/>
@@ -29949,17 +29962,17 @@
       <c r="V180" s="7" t="inlineStr"/>
       <c r="W180" t="inlineStr">
         <is>
-          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="7" t="n"/>
       <c r="C181" s="18" t="n">
-        <v>595</v>
+        <v>800</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
@@ -29971,16 +29984,16 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Ryeland Street, Deeside</t>
+          <t>Fagl Lane, Hope, LL12</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>2152</v>
+        <v>244</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -29992,7 +30005,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Belvoir, Wrexham</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr"/>
@@ -30009,17 +30022,17 @@
       <c r="V181" s="7" t="inlineStr"/>
       <c r="W181" t="inlineStr">
         <is>
-          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="7" t="n"/>
       <c r="C182" s="18" t="n">
-        <v>750</v>
+        <v>595</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" t="n">
         <v>1</v>
@@ -30031,28 +30044,28 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>High Street, Dyserth, LL18</t>
+          <t>Ryeland Street, Deeside</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>232</v>
+        <v>2152</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S182" s="7" t="inlineStr"/>
@@ -30069,14 +30082,14 @@
       <c r="V182" s="7" t="inlineStr"/>
       <c r="W182" t="inlineStr">
         <is>
-          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="B183" s="7" t="n"/>
       <c r="C183" s="18" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="D183" t="n">
         <v>2</v>
@@ -30091,7 +30104,7 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>High Street, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30100,14 +30113,14 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>328</v>
+        <v>232</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -30129,14 +30142,14 @@
       <c r="V183" s="7" t="inlineStr"/>
       <c r="W183" t="inlineStr">
         <is>
-          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="7" t="n"/>
       <c r="C184" s="18" t="n">
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D184" t="n">
         <v>2</v>
@@ -30146,33 +30159,33 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>LL16</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N184" t="n">
-        <v>940</v>
+        <v>328</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr"/>
@@ -30189,17 +30202,17 @@
       <c r="V184" s="7" t="inlineStr"/>
       <c r="W184" t="inlineStr">
         <is>
-          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="7" t="n"/>
       <c r="C185" s="18" t="n">
-        <v>975</v>
+        <v>795</v>
       </c>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E185" t="n">
         <v>1</v>
@@ -30211,16 +30224,16 @@
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Derby Road, Caergwrle, Wrexham</t>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>LL16</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>252</v>
+        <v>940</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -30232,7 +30245,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr"/>
@@ -30249,50 +30262,50 @@
       <c r="V185" s="7" t="inlineStr"/>
       <c r="W185" t="inlineStr">
         <is>
-          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="7" t="n"/>
       <c r="C186" s="18" t="n">
-        <v>985</v>
+        <v>975</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Livingstone Place, St. Asaph, LL17</t>
+          <t>Derby Road, Caergwrle, Wrexham</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr"/>
@@ -30309,12 +30322,72 @@
       <c r="V186" s="7" t="inlineStr"/>
       <c r="W186" t="inlineStr">
         <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>268</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S187" s="7" t="inlineStr"/>
+      <c r="T187" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V187" s="7" t="inlineStr"/>
+      <c r="W187" t="inlineStr">
+        <is>
           <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W186"/>
+  <autoFilter ref="A1:W187"/>
   <dataValidations count="1">
     <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
@@ -30506,6 +30579,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -17326,7 +17326,7 @@
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n">
-        <v>21616</v>
+        <v>21660</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>0</v>
@@ -20772,10 +20772,10 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>1</v>
@@ -20787,12 +20787,12 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Hamilton Court - City Centre</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -20801,7 +20801,7 @@
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n">
-        <v>19576</v>
+        <v>21616</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>0</v>
@@ -20809,12 +20809,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr"/>
@@ -20831,7 +20831,7 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
+          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
         </is>
       </c>
     </row>
@@ -20845,10 +20845,10 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>1300</v>
+        <v>2200</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="8" t="n">
         <v>1</v>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court - City Centre</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -20874,7 +20874,7 @@
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n">
-        <v>21616</v>
+        <v>21984</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>0</v>
@@ -20882,12 +20882,12 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr"/>
@@ -20904,7 +20904,7 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
+          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
         </is>
       </c>
     </row>
@@ -20918,13 +20918,13 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
@@ -20941,7 +20941,9 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I53" s="8" t="n"/>
+      <c r="I53" s="8" t="n">
+        <v>757</v>
+      </c>
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="8" t="n"/>
@@ -20977,7 +20979,7 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
+          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
         </is>
       </c>
     </row>
@@ -21006,7 +21008,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -21050,7 +21052,7 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
+          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
         </is>
       </c>
     </row>
@@ -21064,13 +21066,13 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>2300</v>
+        <v>2095</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
@@ -21079,7 +21081,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
+          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -21123,7 +21125,7 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
+          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
         </is>
       </c>
     </row>
@@ -21137,10 +21139,10 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>2095</v>
+        <v>1400</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="n">
         <v>1</v>
@@ -21152,12 +21154,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -21166,7 +21168,7 @@
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n">
-        <v>21984</v>
+        <v>20908</v>
       </c>
       <c r="O56" s="8" t="n">
         <v>0</v>
@@ -21174,12 +21176,12 @@
       <c r="P56" s="8" t="n"/>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R56" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S56" s="9" t="inlineStr"/>
@@ -21196,7 +21198,7 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -21210,10 +21212,10 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>1</v>
@@ -21225,12 +21227,12 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -21239,7 +21241,7 @@
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n">
-        <v>20908</v>
+        <v>21600</v>
       </c>
       <c r="O57" s="8" t="n">
         <v>0</v>
@@ -21247,12 +21249,12 @@
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr"/>
@@ -21269,7 +21271,7 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -21283,7 +21285,7 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D58" s="8" t="n">
         <v>2</v>
@@ -21298,7 +21300,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Waterloo Road, Midland Mews, BS2</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -21306,13 +21308,15 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I58" s="8" t="n"/>
+      <c r="I58" s="8" t="n">
+        <v>721</v>
+      </c>
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n">
-        <v>21600</v>
+        <v>20856</v>
       </c>
       <c r="O58" s="8" t="n">
         <v>0</v>
@@ -21320,12 +21324,12 @@
       <c r="P58" s="8" t="n"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr"/>
@@ -21342,7 +21346,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
         </is>
       </c>
     </row>
@@ -21356,13 +21360,13 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>1600</v>
+        <v>2085</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
@@ -21371,23 +21375,23 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Waterloo Road, Midland Mews, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I59" s="8" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O59" s="8" t="n">
         <v>0</v>
@@ -21395,12 +21399,12 @@
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr"/>
@@ -21417,7 +21421,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -21431,13 +21435,13 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>2085</v>
+        <v>1640</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
@@ -21446,7 +21450,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -21455,14 +21459,14 @@
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>722</v>
+        <v>570</v>
       </c>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O60" s="8" t="n">
         <v>0</v>
@@ -21475,7 +21479,7 @@
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr"/>
@@ -21492,7 +21496,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -21506,10 +21510,10 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>1640</v>
+        <v>1500</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>1</v>
@@ -21521,23 +21525,21 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>570</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -21550,7 +21552,7 @@
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr"/>
@@ -21567,7 +21569,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
         </is>
       </c>
     </row>
@@ -21581,10 +21583,10 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>1</v>
@@ -21596,21 +21598,23 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I62" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>405</v>
+      </c>
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>20856</v>
+        <v>20316</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -21623,7 +21627,7 @@
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S62" s="9" t="inlineStr"/>
@@ -21640,7 +21644,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -21654,13 +21658,13 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1300</v>
+        <v>2020</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
@@ -21669,7 +21673,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -21678,14 +21682,14 @@
         </is>
       </c>
       <c r="I63" s="8" t="n">
-        <v>405</v>
+        <v>764</v>
       </c>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>20316</v>
+        <v>20856</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21693,12 +21697,12 @@
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21715,7 +21719,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21733,7 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>2020</v>
+        <v>2145</v>
       </c>
       <c r="D64" s="8" t="n">
         <v>2</v>
@@ -21744,7 +21748,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -21753,14 +21757,14 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>764</v>
+        <v>815</v>
       </c>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21773,7 +21777,7 @@
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21790,7 +21794,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21804,13 +21808,13 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>2145</v>
+        <v>1635</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
@@ -21819,7 +21823,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -21828,7 +21832,7 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>815</v>
+        <v>486</v>
       </c>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
@@ -21848,7 +21852,7 @@
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr"/>
@@ -21865,7 +21869,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -21879,13 +21883,13 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>1635</v>
+        <v>1750</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
@@ -21894,23 +21898,23 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>486</v>
+        <v>731</v>
       </c>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>21504</v>
+        <v>4680</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -21923,7 +21927,7 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21940,7 +21944,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -21954,13 +21958,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21969,23 +21973,21 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>731</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="n"/>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>4680</v>
+        <v>21148</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -21993,12 +21995,12 @@
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S67" s="9" t="inlineStr"/>
@@ -22015,7 +22017,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -22029,13 +22031,13 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>2100</v>
+        <v>2220</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -22044,7 +22046,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -22052,13 +22054,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I68" s="8" t="n"/>
+      <c r="I68" s="8" t="n">
+        <v>697</v>
+      </c>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>21148</v>
+        <v>20820</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22071,7 +22075,7 @@
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22088,7 +22092,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -22102,13 +22106,13 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>2220</v>
+        <v>1300</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -22117,7 +22121,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22125,15 +22129,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="8" t="n">
-        <v>697</v>
-      </c>
+      <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>20820</v>
+        <v>21428</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -22141,12 +22143,12 @@
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22163,7 +22165,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22179,7 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D70" s="8" t="n">
         <v>1</v>
@@ -22192,7 +22194,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -22200,13 +22202,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="8" t="n"/>
+      <c r="I70" s="8" t="n">
+        <v>548</v>
+      </c>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n">
-        <v>21428</v>
+        <v>21504</v>
       </c>
       <c r="O70" s="8" t="n">
         <v>0</v>
@@ -22214,12 +22218,12 @@
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S70" s="9" t="inlineStr"/>
@@ -22236,7 +22240,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22254,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1500</v>
+        <v>1615</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>1</v>
@@ -22265,7 +22269,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22274,7 +22278,7 @@
         </is>
       </c>
       <c r="I71" s="8" t="n">
-        <v>548</v>
+        <v>486</v>
       </c>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
@@ -22294,7 +22298,7 @@
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22311,7 +22315,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -22325,10 +22329,10 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1615</v>
+        <v>1965</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>1</v>
@@ -22340,7 +22344,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22349,7 +22353,7 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>486</v>
+        <v>655</v>
       </c>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
@@ -22364,12 +22368,12 @@
       <c r="P72" s="8" t="n"/>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22386,7 +22390,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
         </is>
       </c>
     </row>
@@ -22400,13 +22404,13 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1965</v>
+        <v>2080</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
@@ -22415,7 +22419,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -22424,14 +22428,14 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0</v>
@@ -22444,7 +22448,7 @@
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
@@ -22461,7 +22465,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
+          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
         </is>
       </c>
     </row>
@@ -22475,13 +22479,13 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>2080</v>
+        <v>1400</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
@@ -22490,7 +22494,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -22498,15 +22502,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I74" s="8" t="n">
-        <v>705</v>
-      </c>
+      <c r="I74" s="8" t="n"/>
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n">
-        <v>20820</v>
+        <v>19484</v>
       </c>
       <c r="O74" s="8" t="n">
         <v>0</v>
@@ -22519,7 +22521,7 @@
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
@@ -22536,7 +22538,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -22550,13 +22552,13 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
@@ -22565,7 +22567,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Welsh Back, Bristol, BS1</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -22573,14 +22575,14 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I75" s="8" t="n"/>
+      <c r="I75" s="8" t="n">
+        <v>908</v>
+      </c>
       <c r="J75" s="8" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
-      <c r="N75" s="8" t="n">
-        <v>19484</v>
-      </c>
+      <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n">
         <v>0</v>
       </c>
@@ -22592,7 +22594,7 @@
       </c>
       <c r="R75" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Hello Neighbour, London</t>
         </is>
       </c>
       <c r="S75" s="9" t="inlineStr"/>
@@ -22609,7 +22611,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
         </is>
       </c>
     </row>
@@ -22623,13 +22625,13 @@
         </is>
       </c>
       <c r="C76" s="17" t="n">
-        <v>2000</v>
+        <v>2020</v>
       </c>
       <c r="D76" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
@@ -22638,7 +22640,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -22647,7 +22649,7 @@
         </is>
       </c>
       <c r="I76" s="8" t="n">
-        <v>908</v>
+        <v>705</v>
       </c>
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
@@ -22660,12 +22662,12 @@
       <c r="P76" s="8" t="n"/>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>Hello Neighbour, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
@@ -22682,7 +22684,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
+          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
         </is>
       </c>
     </row>
@@ -22696,7 +22698,7 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>2</v>
@@ -22711,7 +22713,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Eclipse - City Centre</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -22719,9 +22721,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I77" s="8" t="n">
-        <v>705</v>
-      </c>
+      <c r="I77" s="8" t="n"/>
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
@@ -22733,12 +22733,12 @@
       <c r="P77" s="8" t="n"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S77" s="9" t="inlineStr"/>
@@ -22755,7 +22755,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
+          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
         </is>
       </c>
     </row>
@@ -22769,10 +22769,10 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>2175</v>
+        <v>1595</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="n">
         <v>1</v>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -22792,7 +22792,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I78" s="8" t="n"/>
+      <c r="I78" s="8" t="n">
+        <v>499</v>
+      </c>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
@@ -22804,12 +22806,12 @@
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
@@ -22826,7 +22828,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>6a00f91534112c4504453102597619449da3a2c1</t>
+          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22842,7 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>2000</v>
+        <v>2085</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>2</v>
@@ -22855,7 +22857,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Eclipse - City Centre</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -22863,7 +22865,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I79" s="8" t="n"/>
+      <c r="I79" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
@@ -22875,12 +22879,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
@@ -22897,7 +22901,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
+          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22915,7 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>1595</v>
+        <v>1615</v>
       </c>
       <c r="D80" s="8" t="n">
         <v>1</v>
@@ -22926,7 +22930,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -22935,7 +22939,7 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
@@ -22948,12 +22952,12 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S80" s="9" t="inlineStr"/>
@@ -22970,7 +22974,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -22984,7 +22988,7 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>2085</v>
+        <v>2065</v>
       </c>
       <c r="D81" s="8" t="n">
         <v>2</v>
@@ -22999,7 +23003,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -23008,7 +23012,7 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>705</v>
+        <v>641</v>
       </c>
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
@@ -23021,12 +23025,12 @@
       <c r="P81" s="8" t="n"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
@@ -23043,7 +23047,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -23057,13 +23061,13 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1615</v>
+        <v>2185</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
@@ -23081,7 +23085,7 @@
         </is>
       </c>
       <c r="I82" s="8" t="n">
-        <v>487</v>
+        <v>721</v>
       </c>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
@@ -23094,7 +23098,7 @@
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
@@ -23116,7 +23120,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -23130,13 +23134,13 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>2065</v>
+        <v>1565</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
@@ -23145,7 +23149,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -23154,7 +23158,7 @@
         </is>
       </c>
       <c r="I83" s="8" t="n">
-        <v>641</v>
+        <v>484</v>
       </c>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
@@ -23172,7 +23176,7 @@
       </c>
       <c r="R83" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S83" s="9" t="inlineStr"/>
@@ -23189,7 +23193,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -23203,13 +23207,13 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>2185</v>
+        <v>1650</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
@@ -23218,7 +23222,7 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Horizon, Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -23226,9 +23230,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
@@ -23240,12 +23242,12 @@
       <c r="P84" s="8" t="n"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R84" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S84" s="9" t="inlineStr"/>
@@ -23262,7 +23264,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -23276,7 +23278,7 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1565</v>
+        <v>1625</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>1</v>
@@ -23300,7 +23302,7 @@
         </is>
       </c>
       <c r="I85" s="8" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
@@ -23313,7 +23315,7 @@
       <c r="P85" s="8" t="n"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R85" s="8" t="inlineStr">
@@ -23335,7 +23337,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -23349,13 +23351,13 @@
         </is>
       </c>
       <c r="C86" s="17" t="n">
-        <v>1650</v>
+        <v>2175</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
@@ -23364,7 +23366,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -23372,7 +23374,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I86" s="8" t="n"/>
+      <c r="I86" s="8" t="n">
+        <v>722</v>
+      </c>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
@@ -23384,12 +23388,12 @@
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
@@ -23406,7 +23410,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -23420,10 +23424,10 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="8" t="n">
         <v>1</v>
@@ -23435,7 +23439,7 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -23443,9 +23447,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I87" s="8" t="n">
-        <v>485</v>
-      </c>
+      <c r="I87" s="8" t="n"/>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
@@ -23457,12 +23459,12 @@
       <c r="P87" s="8" t="n"/>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S87" s="9" t="inlineStr"/>
@@ -23479,7 +23481,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -23493,7 +23495,7 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>2175</v>
+        <v>1900</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>2</v>
@@ -23508,7 +23510,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -23516,9 +23518,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I88" s="8" t="n">
-        <v>722</v>
-      </c>
+      <c r="I88" s="8" t="n"/>
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
@@ -23530,12 +23530,12 @@
       <c r="P88" s="8" t="n"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
@@ -23552,7 +23552,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>1500</v>
+        <v>1660</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>1</v>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -23590,25 +23590,27 @@
         </is>
       </c>
       <c r="I89" s="8" t="n">
-        <v>721</v>
+        <v>486</v>
       </c>
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
+      <c r="N89" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O89" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="8" t="n"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S89" s="9" t="inlineStr"/>
@@ -23625,7 +23627,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -23639,13 +23641,13 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>2100</v>
+        <v>2175</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
@@ -23654,7 +23656,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -23662,24 +23664,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I90" s="8" t="n"/>
+      <c r="I90" s="8" t="n">
+        <v>814</v>
+      </c>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
-      <c r="N90" s="8" t="n"/>
+      <c r="N90" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="8" t="n"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23696,7 +23702,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -23710,7 +23716,7 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>2</v>
@@ -23725,7 +23731,7 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -23738,19 +23744,21 @@
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
-      <c r="N91" s="8" t="n"/>
+      <c r="N91" s="8" t="n">
+        <v>21816</v>
+      </c>
       <c r="O91" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="8" t="n"/>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr"/>
@@ -23767,7 +23775,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -23781,7 +23789,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>2500</v>
+        <v>2115</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>2</v>
@@ -23796,7 +23804,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Liberty Gardens, Caledonian Road, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -23805,25 +23813,27 @@
         </is>
       </c>
       <c r="I92" s="8" t="n">
-        <v>1238</v>
+        <v>823</v>
       </c>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
-      <c r="N92" s="8" t="n"/>
+      <c r="N92" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="8" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S92" s="9" t="inlineStr"/>
@@ -23840,7 +23850,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -23893,7 +23903,7 @@
       <c r="P93" s="8" t="n"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
@@ -23915,7 +23925,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -23929,7 +23939,7 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>2175</v>
+        <v>1915</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>2</v>
@@ -23953,14 +23963,14 @@
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>814</v>
+        <v>746</v>
       </c>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O94" s="8" t="n">
         <v>0</v>
@@ -23968,7 +23978,7 @@
       <c r="P94" s="8" t="n"/>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R94" s="8" t="inlineStr">
@@ -23990,7 +24000,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -24004,13 +24014,13 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>1500</v>
+        <v>1150</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
@@ -24019,12 +24029,12 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I95" s="8" t="n"/>
@@ -24033,7 +24043,7 @@
       <c r="L95" s="8" t="n"/>
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="8" t="n">
-        <v>21816</v>
+        <v>6872</v>
       </c>
       <c r="O95" s="8" t="n">
         <v>0</v>
@@ -24041,12 +24051,12 @@
       <c r="P95" s="8" t="n"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S95" s="9" t="inlineStr"/>
@@ -24063,7 +24073,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -24077,13 +24087,13 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>1450</v>
+        <v>2450</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
@@ -24092,12 +24102,12 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>The Old Drill Hall, Bristol, BS2</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I96" s="8" t="n"/>
@@ -24105,14 +24115,16 @@
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
-      <c r="N96" s="8" t="n"/>
+      <c r="N96" s="8" t="n">
+        <v>21788</v>
+      </c>
       <c r="O96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="8" t="n"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr">
@@ -24134,7 +24146,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>c847859d6a4555381482a51e75495800df35917d</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -24148,7 +24160,7 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>2115</v>
+        <v>1700</v>
       </c>
       <c r="D97" s="8" t="n">
         <v>2</v>
@@ -24163,7 +24175,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Crescent</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -24171,15 +24183,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I97" s="8" t="n">
-        <v>823</v>
-      </c>
+      <c r="I97" s="8" t="n"/>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n">
-        <v>20820</v>
+        <v>16368</v>
       </c>
       <c r="O97" s="8" t="n">
         <v>0</v>
@@ -24187,12 +24197,12 @@
       <c r="P97" s="8" t="n"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24209,7 +24219,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
         </is>
       </c>
     </row>
@@ -24223,7 +24233,7 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>1660</v>
+        <v>1250</v>
       </c>
       <c r="D98" s="8" t="n">
         <v>1</v>
@@ -24238,7 +24248,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -24246,15 +24256,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="8" t="n">
-        <v>486</v>
-      </c>
+      <c r="I98" s="8" t="n"/>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n">
-        <v>21504</v>
+        <v>21160</v>
       </c>
       <c r="O98" s="8" t="n">
         <v>0</v>
@@ -24262,12 +24270,12 @@
       <c r="P98" s="8" t="n"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R98" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S98" s="9" t="inlineStr"/>
@@ -24284,7 +24292,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -24298,7 +24306,7 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>1915</v>
+        <v>1600</v>
       </c>
       <c r="D99" s="8" t="n">
         <v>2</v>
@@ -24313,23 +24321,21 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Ratcliffe Court, Bristol, BS2</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="n">
-        <v>746</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n">
-        <v>21680</v>
+        <v>20124</v>
       </c>
       <c r="O99" s="8" t="n">
         <v>0</v>
@@ -24337,12 +24343,12 @@
       <c r="P99" s="8" t="n"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24359,7 +24365,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
         </is>
       </c>
     </row>
@@ -24373,13 +24379,13 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>1150</v>
+        <v>2145</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
@@ -24388,21 +24394,23 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I100" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="n">
+        <v>796</v>
+      </c>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n">
-        <v>6872</v>
+        <v>20820</v>
       </c>
       <c r="O100" s="8" t="n">
         <v>0</v>
@@ -24410,12 +24418,12 @@
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24432,7 +24440,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
         </is>
       </c>
     </row>
@@ -24446,13 +24454,13 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>2450</v>
+        <v>1999</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -24461,7 +24469,7 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -24475,7 +24483,7 @@
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n">
-        <v>21788</v>
+        <v>20800</v>
       </c>
       <c r="O101" s="8" t="n">
         <v>0</v>
@@ -24483,7 +24491,7 @@
       <c r="P101" s="8" t="n"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R101" s="8" t="inlineStr">
@@ -24505,7 +24513,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -24519,13 +24527,13 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1700</v>
+        <v>1670</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
@@ -24534,7 +24542,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>The Crescent</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24542,13 +24550,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="8" t="n"/>
+      <c r="I102" s="8" t="n">
+        <v>485</v>
+      </c>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n">
-        <v>16368</v>
+        <v>21504</v>
       </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
@@ -24556,12 +24566,12 @@
       <c r="P102" s="8" t="n"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24578,7 +24588,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -24592,7 +24602,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1250</v>
+        <v>1645</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>1</v>
@@ -24607,7 +24617,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24615,13 +24625,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I103" s="8" t="n"/>
+      <c r="I103" s="8" t="n">
+        <v>517</v>
+      </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n">
-        <v>21160</v>
+        <v>20820</v>
       </c>
       <c r="O103" s="8" t="n">
         <v>0</v>
@@ -24629,12 +24641,12 @@
       <c r="P103" s="8" t="n"/>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24651,7 +24663,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
         </is>
       </c>
     </row>
@@ -24665,7 +24677,7 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1600</v>
+        <v>2120</v>
       </c>
       <c r="D104" s="8" t="n">
         <v>2</v>
@@ -24680,21 +24692,23 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>Ratcliffe Court, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I104" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n">
-        <v>20124</v>
+        <v>20820</v>
       </c>
       <c r="O104" s="8" t="n">
         <v>0</v>
@@ -24702,12 +24716,12 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24724,7 +24738,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -24738,13 +24752,13 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>2145</v>
+        <v>1645</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -24762,7 +24776,7 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>796</v>
+        <v>571</v>
       </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
@@ -24777,7 +24791,7 @@
       <c r="P105" s="8" t="n"/>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr">
@@ -24799,7 +24813,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
+          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
         </is>
       </c>
     </row>
@@ -24813,7 +24827,7 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1999</v>
+        <v>2250</v>
       </c>
       <c r="D106" s="8" t="n">
         <v>2</v>
@@ -24828,7 +24842,7 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Apartments, Bristol, BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -24842,7 +24856,7 @@
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
       <c r="N106" s="8" t="n">
-        <v>20800</v>
+        <v>22132</v>
       </c>
       <c r="O106" s="8" t="n">
         <v>0</v>
@@ -24850,7 +24864,7 @@
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
@@ -24872,7 +24886,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
         </is>
       </c>
     </row>
@@ -24886,10 +24900,10 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1670</v>
+        <v>1600</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="8" t="n">
         <v>1</v>
@@ -24901,23 +24915,21 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="n">
-        <v>485</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="n"/>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n">
-        <v>21504</v>
+        <v>19576</v>
       </c>
       <c r="O107" s="8" t="n">
         <v>0</v>
@@ -24925,12 +24937,12 @@
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S107" s="9" t="inlineStr"/>
@@ -24947,7 +24959,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
         </is>
       </c>
     </row>
@@ -24961,10 +24973,10 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>1645</v>
+        <v>2175</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>1</v>
@@ -24976,7 +24988,7 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
@@ -24984,28 +24996,24 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I108" s="8" t="n">
-        <v>517</v>
-      </c>
+      <c r="I108" s="8" t="n"/>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
-      <c r="N108" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N108" s="8" t="n"/>
       <c r="O108" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -25022,7 +25030,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
+          <t>6a00f91534112c4504453102597619449da3a2c1</t>
         </is>
       </c>
     </row>
@@ -25036,13 +25044,13 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>2120</v>
+        <v>1500</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
@@ -25051,7 +25059,7 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Baldwin Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
@@ -25060,27 +25068,25 @@
         </is>
       </c>
       <c r="I109" s="8" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="J109" s="8" t="n"/>
       <c r="K109" s="8" t="n"/>
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
-      <c r="N109" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N109" s="8" t="n"/>
       <c r="O109" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="8" t="n"/>
       <c r="Q109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R109" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S109" s="9" t="inlineStr"/>
@@ -25097,7 +25103,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
         </is>
       </c>
     </row>
@@ -25111,13 +25117,13 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>1645</v>
+        <v>2500</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
@@ -25126,7 +25132,7 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Liberty Gardens, Caledonian Road, BS1</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -25135,27 +25141,25 @@
         </is>
       </c>
       <c r="I110" s="8" t="n">
-        <v>571</v>
+        <v>1238</v>
       </c>
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
-      <c r="N110" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N110" s="8" t="n"/>
       <c r="O110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="8" t="n"/>
       <c r="Q110" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R110" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S110" s="9" t="inlineStr"/>
@@ -25172,7 +25176,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
+          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
         </is>
       </c>
     </row>
@@ -25186,10 +25190,10 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>2250</v>
+        <v>1450</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>1</v>
@@ -25201,12 +25205,12 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>Apartments, Bristol, BS1</t>
+          <t>The Old Drill Hall, Bristol, BS2</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I111" s="8" t="n"/>
@@ -25214,16 +25218,14 @@
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
-      <c r="N111" s="8" t="n">
-        <v>22132</v>
-      </c>
+      <c r="N111" s="8" t="n"/>
       <c r="O111" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="8" t="n"/>
       <c r="Q111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R111" s="8" t="inlineStr">
@@ -25245,7 +25247,7 @@
       <c r="V111" s="7" t="inlineStr"/>
       <c r="W111" s="8" t="inlineStr">
         <is>
-          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
+          <t>c847859d6a4555381482a51e75495800df35917d</t>
         </is>
       </c>
     </row>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -17141,10 +17141,10 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>1</v>
@@ -17156,21 +17156,23 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>St. Johns Lane, Bedminster, BS3</t>
+          <t>Redcliff Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>731</v>
+      </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n">
-        <v>7112</v>
+        <v>20892</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>0</v>
@@ -17178,17 +17180,17 @@
       <c r="P4" s="8" t="n"/>
       <c r="Q4" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>A2Dominion Group, A2Dominion Lettings</t>
         </is>
       </c>
       <c r="S4" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T4" s="12" t="inlineStr">
@@ -17204,7 +17206,7 @@
       <c r="V4" s="7" t="inlineStr"/>
       <c r="W4" s="8" t="inlineStr">
         <is>
-          <t>91339ed58a9e4347ac017823b498695129a40922</t>
+          <t>c11b7a868ede7c3b0a3d524aa4d4e8f661494706</t>
         </is>
       </c>
     </row>
@@ -17218,10 +17220,10 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>1900</v>
+        <v>1395</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>1</v>
@@ -17233,23 +17235,21 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Redcliff Street, Bristol, BS1</t>
+          <t>Hamilton Court, Bristol, BS2</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>731</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n"/>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="8" t="n"/>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n">
-        <v>20892</v>
+        <v>21660</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>0</v>
@@ -17257,17 +17257,17 @@
       <c r="P5" s="8" t="n"/>
       <c r="Q5" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>A2Dominion Group, A2Dominion Lettings</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S5" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T5" s="12" t="inlineStr">
@@ -17283,7 +17283,7 @@
       <c r="V5" s="7" t="inlineStr"/>
       <c r="W5" s="8" t="inlineStr">
         <is>
-          <t>c11b7a868ede7c3b0a3d524aa4d4e8f661494706</t>
+          <t>55512167c7894bf9991618275f495f9b5aa0a1af</t>
         </is>
       </c>
     </row>
@@ -17297,13 +17297,13 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1395</v>
+        <v>2000</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -17312,12 +17312,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court, Bristol, BS2</t>
+          <t>Deanery Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -17326,7 +17326,7 @@
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n">
-        <v>21660</v>
+        <v>18292</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>0</v>
@@ -17339,12 +17339,12 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S6" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T6" s="12" t="inlineStr">
@@ -17360,7 +17360,7 @@
       <c r="V6" s="7" t="inlineStr"/>
       <c r="W6" s="8" t="inlineStr">
         <is>
-          <t>55512167c7894bf9991618275f495f9b5aa0a1af</t>
+          <t>591cc261a1f5973aaa4a7b3adbcbe4699bcc6440</t>
         </is>
       </c>
     </row>
@@ -17374,13 +17374,13 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>2000</v>
+        <v>1550</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -17389,12 +17389,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Deanery Road, Bristol, BS1</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -17403,7 +17403,7 @@
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n">
-        <v>18292</v>
+        <v>19400</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S7" s="9" t="inlineStr">
@@ -17437,7 +17437,7 @@
       <c r="V7" s="7" t="inlineStr"/>
       <c r="W7" s="8" t="inlineStr">
         <is>
-          <t>591cc261a1f5973aaa4a7b3adbcbe4699bcc6440</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -17451,13 +17451,13 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>1550</v>
+        <v>1900</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
@@ -17466,21 +17466,23 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>783</v>
+      </c>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n">
-        <v>19400</v>
+        <v>4680</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>0</v>
@@ -17488,12 +17490,12 @@
       <c r="P8" s="8" t="n"/>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S8" s="9" t="inlineStr">
@@ -17514,7 +17516,7 @@
       <c r="V8" s="7" t="inlineStr"/>
       <c r="W8" s="8" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17530,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>1900</v>
+        <v>2170</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>2</v>
@@ -17543,23 +17545,23 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>522 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="J9" s="8" t="n"/>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n">
-        <v>4680</v>
+        <v>20800</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>0</v>
@@ -17567,12 +17569,12 @@
       <c r="P9" s="8" t="n"/>
       <c r="Q9" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S9" s="9" t="inlineStr">
@@ -17593,7 +17595,7 @@
       <c r="V9" s="7" t="inlineStr"/>
       <c r="W9" s="8" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>c0573087585d4e3e5716cf3f127e0ed418364345</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17609,7 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>2170</v>
+        <v>2195</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -17622,7 +17624,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>522 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2 0GJ</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -17631,7 +17633,7 @@
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
@@ -17672,7 +17674,7 @@
       <c r="V10" s="7" t="inlineStr"/>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t>c0573087585d4e3e5716cf3f127e0ed418364345</t>
+          <t>ad6f591658988c13d13881686e197fa878817439</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17688,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>2195</v>
+        <v>1995</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>2</v>
@@ -17701,23 +17703,21 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>802 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2 0GJ</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>809</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n">
-        <v>20800</v>
+        <v>18544</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>0</v>
@@ -17730,7 +17730,7 @@
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S11" s="9" t="inlineStr">
@@ -17751,7 +17751,7 @@
       <c r="V11" s="7" t="inlineStr"/>
       <c r="W11" s="8" t="inlineStr">
         <is>
-          <t>ad6f591658988c13d13881686e197fa878817439</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -17765,13 +17765,13 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>1995</v>
+        <v>1450</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
@@ -17780,21 +17780,23 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Bedminster, Berkeley Place, BS3</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>7685</v>
+      </c>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n">
-        <v>18544</v>
+        <v>7648</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>0</v>
@@ -17807,7 +17809,7 @@
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S12" s="9" t="inlineStr">
@@ -17828,7 +17830,7 @@
       <c r="V12" s="7" t="inlineStr"/>
       <c r="W12" s="8" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>4855da62cb452e8973968307d05f937e5ab76b6c</t>
         </is>
       </c>
     </row>
@@ -17842,10 +17844,10 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1450</v>
+        <v>1655</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>1</v>
@@ -17857,23 +17859,23 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Bedminster, Berkeley Place, BS3</t>
+          <t>New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I13" s="8" t="n">
-        <v>7685</v>
+        <v>547</v>
       </c>
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n">
-        <v>7648</v>
+        <v>20800</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>0</v>
@@ -17881,12 +17883,12 @@
       <c r="P13" s="8" t="n"/>
       <c r="Q13" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S13" s="9" t="inlineStr">
@@ -17907,7 +17909,7 @@
       <c r="V13" s="7" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>4855da62cb452e8973968307d05f937e5ab76b6c</t>
+          <t>1f8489d296d842011bdf7a2ca1f952e6b948c3d3</t>
         </is>
       </c>
     </row>
@@ -17921,13 +17923,13 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>1655</v>
+        <v>2500</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -17936,23 +17938,21 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>New Kingsley Road, Bristol, BS2</t>
+          <t>Electricity House, Colston Avenue, BS1</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>547</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n">
-        <v>20800</v>
+        <v>21876</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S14" s="9" t="inlineStr">
@@ -17986,7 +17986,7 @@
       <c r="V14" s="7" t="inlineStr"/>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>1f8489d296d842011bdf7a2ca1f952e6b948c3d3</t>
+          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
         </is>
       </c>
     </row>
@@ -18000,13 +18000,13 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Electricity House, Colston Avenue, BS1</t>
+          <t>The Crescent, Hannover Quay, BS1</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -18029,7 +18029,7 @@
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n">
-        <v>21876</v>
+        <v>16232</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>0</v>
@@ -18063,7 +18063,7 @@
       <c r="V15" s="7" t="inlineStr"/>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
+          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
         </is>
       </c>
     </row>
@@ -18077,13 +18077,13 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>1500</v>
+        <v>1850</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, BS1</t>
+          <t>Park Row, Bristol, BS1</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -18100,26 +18100,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I16" s="8" t="n"/>
+      <c r="I16" s="8" t="n">
+        <v>797</v>
+      </c>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n">
-        <v>16232</v>
-      </c>
+      <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S16" s="9" t="inlineStr">
@@ -18140,7 +18140,7 @@
       <c r="V16" s="7" t="inlineStr"/>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
+          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
         </is>
       </c>
     </row>
@@ -18154,13 +18154,13 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>1495</v>
+        <v>2975</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -18169,21 +18169,23 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, Somerset, BS1</t>
+          <t>Capricorn Place, Hotwells</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="n"/>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1615</v>
+      </c>
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n">
-        <v>20848</v>
+        <v>15104</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>0</v>
@@ -18191,12 +18193,12 @@
       <c r="P17" s="8" t="n"/>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S17" s="9" t="inlineStr">
@@ -18217,7 +18219,7 @@
       <c r="V17" s="7" t="inlineStr"/>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
+          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
         </is>
       </c>
     </row>
@@ -18231,7 +18233,7 @@
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>1850</v>
+        <v>2000</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -18246,7 +18248,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Park Row, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -18254,31 +18256,31 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I18" s="8" t="n">
-        <v>797</v>
-      </c>
+      <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>22020</v>
+      </c>
       <c r="O18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="8" t="n"/>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S18" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T18" s="12" t="inlineStr">
@@ -18294,7 +18296,7 @@
       <c r="V18" s="7" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -18308,13 +18310,13 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>2975</v>
+        <v>1400</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -18323,23 +18325,21 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells</t>
+          <t>The Crescent, Harbourside, Bristol</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>1615</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="8" t="n">
-        <v>15104</v>
+        <v>16368</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>0</v>
@@ -18347,12 +18347,12 @@
       <c r="P19" s="8" t="n"/>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S19" s="9" t="inlineStr">
@@ -18373,7 +18373,7 @@
       <c r="V19" s="7" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -18416,7 +18416,7 @@
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="S20" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
@@ -18450,7 +18450,7 @@
       <c r="V20" s="7" t="inlineStr"/>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -18464,13 +18464,13 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, Bristol</t>
+          <t>Steamship House, Gas Ferry Road, BS1</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -18493,7 +18493,7 @@
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n">
-        <v>16368</v>
+        <v>14420</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>0</v>
@@ -18501,7 +18501,7 @@
       <c r="P21" s="8" t="n"/>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
@@ -18527,7 +18527,7 @@
       <c r="V21" s="7" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>f7b6312c22af08d7f7e765adf92d9a3fb0f82781</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Harbourside, The Crescent, BS1 5JP</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -18564,13 +18564,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I22" s="8" t="n"/>
+      <c r="I22" s="8" t="n">
+        <v>969</v>
+      </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n">
-        <v>22132</v>
+        <v>16368</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>0</v>
@@ -18578,12 +18580,12 @@
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S22" s="9" t="inlineStr">
@@ -18604,7 +18606,7 @@
       <c r="V22" s="7" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>384c19ad899eb10f0c99305f716bbf9cc2030cb0</t>
         </is>
       </c>
     </row>
@@ -18618,13 +18620,13 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1700</v>
+        <v>1350</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
@@ -18633,7 +18635,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Steamship House, Gas Ferry Road, BS1</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -18641,13 +18643,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I23" s="8" t="n"/>
+      <c r="I23" s="8" t="n">
+        <v>491</v>
+      </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n">
-        <v>14420</v>
+        <v>17096</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>0</v>
@@ -18660,7 +18664,7 @@
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>A2Dominion Group, A2Dominion Lettings</t>
         </is>
       </c>
       <c r="S23" s="9" t="inlineStr">
@@ -18681,7 +18685,7 @@
       <c r="V23" s="7" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>f7b6312c22af08d7f7e765adf92d9a3fb0f82781</t>
+          <t>3ab86f4fbffd37f02afac44cadd6ec8a27da6f0a</t>
         </is>
       </c>
     </row>
@@ -18695,7 +18699,7 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -18710,7 +18714,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Harbourside, The Crescent, BS1 5JP</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -18718,15 +18722,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I24" s="8" t="n">
-        <v>969</v>
-      </c>
+      <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n">
-        <v>16368</v>
+        <v>14632</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>0</v>
@@ -18739,7 +18741,7 @@
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S24" s="9" t="inlineStr">
@@ -18760,7 +18762,7 @@
       <c r="V24" s="7" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>384c19ad899eb10f0c99305f716bbf9cc2030cb0</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -18774,13 +18776,13 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -18789,23 +18791,21 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>Sweetman Place, Bristol, BS2</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>491</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n">
-        <v>17096</v>
+        <v>20416</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>0</v>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>A2Dominion Group, A2Dominion Lettings</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S25" s="9" t="inlineStr">
@@ -18839,7 +18839,7 @@
       <c r="V25" s="7" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>3ab86f4fbffd37f02afac44cadd6ec8a27da6f0a</t>
+          <t>54fa42ef8d0349a295f45392644c43dec3321c5b</t>
         </is>
       </c>
     </row>
@@ -18853,13 +18853,13 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>City Centre, Corinthian Court, BS1</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -18876,13 +18876,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I26" s="8" t="n"/>
+      <c r="I26" s="8" t="n">
+        <v>389</v>
+      </c>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n">
-        <v>14632</v>
+        <v>18820</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>0</v>
@@ -18890,12 +18892,12 @@
       <c r="P26" s="8" t="n"/>
       <c r="Q26" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S26" s="9" t="inlineStr">
@@ -18916,7 +18918,7 @@
       <c r="V26" s="7" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>5aed40eba285a7fa0266bfe8eb49613bb2f96c97</t>
         </is>
       </c>
     </row>
@@ -18930,13 +18932,13 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
@@ -18945,21 +18947,23 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Sweetman Place, Bristol, BS2</t>
+          <t>Harbourside, Steamship House, BS1 6GL</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>506</v>
+      </c>
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n">
-        <v>20416</v>
+        <v>14420</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>0</v>
@@ -18967,12 +18971,12 @@
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S27" s="9" t="inlineStr">
@@ -18993,7 +18997,7 @@
       <c r="V27" s="7" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>54fa42ef8d0349a295f45392644c43dec3321c5b</t>
+          <t>bf329b73db0d1de077d78cddc284f1017fcfc43a</t>
         </is>
       </c>
     </row>
@@ -19007,7 +19011,7 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>1</v>
@@ -19022,7 +19026,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Corinthian Court, BS1</t>
+          <t>St. James Barton, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -19030,15 +19034,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I28" s="8" t="n">
-        <v>389</v>
-      </c>
+      <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n">
-        <v>18820</v>
+        <v>22132</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>0</v>
@@ -19051,7 +19053,7 @@
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Balloon Letting Company, Bristol</t>
         </is>
       </c>
       <c r="S28" s="9" t="inlineStr">
@@ -19072,7 +19074,7 @@
       <c r="V28" s="7" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>5aed40eba285a7fa0266bfe8eb49613bb2f96c97</t>
+          <t>f2c75a0f99c7c358be96a67019a6c639e60845fb</t>
         </is>
       </c>
     </row>
@@ -19086,38 +19088,36 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1500</v>
+        <v>3750</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Harbourside, Steamship House, BS1 6GL</t>
+          <t>Dove Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>506</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n">
-        <v>14420</v>
+        <v>21288</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>0</v>
@@ -19130,12 +19130,12 @@
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S29" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
@@ -19151,7 +19151,7 @@
       <c r="V29" s="7" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>bf329b73db0d1de077d78cddc284f1017fcfc43a</t>
+          <t>1bcb0667c3a3efe864816ea971273f0e1ff48f01</t>
         </is>
       </c>
     </row>
@@ -19165,7 +19165,7 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>1</v>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>St. James Barton, Bristol, Somerset, BS1</t>
+          <t>Three Queens Lane, Bristol, BS1</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -19194,7 +19194,7 @@
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n">
-        <v>22132</v>
+        <v>20608</v>
       </c>
       <c r="O30" s="8" t="n">
         <v>0</v>
@@ -19202,12 +19202,12 @@
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>Balloon Letting Company, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S30" s="9" t="inlineStr">
@@ -19228,7 +19228,7 @@
       <c r="V30" s="7" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>f2c75a0f99c7c358be96a67019a6c639e60845fb</t>
+          <t>7c9f52e17d949cd3dc79f3eb8c1020a81c729d66</t>
         </is>
       </c>
     </row>
@@ -19242,27 +19242,27 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>3750</v>
+        <v>1300</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Dove Street, Bristol, BS2</t>
+          <t>St. Johns Lane, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -19271,7 +19271,7 @@
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n">
-        <v>21288</v>
+        <v>7112</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>0</v>
@@ -19279,12 +19279,12 @@
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S31" s="9" t="inlineStr">
@@ -19305,7 +19305,7 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>1bcb0667c3a3efe864816ea971273f0e1ff48f01</t>
+          <t>91339ed58a9e4347ac017823b498695129a40922</t>
         </is>
       </c>
     </row>
@@ -19319,7 +19319,7 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>1300</v>
+        <v>1495</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>1</v>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Three Queens Lane, Bristol, BS1</t>
+          <t>Baldwin Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -19348,7 +19348,7 @@
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n">
-        <v>20608</v>
+        <v>20848</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>0</v>
@@ -19356,7 +19356,7 @@
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
@@ -19382,7 +19382,7 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>7c9f52e17d949cd3dc79f3eb8c1020a81c729d66</t>
+          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
         </is>
       </c>
     </row>
@@ -24383,7 +24383,7 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>1600</v>
+        <v>2145</v>
       </c>
       <c r="D100" s="8" t="n">
         <v>2</v>
@@ -24398,21 +24398,23 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Ratcliffe Court, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I100" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="n">
+        <v>796</v>
+      </c>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n">
-        <v>20124</v>
+        <v>20820</v>
       </c>
       <c r="O100" s="8" t="n">
         <v>0</v>
@@ -24420,12 +24422,12 @@
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24442,7 +24444,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
+          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
         </is>
       </c>
     </row>
@@ -24456,13 +24458,13 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>2145</v>
+        <v>1999</v>
       </c>
       <c r="D101" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -24471,7 +24473,7 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -24479,15 +24481,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I101" s="8" t="n">
-        <v>796</v>
-      </c>
+      <c r="I101" s="8" t="n"/>
       <c r="J101" s="8" t="n"/>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n">
-        <v>20820</v>
+        <v>20800</v>
       </c>
       <c r="O101" s="8" t="n">
         <v>0</v>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24517,7 +24517,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -24531,10 +24531,10 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1999</v>
+        <v>1670</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="8" t="n">
         <v>1</v>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24554,13 +24554,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="8" t="n"/>
+      <c r="I102" s="8" t="n">
+        <v>485</v>
+      </c>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n">
-        <v>20800</v>
+        <v>21504</v>
       </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
@@ -24573,7 +24575,7 @@
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24590,7 +24592,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -24604,7 +24606,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1670</v>
+        <v>1645</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>1</v>
@@ -24619,7 +24621,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24628,14 +24630,14 @@
         </is>
       </c>
       <c r="I103" s="8" t="n">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O103" s="8" t="n">
         <v>0</v>
@@ -24648,7 +24650,7 @@
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24665,7 +24667,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
         </is>
       </c>
     </row>
@@ -24679,13 +24681,13 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1645</v>
+        <v>2120</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
@@ -24703,7 +24705,7 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>517</v>
+        <v>705</v>
       </c>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
@@ -24718,7 +24720,7 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
@@ -24740,7 +24742,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -24754,13 +24756,13 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>2120</v>
+        <v>1645</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -24778,7 +24780,7 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>705</v>
+        <v>571</v>
       </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
@@ -24815,7 +24817,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
         </is>
       </c>
     </row>
@@ -24829,10 +24831,10 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1645</v>
+        <v>2250</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
         <v>1</v>
@@ -24844,7 +24846,7 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Apartments, Bristol, BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -24852,15 +24854,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I106" s="8" t="n">
-        <v>571</v>
-      </c>
+      <c r="I106" s="8" t="n"/>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
       <c r="N106" s="8" t="n">
-        <v>20820</v>
+        <v>22132</v>
       </c>
       <c r="O106" s="8" t="n">
         <v>0</v>
@@ -24873,7 +24873,7 @@
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24890,7 +24890,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
+          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
         </is>
       </c>
     </row>
@@ -24904,7 +24904,7 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>2250</v>
+        <v>1600</v>
       </c>
       <c r="D107" s="8" t="n">
         <v>2</v>
@@ -24919,12 +24919,12 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Apartments, Bristol, BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I107" s="8" t="n"/>
@@ -24933,7 +24933,7 @@
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n">
-        <v>22132</v>
+        <v>19576</v>
       </c>
       <c r="O107" s="8" t="n">
         <v>0</v>
@@ -24941,7 +24941,7 @@
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
@@ -24963,7 +24963,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
+          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
         </is>
       </c>
     </row>
@@ -24983,7 +24983,7 @@
         <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
@@ -24992,12 +24992,12 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Ratcliffe Court, Bristol, BS2</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I108" s="8" t="n"/>
@@ -25006,7 +25006,7 @@
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>19576</v>
+        <v>20124</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
@@ -25036,7 +25036,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
+          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
         </is>
       </c>
     </row>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W205"/>
+  <dimension ref="A1:W206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17249,7 +17249,7 @@
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n">
-        <v>21660</v>
+        <v>21616</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>0</v>
@@ -19242,7 +19242,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1300</v>
+        <v>1555</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>1</v>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>St. Johns Lane, Bedminster, BS3</t>
+          <t>Lombard Street, Bristol, BS3</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -19271,7 +19271,7 @@
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n">
-        <v>7112</v>
+        <v>12036</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>0</v>
@@ -19279,12 +19279,12 @@
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S31" s="9" t="inlineStr">
@@ -19305,7 +19305,7 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>91339ed58a9e4347ac017823b498695129a40922</t>
+          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
         </is>
       </c>
     </row>
@@ -19319,7 +19319,7 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>1495</v>
+        <v>1300</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>1</v>
@@ -19334,12 +19334,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, Somerset, BS1</t>
+          <t>St. Johns Lane, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -19348,7 +19348,7 @@
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n">
-        <v>20848</v>
+        <v>7112</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>0</v>
@@ -19356,17 +19356,17 @@
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T32" s="12" t="inlineStr">
@@ -19382,7 +19382,7 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
+          <t>91339ed58a9e4347ac017823b498695129a40922</t>
         </is>
       </c>
     </row>
@@ -19396,7 +19396,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>1733</v>
+        <v>1495</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>1</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Cheltenham House, Clare Street, Bristol</t>
+          <t>Baldwin Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -19419,26 +19419,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I33" s="8" t="n">
-        <v>455</v>
-      </c>
+      <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
+      <c r="N33" s="8" t="n">
+        <v>20848</v>
+      </c>
       <c r="O33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S33" s="9" t="inlineStr">
@@ -19459,7 +19459,7 @@
       <c r="V33" s="7" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
+          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
         </is>
       </c>
     </row>
@@ -19473,7 +19473,7 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>1400</v>
+        <v>1733</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>1</v>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Number One Bristol, BS1 2NR</t>
+          <t>Cheltenham House, Clare Street, Bristol</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -19497,32 +19497,30 @@
         </is>
       </c>
       <c r="I34" s="8" t="n">
-        <v>527</v>
+        <v>455</v>
       </c>
       <c r="J34" s="8" t="n"/>
       <c r="K34" s="8" t="n"/>
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
-      <c r="N34" s="8" t="n">
-        <v>21804</v>
-      </c>
+      <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S34" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T34" s="12" t="inlineStr">
@@ -19538,7 +19536,7 @@
       <c r="V34" s="7" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>27b085b9bcbec967c008845a19f54e272fc12b87</t>
+          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
         </is>
       </c>
     </row>
@@ -19552,13 +19550,13 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>2200</v>
+        <v>1400</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
@@ -19567,21 +19565,23 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Stillhouse lane</t>
+          <t>City Centre, Number One Bristol, BS1 2NR</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>527</v>
+      </c>
       <c r="J35" s="8" t="n"/>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n">
-        <v>14304</v>
+        <v>21804</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>0</v>
@@ -19589,17 +19589,17 @@
       <c r="P35" s="8" t="n"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S35" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T35" s="12" t="inlineStr">
@@ -19615,7 +19615,7 @@
       <c r="V35" s="7" t="inlineStr"/>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>5cd63c65fc4cff6a9795b3661298e348456cd9ae</t>
+          <t>27b085b9bcbec967c008845a19f54e272fc12b87</t>
         </is>
       </c>
     </row>
@@ -19629,13 +19629,13 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
@@ -19644,23 +19644,21 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
+          <t>Stillhouse lane</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>1033</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="n"/>
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n">
-        <v>20348</v>
+        <v>14304</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>0</v>
@@ -19673,7 +19671,7 @@
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S36" s="9" t="inlineStr">
@@ -19694,7 +19692,7 @@
       <c r="V36" s="7" t="inlineStr"/>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
+          <t>5cd63c65fc4cff6a9795b3661298e348456cd9ae</t>
         </is>
       </c>
     </row>
@@ -19708,13 +19706,13 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
@@ -19723,23 +19721,23 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>North Road, St. Andrews, BS6</t>
+          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>420</v>
+        <v>1033</v>
       </c>
       <c r="J37" s="8" t="n"/>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n">
-        <v>8012</v>
+        <v>20348</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>0</v>
@@ -19747,12 +19745,12 @@
       <c r="P37" s="8" t="n"/>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S37" s="9" t="inlineStr">
@@ -19773,7 +19771,7 @@
       <c r="V37" s="7" t="inlineStr"/>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
+          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
         </is>
       </c>
     </row>
@@ -19802,21 +19800,23 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Boot Lane - Bedminster</t>
+          <t>North Road, St. Andrews, BS6</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="n"/>
+          <t>BS6</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>420</v>
+      </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n">
-        <v>15180</v>
+        <v>8012</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>0</v>
@@ -19824,12 +19824,12 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S38" s="9" t="inlineStr">
@@ -19850,7 +19850,7 @@
       <c r="V38" s="7" t="inlineStr"/>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
+          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>1</v>
@@ -19879,12 +19879,12 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Redfield, Bristol</t>
+          <t>Boot Lane - Bedminster</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -19893,7 +19893,7 @@
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n">
-        <v>9192</v>
+        <v>15180</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>0</v>
@@ -19906,12 +19906,12 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S39" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T39" s="12" t="inlineStr">
@@ -19927,7 +19927,7 @@
       <c r="V39" s="7" t="inlineStr"/>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
+          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>1</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
+          <t>Church Road, Redfield, Bristol</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -19970,7 +19970,7 @@
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n">
-        <v>4996</v>
+        <v>9192</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>0</v>
@@ -19978,17 +19978,17 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S40" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T40" s="12" t="inlineStr">
@@ -20004,7 +20004,7 @@
       <c r="V40" s="7" t="inlineStr"/>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
+          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>1</v>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Bristol, BS5</t>
+          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -20055,12 +20055,12 @@
       <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S41" s="9" t="inlineStr">
@@ -20081,7 +20081,7 @@
       <c r="V41" s="7" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
+          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
         </is>
       </c>
     </row>
@@ -20110,12 +20110,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Manor Road, Bishopston, Bristol</t>
+          <t>Butlers Close, Bristol, BS5</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -20124,7 +20124,7 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n">
-        <v>5396</v>
+        <v>4996</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>0</v>
@@ -20132,12 +20132,12 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S42" s="9" t="inlineStr">
@@ -20158,7 +20158,7 @@
       <c r="V42" s="7" t="inlineStr"/>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
+          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
         </is>
       </c>
     </row>
@@ -20172,7 +20172,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>1</v>
@@ -20187,23 +20187,21 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>Marlborough Street, Eastville, Bristol</t>
+          <t>Manor Road, Bishopston, Bristol</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>366</v>
-      </c>
+          <t>BS7</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n">
-        <v>7920</v>
+        <v>5396</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>0</v>
@@ -20211,17 +20209,17 @@
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S43" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T43" s="12" t="inlineStr">
@@ -20237,7 +20235,7 @@
       <c r="V43" s="7" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
+          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
         </is>
       </c>
     </row>
@@ -20251,7 +20249,7 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>975</v>
+        <v>1200</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>1</v>
@@ -20266,7 +20264,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
+          <t>Marlborough Street, Eastville, Bristol</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -20274,13 +20272,15 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I44" s="8" t="n"/>
+      <c r="I44" s="8" t="n">
+        <v>366</v>
+      </c>
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n">
-        <v>7804</v>
+        <v>7920</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>0</v>
@@ -20293,12 +20293,12 @@
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>Northwood, Bristol</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S44" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T44" s="12" t="inlineStr">
@@ -20314,7 +20314,7 @@
       <c r="V44" s="7" t="inlineStr"/>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
+          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
+          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -20357,7 +20357,7 @@
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n">
-        <v>8640</v>
+        <v>7804</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>0</v>
@@ -20365,17 +20365,17 @@
       <c r="P45" s="8" t="n"/>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Northwood, Bristol</t>
         </is>
       </c>
       <c r="S45" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T45" s="12" t="inlineStr">
@@ -20391,7 +20391,7 @@
       <c r="V45" s="7" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
+          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
         </is>
       </c>
     </row>
@@ -20405,7 +20405,7 @@
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>1100</v>
+        <v>975</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>1</v>
@@ -20420,12 +20420,12 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>Ravenswood Road, Bristol, BS6</t>
+          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -20434,7 +20434,7 @@
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n">
-        <v>16556</v>
+        <v>8640</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>0</v>
@@ -20442,17 +20442,17 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S46" s="9" t="inlineStr">
         <is>
-          <t>bills included</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T46" s="12" t="inlineStr">
@@ -20468,13 +20468,13 @@
       <c r="V46" s="7" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
+          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>1</v>
@@ -20497,12 +20497,12 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Ravenswood Road, Bristol, BS6</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -20511,7 +20511,7 @@
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n">
-        <v>19980</v>
+        <v>16556</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>0</v>
@@ -20519,15 +20519,19 @@
       <c r="P47" s="8" t="n"/>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
-        </is>
-      </c>
-      <c r="S47" s="9" t="inlineStr"/>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S47" s="9" t="inlineStr">
+        <is>
+          <t>bills included</t>
+        </is>
+      </c>
       <c r="T47" s="12" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -20541,7 +20545,7 @@
       <c r="V47" s="7" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
         </is>
       </c>
     </row>
@@ -20555,7 +20559,7 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>1</v>
@@ -20570,12 +20574,12 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -20584,7 +20588,7 @@
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n">
-        <v>15212</v>
+        <v>19980</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>0</v>
@@ -20592,12 +20596,12 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S48" s="9" t="inlineStr"/>
@@ -20614,7 +20618,7 @@
       <c r="V48" s="7" t="inlineStr"/>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -20628,7 +20632,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>1</v>
@@ -20643,12 +20647,12 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol, BS4</t>
+          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -20657,7 +20661,7 @@
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n">
-        <v>6852</v>
+        <v>15212</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>0</v>
@@ -20665,12 +20669,12 @@
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S49" s="9" t="inlineStr"/>
@@ -20687,7 +20691,7 @@
       <c r="V49" s="7" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
+          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
         </is>
       </c>
     </row>
@@ -20701,7 +20705,7 @@
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>1640</v>
+        <v>1200</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>1</v>
@@ -20716,23 +20720,21 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Knowle Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>484</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n">
-        <v>21504</v>
+        <v>6852</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>0</v>
@@ -20740,12 +20742,12 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S50" s="9" t="inlineStr"/>
@@ -20762,7 +20764,7 @@
       <c r="V50" s="7" t="inlineStr"/>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
+          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
         </is>
       </c>
     </row>
@@ -20776,7 +20778,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>1</v>
@@ -20791,7 +20793,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -20799,13 +20801,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I51" s="8" t="n"/>
+      <c r="I51" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J51" s="8" t="n"/>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n">
-        <v>16708</v>
+        <v>21504</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>0</v>
@@ -20813,12 +20817,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr"/>
@@ -20835,7 +20839,7 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
+          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20853,7 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>1</v>
@@ -20864,12 +20868,12 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court - City Centre</t>
+          <t>Hope Quay, Wapping Wharf</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -20878,7 +20882,7 @@
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n">
-        <v>21616</v>
+        <v>16708</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>0</v>
@@ -20891,7 +20895,7 @@
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr"/>
@@ -20908,7 +20912,7 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
+          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
         </is>
       </c>
     </row>
@@ -20922,10 +20926,10 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>2200</v>
+        <v>1300</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>1</v>
@@ -20937,7 +20941,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Hamilton Court - City Centre</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -20951,7 +20955,7 @@
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n">
-        <v>21984</v>
+        <v>21616</v>
       </c>
       <c r="O53" s="8" t="n">
         <v>0</v>
@@ -20959,12 +20963,12 @@
       <c r="P53" s="8" t="n"/>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R53" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S53" s="9" t="inlineStr"/>
@@ -20981,7 +20985,7 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
+          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
         </is>
       </c>
     </row>
@@ -20995,13 +20999,13 @@
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="D54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -21018,9 +21022,7 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I54" s="8" t="n">
-        <v>757</v>
-      </c>
+      <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="n"/>
@@ -21056,7 +21058,7 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
+          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
         </is>
       </c>
     </row>
@@ -21085,7 +21087,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -21093,7 +21095,9 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I55" s="8" t="n"/>
+      <c r="I55" s="8" t="n">
+        <v>757</v>
+      </c>
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="8" t="n"/>
@@ -21129,7 +21133,7 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
+          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
         </is>
       </c>
     </row>
@@ -21143,13 +21147,13 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>2095</v>
+        <v>2300</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
@@ -21158,7 +21162,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -21202,7 +21206,7 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
+          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
         </is>
       </c>
     </row>
@@ -21216,10 +21220,10 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>1400</v>
+        <v>2095</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>1</v>
@@ -21231,12 +21235,12 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -21245,7 +21249,7 @@
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n">
-        <v>20908</v>
+        <v>21984</v>
       </c>
       <c r="O57" s="8" t="n">
         <v>0</v>
@@ -21253,12 +21257,12 @@
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr"/>
@@ -21275,7 +21279,7 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
         </is>
       </c>
     </row>
@@ -21289,10 +21293,10 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="n">
         <v>1</v>
@@ -21304,12 +21308,12 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -21318,7 +21322,7 @@
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n">
-        <v>21600</v>
+        <v>20908</v>
       </c>
       <c r="O58" s="8" t="n">
         <v>0</v>
@@ -21326,12 +21330,12 @@
       <c r="P58" s="8" t="n"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr"/>
@@ -21348,7 +21352,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -21362,7 +21366,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>2</v>
@@ -21377,7 +21381,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Waterloo Road, Midland Mews, BS2</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -21385,15 +21389,13 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I59" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I59" s="8" t="n"/>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n">
-        <v>20856</v>
+        <v>21600</v>
       </c>
       <c r="O59" s="8" t="n">
         <v>0</v>
@@ -21401,12 +21403,12 @@
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr"/>
@@ -21423,7 +21425,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -21437,13 +21439,13 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>2085</v>
+        <v>1600</v>
       </c>
       <c r="D60" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
@@ -21452,23 +21454,23 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Waterloo Road, Midland Mews, BS2</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O60" s="8" t="n">
         <v>0</v>
@@ -21476,12 +21478,12 @@
       <c r="P60" s="8" t="n"/>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr"/>
@@ -21498,7 +21500,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
         </is>
       </c>
     </row>
@@ -21512,13 +21514,13 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>1640</v>
+        <v>2085</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
@@ -21527,7 +21529,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -21536,14 +21538,14 @@
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>570</v>
+        <v>722</v>
       </c>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -21556,7 +21558,7 @@
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr"/>
@@ -21573,7 +21575,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -21587,10 +21589,10 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>1</v>
@@ -21602,21 +21604,23 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I62" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>570</v>
+      </c>
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -21629,7 +21633,7 @@
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S62" s="9" t="inlineStr"/>
@@ -21646,7 +21650,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -21660,10 +21664,10 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="8" t="n">
         <v>1</v>
@@ -21675,23 +21679,21 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>405</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>20316</v>
+        <v>20856</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21704,7 +21706,7 @@
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21721,7 +21723,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
         </is>
       </c>
     </row>
@@ -21735,13 +21737,13 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>2020</v>
+        <v>1300</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
@@ -21750,7 +21752,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -21759,14 +21761,14 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>764</v>
+        <v>405</v>
       </c>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>20856</v>
+        <v>20316</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21774,12 +21776,12 @@
       <c r="P64" s="8" t="n"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21796,7 +21798,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -21810,7 +21812,7 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>2145</v>
+        <v>2020</v>
       </c>
       <c r="D65" s="8" t="n">
         <v>2</v>
@@ -21825,7 +21827,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -21834,14 +21836,14 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>815</v>
+        <v>764</v>
       </c>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O65" s="8" t="n">
         <v>0</v>
@@ -21854,7 +21856,7 @@
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr"/>
@@ -21871,7 +21873,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21885,13 +21887,13 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>1635</v>
+        <v>2145</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
@@ -21900,7 +21902,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -21909,7 +21911,7 @@
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>486</v>
+        <v>815</v>
       </c>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
@@ -21929,7 +21931,7 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21946,7 +21948,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21960,13 +21962,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1750</v>
+        <v>1635</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21975,23 +21977,23 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>731</v>
+        <v>486</v>
       </c>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>4680</v>
+        <v>21504</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -22004,7 +22006,7 @@
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S67" s="9" t="inlineStr"/>
@@ -22021,7 +22023,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -22035,13 +22037,13 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>2100</v>
+        <v>1750</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -22050,21 +22052,23 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>731</v>
+      </c>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>21148</v>
+        <v>4680</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22072,12 +22076,12 @@
       <c r="P68" s="8" t="n"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22094,7 +22098,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -22108,13 +22112,13 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>2220</v>
+        <v>2100</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -22123,7 +22127,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22131,15 +22135,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="8" t="n">
-        <v>697</v>
-      </c>
+      <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>20820</v>
+        <v>21148</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -22152,7 +22154,7 @@
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22169,7 +22171,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -22183,13 +22185,13 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1300</v>
+        <v>2220</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
@@ -22198,7 +22200,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -22206,13 +22208,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="8" t="n"/>
+      <c r="I70" s="8" t="n">
+        <v>697</v>
+      </c>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n">
-        <v>21428</v>
+        <v>20820</v>
       </c>
       <c r="O70" s="8" t="n">
         <v>0</v>
@@ -22220,12 +22224,12 @@
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S70" s="9" t="inlineStr"/>
@@ -22242,7 +22246,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -22256,7 +22260,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>1</v>
@@ -22271,7 +22275,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22279,15 +22283,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I71" s="8" t="n">
-        <v>548</v>
-      </c>
+      <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n">
-        <v>21504</v>
+        <v>21428</v>
       </c>
       <c r="O71" s="8" t="n">
         <v>0</v>
@@ -22295,12 +22297,12 @@
       <c r="P71" s="8" t="n"/>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22317,7 +22319,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -22331,7 +22333,7 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1615</v>
+        <v>1500</v>
       </c>
       <c r="D72" s="8" t="n">
         <v>1</v>
@@ -22346,7 +22348,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22355,7 +22357,7 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
@@ -22375,7 +22377,7 @@
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22392,7 +22394,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -22406,10 +22408,10 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1965</v>
+        <v>1615</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
         <v>1</v>
@@ -22421,7 +22423,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -22430,7 +22432,7 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>655</v>
+        <v>486</v>
       </c>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
@@ -22445,12 +22447,12 @@
       <c r="P73" s="8" t="n"/>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
@@ -22467,7 +22469,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -22481,13 +22483,13 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>2080</v>
+        <v>1965</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
@@ -22496,7 +22498,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -22505,14 +22507,14 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>705</v>
+        <v>655</v>
       </c>
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O74" s="8" t="n">
         <v>0</v>
@@ -22525,7 +22527,7 @@
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
@@ -22542,7 +22544,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
+          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
         </is>
       </c>
     </row>
@@ -22556,13 +22558,13 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>1400</v>
+        <v>2080</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
@@ -22571,7 +22573,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -22579,13 +22581,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I75" s="8" t="n"/>
+      <c r="I75" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J75" s="8" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="8" t="n">
-        <v>19484</v>
+        <v>20820</v>
       </c>
       <c r="O75" s="8" t="n">
         <v>0</v>
@@ -22598,7 +22602,7 @@
       </c>
       <c r="R75" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S75" s="9" t="inlineStr"/>
@@ -22615,7 +22619,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
         </is>
       </c>
     </row>
@@ -22629,13 +22633,13 @@
         </is>
       </c>
       <c r="C76" s="17" t="n">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
@@ -22644,7 +22648,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol, BS1</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -22652,14 +22656,14 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I76" s="8" t="n">
-        <v>908</v>
-      </c>
+      <c r="I76" s="8" t="n"/>
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="n"/>
-      <c r="N76" s="8" t="n"/>
+      <c r="N76" s="8" t="n">
+        <v>19484</v>
+      </c>
       <c r="O76" s="8" t="n">
         <v>0</v>
       </c>
@@ -22671,7 +22675,7 @@
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>Hello Neighbour, London</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
@@ -22688,7 +22692,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -22702,13 +22706,13 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
@@ -22717,7 +22721,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Welsh Back, Bristol, BS1</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -22726,7 +22730,7 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>705</v>
+        <v>908</v>
       </c>
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
@@ -22739,12 +22743,12 @@
       <c r="P77" s="8" t="n"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Hello Neighbour, London</t>
         </is>
       </c>
       <c r="S77" s="9" t="inlineStr"/>
@@ -22761,7 +22765,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
+          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22779,7 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>2000</v>
+        <v>2020</v>
       </c>
       <c r="D78" s="8" t="n">
         <v>2</v>
@@ -22790,7 +22794,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Eclipse - City Centre</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -22798,7 +22802,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I78" s="8" t="n"/>
+      <c r="I78" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
@@ -22810,12 +22816,12 @@
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
@@ -22832,7 +22838,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
+          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
         </is>
       </c>
     </row>
@@ -22846,13 +22852,13 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>1595</v>
+        <v>2000</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
@@ -22861,7 +22867,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Eclipse - City Centre</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -22869,9 +22875,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I79" s="8" t="n">
-        <v>499</v>
-      </c>
+      <c r="I79" s="8" t="n"/>
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
@@ -22883,12 +22887,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
@@ -22905,7 +22909,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
+          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
         </is>
       </c>
     </row>
@@ -22919,13 +22923,13 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>2085</v>
+        <v>1595</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
@@ -22934,7 +22938,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -22943,7 +22947,7 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>705</v>
+        <v>499</v>
       </c>
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
@@ -22956,12 +22960,12 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S80" s="9" t="inlineStr"/>
@@ -22978,7 +22982,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
+          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
         </is>
       </c>
     </row>
@@ -22992,13 +22996,13 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>1615</v>
+        <v>2085</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
@@ -23007,7 +23011,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -23016,7 +23020,7 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>487</v>
+        <v>705</v>
       </c>
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
@@ -23034,7 +23038,7 @@
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
@@ -23051,7 +23055,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
         </is>
       </c>
     </row>
@@ -23065,13 +23069,13 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>2065</v>
+        <v>1615</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
@@ -23080,7 +23084,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -23089,7 +23093,7 @@
         </is>
       </c>
       <c r="I82" s="8" t="n">
-        <v>641</v>
+        <v>487</v>
       </c>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
@@ -23102,12 +23106,12 @@
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S82" s="9" t="inlineStr"/>
@@ -23124,7 +23128,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -23138,7 +23142,7 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>2185</v>
+        <v>2065</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>2</v>
@@ -23153,7 +23157,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -23162,7 +23166,7 @@
         </is>
       </c>
       <c r="I83" s="8" t="n">
-        <v>721</v>
+        <v>641</v>
       </c>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
@@ -23180,7 +23184,7 @@
       </c>
       <c r="R83" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S83" s="9" t="inlineStr"/>
@@ -23197,7 +23201,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -23211,13 +23215,13 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>1565</v>
+        <v>2185</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
@@ -23235,7 +23239,7 @@
         </is>
       </c>
       <c r="I84" s="8" t="n">
-        <v>484</v>
+        <v>721</v>
       </c>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
@@ -23270,7 +23274,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -23284,7 +23288,7 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1650</v>
+        <v>1565</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>1</v>
@@ -23299,7 +23303,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -23307,7 +23311,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I85" s="8" t="n"/>
+      <c r="I85" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
@@ -23319,12 +23325,12 @@
       <c r="P85" s="8" t="n"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
@@ -23341,7 +23347,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -23355,7 +23361,7 @@
         </is>
       </c>
       <c r="C86" s="17" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>1</v>
@@ -23370,7 +23376,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Horizon, Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -23378,9 +23384,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I86" s="8" t="n">
-        <v>485</v>
-      </c>
+      <c r="I86" s="8" t="n"/>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
@@ -23397,7 +23401,7 @@
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
@@ -23414,7 +23418,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -23428,13 +23432,13 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>2175</v>
+        <v>1625</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
@@ -23452,7 +23456,7 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>722</v>
+        <v>485</v>
       </c>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
@@ -23465,7 +23469,7 @@
       <c r="P87" s="8" t="n"/>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr">
@@ -23487,7 +23491,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -23501,13 +23505,13 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>2100</v>
+        <v>2175</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
@@ -23516,7 +23520,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -23524,7 +23528,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I88" s="8" t="n"/>
+      <c r="I88" s="8" t="n">
+        <v>722</v>
+      </c>
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
@@ -23536,12 +23542,12 @@
       <c r="P88" s="8" t="n"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
@@ -23558,7 +23564,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -23572,13 +23578,13 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
@@ -23587,7 +23593,7 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -23607,12 +23613,12 @@
       <c r="P89" s="8" t="n"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S89" s="9" t="inlineStr"/>
@@ -23629,7 +23635,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -23643,13 +23649,13 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>1660</v>
+        <v>1900</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
@@ -23658,7 +23664,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -23666,28 +23672,24 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I90" s="8" t="n">
-        <v>486</v>
-      </c>
+      <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
-      <c r="N90" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N90" s="8" t="n"/>
       <c r="O90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="8" t="n"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23704,7 +23706,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -23718,13 +23720,13 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>2175</v>
+        <v>1660</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
@@ -23733,7 +23735,7 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -23742,7 +23744,7 @@
         </is>
       </c>
       <c r="I91" s="8" t="n">
-        <v>814</v>
+        <v>486</v>
       </c>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
@@ -23762,7 +23764,7 @@
       </c>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr"/>
@@ -23779,7 +23781,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -23793,7 +23795,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>1500</v>
+        <v>2175</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>2</v>
@@ -23808,7 +23810,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -23816,13 +23818,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I92" s="8" t="n"/>
+      <c r="I92" s="8" t="n">
+        <v>814</v>
+      </c>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n">
-        <v>21816</v>
+        <v>21504</v>
       </c>
       <c r="O92" s="8" t="n">
         <v>0</v>
@@ -23835,7 +23839,7 @@
       </c>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S92" s="9" t="inlineStr"/>
@@ -23852,7 +23856,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -23866,7 +23870,7 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>2115</v>
+        <v>1500</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>2</v>
@@ -23881,7 +23885,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -23889,15 +23893,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I93" s="8" t="n">
-        <v>823</v>
-      </c>
+      <c r="I93" s="8" t="n"/>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
       <c r="M93" s="8" t="n"/>
       <c r="N93" s="8" t="n">
-        <v>20820</v>
+        <v>21816</v>
       </c>
       <c r="O93" s="8" t="n">
         <v>0</v>
@@ -23905,12 +23907,12 @@
       <c r="P93" s="8" t="n"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S93" s="9" t="inlineStr"/>
@@ -23927,7 +23929,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -23941,13 +23943,13 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1660</v>
+        <v>2115</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
@@ -23956,7 +23958,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -23965,14 +23967,14 @@
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>486</v>
+        <v>823</v>
       </c>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O94" s="8" t="n">
         <v>0</v>
@@ -23985,7 +23987,7 @@
       </c>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S94" s="9" t="inlineStr"/>
@@ -24002,7 +24004,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -24016,13 +24018,13 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>1915</v>
+        <v>1660</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
@@ -24031,7 +24033,7 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -24040,14 +24042,14 @@
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>746</v>
+        <v>486</v>
       </c>
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="8" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O95" s="8" t="n">
         <v>0</v>
@@ -24060,7 +24062,7 @@
       </c>
       <c r="R95" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S95" s="9" t="inlineStr"/>
@@ -24077,7 +24079,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -24091,13 +24093,13 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>1150</v>
+        <v>1915</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
@@ -24106,21 +24108,23 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I96" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="n">
+        <v>746</v>
+      </c>
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n">
-        <v>6872</v>
+        <v>21680</v>
       </c>
       <c r="O96" s="8" t="n">
         <v>0</v>
@@ -24128,12 +24132,12 @@
       <c r="P96" s="8" t="n"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S96" s="9" t="inlineStr"/>
@@ -24150,7 +24154,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -24164,13 +24168,13 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>2450</v>
+        <v>1150</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
@@ -24179,12 +24183,12 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I97" s="8" t="n"/>
@@ -24193,7 +24197,7 @@
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n">
-        <v>21788</v>
+        <v>6872</v>
       </c>
       <c r="O97" s="8" t="n">
         <v>0</v>
@@ -24206,7 +24210,7 @@
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24223,7 +24227,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -24237,10 +24241,10 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>1700</v>
+        <v>2450</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" s="8" t="n">
         <v>2</v>
@@ -24252,7 +24256,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>The Crescent</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -24266,7 +24270,7 @@
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n">
-        <v>16368</v>
+        <v>21788</v>
       </c>
       <c r="O98" s="8" t="n">
         <v>0</v>
@@ -24279,7 +24283,7 @@
       </c>
       <c r="R98" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S98" s="9" t="inlineStr"/>
@@ -24296,7 +24300,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -24310,13 +24314,13 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>1250</v>
+        <v>1700</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
@@ -24325,7 +24329,7 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>The Crescent</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -24339,7 +24343,7 @@
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n">
-        <v>21160</v>
+        <v>16368</v>
       </c>
       <c r="O99" s="8" t="n">
         <v>0</v>
@@ -24352,7 +24356,7 @@
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24369,7 +24373,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
         </is>
       </c>
     </row>
@@ -24383,13 +24387,13 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>2145</v>
+        <v>1250</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
@@ -24398,7 +24402,7 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -24406,15 +24410,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I100" s="8" t="n">
-        <v>796</v>
-      </c>
+      <c r="I100" s="8" t="n"/>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n">
-        <v>20820</v>
+        <v>21160</v>
       </c>
       <c r="O100" s="8" t="n">
         <v>0</v>
@@ -24422,12 +24424,12 @@
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24444,7 +24446,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -24458,13 +24460,13 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>1999</v>
+        <v>2145</v>
       </c>
       <c r="D101" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -24473,7 +24475,7 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -24481,13 +24483,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I101" s="8" t="n"/>
+      <c r="I101" s="8" t="n">
+        <v>796</v>
+      </c>
       <c r="J101" s="8" t="n"/>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n">
-        <v>20800</v>
+        <v>20820</v>
       </c>
       <c r="O101" s="8" t="n">
         <v>0</v>
@@ -24500,7 +24504,7 @@
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24517,7 +24521,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
         </is>
       </c>
     </row>
@@ -24531,10 +24535,10 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1670</v>
+        <v>1999</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" s="8" t="n">
         <v>1</v>
@@ -24546,7 +24550,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24554,15 +24558,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="8" t="n">
-        <v>485</v>
-      </c>
+      <c r="I102" s="8" t="n"/>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n">
-        <v>21504</v>
+        <v>20800</v>
       </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
@@ -24575,7 +24577,7 @@
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24592,7 +24594,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24608,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1645</v>
+        <v>1670</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>1</v>
@@ -24621,7 +24623,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24630,14 +24632,14 @@
         </is>
       </c>
       <c r="I103" s="8" t="n">
-        <v>517</v>
+        <v>485</v>
       </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O103" s="8" t="n">
         <v>0</v>
@@ -24650,7 +24652,7 @@
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24667,7 +24669,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -24681,13 +24683,13 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>2120</v>
+        <v>1645</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
@@ -24705,7 +24707,7 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>705</v>
+        <v>517</v>
       </c>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
@@ -24720,7 +24722,7 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
@@ -24742,7 +24744,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
         </is>
       </c>
     </row>
@@ -24756,13 +24758,13 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1645</v>
+        <v>2120</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -24780,7 +24782,7 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>571</v>
+        <v>705</v>
       </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
@@ -24817,7 +24819,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -24831,10 +24833,10 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>2250</v>
+        <v>1645</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="8" t="n">
         <v>1</v>
@@ -24846,7 +24848,7 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Apartments, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -24854,13 +24856,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I106" s="8" t="n"/>
+      <c r="I106" s="8" t="n">
+        <v>571</v>
+      </c>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
       <c r="N106" s="8" t="n">
-        <v>22132</v>
+        <v>20820</v>
       </c>
       <c r="O106" s="8" t="n">
         <v>0</v>
@@ -24873,7 +24877,7 @@
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24890,7 +24894,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
+          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
         </is>
       </c>
     </row>
@@ -24904,7 +24908,7 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D107" s="8" t="n">
         <v>2</v>
@@ -24919,12 +24923,12 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Apartments, Bristol, BS1</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I107" s="8" t="n"/>
@@ -24933,7 +24937,7 @@
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n">
-        <v>19576</v>
+        <v>22132</v>
       </c>
       <c r="O107" s="8" t="n">
         <v>0</v>
@@ -24941,7 +24945,7 @@
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
@@ -24963,7 +24967,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
+          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
         </is>
       </c>
     </row>
@@ -24983,7 +24987,7 @@
         <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
@@ -24992,12 +24996,12 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Ratcliffe Court, Bristol, BS2</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I108" s="8" t="n"/>
@@ -25006,7 +25010,7 @@
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>20124</v>
+        <v>19576</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -25014,7 +25018,7 @@
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
@@ -25036,7 +25040,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
+          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25060,7 @@
         <v>2</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
@@ -25065,12 +25069,12 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Ratcliffe Court, Bristol, BS2</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I109" s="8" t="n"/>
@@ -25079,7 +25083,7 @@
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
       <c r="N109" s="8" t="n">
-        <v>19576</v>
+        <v>20124</v>
       </c>
       <c r="O109" s="8" t="n">
         <v>0</v>
@@ -25087,7 +25091,7 @@
       <c r="P109" s="8" t="n"/>
       <c r="Q109" s="8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R109" s="8" t="inlineStr">
@@ -25109,7 +25113,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
+          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
         </is>
       </c>
     </row>
@@ -25123,10 +25127,10 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>2175</v>
+        <v>1600</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>1</v>
@@ -25138,12 +25142,12 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I110" s="8" t="n"/>
@@ -25151,14 +25155,16 @@
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
-      <c r="N110" s="8" t="n"/>
+      <c r="N110" s="8" t="n">
+        <v>19576</v>
+      </c>
       <c r="O110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="8" t="n"/>
       <c r="Q110" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R110" s="8" t="inlineStr">
@@ -25180,7 +25186,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>6a00f91534112c4504453102597619449da3a2c1</t>
+          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
         </is>
       </c>
     </row>
@@ -25194,10 +25200,10 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>1500</v>
+        <v>2175</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>1</v>
@@ -25209,7 +25215,7 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
@@ -25217,9 +25223,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I111" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n"/>
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
@@ -25231,12 +25235,12 @@
       <c r="P111" s="8" t="n"/>
       <c r="Q111" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R111" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S111" s="9" t="inlineStr"/>
@@ -25253,7 +25257,7 @@
       <c r="V111" s="7" t="inlineStr"/>
       <c r="W111" s="8" t="inlineStr">
         <is>
-          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
+          <t>6a00f91534112c4504453102597619449da3a2c1</t>
         </is>
       </c>
     </row>
@@ -25267,13 +25271,13 @@
         </is>
       </c>
       <c r="C112" s="17" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
@@ -25282,7 +25286,7 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>Liberty Gardens, Caledonian Road, BS1</t>
+          <t>Baldwin Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
@@ -25291,7 +25295,7 @@
         </is>
       </c>
       <c r="I112" s="8" t="n">
-        <v>1238</v>
+        <v>721</v>
       </c>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
@@ -25304,12 +25308,12 @@
       <c r="P112" s="8" t="n"/>
       <c r="Q112" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R112" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S112" s="9" t="inlineStr"/>
@@ -25326,7 +25330,7 @@
       <c r="V112" s="7" t="inlineStr"/>
       <c r="W112" s="8" t="inlineStr">
         <is>
-          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
+          <t>02aa80149673ef91597cd6a5dd8c1688c9e61b9f</t>
         </is>
       </c>
     </row>
@@ -25340,13 +25344,13 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>1450</v>
+        <v>2500</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
@@ -25355,15 +25359,17 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>The Old Drill Hall, Bristol, BS2</t>
+          <t>Liberty Gardens, Caledonian Road, BS1</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="n">
+        <v>1238</v>
+      </c>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
@@ -25375,12 +25381,12 @@
       <c r="P113" s="8" t="n"/>
       <c r="Q113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R113" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S113" s="9" t="inlineStr"/>
@@ -25397,7 +25403,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>c847859d6a4555381482a51e75495800df35917d</t>
+          <t>5190fc249258ef945384f72c42f49bfb1154cc31</t>
         </is>
       </c>
     </row>
@@ -25411,7 +25417,7 @@
         </is>
       </c>
       <c r="C114" s="17" t="n">
-        <v>1200</v>
+        <v>1450</v>
       </c>
       <c r="D114" s="8" t="n">
         <v>1</v>
@@ -25426,12 +25432,12 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>The Old Drill Hall, Bristol, BS2</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I114" s="8" t="n"/>
@@ -25439,16 +25445,14 @@
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
-      <c r="N114" s="8" t="n">
-        <v>19576</v>
-      </c>
+      <c r="N114" s="8" t="n"/>
       <c r="O114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="8" t="n"/>
       <c r="Q114" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R114" s="8" t="inlineStr">
@@ -25470,7 +25474,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
+          <t>c847859d6a4555381482a51e75495800df35917d</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25488,7 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1395</v>
+        <v>1200</v>
       </c>
       <c r="D115" s="8" t="n">
         <v>1</v>
@@ -25499,12 +25503,12 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>Hall Floor Flat, Queens Parade</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I115" s="8" t="n"/>
@@ -25513,7 +25517,7 @@
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
       <c r="N115" s="8" t="n">
-        <v>18020</v>
+        <v>19576</v>
       </c>
       <c r="O115" s="8" t="n">
         <v>0</v>
@@ -25521,12 +25525,12 @@
       <c r="P115" s="8" t="n"/>
       <c r="Q115" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R115" s="8" t="inlineStr">
         <is>
-          <t>Flatline Letting and Property Management, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S115" s="9" t="inlineStr"/>
@@ -25543,7 +25547,7 @@
       <c r="V115" s="7" t="inlineStr"/>
       <c r="W115" s="8" t="inlineStr">
         <is>
-          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
+          <t>5d815f051578f3b3e8e13833c866551b7a5fab5d</t>
         </is>
       </c>
     </row>
@@ -25557,7 +25561,7 @@
         </is>
       </c>
       <c r="C116" s="17" t="n">
-        <v>1500</v>
+        <v>1395</v>
       </c>
       <c r="D116" s="8" t="n">
         <v>1</v>
@@ -25572,12 +25576,12 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter Apts, Bristol, BS2</t>
+          <t>Hall Floor Flat, Queens Parade</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I116" s="8" t="n"/>
@@ -25585,19 +25589,21 @@
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
-      <c r="N116" s="8" t="n"/>
+      <c r="N116" s="8" t="n">
+        <v>18020</v>
+      </c>
       <c r="O116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="8" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R116" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Flatline Letting and Property Management, Clifton</t>
         </is>
       </c>
       <c r="S116" s="9" t="inlineStr"/>
@@ -25614,7 +25620,7 @@
       <c r="V116" s="7" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
+          <t>e6af522bcebd8a9b957004592288de3325fd136d</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25634,7 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D117" s="8" t="n">
         <v>1</v>
@@ -25643,12 +25649,12 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>St Johns Lane, Bedminster</t>
+          <t>Kings Quarter Apts, Bristol, BS2</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I117" s="8" t="n"/>
@@ -25663,12 +25669,12 @@
       <c r="P117" s="8" t="n"/>
       <c r="Q117" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R117" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S117" s="9" t="inlineStr"/>
@@ -25685,7 +25691,7 @@
       <c r="V117" s="7" t="inlineStr"/>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
+          <t>16bc60cc8da0726548fa3f99c366675cdb1f42e9</t>
         </is>
       </c>
     </row>
@@ -25699,7 +25705,7 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D118" s="8" t="n">
         <v>1</v>
@@ -25714,36 +25720,32 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>Buchanans Wharf North, Ferry Street, BS1</t>
+          <t>St Johns Lane, Bedminster</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I118" s="8" t="n">
-        <v>431</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="n"/>
       <c r="J118" s="8" t="n"/>
       <c r="K118" s="8" t="n"/>
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
-      <c r="N118" s="8" t="n">
-        <v>20896</v>
-      </c>
+      <c r="N118" s="8" t="n"/>
       <c r="O118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="8" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R118" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S118" s="9" t="inlineStr"/>
@@ -25760,7 +25762,7 @@
       <c r="V118" s="7" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
+          <t>814abaaca9ffc0a6d92064013ab271b3138bf62e</t>
         </is>
       </c>
     </row>
@@ -25774,7 +25776,7 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D119" s="8" t="n">
         <v>1</v>
@@ -25789,7 +25791,7 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol</t>
+          <t>Buchanans Wharf North, Ferry Street, BS1</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -25797,13 +25799,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I119" s="8" t="n"/>
+      <c r="I119" s="8" t="n">
+        <v>431</v>
+      </c>
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
       <c r="N119" s="8" t="n">
-        <v>22196</v>
+        <v>20896</v>
       </c>
       <c r="O119" s="8" t="n">
         <v>0</v>
@@ -25811,12 +25815,12 @@
       <c r="P119" s="8" t="n"/>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R119" s="8" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S119" s="9" t="inlineStr"/>
@@ -25833,7 +25837,7 @@
       <c r="V119" s="7" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
+          <t>5ba1fa8752999be6b821f0504211d7d8eb80ce10</t>
         </is>
       </c>
     </row>
@@ -25847,13 +25851,13 @@
         </is>
       </c>
       <c r="C120" s="17" t="n">
-        <v>2150</v>
+        <v>1500</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
@@ -25862,7 +25866,7 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Eclipse, Bristol</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
@@ -25870,15 +25874,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I120" s="8" t="n">
-        <v>796</v>
-      </c>
+      <c r="I120" s="8" t="n"/>
       <c r="J120" s="8" t="n"/>
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n">
-        <v>20820</v>
+        <v>22196</v>
       </c>
       <c r="O120" s="8" t="n">
         <v>0</v>
@@ -25886,12 +25888,12 @@
       <c r="P120" s="8" t="n"/>
       <c r="Q120" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R120" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S120" s="9" t="inlineStr"/>
@@ -25908,7 +25910,7 @@
       <c r="V120" s="7" t="inlineStr"/>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
+          <t>1f280847ed6fd5479fec83135122bcca82127aca</t>
         </is>
       </c>
     </row>
@@ -25922,13 +25924,13 @@
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1640</v>
+        <v>2150</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
@@ -25937,7 +25939,7 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
@@ -25946,7 +25948,7 @@
         </is>
       </c>
       <c r="I121" s="8" t="n">
-        <v>494</v>
+        <v>796</v>
       </c>
       <c r="J121" s="8" t="n"/>
       <c r="K121" s="8" t="n"/>
@@ -25961,7 +25963,7 @@
       <c r="P121" s="8" t="n"/>
       <c r="Q121" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R121" s="8" t="inlineStr">
@@ -25983,7 +25985,7 @@
       <c r="V121" s="7" t="inlineStr"/>
       <c r="W121" s="8" t="inlineStr">
         <is>
-          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
+          <t>bd2b916fd9a50538d78c666b2f7f13b72365e45d</t>
         </is>
       </c>
     </row>
@@ -25997,7 +25999,7 @@
         </is>
       </c>
       <c r="C122" s="17" t="n">
-        <v>1250</v>
+        <v>1640</v>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
@@ -26012,7 +26014,7 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
@@ -26020,13 +26022,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I122" s="8" t="n"/>
+      <c r="I122" s="8" t="n">
+        <v>494</v>
+      </c>
       <c r="J122" s="8" t="n"/>
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
       <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n">
-        <v>21160</v>
+        <v>20820</v>
       </c>
       <c r="O122" s="8" t="n">
         <v>0</v>
@@ -26034,12 +26038,12 @@
       <c r="P122" s="8" t="n"/>
       <c r="Q122" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R122" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S122" s="9" t="inlineStr"/>
@@ -26056,7 +26060,7 @@
       <c r="V122" s="7" t="inlineStr"/>
       <c r="W122" s="8" t="inlineStr">
         <is>
-          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
+          <t>4befb7bf5d6a442fc0e5e50c91ff416803691ffe</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26074,7 @@
         </is>
       </c>
       <c r="C123" s="17" t="n">
-        <v>1640</v>
+        <v>1250</v>
       </c>
       <c r="D123" s="8" t="n">
         <v>1</v>
@@ -26085,7 +26089,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
@@ -26093,15 +26097,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I123" s="8" t="n">
-        <v>495</v>
-      </c>
+      <c r="I123" s="8" t="n"/>
       <c r="J123" s="8" t="n"/>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n">
-        <v>20820</v>
+        <v>21160</v>
       </c>
       <c r="O123" s="8" t="n">
         <v>0</v>
@@ -26114,7 +26116,7 @@
       </c>
       <c r="R123" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S123" s="9" t="inlineStr"/>
@@ -26131,7 +26133,7 @@
       <c r="V123" s="7" t="inlineStr"/>
       <c r="W123" s="8" t="inlineStr">
         <is>
-          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
+          <t>cec48afdcb3b0f32bf5486882e7064ff473349a5</t>
         </is>
       </c>
     </row>
@@ -26145,13 +26147,13 @@
         </is>
       </c>
       <c r="C124" s="17" t="n">
-        <v>1890</v>
+        <v>1640</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
@@ -26160,7 +26162,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
@@ -26169,14 +26171,14 @@
         </is>
       </c>
       <c r="I124" s="8" t="n">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="J124" s="8" t="n"/>
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
       <c r="M124" s="8" t="n"/>
       <c r="N124" s="8" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O124" s="8" t="n">
         <v>0</v>
@@ -26189,7 +26191,7 @@
       </c>
       <c r="R124" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S124" s="9" t="inlineStr"/>
@@ -26206,7 +26208,7 @@
       <c r="V124" s="7" t="inlineStr"/>
       <c r="W124" s="8" t="inlineStr">
         <is>
-          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
+          <t>a84bda0f5c718d805f89938180ca4961c8b18536</t>
         </is>
       </c>
     </row>
@@ -26220,13 +26222,13 @@
         </is>
       </c>
       <c r="C125" s="17" t="n">
-        <v>1635</v>
+        <v>1890</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
@@ -26235,7 +26237,7 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
@@ -26244,14 +26246,14 @@
         </is>
       </c>
       <c r="I125" s="8" t="n">
-        <v>517</v>
+        <v>702</v>
       </c>
       <c r="J125" s="8" t="n"/>
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
       <c r="M125" s="8" t="n"/>
       <c r="N125" s="8" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O125" s="8" t="n">
         <v>0</v>
@@ -26259,12 +26261,12 @@
       <c r="P125" s="8" t="n"/>
       <c r="Q125" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R125" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S125" s="9" t="inlineStr"/>
@@ -26281,7 +26283,7 @@
       <c r="V125" s="7" t="inlineStr"/>
       <c r="W125" s="8" t="inlineStr">
         <is>
-          <t>acf18902969821dd75405f7916c6929252fb214a</t>
+          <t>1f0a7f3333273547869d931a9745fe155703fa6e</t>
         </is>
       </c>
     </row>
@@ -26295,13 +26297,13 @@
         </is>
       </c>
       <c r="C126" s="17" t="n">
-        <v>1855</v>
+        <v>1635</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
@@ -26310,7 +26312,7 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
@@ -26319,14 +26321,14 @@
         </is>
       </c>
       <c r="I126" s="8" t="n">
-        <v>607</v>
+        <v>517</v>
       </c>
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O126" s="8" t="n">
         <v>0</v>
@@ -26339,7 +26341,7 @@
       </c>
       <c r="R126" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S126" s="9" t="inlineStr"/>
@@ -26356,7 +26358,7 @@
       <c r="V126" s="7" t="inlineStr"/>
       <c r="W126" s="8" t="inlineStr">
         <is>
-          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
+          <t>acf18902969821dd75405f7916c6929252fb214a</t>
         </is>
       </c>
     </row>
@@ -26370,7 +26372,7 @@
         </is>
       </c>
       <c r="C127" s="17" t="n">
-        <v>2180</v>
+        <v>1855</v>
       </c>
       <c r="D127" s="8" t="n">
         <v>2</v>
@@ -26385,7 +26387,7 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
@@ -26394,14 +26396,14 @@
         </is>
       </c>
       <c r="I127" s="8" t="n">
-        <v>767</v>
+        <v>607</v>
       </c>
       <c r="J127" s="8" t="n"/>
       <c r="K127" s="8" t="n"/>
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O127" s="8" t="n">
         <v>0</v>
@@ -26414,7 +26416,7 @@
       </c>
       <c r="R127" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S127" s="9" t="inlineStr"/>
@@ -26431,7 +26433,7 @@
       <c r="V127" s="7" t="inlineStr"/>
       <c r="W127" s="8" t="inlineStr">
         <is>
-          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
+          <t>d8ab1266535e82497069e60d02be4464698a0511</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26447,7 @@
         </is>
       </c>
       <c r="C128" s="17" t="n">
-        <v>2090</v>
+        <v>2180</v>
       </c>
       <c r="D128" s="8" t="n">
         <v>2</v>
@@ -26469,20 +26471,22 @@
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>705</v>
+        <v>767</v>
       </c>
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="n"/>
-      <c r="N128" s="8" t="n"/>
+      <c r="N128" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O128" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="8" t="n"/>
       <c r="Q128" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R128" s="8" t="inlineStr">
@@ -26504,7 +26508,7 @@
       <c r="V128" s="7" t="inlineStr"/>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>f37bb95403b6c94c61951f944bce88c63865f963</t>
+          <t>667abce8d183bc62cc3be92fd69a5561abf50f35</t>
         </is>
       </c>
     </row>
@@ -26518,13 +26522,13 @@
         </is>
       </c>
       <c r="C129" s="17" t="n">
-        <v>1635</v>
+        <v>2090</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
@@ -26542,7 +26546,7 @@
         </is>
       </c>
       <c r="I129" s="8" t="n">
-        <v>546</v>
+        <v>705</v>
       </c>
       <c r="J129" s="8" t="n"/>
       <c r="K129" s="8" t="n"/>
@@ -26577,7 +26581,7 @@
       <c r="V129" s="7" t="inlineStr"/>
       <c r="W129" s="8" t="inlineStr">
         <is>
-          <t>36d0812581d3df99e6949e941acc69f0f62aaaf1</t>
+          <t>f37bb95403b6c94c61951f944bce88c63865f963</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26595,7 @@
         </is>
       </c>
       <c r="C130" s="17" t="n">
-        <v>1545</v>
+        <v>1635</v>
       </c>
       <c r="D130" s="8" t="n">
         <v>1</v>
@@ -26606,7 +26610,7 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
@@ -26615,7 +26619,7 @@
         </is>
       </c>
       <c r="I130" s="8" t="n">
-        <v>484</v>
+        <v>546</v>
       </c>
       <c r="J130" s="8" t="n"/>
       <c r="K130" s="8" t="n"/>
@@ -26628,12 +26632,12 @@
       <c r="P130" s="8" t="n"/>
       <c r="Q130" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R130" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S130" s="9" t="inlineStr"/>
@@ -26650,7 +26654,7 @@
       <c r="V130" s="7" t="inlineStr"/>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
+          <t>36d0812581d3df99e6949e941acc69f0f62aaaf1</t>
         </is>
       </c>
     </row>
@@ -26664,13 +26668,13 @@
         </is>
       </c>
       <c r="C131" s="17" t="n">
-        <v>2280</v>
+        <v>1545</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
@@ -26679,7 +26683,7 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
@@ -26688,7 +26692,7 @@
         </is>
       </c>
       <c r="I131" s="8" t="n">
-        <v>885</v>
+        <v>484</v>
       </c>
       <c r="J131" s="8" t="n"/>
       <c r="K131" s="8" t="n"/>
@@ -26706,7 +26710,7 @@
       </c>
       <c r="R131" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S131" s="9" t="inlineStr"/>
@@ -26723,7 +26727,7 @@
       <c r="V131" s="7" t="inlineStr"/>
       <c r="W131" s="8" t="inlineStr">
         <is>
-          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
+          <t>011fad516bf780538b4178c1c9ffdef894ddee3a</t>
         </is>
       </c>
     </row>
@@ -26737,13 +26741,13 @@
         </is>
       </c>
       <c r="C132" s="17" t="n">
-        <v>1630</v>
+        <v>2280</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
@@ -26761,7 +26765,7 @@
         </is>
       </c>
       <c r="I132" s="8" t="n">
-        <v>546</v>
+        <v>885</v>
       </c>
       <c r="J132" s="8" t="n"/>
       <c r="K132" s="8" t="n"/>
@@ -26796,7 +26800,7 @@
       <c r="V132" s="7" t="inlineStr"/>
       <c r="W132" s="8" t="inlineStr">
         <is>
-          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
+          <t>e88181834931577dd3688cc01a75b444cc7b828a</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26838,7 @@
         </is>
       </c>
       <c r="I133" s="8" t="n">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="J133" s="8" t="n"/>
       <c r="K133" s="8" t="n"/>
@@ -26847,7 +26851,7 @@
       <c r="P133" s="8" t="n"/>
       <c r="Q133" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R133" s="8" t="inlineStr">
@@ -26869,7 +26873,7 @@
       <c r="V133" s="7" t="inlineStr"/>
       <c r="W133" s="8" t="inlineStr">
         <is>
-          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
+          <t>0a630af399761fe727a9a385e8885adc0a184512</t>
         </is>
       </c>
     </row>
@@ -26883,13 +26887,13 @@
         </is>
       </c>
       <c r="C134" s="17" t="n">
-        <v>2145</v>
+        <v>1630</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
@@ -26907,7 +26911,7 @@
         </is>
       </c>
       <c r="I134" s="8" t="n">
-        <v>713</v>
+        <v>517</v>
       </c>
       <c r="J134" s="8" t="n"/>
       <c r="K134" s="8" t="n"/>
@@ -26920,7 +26924,7 @@
       <c r="P134" s="8" t="n"/>
       <c r="Q134" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R134" s="8" t="inlineStr">
@@ -26942,7 +26946,7 @@
       <c r="V134" s="7" t="inlineStr"/>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>6e6f162488026493723e3419801548c31fd0e534</t>
+          <t>76d2e1a20991a640c0842b1b569842b6440e16ca</t>
         </is>
       </c>
     </row>
@@ -26956,7 +26960,7 @@
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>2155</v>
+        <v>2145</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>2</v>
@@ -26980,7 +26984,7 @@
         </is>
       </c>
       <c r="I135" s="8" t="n">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="J135" s="8" t="n"/>
       <c r="K135" s="8" t="n"/>
@@ -26993,7 +26997,7 @@
       <c r="P135" s="8" t="n"/>
       <c r="Q135" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R135" s="8" t="inlineStr">
@@ -27015,7 +27019,7 @@
       <c r="V135" s="7" t="inlineStr"/>
       <c r="W135" s="8" t="inlineStr">
         <is>
-          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
+          <t>6e6f162488026493723e3419801548c31fd0e534</t>
         </is>
       </c>
     </row>
@@ -27029,13 +27033,13 @@
         </is>
       </c>
       <c r="C136" s="17" t="n">
-        <v>1700</v>
+        <v>2155</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
@@ -27044,7 +27048,7 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
@@ -27052,26 +27056,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I136" s="8" t="n"/>
+      <c r="I136" s="8" t="n">
+        <v>697</v>
+      </c>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
-      <c r="N136" s="8" t="n">
-        <v>21096</v>
-      </c>
+      <c r="N136" s="8" t="n"/>
       <c r="O136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="8" t="n"/>
       <c r="Q136" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R136" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S136" s="9" t="inlineStr"/>
@@ -27088,7 +27092,7 @@
       <c r="V136" s="7" t="inlineStr"/>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
+          <t>487d14778bce8db3fa213abd54e4d172bacd168a</t>
         </is>
       </c>
     </row>
@@ -27102,13 +27106,13 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="D137" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
@@ -27117,7 +27121,7 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
@@ -27125,26 +27129,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I137" s="8" t="n">
-        <v>624</v>
-      </c>
+      <c r="I137" s="8" t="n"/>
       <c r="J137" s="8" t="n"/>
       <c r="K137" s="8" t="n"/>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
-      <c r="N137" s="8" t="n"/>
+      <c r="N137" s="8" t="n">
+        <v>21096</v>
+      </c>
       <c r="O137" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="8" t="n"/>
       <c r="Q137" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R137" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S137" s="9" t="inlineStr"/>
@@ -27161,7 +27165,7 @@
       <c r="V137" s="7" t="inlineStr"/>
       <c r="W137" s="8" t="inlineStr">
         <is>
-          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
+          <t>81c5cff59ffc26cbab314aad4966fcf24673b018</t>
         </is>
       </c>
     </row>
@@ -27175,13 +27179,13 @@
         </is>
       </c>
       <c r="C138" s="17" t="n">
-        <v>1540</v>
+        <v>1600</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
@@ -27190,7 +27194,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Marsh House, Marsh Street, BS1</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
@@ -27199,27 +27203,25 @@
         </is>
       </c>
       <c r="I138" s="8" t="n">
-        <v>451</v>
+        <v>624</v>
       </c>
       <c r="J138" s="8" t="n"/>
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
       <c r="M138" s="8" t="n"/>
-      <c r="N138" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N138" s="8" t="n"/>
       <c r="O138" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="8" t="n"/>
       <c r="Q138" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R138" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S138" s="9" t="inlineStr"/>
@@ -27236,7 +27238,7 @@
       <c r="V138" s="7" t="inlineStr"/>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
+          <t>c81e28d1f292fc02a3d7f94674eacc5eaaf75c7b</t>
         </is>
       </c>
     </row>
@@ -27250,13 +27252,13 @@
         </is>
       </c>
       <c r="C139" s="17" t="n">
-        <v>2095</v>
+        <v>1540</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
@@ -27274,7 +27276,7 @@
         </is>
       </c>
       <c r="I139" s="8" t="n">
-        <v>705</v>
+        <v>451</v>
       </c>
       <c r="J139" s="8" t="n"/>
       <c r="K139" s="8" t="n"/>
@@ -27311,7 +27313,7 @@
       <c r="V139" s="7" t="inlineStr"/>
       <c r="W139" s="8" t="inlineStr">
         <is>
-          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
+          <t>824c36c2d3a0e83cbee4b39af6447bcd28387770</t>
         </is>
       </c>
     </row>
@@ -27325,13 +27327,13 @@
         </is>
       </c>
       <c r="C140" s="17" t="n">
-        <v>1630</v>
+        <v>2095</v>
       </c>
       <c r="D140" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
@@ -27349,7 +27351,7 @@
         </is>
       </c>
       <c r="I140" s="8" t="n">
-        <v>560</v>
+        <v>705</v>
       </c>
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
@@ -27364,7 +27366,7 @@
       <c r="P140" s="8" t="n"/>
       <c r="Q140" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R140" s="8" t="inlineStr">
@@ -27386,7 +27388,7 @@
       <c r="V140" s="7" t="inlineStr"/>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
+          <t>e2c2bae80b390d851516faec1c36e11343db8533</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27402,7 @@
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1250</v>
+        <v>1630</v>
       </c>
       <c r="D141" s="8" t="n">
         <v>1</v>
@@ -27415,21 +27417,23 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>Kings Quarter - City Centre</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I141" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="n">
+        <v>560</v>
+      </c>
       <c r="J141" s="8" t="n"/>
       <c r="K141" s="8" t="n"/>
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n">
-        <v>21812</v>
+        <v>20820</v>
       </c>
       <c r="O141" s="8" t="n">
         <v>0</v>
@@ -27437,12 +27441,12 @@
       <c r="P141" s="8" t="n"/>
       <c r="Q141" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R141" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S141" s="9" t="inlineStr"/>
@@ -27459,7 +27463,7 @@
       <c r="V141" s="7" t="inlineStr"/>
       <c r="W141" s="8" t="inlineStr">
         <is>
-          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
+          <t>0afbcf3acfc8707595a116822a42ea844dc8ad7e</t>
         </is>
       </c>
     </row>
@@ -27473,13 +27477,13 @@
         </is>
       </c>
       <c r="C142" s="17" t="n">
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
@@ -27488,12 +27492,12 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+          <t>Kings Quarter - City Centre</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I142" s="8" t="n"/>
@@ -27502,7 +27506,7 @@
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n">
-        <v>17744</v>
+        <v>21812</v>
       </c>
       <c r="O142" s="8" t="n">
         <v>0</v>
@@ -27510,12 +27514,12 @@
       <c r="P142" s="8" t="n"/>
       <c r="Q142" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R142" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S142" s="9" t="inlineStr"/>
@@ -27532,7 +27536,7 @@
       <c r="V142" s="7" t="inlineStr"/>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+          <t>5fbd2f44945b6c199bb7273fcb0d473f457725e9</t>
         </is>
       </c>
     </row>
@@ -27546,13 +27550,13 @@
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1375</v>
+        <v>1750</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
@@ -27561,7 +27565,7 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
@@ -27574,19 +27578,21 @@
       <c r="K143" s="8" t="n"/>
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
-      <c r="N143" s="8" t="n"/>
+      <c r="N143" s="8" t="n">
+        <v>17744</v>
+      </c>
       <c r="O143" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="8" t="n"/>
       <c r="Q143" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R143" s="8" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S143" s="9" t="inlineStr"/>
@@ -27603,7 +27609,7 @@
       <c r="V143" s="7" t="inlineStr"/>
       <c r="W143" s="8" t="inlineStr">
         <is>
-          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
+          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
         </is>
       </c>
     </row>
@@ -27617,7 +27623,7 @@
         </is>
       </c>
       <c r="C144" s="17" t="n">
-        <v>1200</v>
+        <v>1375</v>
       </c>
       <c r="D144" s="8" t="n">
         <v>1</v>
@@ -27632,12 +27638,12 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I144" s="8" t="n"/>
@@ -27645,21 +27651,19 @@
       <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
       <c r="M144" s="8" t="n"/>
-      <c r="N144" s="8" t="n">
-        <v>8636</v>
-      </c>
+      <c r="N144" s="8" t="n"/>
       <c r="O144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="8" t="n"/>
       <c r="Q144" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R144" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S144" s="9" t="inlineStr"/>
@@ -27676,7 +27680,7 @@
       <c r="V144" s="7" t="inlineStr"/>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
+          <t>2e1c6d3bc342a1d942c158aca3d03e3e49209395</t>
         </is>
       </c>
     </row>
@@ -27690,7 +27694,7 @@
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D145" s="8" t="n">
         <v>1</v>
@@ -27705,12 +27709,12 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
+          <t>Alma Road, Flat 6, Clifton, Bristol, BS8</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>BS13</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I145" s="8" t="n"/>
@@ -27719,7 +27723,7 @@
       <c r="L145" s="8" t="n"/>
       <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n">
-        <v>4936</v>
+        <v>8636</v>
       </c>
       <c r="O145" s="8" t="n">
         <v>0</v>
@@ -27732,7 +27736,7 @@
       </c>
       <c r="R145" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S145" s="9" t="inlineStr"/>
@@ -27749,7 +27753,7 @@
       <c r="V145" s="7" t="inlineStr"/>
       <c r="W145" s="8" t="inlineStr">
         <is>
-          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
+          <t>de364d91e6b651d1cfef840c60f9266ca9665382</t>
         </is>
       </c>
     </row>
@@ -27778,12 +27782,12 @@
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>Flat B, City Road, Bristol</t>
+          <t>St Peter's Rise, Headley Park, Bristol, BS13</t>
         </is>
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS13</t>
         </is>
       </c>
       <c r="I146" s="8" t="n"/>
@@ -27792,7 +27796,7 @@
       <c r="L146" s="8" t="n"/>
       <c r="M146" s="8" t="n"/>
       <c r="N146" s="8" t="n">
-        <v>20108</v>
+        <v>4936</v>
       </c>
       <c r="O146" s="8" t="n">
         <v>0</v>
@@ -27805,7 +27809,7 @@
       </c>
       <c r="R146" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S146" s="9" t="inlineStr"/>
@@ -27822,7 +27826,7 @@
       <c r="V146" s="7" t="inlineStr"/>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
+          <t>d84ed54d6320edc245d61712b43d63702c789d06</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27840,7 @@
         </is>
       </c>
       <c r="C147" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D147" s="8" t="n">
         <v>1</v>
@@ -27851,23 +27855,21 @@
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Unity Street, BS1 5HH</t>
+          <t>Flat B, City Road, Bristol</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I147" s="8" t="n">
-        <v>452</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n">
-        <v>20772</v>
+        <v>20108</v>
       </c>
       <c r="O147" s="8" t="n">
         <v>0</v>
@@ -27875,12 +27877,12 @@
       <c r="P147" s="8" t="n"/>
       <c r="Q147" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R147" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S147" s="9" t="inlineStr"/>
@@ -27897,7 +27899,7 @@
       <c r="V147" s="7" t="inlineStr"/>
       <c r="W147" s="8" t="inlineStr">
         <is>
-          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
+          <t>144b3ddc5d76a111148e107efa0e01de8a7835b3</t>
         </is>
       </c>
     </row>
@@ -27914,7 +27916,7 @@
         <v>1200</v>
       </c>
       <c r="D148" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>1</v>
@@ -27926,21 +27928,23 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
+          <t>City Centre, Unity Street, BS1 5HH</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I148" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="n">
+        <v>452</v>
+      </c>
       <c r="J148" s="8" t="n"/>
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
       <c r="N148" s="8" t="n">
-        <v>4160</v>
+        <v>20772</v>
       </c>
       <c r="O148" s="8" t="n">
         <v>0</v>
@@ -27953,7 +27957,7 @@
       </c>
       <c r="R148" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S148" s="9" t="inlineStr"/>
@@ -27970,7 +27974,7 @@
       <c r="V148" s="7" t="inlineStr"/>
       <c r="W148" s="8" t="inlineStr">
         <is>
-          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
+          <t>bc1549c52c7b716065fff0163d60cc723a0ab301</t>
         </is>
       </c>
     </row>
@@ -27984,10 +27988,10 @@
         </is>
       </c>
       <c r="C149" s="17" t="n">
-        <v>965</v>
+        <v>1200</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="8" t="n">
         <v>1</v>
@@ -27999,12 +28003,12 @@
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>Boulevard View, Whitchurch Lane</t>
+          <t>Bull Lane, Crews Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I149" s="8" t="n"/>
@@ -28013,7 +28017,7 @@
       <c r="L149" s="8" t="n"/>
       <c r="M149" s="8" t="n"/>
       <c r="N149" s="8" t="n">
-        <v>5764</v>
+        <v>4160</v>
       </c>
       <c r="O149" s="8" t="n">
         <v>0</v>
@@ -28026,7 +28030,7 @@
       </c>
       <c r="R149" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S149" s="9" t="inlineStr"/>
@@ -28043,7 +28047,7 @@
       <c r="V149" s="7" t="inlineStr"/>
       <c r="W149" s="8" t="inlineStr">
         <is>
-          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
+          <t>297b43bd732a4c243907fc8bc1c888a888e057d1</t>
         </is>
       </c>
     </row>
@@ -28057,7 +28061,7 @@
         </is>
       </c>
       <c r="C150" s="17" t="n">
-        <v>1200</v>
+        <v>965</v>
       </c>
       <c r="D150" s="8" t="n">
         <v>1</v>
@@ -28072,23 +28076,21 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>Braggs Lane, Bristol</t>
+          <t>Boulevard View, Whitchurch Lane</t>
         </is>
       </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I150" s="8" t="n">
-        <v>409</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="n"/>
       <c r="J150" s="8" t="n"/>
       <c r="K150" s="8" t="n"/>
       <c r="L150" s="8" t="n"/>
       <c r="M150" s="8" t="n"/>
       <c r="N150" s="8" t="n">
-        <v>20360</v>
+        <v>5764</v>
       </c>
       <c r="O150" s="8" t="n">
         <v>0</v>
@@ -28101,7 +28103,7 @@
       </c>
       <c r="R150" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S150" s="9" t="inlineStr"/>
@@ -28118,7 +28120,7 @@
       <c r="V150" s="7" t="inlineStr"/>
       <c r="W150" s="8" t="inlineStr">
         <is>
-          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
+          <t>ecef3f674f68cbf8b8e0c35c0fe5f8b0099a6a5b</t>
         </is>
       </c>
     </row>
@@ -28147,7 +28149,7 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>Montague Court, Bristol</t>
+          <t>Braggs Lane, Bristol</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
@@ -28155,13 +28157,15 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I151" s="8" t="n"/>
+      <c r="I151" s="8" t="n">
+        <v>409</v>
+      </c>
       <c r="J151" s="8" t="n"/>
       <c r="K151" s="8" t="n"/>
       <c r="L151" s="8" t="n"/>
       <c r="M151" s="8" t="n"/>
       <c r="N151" s="8" t="n">
-        <v>21632</v>
+        <v>20360</v>
       </c>
       <c r="O151" s="8" t="n">
         <v>0</v>
@@ -28174,7 +28178,7 @@
       </c>
       <c r="R151" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S151" s="9" t="inlineStr"/>
@@ -28191,7 +28195,7 @@
       <c r="V151" s="7" t="inlineStr"/>
       <c r="W151" s="8" t="inlineStr">
         <is>
-          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
+          <t>b7418b86260a082ce0b767afb48615e82b4efe93</t>
         </is>
       </c>
     </row>
@@ -28205,7 +28209,7 @@
         </is>
       </c>
       <c r="C152" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D152" s="8" t="n">
         <v>1</v>
@@ -28220,23 +28224,21 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
+          <t>Montague Court, Bristol</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I152" s="8" t="n">
-        <v>397</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="n"/>
       <c r="J152" s="8" t="n"/>
       <c r="K152" s="8" t="n"/>
       <c r="L152" s="8" t="n"/>
       <c r="M152" s="8" t="n"/>
       <c r="N152" s="8" t="n">
-        <v>15212</v>
+        <v>21632</v>
       </c>
       <c r="O152" s="8" t="n">
         <v>0</v>
@@ -28244,12 +28246,12 @@
       <c r="P152" s="8" t="n"/>
       <c r="Q152" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R152" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S152" s="9" t="inlineStr"/>
@@ -28266,7 +28268,7 @@
       <c r="V152" s="7" t="inlineStr"/>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
+          <t>99885bbff0ab6c180a4c8ba4e0379c6f0ab42f06</t>
         </is>
       </c>
     </row>
@@ -28280,7 +28282,7 @@
         </is>
       </c>
       <c r="C153" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D153" s="8" t="n">
         <v>1</v>
@@ -28295,23 +28297,23 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>Barton Close, St. Annes Park, BS4</t>
+          <t>Bedminster Parade, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I153" s="8" t="n">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="J153" s="8" t="n"/>
       <c r="K153" s="8" t="n"/>
       <c r="L153" s="8" t="n"/>
       <c r="M153" s="8" t="n"/>
       <c r="N153" s="8" t="n">
-        <v>5212</v>
+        <v>15212</v>
       </c>
       <c r="O153" s="8" t="n">
         <v>0</v>
@@ -28324,7 +28326,7 @@
       </c>
       <c r="R153" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S153" s="9" t="inlineStr"/>
@@ -28341,7 +28343,7 @@
       <c r="V153" s="7" t="inlineStr"/>
       <c r="W153" s="8" t="inlineStr">
         <is>
-          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
+          <t>c5ac268b24abaa99234fcf1c93fefdbb7e77813a</t>
         </is>
       </c>
     </row>
@@ -28370,21 +28372,23 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Barton Close, St. Annes Park, BS4</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I154" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="n">
+        <v>441</v>
+      </c>
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
       <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n">
-        <v>7112</v>
+        <v>5212</v>
       </c>
       <c r="O154" s="8" t="n">
         <v>0</v>
@@ -28397,7 +28401,7 @@
       </c>
       <c r="R154" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S154" s="9" t="inlineStr"/>
@@ -28414,7 +28418,7 @@
       <c r="V154" s="7" t="inlineStr"/>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
+          <t>f5910166d7abf794c3d121c920cea7bb7aaab2d9</t>
         </is>
       </c>
     </row>
@@ -28443,23 +28447,21 @@
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>Chapel Street, St Philips, Bristol, BS2</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I155" s="8" t="n">
-        <v>549</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I155" s="8" t="n"/>
       <c r="J155" s="8" t="n"/>
       <c r="K155" s="8" t="n"/>
       <c r="L155" s="8" t="n"/>
       <c r="M155" s="8" t="n"/>
       <c r="N155" s="8" t="n">
-        <v>11732</v>
+        <v>7112</v>
       </c>
       <c r="O155" s="8" t="n">
         <v>0</v>
@@ -28472,7 +28474,7 @@
       </c>
       <c r="R155" s="8" t="inlineStr">
         <is>
-          <t>Morgan &amp; Sons, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S155" s="9" t="inlineStr"/>
@@ -28489,7 +28491,7 @@
       <c r="V155" s="7" t="inlineStr"/>
       <c r="W155" s="8" t="inlineStr">
         <is>
-          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
+          <t>8a0efeef760593a517251fb9f7aa92b7e20ff405</t>
         </is>
       </c>
     </row>
@@ -28503,7 +28505,7 @@
         </is>
       </c>
       <c r="C156" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D156" s="8" t="n">
         <v>1</v>
@@ -28518,23 +28520,23 @@
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
+          <t>Chapel Street, St Philips, Bristol, BS2</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I156" s="8" t="n">
-        <v>211</v>
+        <v>549</v>
       </c>
       <c r="J156" s="8" t="n"/>
       <c r="K156" s="8" t="n"/>
       <c r="L156" s="8" t="n"/>
       <c r="M156" s="8" t="n"/>
       <c r="N156" s="8" t="n">
-        <v>14596</v>
+        <v>11732</v>
       </c>
       <c r="O156" s="8" t="n">
         <v>0</v>
@@ -28542,12 +28544,12 @@
       <c r="P156" s="8" t="n"/>
       <c r="Q156" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R156" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>Morgan &amp; Sons, Bristol</t>
         </is>
       </c>
       <c r="S156" s="9" t="inlineStr"/>
@@ -28564,7 +28566,7 @@
       <c r="V156" s="7" t="inlineStr"/>
       <c r="W156" s="8" t="inlineStr">
         <is>
-          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
+          <t>ef55f6374006e7f3e9b91e752a031c654a098e1f</t>
         </is>
       </c>
     </row>
@@ -28578,7 +28580,7 @@
         </is>
       </c>
       <c r="C157" s="17" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D157" s="8" t="n">
         <v>1</v>
@@ -28593,21 +28595,23 @@
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
+          <t>Harbourside Apartments, 32-34 Hotwell Road, Bristol, BS8</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
-        </is>
-      </c>
-      <c r="I157" s="8" t="n"/>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I157" s="8" t="n">
+        <v>211</v>
+      </c>
       <c r="J157" s="8" t="n"/>
       <c r="K157" s="8" t="n"/>
       <c r="L157" s="8" t="n"/>
       <c r="M157" s="8" t="n"/>
       <c r="N157" s="8" t="n">
-        <v>5316</v>
+        <v>14596</v>
       </c>
       <c r="O157" s="8" t="n">
         <v>0</v>
@@ -28615,12 +28619,12 @@
       <c r="P157" s="8" t="n"/>
       <c r="Q157" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R157" s="8" t="inlineStr">
         <is>
-          <t>Holbrook Moran, Redfield</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S157" s="9" t="inlineStr"/>
@@ -28637,7 +28641,7 @@
       <c r="V157" s="7" t="inlineStr"/>
       <c r="W157" s="8" t="inlineStr">
         <is>
-          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
+          <t>cbabe39dc6d60b35752a40f29ab9452202acb80f</t>
         </is>
       </c>
     </row>
@@ -28666,12 +28670,12 @@
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>Netham Road, St George, Bristol, Bristol City</t>
+          <t>Tortworth Court, Tortworth Road, Horfield, Bristol</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I158" s="8" t="n"/>
@@ -28680,7 +28684,7 @@
       <c r="L158" s="8" t="n"/>
       <c r="M158" s="8" t="n"/>
       <c r="N158" s="8" t="n">
-        <v>7112</v>
+        <v>5316</v>
       </c>
       <c r="O158" s="8" t="n">
         <v>0</v>
@@ -28693,7 +28697,7 @@
       </c>
       <c r="R158" s="8" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Holbrook Moran, Redfield</t>
         </is>
       </c>
       <c r="S158" s="9" t="inlineStr"/>
@@ -28710,7 +28714,7 @@
       <c r="V158" s="7" t="inlineStr"/>
       <c r="W158" s="8" t="inlineStr">
         <is>
-          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
+          <t>a84a17170db7124059e6b156a1ae2181a8dd775e</t>
         </is>
       </c>
     </row>
@@ -28724,7 +28728,7 @@
         </is>
       </c>
       <c r="C159" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D159" s="8" t="n">
         <v>1</v>
@@ -28739,7 +28743,7 @@
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>Seymour Road, Bristol, BS5</t>
+          <t>Netham Road, St George, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
@@ -28747,15 +28751,13 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I159" s="8" t="n">
-        <v>484</v>
-      </c>
+      <c r="I159" s="8" t="n"/>
       <c r="J159" s="8" t="n"/>
       <c r="K159" s="8" t="n"/>
       <c r="L159" s="8" t="n"/>
       <c r="M159" s="8" t="n"/>
       <c r="N159" s="8" t="n">
-        <v>17164</v>
+        <v>7112</v>
       </c>
       <c r="O159" s="8" t="n">
         <v>0</v>
@@ -28763,12 +28765,12 @@
       <c r="P159" s="8" t="n"/>
       <c r="Q159" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R159" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S159" s="9" t="inlineStr"/>
@@ -28785,7 +28787,7 @@
       <c r="V159" s="7" t="inlineStr"/>
       <c r="W159" s="8" t="inlineStr">
         <is>
-          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
+          <t>db2a5e02a3c10590c5cff5921a380c56b0683cc6</t>
         </is>
       </c>
     </row>
@@ -28814,21 +28816,23 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>Pinkhams Twist, Bristol</t>
+          <t>Seymour Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
-        </is>
-      </c>
-      <c r="I160" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I160" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J160" s="8" t="n"/>
       <c r="K160" s="8" t="n"/>
       <c r="L160" s="8" t="n"/>
       <c r="M160" s="8" t="n"/>
       <c r="N160" s="8" t="n">
-        <v>4276</v>
+        <v>17164</v>
       </c>
       <c r="O160" s="8" t="n">
         <v>0</v>
@@ -28836,12 +28840,12 @@
       <c r="P160" s="8" t="n"/>
       <c r="Q160" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R160" s="8" t="inlineStr">
         <is>
-          <t>Hunters, Whitchurch</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S160" s="9" t="inlineStr"/>
@@ -28858,7 +28862,7 @@
       <c r="V160" s="7" t="inlineStr"/>
       <c r="W160" s="8" t="inlineStr">
         <is>
-          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
+          <t>1677ebd43e26e44c6ed83a5fdce71b66bc0f7dad</t>
         </is>
       </c>
     </row>
@@ -28872,7 +28876,7 @@
         </is>
       </c>
       <c r="C161" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D161" s="8" t="n">
         <v>1</v>
@@ -28882,17 +28886,17 @@
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>Alexandra Park, Redland, Bristol, BS6</t>
+          <t>Pinkhams Twist, Bristol</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS14</t>
         </is>
       </c>
       <c r="I161" s="8" t="n"/>
@@ -28901,7 +28905,7 @@
       <c r="L161" s="8" t="n"/>
       <c r="M161" s="8" t="n"/>
       <c r="N161" s="8" t="n">
-        <v>12812</v>
+        <v>4276</v>
       </c>
       <c r="O161" s="8" t="n">
         <v>0</v>
@@ -28914,7 +28918,7 @@
       </c>
       <c r="R161" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Hunters, Whitchurch</t>
         </is>
       </c>
       <c r="S161" s="9" t="inlineStr"/>
@@ -28931,7 +28935,7 @@
       <c r="V161" s="7" t="inlineStr"/>
       <c r="W161" s="8" t="inlineStr">
         <is>
-          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
+          <t>a4ad0b3e107526f57126e848274507d4a2d88310</t>
         </is>
       </c>
     </row>
@@ -28945,7 +28949,7 @@
         </is>
       </c>
       <c r="C162" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D162" s="8" t="n">
         <v>1</v>
@@ -28955,17 +28959,17 @@
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
+          <t>Alexandra Park, Redland, Bristol, BS6</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I162" s="8" t="n"/>
@@ -28974,7 +28978,7 @@
       <c r="L162" s="8" t="n"/>
       <c r="M162" s="8" t="n"/>
       <c r="N162" s="8" t="n">
-        <v>18020</v>
+        <v>12812</v>
       </c>
       <c r="O162" s="8" t="n">
         <v>0</v>
@@ -28987,7 +28991,7 @@
       </c>
       <c r="R162" s="8" t="inlineStr">
         <is>
-          <t>West Coast Properties, Bishopston</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S162" s="9" t="inlineStr"/>
@@ -29004,7 +29008,7 @@
       <c r="V162" s="7" t="inlineStr"/>
       <c r="W162" s="8" t="inlineStr">
         <is>
-          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
+          <t>4bffe5bcc3b220c2e55881771c8cb06946a8f773</t>
         </is>
       </c>
     </row>
@@ -29018,10 +29022,10 @@
         </is>
       </c>
       <c r="C163" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D163" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="8" t="n">
         <v>1</v>
@@ -29033,23 +29037,21 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Bristol, BS5</t>
+          <t>Lower College Street, Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I163" s="8" t="n">
-        <v>3057</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I163" s="8" t="n"/>
       <c r="J163" s="8" t="n"/>
       <c r="K163" s="8" t="n"/>
       <c r="L163" s="8" t="n"/>
       <c r="M163" s="8" t="n"/>
       <c r="N163" s="8" t="n">
-        <v>11864</v>
+        <v>18020</v>
       </c>
       <c r="O163" s="8" t="n">
         <v>0</v>
@@ -29057,12 +29059,12 @@
       <c r="P163" s="8" t="n"/>
       <c r="Q163" s="8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R163" s="8" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>West Coast Properties, Bishopston</t>
         </is>
       </c>
       <c r="S163" s="9" t="inlineStr"/>
@@ -29079,7 +29081,7 @@
       <c r="V163" s="7" t="inlineStr"/>
       <c r="W163" s="8" t="inlineStr">
         <is>
-          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
+          <t>b6b3d8e95529c1ffc6a7e396f88cd883930e9d79</t>
         </is>
       </c>
     </row>
@@ -29093,10 +29095,10 @@
         </is>
       </c>
       <c r="C164" s="17" t="n">
-        <v>995</v>
+        <v>1150</v>
       </c>
       <c r="D164" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="8" t="n">
         <v>1</v>
@@ -29108,21 +29110,23 @@
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>Two Mile Hill Road, Kingswood, Bristol</t>
+          <t>Church Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>BS15</t>
-        </is>
-      </c>
-      <c r="I164" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I164" s="8" t="n">
+        <v>3057</v>
+      </c>
       <c r="J164" s="8" t="n"/>
       <c r="K164" s="8" t="n"/>
       <c r="L164" s="8" t="n"/>
       <c r="M164" s="8" t="n"/>
       <c r="N164" s="8" t="n">
-        <v>5116</v>
+        <v>11864</v>
       </c>
       <c r="O164" s="8" t="n">
         <v>0</v>
@@ -29130,12 +29134,12 @@
       <c r="P164" s="8" t="n"/>
       <c r="Q164" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="R164" s="8" t="inlineStr">
         <is>
-          <t>TLS Estate Agents, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S164" s="9" t="inlineStr"/>
@@ -29152,7 +29156,7 @@
       <c r="V164" s="7" t="inlineStr"/>
       <c r="W164" s="8" t="inlineStr">
         <is>
-          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
+          <t>765c51adc42a96d23086446a7ab5c6c6fb234cca</t>
         </is>
       </c>
     </row>
@@ -29166,7 +29170,7 @@
         </is>
       </c>
       <c r="C165" s="17" t="n">
-        <v>1100</v>
+        <v>995</v>
       </c>
       <c r="D165" s="8" t="n">
         <v>1</v>
@@ -29176,17 +29180,17 @@
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>Robertson Drive, St Annes Park</t>
+          <t>Two Mile Hill Road, Kingswood, Bristol</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS15</t>
         </is>
       </c>
       <c r="I165" s="8" t="n"/>
@@ -29195,7 +29199,7 @@
       <c r="L165" s="8" t="n"/>
       <c r="M165" s="8" t="n"/>
       <c r="N165" s="8" t="n">
-        <v>4252</v>
+        <v>5116</v>
       </c>
       <c r="O165" s="8" t="n">
         <v>0</v>
@@ -29208,7 +29212,7 @@
       </c>
       <c r="R165" s="8" t="inlineStr">
         <is>
-          <t>D W Smith &amp; Company, Hanham</t>
+          <t>TLS Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S165" s="9" t="inlineStr"/>
@@ -29225,7 +29229,7 @@
       <c r="V165" s="7" t="inlineStr"/>
       <c r="W165" s="8" t="inlineStr">
         <is>
-          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
+          <t>4127db1eec9e5102c45835506c359c90057d0332</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29243,7 @@
         </is>
       </c>
       <c r="C166" s="17" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D166" s="8" t="n">
         <v>1</v>
@@ -29249,12 +29253,12 @@
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
+          <t>Robertson Drive, St Annes Park</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
@@ -29262,15 +29266,13 @@
           <t>BS4</t>
         </is>
       </c>
-      <c r="I166" s="8" t="n">
-        <v>527</v>
-      </c>
+      <c r="I166" s="8" t="n"/>
       <c r="J166" s="8" t="n"/>
       <c r="K166" s="8" t="n"/>
       <c r="L166" s="8" t="n"/>
       <c r="M166" s="8" t="n"/>
       <c r="N166" s="8" t="n">
-        <v>5548</v>
+        <v>4252</v>
       </c>
       <c r="O166" s="8" t="n">
         <v>0</v>
@@ -29278,12 +29280,12 @@
       <c r="P166" s="8" t="n"/>
       <c r="Q166" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R166" s="8" t="inlineStr">
         <is>
-          <t>Sheedy &amp; Co, Covering Bristol</t>
+          <t>D W Smith &amp; Company, Hanham</t>
         </is>
       </c>
       <c r="S166" s="9" t="inlineStr"/>
@@ -29300,7 +29302,7 @@
       <c r="V166" s="7" t="inlineStr"/>
       <c r="W166" s="8" t="inlineStr">
         <is>
-          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
+          <t>da7b12e8670a61ba0296492df23cc29a51d7d8e0</t>
         </is>
       </c>
     </row>
@@ -29314,7 +29316,7 @@
         </is>
       </c>
       <c r="C167" s="17" t="n">
-        <v>1195</v>
+        <v>1150</v>
       </c>
       <c r="D167" s="8" t="n">
         <v>1</v>
@@ -29329,23 +29331,23 @@
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>Whitehall Road, Bristol, BS5</t>
+          <t>Flat, Newquay Road, Knowle, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I167" s="8" t="n">
-        <v>409</v>
+        <v>527</v>
       </c>
       <c r="J167" s="8" t="n"/>
       <c r="K167" s="8" t="n"/>
       <c r="L167" s="8" t="n"/>
       <c r="M167" s="8" t="n"/>
       <c r="N167" s="8" t="n">
-        <v>10420</v>
+        <v>5548</v>
       </c>
       <c r="O167" s="8" t="n">
         <v>0</v>
@@ -29353,12 +29355,12 @@
       <c r="P167" s="8" t="n"/>
       <c r="Q167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R167" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>Sheedy &amp; Co, Covering Bristol</t>
         </is>
       </c>
       <c r="S167" s="9" t="inlineStr"/>
@@ -29375,7 +29377,7 @@
       <c r="V167" s="7" t="inlineStr"/>
       <c r="W167" s="8" t="inlineStr">
         <is>
-          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
+          <t>d6e7992bdb7662462ebba6fc8f5a0a065f5c0c34</t>
         </is>
       </c>
     </row>
@@ -29389,7 +29391,7 @@
         </is>
       </c>
       <c r="C168" s="17" t="n">
-        <v>850</v>
+        <v>1195</v>
       </c>
       <c r="D168" s="8" t="n">
         <v>1</v>
@@ -29413,7 +29415,7 @@
         </is>
       </c>
       <c r="I168" s="8" t="n">
-        <v>248</v>
+        <v>409</v>
       </c>
       <c r="J168" s="8" t="n"/>
       <c r="K168" s="8" t="n"/>
@@ -29450,7 +29452,7 @@
       <c r="V168" s="7" t="inlineStr"/>
       <c r="W168" s="8" t="inlineStr">
         <is>
-          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
+          <t>98d53bc43440611cb699e6844ca898806a2f4b28</t>
         </is>
       </c>
     </row>
@@ -29464,13 +29466,13 @@
         </is>
       </c>
       <c r="C169" s="17" t="n">
-        <v>1600</v>
+        <v>850</v>
       </c>
       <c r="D169" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
@@ -29479,21 +29481,23 @@
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>Central Quay North</t>
+          <t>Whitehall Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I169" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I169" s="8" t="n">
+        <v>248</v>
+      </c>
       <c r="J169" s="8" t="n"/>
       <c r="K169" s="8" t="n"/>
       <c r="L169" s="8" t="n"/>
       <c r="M169" s="8" t="n"/>
       <c r="N169" s="8" t="n">
-        <v>20792</v>
+        <v>10420</v>
       </c>
       <c r="O169" s="8" t="n">
         <v>0</v>
@@ -29501,12 +29505,12 @@
       <c r="P169" s="8" t="n"/>
       <c r="Q169" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R169" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S169" s="9" t="inlineStr"/>
@@ -29523,7 +29527,7 @@
       <c r="V169" s="7" t="inlineStr"/>
       <c r="W169" s="8" t="inlineStr">
         <is>
-          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
+          <t>17396b2e44a31a6428a3598c1935528dc4d5bd81</t>
         </is>
       </c>
     </row>
@@ -29552,7 +29556,7 @@
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol</t>
+          <t>Central Quay North</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
@@ -29565,7 +29569,9 @@
       <c r="K170" s="8" t="n"/>
       <c r="L170" s="8" t="n"/>
       <c r="M170" s="8" t="n"/>
-      <c r="N170" s="8" t="n"/>
+      <c r="N170" s="8" t="n">
+        <v>20792</v>
+      </c>
       <c r="O170" s="8" t="n">
         <v>0</v>
       </c>
@@ -29577,7 +29583,7 @@
       </c>
       <c r="R170" s="8" t="inlineStr">
         <is>
-          <t>Stonebridge Shaw, Portishead</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S170" s="9" t="inlineStr"/>
@@ -29594,7 +29600,7 @@
       <c r="V170" s="7" t="inlineStr"/>
       <c r="W170" s="8" t="inlineStr">
         <is>
-          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
+          <t>8419d14a9ba13a5a7785694e74cc8e87937eb3c1</t>
         </is>
       </c>
     </row>
@@ -29608,13 +29614,13 @@
         </is>
       </c>
       <c r="C171" s="17" t="n">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="D171" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
@@ -29623,12 +29629,12 @@
       </c>
       <c r="G171" s="9" t="inlineStr">
         <is>
-          <t>St Michaels Hill Ref 708</t>
+          <t>Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I171" s="8" t="n"/>
@@ -29636,21 +29642,19 @@
       <c r="K171" s="8" t="n"/>
       <c r="L171" s="8" t="n"/>
       <c r="M171" s="8" t="n"/>
-      <c r="N171" s="8" t="n">
-        <v>19512</v>
-      </c>
+      <c r="N171" s="8" t="n"/>
       <c r="O171" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P171" s="8" t="n"/>
       <c r="Q171" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R171" s="8" t="inlineStr">
         <is>
-          <t>Jackson Property Management Ltd, Bristol</t>
+          <t>Stonebridge Shaw, Portishead</t>
         </is>
       </c>
       <c r="S171" s="9" t="inlineStr"/>
@@ -29667,7 +29671,7 @@
       <c r="V171" s="7" t="inlineStr"/>
       <c r="W171" s="8" t="inlineStr">
         <is>
-          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
+          <t>7a1b3f42641b30502df555b92790f9c12b03583c</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29685,7 @@
         </is>
       </c>
       <c r="C172" s="17" t="n">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="D172" s="8" t="n">
         <v>1</v>
@@ -29696,12 +29700,12 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
+          <t>St Michaels Hill Ref 708</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>BS14</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I172" s="8" t="n"/>
@@ -29710,7 +29714,7 @@
       <c r="L172" s="8" t="n"/>
       <c r="M172" s="8" t="n"/>
       <c r="N172" s="8" t="n">
-        <v>2652</v>
+        <v>19512</v>
       </c>
       <c r="O172" s="8" t="n">
         <v>0</v>
@@ -29718,12 +29722,12 @@
       <c r="P172" s="8" t="n"/>
       <c r="Q172" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R172" s="8" t="inlineStr">
         <is>
-          <t>Millennium Lettings &amp; Management, Bristol</t>
+          <t>Jackson Property Management Ltd, Bristol</t>
         </is>
       </c>
       <c r="S172" s="9" t="inlineStr"/>
@@ -29740,7 +29744,7 @@
       <c r="V172" s="7" t="inlineStr"/>
       <c r="W172" s="8" t="inlineStr">
         <is>
-          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+          <t>ad53fb9cd96ec72adbc7f3d6c8a52caba547cc20</t>
         </is>
       </c>
     </row>
@@ -29754,7 +29758,7 @@
         </is>
       </c>
       <c r="C173" s="17" t="n">
-        <v>1200</v>
+        <v>1095</v>
       </c>
       <c r="D173" s="8" t="n">
         <v>1</v>
@@ -29769,23 +29773,21 @@
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>Old Market, Verdigris, BS2 0AF</t>
+          <t>Manor House Lane, Whitchurch, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I173" s="8" t="n">
-        <v>388</v>
-      </c>
+          <t>BS14</t>
+        </is>
+      </c>
+      <c r="I173" s="8" t="n"/>
       <c r="J173" s="8" t="n"/>
       <c r="K173" s="8" t="n"/>
       <c r="L173" s="8" t="n"/>
       <c r="M173" s="8" t="n"/>
       <c r="N173" s="8" t="n">
-        <v>21220</v>
+        <v>2652</v>
       </c>
       <c r="O173" s="8" t="n">
         <v>0</v>
@@ -29793,12 +29795,12 @@
       <c r="P173" s="8" t="n"/>
       <c r="Q173" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R173" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Millennium Lettings &amp; Management, Bristol</t>
         </is>
       </c>
       <c r="S173" s="9" t="inlineStr"/>
@@ -29815,74 +29817,89 @@
       <c r="V173" s="7" t="inlineStr"/>
       <c r="W173" s="8" t="inlineStr">
         <is>
+          <t>ab692cb96ad18ebe26a6d19d737d0b539752370a</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D174" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>Old Market, Verdigris, BS2 0AF</t>
+        </is>
+      </c>
+      <c r="H174" s="8" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I174" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="J174" s="8" t="n"/>
+      <c r="K174" s="8" t="n"/>
+      <c r="L174" s="8" t="n"/>
+      <c r="M174" s="8" t="n"/>
+      <c r="N174" s="8" t="n">
+        <v>21220</v>
+      </c>
+      <c r="O174" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="8" t="n"/>
+      <c r="Q174" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R174" s="8" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S174" s="9" t="inlineStr"/>
+      <c r="T174" s="12" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V174" s="7" t="inlineStr"/>
+      <c r="W174" s="8" t="inlineStr">
+        <is>
           <t>4bd094575ff83a26d208b8ea7ce8140210cc94b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" s="7" t="n"/>
-      <c r="C174" s="18" t="n">
-        <v>800</v>
-      </c>
-      <c r="D174" t="n">
-        <v>2</v>
-      </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>LL11</t>
-        </is>
-      </c>
-      <c r="N174" t="n">
-        <v>448</v>
-      </c>
-      <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S174" s="7" t="inlineStr"/>
-      <c r="T174" s="14" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V174" s="7" t="inlineStr"/>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="7" t="n"/>
       <c r="C175" s="18" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D175" t="n">
         <v>2</v>
@@ -29897,28 +29914,28 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>Rehoboth Court, Coedpoeth, Wrexham, LL11</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>328</v>
+        <v>448</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S175" s="7" t="inlineStr"/>
@@ -29935,17 +29952,17 @@
       <c r="V175" s="7" t="inlineStr"/>
       <c r="W175" t="inlineStr">
         <is>
-          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
+          <t>c4ca3b08a858fe282766d1680bb80dd10c24ce32</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="7" t="n"/>
       <c r="C176" s="18" t="n">
-        <v>625</v>
+        <v>900</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -29957,28 +29974,28 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>Field View, Mancot, Deeside, CH5 2EY</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>824</v>
+        <v>328</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Habodel Property Services Ltd, Doncaster</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S176" s="7" t="inlineStr"/>
@@ -29995,50 +30012,50 @@
       <c r="V176" s="7" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
-          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
+          <t>19dde05bbe4ff1dc0306104719519db3f4baa597</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="7" t="n"/>
       <c r="C177" s="18" t="n">
-        <v>795</v>
+        <v>625</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>1</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Cilcain, The Square, CH7</t>
+          <t>Field View, Mancot, Deeside, CH5 2EY</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Williams Estates, Rhuddlan</t>
+          <t>Habodel Property Services Ltd, Doncaster</t>
         </is>
       </c>
       <c r="S177" s="7" t="inlineStr"/>
@@ -30055,14 +30072,14 @@
       <c r="V177" s="7" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
+          <t>c123bf34773b0afd208b42a23676d0de104b0aa4</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="7" t="n"/>
       <c r="C178" s="18" t="n">
-        <v>950</v>
+        <v>795</v>
       </c>
       <c r="D178" t="n">
         <v>2</v>
@@ -30077,28 +30094,28 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
+          <t>Cilcain, The Square, CH7</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Williams Estates, Rhuddlan</t>
         </is>
       </c>
       <c r="S178" s="7" t="inlineStr"/>
@@ -30115,14 +30132,14 @@
       <c r="V178" s="7" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
-          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
+          <t>87b32c4489714d9b512693daad46cef94dcd76a1</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="7" t="n"/>
       <c r="C179" s="18" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
@@ -30132,36 +30149,33 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Hill Top Close, Ewloe, CH5</t>
+          <t>Cae Masarn, Pentre Halkyn, Holywell, Flintshire, CH8</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>721</v>
+          <t>CH8</t>
+        </is>
       </c>
       <c r="N179" t="n">
-        <v>472</v>
+        <v>56</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Reades, Hawarden Lettings</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S179" s="7" t="inlineStr"/>
@@ -30178,29 +30192,29 @@
       <c r="V179" s="7" t="inlineStr"/>
       <c r="W179" t="inlineStr">
         <is>
-          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
+          <t>21cedfdeff38e71da260f36d15fc7a90e3806efc</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="7" t="n"/>
       <c r="C180" s="18" t="n">
-        <v>650</v>
+        <v>925</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
         <v>1</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Chester Road East, Shotton, Deeside</t>
+          <t>Hill Top Close, Ewloe, CH5</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30209,10 +30223,10 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>474</v>
+        <v>721</v>
       </c>
       <c r="N180" t="n">
-        <v>2016</v>
+        <v>472</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -30224,7 +30238,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Reades, Hawarden Lettings</t>
         </is>
       </c>
       <c r="S180" s="7" t="inlineStr"/>
@@ -30241,38 +30255,41 @@
       <c r="V180" s="7" t="inlineStr"/>
       <c r="W180" t="inlineStr">
         <is>
-          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
+          <t>1b94ffba8e84bd8bda3a33b448f8f35102e29484</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="7" t="n"/>
       <c r="C181" s="18" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
+          <t>Chester Road East, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>LL11</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>474</v>
       </c>
       <c r="N181" t="n">
-        <v>1300</v>
+        <v>2016</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -30284,7 +30301,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S181" s="7" t="inlineStr"/>
@@ -30301,14 +30318,14 @@
       <c r="V181" s="7" t="inlineStr"/>
       <c r="W181" t="inlineStr">
         <is>
-          <t>40274ada7dfa710e5054184216178477a704016c</t>
+          <t>f80c03a584803371ab95595ae7a449a94715fbd1</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="7" t="n"/>
       <c r="C182" s="18" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="D182" t="n">
         <v>2</v>
@@ -30318,21 +30335,21 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>Kiln Close, Buckley, Flintshire, CH7</t>
+          <t>Sycamore Terrace, Rhosrobin, Wrexham</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>CH7</t>
+          <t>LL11</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>936</v>
+        <v>1300</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -30344,7 +30361,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S182" s="7" t="inlineStr"/>
@@ -30361,7 +30378,7 @@
       <c r="V182" s="7" t="inlineStr"/>
       <c r="W182" t="inlineStr">
         <is>
-          <t>780cbc2857d57b036f046702f312e0298790c096</t>
+          <t>40274ada7dfa710e5054184216178477a704016c</t>
         </is>
       </c>
     </row>
@@ -30378,33 +30395,33 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>9 Park Road, Ruthin</t>
+          <t>Kiln Close, Buckley, Flintshire, CH7</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>LL15</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N183" t="n">
-        <v>576</v>
+        <v>936</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Ruthin</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S183" s="7" t="inlineStr"/>
@@ -30421,14 +30438,14 @@
       <c r="V183" s="7" t="inlineStr"/>
       <c r="W183" t="inlineStr">
         <is>
-          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
+          <t>780cbc2857d57b036f046702f312e0298790c096</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="7" t="n"/>
       <c r="C184" s="18" t="n">
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D184" t="n">
         <v>2</v>
@@ -30443,19 +30460,16 @@
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>Gladstone Street, Mold</t>
+          <t>9 Park Road, Ruthin</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
-      </c>
-      <c r="I184" t="n">
-        <v>905</v>
+          <t>LL15</t>
+        </is>
       </c>
       <c r="N184" t="n">
-        <v>1356</v>
+        <v>576</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -30467,7 +30481,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Cavendish Rentals Ltd, Ruthin</t>
         </is>
       </c>
       <c r="S184" s="7" t="inlineStr"/>
@@ -30484,14 +30498,14 @@
       <c r="V184" s="7" t="inlineStr"/>
       <c r="W184" t="inlineStr">
         <is>
-          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
+          <t>c771916d30aebac19d1f346f767747d7b73a7d6c</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="7" t="n"/>
       <c r="C185" s="18" t="n">
-        <v>1200</v>
+        <v>795</v>
       </c>
       <c r="D185" t="n">
         <v>2</v>
@@ -30501,24 +30515,24 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Llwyn Dinas Fechan, St. Asaph</t>
+          <t>Gladstone Street, Mold</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>710</v>
+        <v>905</v>
       </c>
       <c r="N185" t="n">
-        <v>248</v>
+        <v>1356</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -30530,7 +30544,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Thomas Property Group, Chester</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S185" s="7" t="inlineStr"/>
@@ -30547,14 +30561,14 @@
       <c r="V185" s="7" t="inlineStr"/>
       <c r="W185" t="inlineStr">
         <is>
-          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
+          <t>0fe090dd4efb58d6db540fc88a63048e9a1b679d</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="7" t="n"/>
       <c r="C186" s="18" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="D186" t="n">
         <v>2</v>
@@ -30564,36 +30578,36 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Central Drive, Shotton, Deeside</t>
+          <t>Llwyn Dinas Fechan, St. Asaph</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL17</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>636</v>
+        <v>710</v>
       </c>
       <c r="N186" t="n">
-        <v>1924</v>
+        <v>248</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Thomas Property Group, Chester</t>
         </is>
       </c>
       <c r="S186" s="7" t="inlineStr"/>
@@ -30610,20 +30624,20 @@
       <c r="V186" s="7" t="inlineStr"/>
       <c r="W186" t="inlineStr">
         <is>
-          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
+          <t>01f8dda2f09c16566df7d00ae192327104586ec6</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="7" t="n"/>
       <c r="C187" s="18" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="D187" t="n">
         <v>2</v>
       </c>
       <c r="E187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -30632,16 +30646,19 @@
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Llys Y Ddol, Mold</t>
+          <t>Central Drive, Shotton, Deeside</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>636</v>
       </c>
       <c r="N187" t="n">
-        <v>1368</v>
+        <v>1924</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -30653,7 +30670,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S187" s="7" t="inlineStr"/>
@@ -30670,53 +30687,50 @@
       <c r="V187" s="7" t="inlineStr"/>
       <c r="W187" t="inlineStr">
         <is>
-          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
+          <t>a8679975fd318f064c6646b7ec603ef505c73b91</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="7" t="n"/>
       <c r="C188" s="18" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Mill View Road, Shotton, CH5</t>
+          <t>Llys Y Ddol, Mold</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>CH5</t>
-        </is>
-      </c>
-      <c r="I188" t="n">
-        <v>1087</v>
+          <t>CH7</t>
+        </is>
       </c>
       <c r="N188" t="n">
-        <v>2236</v>
+        <v>1368</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S188" s="7" t="inlineStr"/>
@@ -30733,20 +30747,20 @@
       <c r="V188" s="7" t="inlineStr"/>
       <c r="W188" t="inlineStr">
         <is>
-          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
+          <t>454191bb7bc0e7fb7e64e3fd4f1802d398e2254c</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="B189" s="7" t="n"/>
       <c r="C189" s="18" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="D189" t="n">
         <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -30755,19 +30769,19 @@
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Chestnut Way, Penyffordd, Chester</t>
+          <t>Mill View Road, Shotton, CH5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>CH4</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>765</v>
+        <v>1087</v>
       </c>
       <c r="N189" t="n">
-        <v>144</v>
+        <v>2236</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -30779,7 +30793,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Reid and Roberts, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S189" s="7" t="inlineStr"/>
@@ -30796,20 +30810,20 @@
       <c r="V189" s="7" t="inlineStr"/>
       <c r="W189" t="inlineStr">
         <is>
-          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
+          <t>709d3dbb0469602a30f2232c43318e1004ee28e3</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="B190" s="7" t="n"/>
       <c r="C190" s="18" t="n">
-        <v>975</v>
+        <v>1100</v>
       </c>
       <c r="D190" t="n">
         <v>3</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -30818,16 +30832,19 @@
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
+          <t>Chestnut Way, Penyffordd, Chester</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>LL18</t>
-        </is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>765</v>
       </c>
       <c r="N190" t="n">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -30839,7 +30856,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Reid and Roberts, Mold</t>
         </is>
       </c>
       <c r="S190" s="7" t="inlineStr"/>
@@ -30856,14 +30873,14 @@
       <c r="V190" s="7" t="inlineStr"/>
       <c r="W190" t="inlineStr">
         <is>
-          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
+          <t>0c6f7f5dcf9483acf81dd96394cb138955cd345f</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="7" t="n"/>
       <c r="C191" s="18" t="n">
-        <v>875</v>
+        <v>975</v>
       </c>
       <c r="D191" t="n">
         <v>3</v>
@@ -30878,28 +30895,28 @@
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
+          <t>Maes Offa, Trelawynd, Rhyl, Flintshire, LL18</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N191" t="n">
-        <v>540</v>
+        <v>32</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S191" s="7" t="inlineStr"/>
@@ -30916,47 +30933,50 @@
       <c r="V191" s="7" t="inlineStr"/>
       <c r="W191" t="inlineStr">
         <is>
-          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
+          <t>7010522a251f536737688e6768df8c1ca7b26c26</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="B192" s="7" t="n"/>
       <c r="C192" s="18" t="n">
-        <v>725</v>
+        <v>875</v>
       </c>
       <c r="D192" t="n">
+        <v>3</v>
+      </c>
+      <c r="E192" t="n">
         <v>1</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>High Street, Connah's Quay, CH5</t>
+          <t>Glan Y Don, Greenfield, Holywell, CH8 7HG</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N192" t="n">
-        <v>1904</v>
+        <v>540</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Pinewood Estate Agency, Deeside</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S192" s="7" t="inlineStr"/>
@@ -30973,21 +30993,18 @@
       <c r="V192" s="7" t="inlineStr"/>
       <c r="W192" t="inlineStr">
         <is>
-          <t>db6095b2965d70713395b1458e1bc20535687531</t>
+          <t>2de321765047d8487aaad5d86e92b523486e594c</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="B193" s="7" t="n"/>
       <c r="C193" s="18" t="n">
-        <v>625</v>
+        <v>725</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" t="n">
-        <v>1</v>
-      </c>
       <c r="F193" t="inlineStr">
         <is>
           <t>flat</t>
@@ -30995,28 +31012,28 @@
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>Well Street, Holywell</t>
+          <t>High Street, Connah's Quay, CH5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>CH8</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N193" t="n">
-        <v>904</v>
+        <v>1904</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Pinewood Estate Agency, Deeside</t>
         </is>
       </c>
       <c r="S193" s="7" t="inlineStr"/>
@@ -31033,50 +31050,50 @@
       <c r="V193" s="7" t="inlineStr"/>
       <c r="W193" t="inlineStr">
         <is>
-          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
+          <t>db6095b2965d70713395b1458e1bc20535687531</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="B194" s="7" t="n"/>
       <c r="C194" s="18" t="n">
-        <v>900</v>
+        <v>625</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
+          <t>Well Street, Holywell</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>CH6</t>
+          <t>CH8</t>
         </is>
       </c>
       <c r="N194" t="n">
-        <v>200</v>
+        <v>904</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>William Gleave, Deeside</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S194" s="7" t="inlineStr"/>
@@ -31093,41 +31110,38 @@
       <c r="V194" s="7" t="inlineStr"/>
       <c r="W194" t="inlineStr">
         <is>
-          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
+          <t>2723b2ee048a058cfba581ae81cc808012ed35c5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="7" t="n"/>
       <c r="C195" s="18" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="D195" t="n">
         <v>2</v>
       </c>
       <c r="E195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>semi_detached</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>Rue St. Gregoire, Holywell, CH8</t>
+          <t>Bryntirion Road, Bagillt, Flintshire, CH6</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>CH8</t>
-        </is>
-      </c>
-      <c r="I195" t="n">
-        <v>657</v>
+          <t>CH6</t>
+        </is>
       </c>
       <c r="N195" t="n">
-        <v>876</v>
+        <v>200</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -31139,7 +31153,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Currans, North Wales</t>
+          <t>William Gleave, Deeside</t>
         </is>
       </c>
       <c r="S195" s="7" t="inlineStr"/>
@@ -31156,38 +31170,41 @@
       <c r="V195" s="7" t="inlineStr"/>
       <c r="W195" t="inlineStr">
         <is>
-          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
+          <t>0c1595e8a037ae10970a3d68c03447fcb7c78d28</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="B196" s="7" t="n"/>
       <c r="C196" s="18" t="n">
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="D196" t="n">
         <v>2</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>semi_detached</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>29 Tai Maes, Mold</t>
+          <t>Rue St. Gregoire, Holywell, CH8</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>CH7</t>
-        </is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>657</v>
       </c>
       <c r="N196" t="n">
-        <v>1356</v>
+        <v>876</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -31199,7 +31216,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Cavendish Rentals Ltd, Mold</t>
+          <t>Currans, North Wales</t>
         </is>
       </c>
       <c r="S196" s="7" t="inlineStr"/>
@@ -31216,17 +31233,17 @@
       <c r="V196" s="7" t="inlineStr"/>
       <c r="W196" t="inlineStr">
         <is>
-          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
+          <t>dc3b6e39f27fc3549e5a88505b34a5efb8d772c4</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="B197" s="7" t="n"/>
       <c r="C197" s="18" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
         <v>1</v>
@@ -31238,7 +31255,7 @@
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>St Marys Mews, Mold</t>
+          <t>29 Tai Maes, Mold</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -31247,14 +31264,14 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1372</v>
+        <v>1356</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -31276,38 +31293,38 @@
       <c r="V197" s="7" t="inlineStr"/>
       <c r="W197" t="inlineStr">
         <is>
-          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
+          <t>e07eb711fdcf6d56ea28189fffc8e0176a5a3a88</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="7" t="n"/>
       <c r="C198" s="18" t="n">
-        <v>875</v>
+        <v>600</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>Castle Street, Caergwrle</t>
+          <t>St Marys Mews, Mold</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>CH7</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>264</v>
+        <v>1372</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -31319,7 +31336,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Town &amp; Country Estate Agents, Wrexham</t>
+          <t>Cavendish Rentals Ltd, Mold</t>
         </is>
       </c>
       <c r="S198" s="7" t="inlineStr"/>
@@ -31336,29 +31353,29 @@
       <c r="V198" s="7" t="inlineStr"/>
       <c r="W198" t="inlineStr">
         <is>
-          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
+          <t>af36d8744de8391ae981eb3d46fe462a829b50fc</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="7" t="n"/>
       <c r="C199" s="18" t="n">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="D199" t="n">
         <v>2</v>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>Fagl Lane, Hope, LL12</t>
+          <t>Castle Street, Caergwrle</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -31367,19 +31384,19 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Belvoir, Wrexham</t>
+          <t>Town &amp; Country Estate Agents, Wrexham</t>
         </is>
       </c>
       <c r="S199" s="7" t="inlineStr"/>
@@ -31396,17 +31413,17 @@
       <c r="V199" s="7" t="inlineStr"/>
       <c r="W199" t="inlineStr">
         <is>
-          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
+          <t>64420bc3a588da08d4b7e360992c14bddef406b0</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="7" t="n"/>
       <c r="C200" s="18" t="n">
-        <v>595</v>
+        <v>800</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E200" t="n">
         <v>1</v>
@@ -31418,16 +31435,16 @@
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>Ryeland Street, Deeside</t>
+          <t>Fagl Lane, Hope, LL12</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>CH5</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>2152</v>
+        <v>244</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -31439,7 +31456,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Belvoir, Wrexham</t>
         </is>
       </c>
       <c r="S200" s="7" t="inlineStr"/>
@@ -31456,17 +31473,17 @@
       <c r="V200" s="7" t="inlineStr"/>
       <c r="W200" t="inlineStr">
         <is>
-          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
+          <t>2e367fcb5325f10c32c7f8598ffffb977d48bccf</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="7" t="n"/>
       <c r="C201" s="18" t="n">
-        <v>750</v>
+        <v>595</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" t="n">
         <v>1</v>
@@ -31478,28 +31495,28 @@
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>High Street, Dyserth, LL18</t>
+          <t>Ryeland Street, Deeside</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>LL18</t>
+          <t>CH5</t>
         </is>
       </c>
       <c r="N201" t="n">
-        <v>232</v>
+        <v>2152</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Fifty North West, Chester</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr"/>
@@ -31516,14 +31533,14 @@
       <c r="V201" s="7" t="inlineStr"/>
       <c r="W201" t="inlineStr">
         <is>
-          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
+          <t>3502024b9ccf3c5846dbd8b2f4e5148495660759</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="B202" s="7" t="n"/>
       <c r="C202" s="18" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="D202" t="n">
         <v>2</v>
@@ -31538,7 +31555,7 @@
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>Newmarket Road, Dyserth, LL18</t>
+          <t>High Street, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -31547,14 +31564,14 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>328</v>
+        <v>232</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -31576,14 +31593,14 @@
       <c r="V202" s="7" t="inlineStr"/>
       <c r="W202" t="inlineStr">
         <is>
-          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
+          <t>c2d205c9da5502fe82c6529faa7073858d43318b</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="B203" s="7" t="n"/>
       <c r="C203" s="18" t="n">
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D203" t="n">
         <v>2</v>
@@ -31593,33 +31610,33 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
+          <t>Newmarket Road, Dyserth, LL18</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>LL16</t>
+          <t>LL18</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>940</v>
+        <v>328</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Monopoly, Denbigh</t>
+          <t>Fifty North West, Chester</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr"/>
@@ -31636,17 +31653,17 @@
       <c r="V203" s="7" t="inlineStr"/>
       <c r="W203" t="inlineStr">
         <is>
-          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
+          <t>8e3b047de4dea7640f383c9c16a3741e55ca202e</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="B204" s="7" t="n"/>
       <c r="C204" s="18" t="n">
-        <v>975</v>
+        <v>795</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E204" t="n">
         <v>1</v>
@@ -31658,16 +31675,16 @@
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>Derby Road, Caergwrle, Wrexham</t>
+          <t>Tower Terrace, Denbigh, Denbighshire, LL16</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>LL12</t>
+          <t>LL16</t>
         </is>
       </c>
       <c r="N204" t="n">
-        <v>252</v>
+        <v>940</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -31679,7 +31696,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Bowen, Wrexham</t>
+          <t>Monopoly, Denbigh</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr"/>
@@ -31696,50 +31713,50 @@
       <c r="V204" s="7" t="inlineStr"/>
       <c r="W204" t="inlineStr">
         <is>
-          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+          <t>a759cdaa8d9f724f2ecce2ccbf99e547c19fde5a</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="B205" s="7" t="n"/>
       <c r="C205" s="18" t="n">
-        <v>985</v>
+        <v>975</v>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>Livingstone Place, St. Asaph, LL17</t>
+          <t>Derby Road, Caergwrle, Wrexham</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>LL17</t>
+          <t>LL12</t>
         </is>
       </c>
       <c r="N205" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bowen, Wrexham</t>
         </is>
       </c>
       <c r="S205" s="7" t="inlineStr"/>
@@ -31756,12 +31773,72 @@
       <c r="V205" s="7" t="inlineStr"/>
       <c r="W205" t="inlineStr">
         <is>
+          <t>9c715b658948566fb2a4a4b90c3c6b2f1f91a752</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="7" t="n"/>
+      <c r="C206" s="18" t="n">
+        <v>985</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2</v>
+      </c>
+      <c r="E206" t="n">
+        <v>2</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Livingstone Place, St. Asaph, LL17</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>LL17</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>268</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S206" s="7" t="inlineStr"/>
+      <c r="T206" s="14" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V206" s="7" t="inlineStr"/>
+      <c r="W206" t="inlineStr">
+        <is>
           <t>b0ba112a09e1577fca8332db332a7e1693926a4e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W205"/>
+  <autoFilter ref="A1:W206"/>
   <dataValidations count="1">
     <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
@@ -31972,6 +32049,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T206" r:id="rId205"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -19242,7 +19242,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1555</v>
+        <v>1300</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>1</v>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Lombard Street, Bristol, BS3</t>
+          <t>St. Johns Lane, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -19271,7 +19271,7 @@
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n">
-        <v>12036</v>
+        <v>7112</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>0</v>
@@ -19279,12 +19279,12 @@
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S31" s="9" t="inlineStr">
@@ -19305,7 +19305,7 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
+          <t>91339ed58a9e4347ac017823b498695129a40922</t>
         </is>
       </c>
     </row>
@@ -19319,7 +19319,7 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>1300</v>
+        <v>1495</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>1</v>
@@ -19334,12 +19334,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>St. Johns Lane, Bedminster, BS3</t>
+          <t>Baldwin Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -19348,7 +19348,7 @@
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n">
-        <v>7112</v>
+        <v>20848</v>
       </c>
       <c r="O32" s="8" t="n">
         <v>0</v>
@@ -19356,17 +19356,17 @@
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T32" s="12" t="inlineStr">
@@ -19382,7 +19382,7 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>91339ed58a9e4347ac017823b498695129a40922</t>
+          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
         </is>
       </c>
     </row>
@@ -19396,7 +19396,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>1495</v>
+        <v>1733</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>1</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, Somerset, BS1</t>
+          <t>Cheltenham House, Clare Street, Bristol</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -19419,26 +19419,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I33" s="8" t="n"/>
+      <c r="I33" s="8" t="n">
+        <v>455</v>
+      </c>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n">
-        <v>20848</v>
-      </c>
+      <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S33" s="9" t="inlineStr">
@@ -19459,7 +19459,7 @@
       <c r="V33" s="7" t="inlineStr"/>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>21a50ee847cce4668d3bf6b9117fdfe0f1917533</t>
+          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
         </is>
       </c>
     </row>
@@ -19473,7 +19473,7 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>1733</v>
+        <v>1400</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>1</v>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Cheltenham House, Clare Street, Bristol</t>
+          <t>City Centre, Number One Bristol, BS1 2NR</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -19497,30 +19497,32 @@
         </is>
       </c>
       <c r="I34" s="8" t="n">
-        <v>455</v>
+        <v>527</v>
       </c>
       <c r="J34" s="8" t="n"/>
       <c r="K34" s="8" t="n"/>
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
-      <c r="N34" s="8" t="n"/>
+      <c r="N34" s="8" t="n">
+        <v>21804</v>
+      </c>
       <c r="O34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S34" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T34" s="12" t="inlineStr">
@@ -19536,7 +19538,7 @@
       <c r="V34" s="7" t="inlineStr"/>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>7aeb8331a46bbe8acd8189d3a63f58f7e3892936</t>
+          <t>27b085b9bcbec967c008845a19f54e272fc12b87</t>
         </is>
       </c>
     </row>
@@ -19550,13 +19552,13 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
@@ -19565,23 +19567,21 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Number One Bristol, BS1 2NR</t>
+          <t>Stillhouse lane</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>527</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="n"/>
       <c r="J35" s="8" t="n"/>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n">
-        <v>21804</v>
+        <v>14304</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>0</v>
@@ -19589,17 +19589,17 @@
       <c r="P35" s="8" t="n"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S35" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T35" s="12" t="inlineStr">
@@ -19615,7 +19615,7 @@
       <c r="V35" s="7" t="inlineStr"/>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>27b085b9bcbec967c008845a19f54e272fc12b87</t>
+          <t>5cd63c65fc4cff6a9795b3661298e348456cd9ae</t>
         </is>
       </c>
     </row>
@@ -19629,13 +19629,13 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>2200</v>
+        <v>3200</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
@@ -19644,21 +19644,23 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Stillhouse lane</t>
+          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>1033</v>
+      </c>
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n">
-        <v>14304</v>
+        <v>20348</v>
       </c>
       <c r="O36" s="8" t="n">
         <v>0</v>
@@ -19671,7 +19673,7 @@
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S36" s="9" t="inlineStr">
@@ -19692,7 +19694,7 @@
       <c r="V36" s="7" t="inlineStr"/>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>5cd63c65fc4cff6a9795b3661298e348456cd9ae</t>
+          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
         </is>
       </c>
     </row>
@@ -19706,13 +19708,13 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>3200</v>
+        <v>1200</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
@@ -19721,23 +19723,23 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Redcliff Backs, The Custom House Redcliff Backs, BS1</t>
+          <t>North Road, St. Andrews, BS6</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1033</v>
+        <v>420</v>
       </c>
       <c r="J37" s="8" t="n"/>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n">
-        <v>20348</v>
+        <v>8012</v>
       </c>
       <c r="O37" s="8" t="n">
         <v>0</v>
@@ -19745,12 +19747,12 @@
       <c r="P37" s="8" t="n"/>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S37" s="9" t="inlineStr">
@@ -19771,7 +19773,7 @@
       <c r="V37" s="7" t="inlineStr"/>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>dc59104b573c7cdb75e715aaeca492455c19e7d4</t>
+          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
         </is>
       </c>
     </row>
@@ -19800,23 +19802,21 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>North Road, St. Andrews, BS6</t>
+          <t>Boot Lane - Bedminster</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>420</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="n"/>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n">
-        <v>8012</v>
+        <v>15180</v>
       </c>
       <c r="O38" s="8" t="n">
         <v>0</v>
@@ -19824,12 +19824,12 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S38" s="9" t="inlineStr">
@@ -19850,7 +19850,7 @@
       <c r="V38" s="7" t="inlineStr"/>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>a8afb5f086b1cf94d7c3bca118dd00b4440ca1b3</t>
+          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>1</v>
@@ -19879,12 +19879,12 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Boot Lane - Bedminster</t>
+          <t>Church Road, Redfield, Bristol</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -19893,7 +19893,7 @@
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n">
-        <v>15180</v>
+        <v>9192</v>
       </c>
       <c r="O39" s="8" t="n">
         <v>0</v>
@@ -19906,12 +19906,12 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>House + Co Property, Bristol</t>
         </is>
       </c>
       <c r="S39" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T39" s="12" t="inlineStr">
@@ -19927,7 +19927,7 @@
       <c r="V39" s="7" t="inlineStr"/>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>d0acdc25c6b4269d541e14519dfdbb42337f1828</t>
+          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>1</v>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Church Road, Redfield, Bristol</t>
+          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -19970,7 +19970,7 @@
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n">
-        <v>9192</v>
+        <v>4996</v>
       </c>
       <c r="O40" s="8" t="n">
         <v>0</v>
@@ -19978,17 +19978,17 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>House + Co Property, Bristol</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S40" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T40" s="12" t="inlineStr">
@@ -20004,7 +20004,7 @@
       <c r="V40" s="7" t="inlineStr"/>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>7a41aac9e360b75a3e49c55b3cf8e321e60f6e4c</t>
+          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>1</v>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Crew's Hole, Bristol, BS5</t>
+          <t>Butlers Close, Bristol, BS5</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -20055,12 +20055,12 @@
       <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>Parks Estate Agents, Bristol</t>
         </is>
       </c>
       <c r="S41" s="9" t="inlineStr">
@@ -20081,7 +20081,7 @@
       <c r="V41" s="7" t="inlineStr"/>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>b41de22f35bcc18a3460e5242a89db630aea48eb</t>
+          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
         </is>
       </c>
     </row>
@@ -20110,12 +20110,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Butlers Close, Bristol, BS5</t>
+          <t>Manor Road, Bishopston, Bristol</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS7</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -20124,7 +20124,7 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n">
-        <v>4996</v>
+        <v>5396</v>
       </c>
       <c r="O42" s="8" t="n">
         <v>0</v>
@@ -20132,12 +20132,12 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>Parks Estate Agents, Bristol</t>
+          <t>Connells Lettings, Southville</t>
         </is>
       </c>
       <c r="S42" s="9" t="inlineStr">
@@ -20158,7 +20158,7 @@
       <c r="V42" s="7" t="inlineStr"/>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>7cdb078ade9559511282395915101ace88ed6ee0</t>
+          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
         </is>
       </c>
     </row>
@@ -20172,7 +20172,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>1</v>
@@ -20187,21 +20187,23 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>Manor Road, Bishopston, Bristol</t>
+          <t>Marlborough Street, Eastville, Bristol</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>BS7</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="n"/>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>366</v>
+      </c>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n">
-        <v>5396</v>
+        <v>7920</v>
       </c>
       <c r="O43" s="8" t="n">
         <v>0</v>
@@ -20209,17 +20211,17 @@
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>Connells Lettings, Southville</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S43" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T43" s="12" t="inlineStr">
@@ -20235,7 +20237,7 @@
       <c r="V43" s="7" t="inlineStr"/>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>c5162861f3e11f0b7ccc2c9cecdfe5e060141029</t>
+          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20251,7 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>1200</v>
+        <v>975</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>1</v>
@@ -20264,7 +20266,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Marlborough Street, Eastville, Bristol</t>
+          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -20272,15 +20274,13 @@
           <t>BS5</t>
         </is>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>366</v>
-      </c>
+      <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n">
-        <v>7920</v>
+        <v>7804</v>
       </c>
       <c r="O44" s="8" t="n">
         <v>0</v>
@@ -20293,12 +20293,12 @@
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Northwood, Bristol</t>
         </is>
       </c>
       <c r="S44" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T44" s="12" t="inlineStr">
@@ -20314,7 +20314,7 @@
       <c r="V44" s="7" t="inlineStr"/>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>c9ead95c194e86c58ad819b434342e19c802a4f6</t>
+          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Hudd's Vale Road, St George, Bristol, BS5</t>
+          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -20357,7 +20357,7 @@
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n">
-        <v>7804</v>
+        <v>8640</v>
       </c>
       <c r="O45" s="8" t="n">
         <v>0</v>
@@ -20365,17 +20365,17 @@
       <c r="P45" s="8" t="n"/>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>Northwood, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S45" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T45" s="12" t="inlineStr">
@@ -20391,7 +20391,7 @@
       <c r="V45" s="7" t="inlineStr"/>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>395007b279a3467e781f0aa9438723752e1eb50f</t>
+          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
         </is>
       </c>
     </row>
@@ -20405,7 +20405,7 @@
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>975</v>
+        <v>1100</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>1</v>
@@ -20420,12 +20420,12 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>Roseberry Park, Roseberry Mews Roseberry Park, BS5</t>
+          <t>Ravenswood Road, Bristol, BS6</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS6</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -20434,7 +20434,7 @@
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n">
-        <v>8640</v>
+        <v>16556</v>
       </c>
       <c r="O46" s="8" t="n">
         <v>0</v>
@@ -20442,17 +20442,17 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S46" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>bills included</t>
         </is>
       </c>
       <c r="T46" s="12" t="inlineStr">
@@ -20468,13 +20468,13 @@
       <c r="V46" s="7" t="inlineStr"/>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>6b0cdf0711902be9b117a15d1a608cca17cc2d3f</t>
+          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>1</v>
@@ -20497,12 +20497,12 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Ravenswood Road, Bristol, BS6</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>BS6</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -20511,7 +20511,7 @@
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n">
-        <v>16556</v>
+        <v>19980</v>
       </c>
       <c r="O47" s="8" t="n">
         <v>0</v>
@@ -20519,19 +20519,15 @@
       <c r="P47" s="8" t="n"/>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S47" s="9" t="inlineStr">
-        <is>
-          <t>bills included</t>
-        </is>
-      </c>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+        </is>
+      </c>
+      <c r="S47" s="9" t="inlineStr"/>
       <c r="T47" s="12" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -20545,7 +20541,7 @@
       <c r="V47" s="7" t="inlineStr"/>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>1c315268eed469425b8c480540e07721a1a3c908</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20555,7 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>1</v>
@@ -20574,12 +20570,12 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -20588,7 +20584,7 @@
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n">
-        <v>19980</v>
+        <v>15212</v>
       </c>
       <c r="O48" s="8" t="n">
         <v>0</v>
@@ -20596,12 +20592,12 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S48" s="9" t="inlineStr"/>
@@ -20618,7 +20614,7 @@
       <c r="V48" s="7" t="inlineStr"/>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
         </is>
       </c>
     </row>
@@ -20632,7 +20628,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>1</v>
@@ -20647,12 +20643,12 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Bedminster Parade Bedminster, Bristol, BS3</t>
+          <t>Knowle Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -20661,7 +20657,7 @@
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n">
-        <v>15212</v>
+        <v>6852</v>
       </c>
       <c r="O49" s="8" t="n">
         <v>0</v>
@@ -20669,12 +20665,12 @@
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S49" s="9" t="inlineStr"/>
@@ -20691,7 +20687,7 @@
       <c r="V49" s="7" t="inlineStr"/>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>50cb5f4990ae3655c686a0bb94886a0f25eb2ec9</t>
+          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20701,7 @@
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>1200</v>
+        <v>1640</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>1</v>
@@ -20720,21 +20716,23 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol, BS4</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>484</v>
+      </c>
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n">
-        <v>6852</v>
+        <v>21504</v>
       </c>
       <c r="O50" s="8" t="n">
         <v>0</v>
@@ -20742,12 +20740,12 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S50" s="9" t="inlineStr"/>
@@ -20764,7 +20762,7 @@
       <c r="V50" s="7" t="inlineStr"/>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>bbb9b81c216b0de31ba8859ef50a78ed36377871</t>
+          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20776,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1640</v>
+        <v>1600</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>1</v>
@@ -20793,7 +20791,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hope Quay, Wapping Wharf</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -20801,15 +20799,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I51" s="8" t="n">
-        <v>484</v>
-      </c>
+      <c r="I51" s="8" t="n"/>
       <c r="J51" s="8" t="n"/>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n">
-        <v>21504</v>
+        <v>16708</v>
       </c>
       <c r="O51" s="8" t="n">
         <v>0</v>
@@ -20817,12 +20813,12 @@
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S51" s="9" t="inlineStr"/>
@@ -20839,7 +20835,7 @@
       <c r="V51" s="7" t="inlineStr"/>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>5d39df649daaa86eebac0b90b2a33fa18f365ed3</t>
+          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20849,7 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>1</v>
@@ -20868,12 +20864,12 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf</t>
+          <t>Hamilton Court - City Centre</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -20882,7 +20878,7 @@
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n">
-        <v>16708</v>
+        <v>21616</v>
       </c>
       <c r="O52" s="8" t="n">
         <v>0</v>
@@ -20895,7 +20891,7 @@
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S52" s="9" t="inlineStr"/>
@@ -20912,7 +20908,7 @@
       <c r="V52" s="7" t="inlineStr"/>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>0dbbb656d8ffbae712c9077ec0f7c1849746bd0b</t>
+          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
         </is>
       </c>
     </row>
@@ -20926,10 +20922,10 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1300</v>
+        <v>2200</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>1</v>
@@ -20941,7 +20937,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court - City Centre</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -20955,7 +20951,7 @@
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n">
-        <v>21616</v>
+        <v>21984</v>
       </c>
       <c r="O53" s="8" t="n">
         <v>0</v>
@@ -20963,12 +20959,12 @@
       <c r="P53" s="8" t="n"/>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R53" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S53" s="9" t="inlineStr"/>
@@ -20985,7 +20981,7 @@
       <c r="V53" s="7" t="inlineStr"/>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>8bd3f395f80d9e75d404d499c9b227ed567374e3</t>
+          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
         </is>
       </c>
     </row>
@@ -20999,13 +20995,13 @@
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="D54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -21022,7 +21018,9 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I54" s="8" t="n"/>
+      <c r="I54" s="8" t="n">
+        <v>757</v>
+      </c>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="n"/>
@@ -21058,7 +21056,7 @@
       <c r="V54" s="7" t="inlineStr"/>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>406fab2577557efdd9382cee302acdc7a788c3d8</t>
+          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
         </is>
       </c>
     </row>
@@ -21087,7 +21085,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -21095,9 +21093,7 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I55" s="8" t="n">
-        <v>757</v>
-      </c>
+      <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="8" t="n"/>
@@ -21133,7 +21129,7 @@
       <c r="V55" s="7" t="inlineStr"/>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>82dded0955660a8ec4af3acb8db470436bdc522b</t>
+          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
         </is>
       </c>
     </row>
@@ -21147,13 +21143,13 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>2300</v>
+        <v>2095</v>
       </c>
       <c r="D56" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
@@ -21162,7 +21158,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol, BS2 0ND</t>
+          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -21206,7 +21202,7 @@
       <c r="V56" s="7" t="inlineStr"/>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>fc4abec405a6b435cb290523f6e7784fc2de1099</t>
+          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
         </is>
       </c>
     </row>
@@ -21220,10 +21216,10 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>2095</v>
+        <v>1400</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>1</v>
@@ -21235,12 +21231,12 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, BS2 0ND, Bristol</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -21249,7 +21245,7 @@
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n">
-        <v>21984</v>
+        <v>20908</v>
       </c>
       <c r="O57" s="8" t="n">
         <v>0</v>
@@ -21257,12 +21253,12 @@
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R57" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S57" s="9" t="inlineStr"/>
@@ -21279,7 +21275,7 @@
       <c r="V57" s="7" t="inlineStr"/>
       <c r="W57" s="8" t="inlineStr">
         <is>
-          <t>7a4bff96a8fb36d99cc3d7825e84bee85f8c5ba7</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -21293,10 +21289,10 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="8" t="n">
         <v>1</v>
@@ -21308,12 +21304,12 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -21322,7 +21318,7 @@
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n">
-        <v>20908</v>
+        <v>21600</v>
       </c>
       <c r="O58" s="8" t="n">
         <v>0</v>
@@ -21330,12 +21326,12 @@
       <c r="P58" s="8" t="n"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S58" s="9" t="inlineStr"/>
@@ -21352,7 +21348,7 @@
       <c r="V58" s="7" t="inlineStr"/>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21362,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>2</v>
@@ -21381,7 +21377,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Waterloo Road, Midland Mews, BS2</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -21389,13 +21385,15 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I59" s="8" t="n"/>
+      <c r="I59" s="8" t="n">
+        <v>721</v>
+      </c>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n">
-        <v>21600</v>
+        <v>20856</v>
       </c>
       <c r="O59" s="8" t="n">
         <v>0</v>
@@ -21403,12 +21401,12 @@
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R59" s="8" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S59" s="9" t="inlineStr"/>
@@ -21425,7 +21423,7 @@
       <c r="V59" s="7" t="inlineStr"/>
       <c r="W59" s="8" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21437,7 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D60" s="8" t="n">
         <v>2</v>
@@ -21454,7 +21452,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Waterloo Road, Midland Mews, BS2</t>
+          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -21462,9 +21460,7 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I60" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I60" s="8" t="n"/>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
@@ -21478,12 +21474,12 @@
       <c r="P60" s="8" t="n"/>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S60" s="9" t="inlineStr"/>
@@ -21500,7 +21496,7 @@
       <c r="V60" s="7" t="inlineStr"/>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>cf8a979c7c13e868d74a6828d64c93a46d2e7209</t>
+          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
         </is>
       </c>
     </row>
@@ -21514,13 +21510,13 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>2085</v>
+        <v>1300</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
@@ -21529,7 +21525,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -21538,14 +21534,14 @@
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>722</v>
+        <v>405</v>
       </c>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n">
-        <v>21504</v>
+        <v>20316</v>
       </c>
       <c r="O61" s="8" t="n">
         <v>0</v>
@@ -21558,7 +21554,7 @@
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S61" s="9" t="inlineStr"/>
@@ -21575,7 +21571,7 @@
       <c r="V61" s="7" t="inlineStr"/>
       <c r="W61" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -21589,13 +21585,13 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>1640</v>
+        <v>2020</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
@@ -21613,14 +21609,14 @@
         </is>
       </c>
       <c r="I62" s="8" t="n">
-        <v>570</v>
+        <v>764</v>
       </c>
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O62" s="8" t="n">
         <v>0</v>
@@ -21628,7 +21624,7 @@
       <c r="P62" s="8" t="n"/>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R62" s="8" t="inlineStr">
@@ -21650,7 +21646,7 @@
       <c r="V62" s="7" t="inlineStr"/>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21664,13 +21660,13 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1500</v>
+        <v>2145</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
@@ -21679,21 +21675,23 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Midland Mews Waterloo Road Old Market, Bristol, BS2</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>815</v>
+      </c>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21701,12 +21699,12 @@
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21723,7 +21721,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>f83555c1dc6f03087d999787a76db9b49794ddb4</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21737,7 +21735,7 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1300</v>
+        <v>1635</v>
       </c>
       <c r="D64" s="8" t="n">
         <v>1</v>
@@ -21752,7 +21750,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -21761,14 +21759,14 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>405</v>
+        <v>486</v>
       </c>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>20316</v>
+        <v>21504</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21776,12 +21774,12 @@
       <c r="P64" s="8" t="n"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21798,7 +21796,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21810,7 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>2020</v>
+        <v>1750</v>
       </c>
       <c r="D65" s="8" t="n">
         <v>2</v>
@@ -21827,23 +21825,23 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n">
-        <v>20856</v>
+        <v>4680</v>
       </c>
       <c r="O65" s="8" t="n">
         <v>0</v>
@@ -21856,7 +21854,7 @@
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr"/>
@@ -21873,7 +21871,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -21887,13 +21885,13 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>2145</v>
+        <v>2100</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
@@ -21902,7 +21900,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -21910,15 +21908,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I66" s="8" t="n">
-        <v>815</v>
-      </c>
+      <c r="I66" s="8" t="n"/>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>21504</v>
+        <v>21148</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -21926,12 +21922,12 @@
       <c r="P66" s="8" t="n"/>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21948,7 +21944,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -21962,13 +21958,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1635</v>
+        <v>2220</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21977,7 +21973,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -21986,14 +21982,14 @@
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>486</v>
+        <v>697</v>
       </c>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -22001,12 +21997,12 @@
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S67" s="9" t="inlineStr"/>
@@ -22023,7 +22019,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -22037,13 +22033,13 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>1750</v>
+        <v>1300</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -22052,23 +22048,21 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>731</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="n"/>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>4680</v>
+        <v>21428</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22076,12 +22070,12 @@
       <c r="P68" s="8" t="n"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22098,7 +22092,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22106,7 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>1</v>
@@ -22127,7 +22121,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22135,13 +22129,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="8" t="n"/>
+      <c r="I69" s="8" t="n">
+        <v>548</v>
+      </c>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>21148</v>
+        <v>21504</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -22149,12 +22145,12 @@
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22171,7 +22167,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -22185,13 +22181,13 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>2220</v>
+        <v>1615</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
@@ -22200,7 +22196,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -22209,14 +22205,14 @@
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>697</v>
+        <v>486</v>
       </c>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O70" s="8" t="n">
         <v>0</v>
@@ -22224,12 +22220,12 @@
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S70" s="9" t="inlineStr"/>
@@ -22246,7 +22242,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -22260,10 +22256,10 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1300</v>
+        <v>1965</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="8" t="n">
         <v>1</v>
@@ -22275,7 +22271,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22283,13 +22279,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I71" s="8" t="n"/>
+      <c r="I71" s="8" t="n">
+        <v>655</v>
+      </c>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n">
-        <v>21428</v>
+        <v>21504</v>
       </c>
       <c r="O71" s="8" t="n">
         <v>0</v>
@@ -22297,12 +22295,12 @@
       <c r="P71" s="8" t="n"/>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22319,7 +22317,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
         </is>
       </c>
     </row>
@@ -22333,13 +22331,13 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1500</v>
+        <v>2080</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
@@ -22348,7 +22346,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22357,14 +22355,14 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>548</v>
+        <v>705</v>
       </c>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O72" s="8" t="n">
         <v>0</v>
@@ -22372,12 +22370,12 @@
       <c r="P72" s="8" t="n"/>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22394,7 +22392,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
         </is>
       </c>
     </row>
@@ -22408,7 +22406,7 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1615</v>
+        <v>1400</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>1</v>
@@ -22423,7 +22421,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -22431,15 +22429,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I73" s="8" t="n">
-        <v>486</v>
-      </c>
+      <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n">
-        <v>21504</v>
+        <v>19484</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0</v>
@@ -22447,12 +22443,12 @@
       <c r="P73" s="8" t="n"/>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
@@ -22469,7 +22465,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -22483,13 +22479,13 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>1965</v>
+        <v>2000</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
@@ -22498,7 +22494,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Welsh Back, Bristol, BS1</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -22507,15 +22503,13 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>655</v>
+        <v>908</v>
       </c>
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
-      <c r="N74" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N74" s="8" t="n"/>
       <c r="O74" s="8" t="n">
         <v>0</v>
       </c>
@@ -22527,7 +22521,7 @@
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Hello Neighbour, London</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
@@ -22544,7 +22538,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
+          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
         </is>
       </c>
     </row>
@@ -22558,7 +22552,7 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>2080</v>
+        <v>2020</v>
       </c>
       <c r="D75" s="8" t="n">
         <v>2</v>
@@ -22588,16 +22582,14 @@
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
-      <c r="N75" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="8" t="n"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R75" s="8" t="inlineStr">
@@ -22619,7 +22611,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
+          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
         </is>
       </c>
     </row>
@@ -22633,13 +22625,13 @@
         </is>
       </c>
       <c r="C76" s="17" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
@@ -22648,7 +22640,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Eclipse - City Centre</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -22661,21 +22653,19 @@
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="n"/>
-      <c r="N76" s="8" t="n">
-        <v>19484</v>
-      </c>
+      <c r="N76" s="8" t="n"/>
       <c r="O76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="8" t="n"/>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
@@ -22692,7 +22682,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
         </is>
       </c>
     </row>
@@ -22706,13 +22696,13 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2000</v>
+        <v>2085</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
@@ -22721,7 +22711,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -22730,7 +22720,7 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>908</v>
+        <v>705</v>
       </c>
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
@@ -22743,12 +22733,12 @@
       <c r="P77" s="8" t="n"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>Hello Neighbour, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S77" s="9" t="inlineStr"/>
@@ -22765,7 +22755,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
+          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
         </is>
       </c>
     </row>
@@ -22779,13 +22769,13 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>2020</v>
+        <v>1615</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
@@ -22794,7 +22784,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -22803,7 +22793,7 @@
         </is>
       </c>
       <c r="I78" s="8" t="n">
-        <v>705</v>
+        <v>487</v>
       </c>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
@@ -22816,12 +22806,12 @@
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
@@ -22838,7 +22828,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22842,7 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>2000</v>
+        <v>2065</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>2</v>
@@ -22867,7 +22857,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Eclipse - City Centre</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -22875,7 +22865,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I79" s="8" t="n"/>
+      <c r="I79" s="8" t="n">
+        <v>641</v>
+      </c>
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
@@ -22887,12 +22879,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
@@ -22909,7 +22901,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -22923,13 +22915,13 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>1595</v>
+        <v>2185</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
@@ -22938,7 +22930,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -22947,7 +22939,7 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>499</v>
+        <v>721</v>
       </c>
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
@@ -22960,12 +22952,12 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S80" s="9" t="inlineStr"/>
@@ -22982,7 +22974,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -22996,13 +22988,13 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>2085</v>
+        <v>1565</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
@@ -23011,7 +23003,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -23020,7 +23012,7 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>705</v>
+        <v>484</v>
       </c>
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
@@ -23033,12 +23025,12 @@
       <c r="P81" s="8" t="n"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
@@ -23055,7 +23047,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -23069,7 +23061,7 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1615</v>
+        <v>1650</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>1</v>
@@ -23084,7 +23076,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Horizon, Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -23092,9 +23084,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I82" s="8" t="n">
-        <v>487</v>
-      </c>
+      <c r="I82" s="8" t="n"/>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
@@ -23106,12 +23096,12 @@
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S82" s="9" t="inlineStr"/>
@@ -23128,7 +23118,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -23142,13 +23132,13 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>2065</v>
+        <v>2100</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
@@ -23157,7 +23147,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -23165,9 +23155,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I83" s="8" t="n">
-        <v>641</v>
-      </c>
+      <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
@@ -23179,12 +23167,12 @@
       <c r="P83" s="8" t="n"/>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R83" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S83" s="9" t="inlineStr"/>
@@ -23201,7 +23189,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -23215,13 +23203,13 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>2185</v>
+        <v>1660</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
@@ -23239,20 +23227,22 @@
         </is>
       </c>
       <c r="I84" s="8" t="n">
-        <v>721</v>
+        <v>486</v>
       </c>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
-      <c r="N84" s="8" t="n"/>
+      <c r="N84" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O84" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="8" t="n"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R84" s="8" t="inlineStr">
@@ -23274,7 +23264,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -23288,13 +23278,13 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1565</v>
+        <v>2175</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
@@ -23303,7 +23293,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -23312,25 +23302,27 @@
         </is>
       </c>
       <c r="I85" s="8" t="n">
-        <v>484</v>
+        <v>814</v>
       </c>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
-      <c r="N85" s="8" t="n"/>
+      <c r="N85" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O85" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="8" t="n"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
@@ -23347,7 +23339,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -23361,13 +23353,13 @@
         </is>
       </c>
       <c r="C86" s="17" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
@@ -23376,7 +23368,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, Bristol, BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -23389,19 +23381,21 @@
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
       <c r="M86" s="8" t="n"/>
-      <c r="N86" s="8" t="n"/>
+      <c r="N86" s="8" t="n">
+        <v>21816</v>
+      </c>
       <c r="O86" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S86" s="9" t="inlineStr"/>
@@ -23418,7 +23412,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -23432,13 +23426,13 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>1625</v>
+        <v>2115</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
@@ -23447,7 +23441,7 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -23456,25 +23450,27 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>485</v>
+        <v>823</v>
       </c>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="8" t="n"/>
-      <c r="N87" s="8" t="n"/>
+      <c r="N87" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O87" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="8" t="n"/>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S87" s="9" t="inlineStr"/>
@@ -23491,7 +23487,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -23505,13 +23501,13 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>2175</v>
+        <v>1660</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
@@ -23529,20 +23525,22 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>722</v>
+        <v>486</v>
       </c>
       <c r="J88" s="8" t="n"/>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="n"/>
-      <c r="N88" s="8" t="n"/>
+      <c r="N88" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O88" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="8" t="n"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr">
@@ -23564,7 +23562,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -23578,13 +23576,13 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>2100</v>
+        <v>1915</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
@@ -23593,7 +23591,7 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -23601,24 +23599,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I89" s="8" t="n"/>
+      <c r="I89" s="8" t="n">
+        <v>746</v>
+      </c>
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
+      <c r="N89" s="8" t="n">
+        <v>21680</v>
+      </c>
       <c r="O89" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="8" t="n"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S89" s="9" t="inlineStr"/>
@@ -23635,7 +23637,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -23649,13 +23651,13 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>1900</v>
+        <v>1150</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
@@ -23664,12 +23666,12 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I90" s="8" t="n"/>
@@ -23677,19 +23679,21 @@
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
-      <c r="N90" s="8" t="n"/>
+      <c r="N90" s="8" t="n">
+        <v>6872</v>
+      </c>
       <c r="O90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="8" t="n"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23706,7 +23710,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -23720,13 +23724,13 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>1660</v>
+        <v>2450</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
@@ -23735,7 +23739,7 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -23743,15 +23747,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I91" s="8" t="n">
-        <v>486</v>
-      </c>
+      <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n">
-        <v>21504</v>
+        <v>21788</v>
       </c>
       <c r="O91" s="8" t="n">
         <v>0</v>
@@ -23759,12 +23761,12 @@
       <c r="P91" s="8" t="n"/>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr"/>
@@ -23781,7 +23783,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -23795,7 +23797,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>2175</v>
+        <v>1700</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>2</v>
@@ -23810,7 +23812,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>The Crescent</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -23818,15 +23820,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I92" s="8" t="n">
-        <v>814</v>
-      </c>
+      <c r="I92" s="8" t="n"/>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n">
-        <v>21504</v>
+        <v>16368</v>
       </c>
       <c r="O92" s="8" t="n">
         <v>0</v>
@@ -23834,12 +23834,12 @@
       <c r="P92" s="8" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S92" s="9" t="inlineStr"/>
@@ -23856,7 +23856,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
         </is>
       </c>
     </row>
@@ -23870,13 +23870,13 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -23899,7 +23899,7 @@
       <c r="L93" s="8" t="n"/>
       <c r="M93" s="8" t="n"/>
       <c r="N93" s="8" t="n">
-        <v>21816</v>
+        <v>21160</v>
       </c>
       <c r="O93" s="8" t="n">
         <v>0</v>
@@ -23907,12 +23907,12 @@
       <c r="P93" s="8" t="n"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S93" s="9" t="inlineStr"/>
@@ -23929,7 +23929,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -23943,13 +23943,13 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>2115</v>
+        <v>1999</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -23966,15 +23966,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I94" s="8" t="n">
-        <v>823</v>
-      </c>
+      <c r="I94" s="8" t="n"/>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n">
-        <v>20820</v>
+        <v>20800</v>
       </c>
       <c r="O94" s="8" t="n">
         <v>0</v>
@@ -23982,12 +23980,12 @@
       <c r="P94" s="8" t="n"/>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S94" s="9" t="inlineStr"/>
@@ -24004,7 +24002,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -24018,7 +24016,7 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>1660</v>
+        <v>1670</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>1</v>
@@ -24042,7 +24040,7 @@
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
@@ -24057,7 +24055,7 @@
       <c r="P95" s="8" t="n"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
@@ -24079,7 +24077,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -24093,13 +24091,13 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>1915</v>
+        <v>1645</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
@@ -24108,7 +24106,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -24117,14 +24115,14 @@
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>746</v>
+        <v>517</v>
       </c>
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O96" s="8" t="n">
         <v>0</v>
@@ -24132,12 +24130,12 @@
       <c r="P96" s="8" t="n"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S96" s="9" t="inlineStr"/>
@@ -24154,7 +24152,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
         </is>
       </c>
     </row>
@@ -24168,13 +24166,13 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>1150</v>
+        <v>2120</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
@@ -24183,21 +24181,23 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I97" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n">
-        <v>6872</v>
+        <v>20820</v>
       </c>
       <c r="O97" s="8" t="n">
         <v>0</v>
@@ -24205,12 +24205,12 @@
       <c r="P97" s="8" t="n"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24227,7 +24227,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -24241,13 +24241,13 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>2450</v>
+        <v>1645</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -24264,13 +24264,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="8" t="n"/>
+      <c r="I98" s="8" t="n">
+        <v>571</v>
+      </c>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n">
-        <v>21788</v>
+        <v>20820</v>
       </c>
       <c r="O98" s="8" t="n">
         <v>0</v>
@@ -24278,12 +24280,12 @@
       <c r="P98" s="8" t="n"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R98" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S98" s="9" t="inlineStr"/>
@@ -24300,7 +24302,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
         </is>
       </c>
     </row>
@@ -24314,13 +24316,13 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>1700</v>
+        <v>1950</v>
       </c>
       <c r="D99" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
@@ -24329,7 +24331,7 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>The Crescent</t>
+          <t>Apartments, Bristol, BS1</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -24343,7 +24345,7 @@
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n">
-        <v>16368</v>
+        <v>22132</v>
       </c>
       <c r="O99" s="8" t="n">
         <v>0</v>
@@ -24351,12 +24353,12 @@
       <c r="P99" s="8" t="n"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24373,7 +24375,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
+          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
         </is>
       </c>
     </row>
@@ -24387,10 +24389,10 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>1</v>
@@ -24402,12 +24404,12 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I100" s="8" t="n"/>
@@ -24416,7 +24418,7 @@
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n">
-        <v>21160</v>
+        <v>19576</v>
       </c>
       <c r="O100" s="8" t="n">
         <v>0</v>
@@ -24424,12 +24426,12 @@
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24446,7 +24448,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
         </is>
       </c>
     </row>
@@ -24460,13 +24462,13 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>2145</v>
+        <v>1555</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -24475,23 +24477,21 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Lombard Street, Bristol, BS3</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I101" s="8" t="n">
-        <v>796</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="n"/>
       <c r="J101" s="8" t="n"/>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n">
-        <v>20820</v>
+        <v>12036</v>
       </c>
       <c r="O101" s="8" t="n">
         <v>0</v>
@@ -24499,12 +24499,12 @@
       <c r="P101" s="8" t="n"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24521,7 +24521,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
+          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
         </is>
       </c>
     </row>
@@ -24535,13 +24535,13 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1999</v>
+        <v>2085</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -24558,13 +24558,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="8" t="n"/>
+      <c r="I102" s="8" t="n">
+        <v>722</v>
+      </c>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n">
-        <v>20800</v>
+        <v>21504</v>
       </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
@@ -24572,12 +24574,12 @@
       <c r="P102" s="8" t="n"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24594,7 +24596,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24610,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1670</v>
+        <v>1640</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>1</v>
@@ -24623,7 +24625,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24632,14 +24634,14 @@
         </is>
       </c>
       <c r="I103" s="8" t="n">
-        <v>485</v>
+        <v>570</v>
       </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O103" s="8" t="n">
         <v>0</v>
@@ -24647,12 +24649,12 @@
       <c r="P103" s="8" t="n"/>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24669,7 +24671,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24685,7 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1645</v>
+        <v>1595</v>
       </c>
       <c r="D104" s="8" t="n">
         <v>1</v>
@@ -24698,7 +24700,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
@@ -24707,27 +24709,25 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
-      <c r="N104" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N104" s="8" t="n"/>
       <c r="O104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24744,7 +24744,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
+          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
         </is>
       </c>
     </row>
@@ -24758,13 +24758,13 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>2120</v>
+        <v>1625</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
@@ -24782,27 +24782,25 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>705</v>
+        <v>485</v>
       </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
-      <c r="N105" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N105" s="8" t="n"/>
       <c r="O105" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="8" t="n"/>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S105" s="9" t="inlineStr"/>
@@ -24819,7 +24817,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -24833,13 +24831,13 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1645</v>
+        <v>2175</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
@@ -24848,7 +24846,7 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -24857,27 +24855,25 @@
         </is>
       </c>
       <c r="I106" s="8" t="n">
-        <v>571</v>
+        <v>722</v>
       </c>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N106" s="8" t="n"/>
       <c r="O106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24894,7 +24890,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -24908,13 +24904,13 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>2250</v>
+        <v>1900</v>
       </c>
       <c r="D107" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -24923,7 +24919,7 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Apartments, Bristol, BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
@@ -24936,21 +24932,19 @@
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
-      <c r="N107" s="8" t="n">
-        <v>22132</v>
-      </c>
+      <c r="N107" s="8" t="n"/>
       <c r="O107" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S107" s="9" t="inlineStr"/>
@@ -24967,7 +24961,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -24981,13 +24975,13 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>1600</v>
+        <v>2145</v>
       </c>
       <c r="D108" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
@@ -24996,21 +24990,23 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="n">
+        <v>796</v>
+      </c>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>19576</v>
+        <v>20820</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -25018,12 +25014,12 @@
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -25040,7 +25036,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
+          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
         </is>
       </c>
     </row>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="C3" s="17" t="n">
-        <v>1200</v>
+        <v>1900</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>1</v>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Caslon Court, Somerset Street, BS1</t>
+          <t>Redcliff Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -17087,13 +17087,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I3" s="8" t="n"/>
+      <c r="I3" s="8" t="n">
+        <v>731</v>
+      </c>
       <c r="J3" s="8" t="n"/>
       <c r="K3" s="8" t="n"/>
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="8" t="n"/>
       <c r="N3" s="8" t="n">
-        <v>18424</v>
+        <v>20892</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>0</v>
@@ -17101,12 +17103,12 @@
       <c r="P3" s="8" t="n"/>
       <c r="Q3" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R3" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>A2Dominion Group, A2Dominion Lettings</t>
         </is>
       </c>
       <c r="S3" s="9" t="inlineStr">
@@ -17127,7 +17129,7 @@
       <c r="V3" s="7" t="inlineStr"/>
       <c r="W3" s="8" t="inlineStr">
         <is>
-          <t>f6187d8c2bb085d8ddb57c1f8b8dc96ceada86aa</t>
+          <t>c11b7a868ede7c3b0a3d524aa4d4e8f661494706</t>
         </is>
       </c>
     </row>
@@ -17141,10 +17143,10 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>1900</v>
+        <v>1395</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>1</v>
@@ -17156,23 +17158,21 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Redcliff Street, Bristol, BS1</t>
+          <t>Hamilton Court, Bristol, BS2</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>731</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n">
-        <v>20892</v>
+        <v>21660</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>0</v>
@@ -17180,17 +17180,17 @@
       <c r="P4" s="8" t="n"/>
       <c r="Q4" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
-          <t>A2Dominion Group, A2Dominion Lettings</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S4" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T4" s="12" t="inlineStr">
@@ -17206,7 +17206,7 @@
       <c r="V4" s="7" t="inlineStr"/>
       <c r="W4" s="8" t="inlineStr">
         <is>
-          <t>c11b7a868ede7c3b0a3d524aa4d4e8f661494706</t>
+          <t>55512167c7894bf9991618275f495f9b5aa0a1af</t>
         </is>
       </c>
     </row>
@@ -17220,13 +17220,13 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>1395</v>
+        <v>2000</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -17235,12 +17235,12 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Hamilton Court, Bristol, BS2</t>
+          <t>Deanery Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I5" s="8" t="n"/>
@@ -17249,7 +17249,7 @@
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n">
-        <v>21660</v>
+        <v>18292</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>0</v>
@@ -17262,12 +17262,12 @@
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S5" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T5" s="12" t="inlineStr">
@@ -17283,7 +17283,7 @@
       <c r="V5" s="7" t="inlineStr"/>
       <c r="W5" s="8" t="inlineStr">
         <is>
-          <t>55512167c7894bf9991618275f495f9b5aa0a1af</t>
+          <t>591cc261a1f5973aaa4a7b3adbcbe4699bcc6440</t>
         </is>
       </c>
     </row>
@@ -17297,13 +17297,13 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>2000</v>
+        <v>1550</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -17312,12 +17312,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Deanery Road, Bristol, BS1</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -17326,7 +17326,7 @@
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n">
-        <v>18292</v>
+        <v>19400</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>0</v>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S6" s="9" t="inlineStr">
@@ -17360,7 +17360,7 @@
       <c r="V6" s="7" t="inlineStr"/>
       <c r="W6" s="8" t="inlineStr">
         <is>
-          <t>591cc261a1f5973aaa4a7b3adbcbe4699bcc6440</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -17374,13 +17374,13 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>1550</v>
+        <v>1900</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -17389,21 +17389,23 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>783</v>
+      </c>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n">
-        <v>19400</v>
+        <v>4680</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>0</v>
@@ -17411,12 +17413,12 @@
       <c r="P7" s="8" t="n"/>
       <c r="Q7" s="8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S7" s="9" t="inlineStr">
@@ -17437,7 +17439,7 @@
       <c r="V7" s="7" t="inlineStr"/>
       <c r="W7" s="8" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17453,7 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>1900</v>
+        <v>2170</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -17466,23 +17468,23 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>522 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n">
-        <v>4680</v>
+        <v>20800</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>0</v>
@@ -17490,12 +17492,12 @@
       <c r="P8" s="8" t="n"/>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S8" s="9" t="inlineStr">
@@ -17516,7 +17518,7 @@
       <c r="V8" s="7" t="inlineStr"/>
       <c r="W8" s="8" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>c0573087585d4e3e5716cf3f127e0ed418364345</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17532,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>2170</v>
+        <v>2195</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>2</v>
@@ -17545,7 +17547,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>522 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2 0GJ</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -17554,7 +17556,7 @@
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="J9" s="8" t="n"/>
       <c r="K9" s="8" t="n"/>
@@ -17595,7 +17597,7 @@
       <c r="V9" s="7" t="inlineStr"/>
       <c r="W9" s="8" t="inlineStr">
         <is>
-          <t>c0573087585d4e3e5716cf3f127e0ed418364345</t>
+          <t>ad6f591658988c13d13881686e197fa878817439</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17611,7 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>2195</v>
+        <v>1995</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -17624,23 +17626,21 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>802 Rosewood, Box Makers Yard, New Kingsley Road, Bristol, BS2 0GJ</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>809</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n">
-        <v>20800</v>
+        <v>18544</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S10" s="9" t="inlineStr">
@@ -17674,7 +17674,7 @@
       <c r="V10" s="7" t="inlineStr"/>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t>ad6f591658988c13d13881686e197fa878817439</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -17688,13 +17688,13 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>1995</v>
+        <v>1655</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -17703,21 +17703,23 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>547</v>
+      </c>
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n">
-        <v>18544</v>
+        <v>20800</v>
       </c>
       <c r="O11" s="8" t="n">
         <v>0</v>
@@ -17725,12 +17727,12 @@
       <c r="P11" s="8" t="n"/>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S11" s="9" t="inlineStr">
@@ -17751,7 +17753,7 @@
       <c r="V11" s="7" t="inlineStr"/>
       <c r="W11" s="8" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>1f8489d296d842011bdf7a2ca1f952e6b948c3d3</t>
         </is>
       </c>
     </row>
@@ -17765,13 +17767,13 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>1450</v>
+        <v>2500</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
@@ -17780,23 +17782,21 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Bedminster, Berkeley Place, BS3</t>
+          <t>Electricity House, Colston Avenue, BS1</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>7685</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n">
-        <v>7648</v>
+        <v>21876</v>
       </c>
       <c r="O12" s="8" t="n">
         <v>0</v>
@@ -17804,12 +17804,12 @@
       <c r="P12" s="8" t="n"/>
       <c r="Q12" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S12" s="9" t="inlineStr">
@@ -17830,7 +17830,7 @@
       <c r="V12" s="7" t="inlineStr"/>
       <c r="W12" s="8" t="inlineStr">
         <is>
-          <t>4855da62cb452e8973968307d05f937e5ab76b6c</t>
+          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1655</v>
+        <v>1500</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>1</v>
@@ -17859,23 +17859,21 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>New Kingsley Road, Bristol, BS2</t>
+          <t>The Crescent, Hannover Quay, BS1</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>547</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n">
-        <v>20800</v>
+        <v>16232</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>0</v>
@@ -17888,7 +17886,7 @@
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S13" s="9" t="inlineStr">
@@ -17909,7 +17907,7 @@
       <c r="V13" s="7" t="inlineStr"/>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>1f8489d296d842011bdf7a2ca1f952e6b948c3d3</t>
+          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
         </is>
       </c>
     </row>
@@ -17923,7 +17921,7 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2500</v>
+        <v>1850</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -17938,7 +17936,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Electricity House, Colston Avenue, BS1</t>
+          <t>Park Row, Bristol, BS1</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -17946,26 +17944,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I14" s="8" t="n"/>
+      <c r="I14" s="8" t="n">
+        <v>797</v>
+      </c>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n">
-        <v>21876</v>
-      </c>
+      <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="8" t="n"/>
       <c r="Q14" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S14" s="9" t="inlineStr">
@@ -17986,7 +17984,7 @@
       <c r="V14" s="7" t="inlineStr"/>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
+          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
         </is>
       </c>
     </row>
@@ -18000,13 +17998,13 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>1500</v>
+        <v>2975</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -18015,21 +18013,23 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, BS1</t>
+          <t>Capricorn Place, Hotwells</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="n"/>
+          <t>BS8</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>1615</v>
+      </c>
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n">
-        <v>16232</v>
+        <v>15104</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>0</v>
@@ -18037,12 +18037,12 @@
       <c r="P15" s="8" t="n"/>
       <c r="Q15" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S15" s="9" t="inlineStr">
@@ -18063,7 +18063,7 @@
       <c r="V15" s="7" t="inlineStr"/>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
+          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>1850</v>
+        <v>2000</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -18092,7 +18092,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Park Row, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -18100,31 +18100,31 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I16" s="8" t="n">
-        <v>797</v>
-      </c>
+      <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
+      <c r="N16" s="8" t="n">
+        <v>22020</v>
+      </c>
       <c r="O16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S16" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T16" s="12" t="inlineStr">
@@ -18140,7 +18140,7 @@
       <c r="V16" s="7" t="inlineStr"/>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>50b953f0114e0c02556c27be640db0024cba0be6</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -18154,13 +18154,13 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>2975</v>
+        <v>1400</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -18169,23 +18169,21 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells</t>
+          <t>The Crescent, Harbourside, Bristol</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>BS8</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>1615</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n">
-        <v>15104</v>
+        <v>16368</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>0</v>
@@ -18193,12 +18191,12 @@
       <c r="P17" s="8" t="n"/>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S17" s="9" t="inlineStr">
@@ -18219,7 +18217,7 @@
       <c r="V17" s="7" t="inlineStr"/>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t>24fea285cbc5f197ed72b50a372f175ddb5fa732</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18231,7 @@
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -18248,7 +18246,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -18262,7 +18260,7 @@
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O18" s="8" t="n">
         <v>0</v>
@@ -18280,7 +18278,7 @@
       </c>
       <c r="S18" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T18" s="12" t="inlineStr">
@@ -18296,7 +18294,7 @@
       <c r="V18" s="7" t="inlineStr"/>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -18310,13 +18308,13 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -18325,7 +18323,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, Bristol</t>
+          <t>Steamship House, Gas Ferry Road, BS1</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -18339,7 +18337,7 @@
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="8" t="n">
-        <v>16368</v>
+        <v>14420</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>0</v>
@@ -18347,7 +18345,7 @@
       <c r="P19" s="8" t="n"/>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
@@ -18373,7 +18371,7 @@
       <c r="V19" s="7" t="inlineStr"/>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>f7b6312c22af08d7f7e765adf92d9a3fb0f82781</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18385,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -18402,7 +18400,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Harbourside, The Crescent, BS1 5JP</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -18410,13 +18408,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I20" s="8" t="n"/>
+      <c r="I20" s="8" t="n">
+        <v>969</v>
+      </c>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n">
-        <v>22132</v>
+        <v>16368</v>
       </c>
       <c r="O20" s="8" t="n">
         <v>0</v>
@@ -18424,12 +18424,12 @@
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S20" s="9" t="inlineStr">
@@ -18450,7 +18450,7 @@
       <c r="V20" s="7" t="inlineStr"/>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>384c19ad899eb10f0c99305f716bbf9cc2030cb0</t>
         </is>
       </c>
     </row>
@@ -18464,13 +18464,13 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1700</v>
+        <v>1350</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Steamship House, Gas Ferry Road, BS1</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -18487,13 +18487,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I21" s="8" t="n"/>
+      <c r="I21" s="8" t="n">
+        <v>491</v>
+      </c>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n">
-        <v>14420</v>
+        <v>17096</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>0</v>
@@ -18506,7 +18508,7 @@
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>A2Dominion Group, A2Dominion Lettings</t>
         </is>
       </c>
       <c r="S21" s="9" t="inlineStr">
@@ -18527,7 +18529,7 @@
       <c r="V21" s="7" t="inlineStr"/>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>f7b6312c22af08d7f7e765adf92d9a3fb0f82781</t>
+          <t>3ab86f4fbffd37f02afac44cadd6ec8a27da6f0a</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18543,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -18556,7 +18558,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Harbourside, The Crescent, BS1 5JP</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -18564,15 +18566,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I22" s="8" t="n">
-        <v>969</v>
-      </c>
+      <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n">
-        <v>16368</v>
+        <v>14632</v>
       </c>
       <c r="O22" s="8" t="n">
         <v>0</v>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S22" s="9" t="inlineStr">
@@ -18606,7 +18606,7 @@
       <c r="V22" s="7" t="inlineStr"/>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>384c19ad899eb10f0c99305f716bbf9cc2030cb0</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -18620,13 +18620,13 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
@@ -18635,23 +18635,21 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>Sweetman Place, Bristol, BS2</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>491</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n">
-        <v>17096</v>
+        <v>20416</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>0</v>
@@ -18664,7 +18662,7 @@
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>A2Dominion Group, A2Dominion Lettings</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S23" s="9" t="inlineStr">
@@ -18685,7 +18683,7 @@
       <c r="V23" s="7" t="inlineStr"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>3ab86f4fbffd37f02afac44cadd6ec8a27da6f0a</t>
+          <t>54fa42ef8d0349a295f45392644c43dec3321c5b</t>
         </is>
       </c>
     </row>
@@ -18699,13 +18697,13 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
@@ -18714,7 +18712,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>City Centre, Corinthian Court, BS1</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -18722,13 +18720,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I24" s="8" t="n"/>
+      <c r="I24" s="8" t="n">
+        <v>389</v>
+      </c>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n">
-        <v>14632</v>
+        <v>18820</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>0</v>
@@ -18736,12 +18736,12 @@
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S24" s="9" t="inlineStr">
@@ -18762,7 +18762,7 @@
       <c r="V24" s="7" t="inlineStr"/>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>5aed40eba285a7fa0266bfe8eb49613bb2f96c97</t>
         </is>
       </c>
     </row>
@@ -18776,13 +18776,13 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -18791,21 +18791,23 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Sweetman Place, Bristol, BS2</t>
+          <t>Harbourside, Steamship House, BS1 6GL</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>506</v>
+      </c>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n">
-        <v>20416</v>
+        <v>14420</v>
       </c>
       <c r="O25" s="8" t="n">
         <v>0</v>
@@ -18813,12 +18815,12 @@
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S25" s="9" t="inlineStr">
@@ -18839,7 +18841,7 @@
       <c r="V25" s="7" t="inlineStr"/>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>54fa42ef8d0349a295f45392644c43dec3321c5b</t>
+          <t>bf329b73db0d1de077d78cddc284f1017fcfc43a</t>
         </is>
       </c>
     </row>
@@ -18853,7 +18855,7 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>1</v>
@@ -18868,7 +18870,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Corinthian Court, BS1</t>
+          <t>St. James Barton, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -18876,15 +18878,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I26" s="8" t="n">
-        <v>389</v>
-      </c>
+      <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n">
-        <v>18820</v>
+        <v>22132</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>0</v>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Balloon Letting Company, Bristol</t>
         </is>
       </c>
       <c r="S26" s="9" t="inlineStr">
@@ -18918,7 +18918,7 @@
       <c r="V26" s="7" t="inlineStr"/>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>5aed40eba285a7fa0266bfe8eb49613bb2f96c97</t>
+          <t>f2c75a0f99c7c358be96a67019a6c639e60845fb</t>
         </is>
       </c>
     </row>
@@ -18932,10 +18932,10 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1500</v>
+        <v>1950</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>1</v>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Harbourside, Steamship House, BS1 6GL</t>
+          <t>Apartments, Bristol, BS1</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -18955,15 +18955,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I27" s="8" t="n">
-        <v>506</v>
-      </c>
+      <c r="I27" s="8" t="n"/>
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n">
-        <v>14420</v>
+        <v>22132</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>0</v>
@@ -18976,12 +18974,12 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S27" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>bills included</t>
         </is>
       </c>
       <c r="T27" s="12" t="inlineStr">
@@ -18997,7 +18995,7 @@
       <c r="V27" s="7" t="inlineStr"/>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>bf329b73db0d1de077d78cddc284f1017fcfc43a</t>
+          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
         </is>
       </c>
     </row>
@@ -19011,27 +19009,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1400</v>
+        <v>3750</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>St. James Barton, Bristol, Somerset, BS1</t>
+          <t>Dove Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -19040,7 +19038,7 @@
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n">
-        <v>22132</v>
+        <v>21288</v>
       </c>
       <c r="O28" s="8" t="n">
         <v>0</v>
@@ -19053,12 +19051,12 @@
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>Balloon Letting Company, Bristol</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S28" s="9" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T28" s="12" t="inlineStr">
@@ -19074,7 +19072,7 @@
       <c r="V28" s="7" t="inlineStr"/>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>f2c75a0f99c7c358be96a67019a6c639e60845fb</t>
+          <t>1bcb0667c3a3efe864816ea971273f0e1ff48f01</t>
         </is>
       </c>
     </row>
@@ -19088,10 +19086,10 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1950</v>
+        <v>1300</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>1</v>
@@ -19103,7 +19101,7 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Apartments, Bristol, BS1</t>
+          <t>Three Queens Lane, Bristol, BS1</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -19117,7 +19115,7 @@
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n">
-        <v>22132</v>
+        <v>20608</v>
       </c>
       <c r="O29" s="8" t="n">
         <v>0</v>
@@ -19125,17 +19123,17 @@
       <c r="P29" s="8" t="n"/>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S29" s="9" t="inlineStr">
         <is>
-          <t>bills included</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
@@ -19151,7 +19149,7 @@
       <c r="V29" s="7" t="inlineStr"/>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>b3bc6f44f28301ca7ff059723f3c836424cd082f</t>
+          <t>7c9f52e17d949cd3dc79f3eb8c1020a81c729d66</t>
         </is>
       </c>
     </row>
@@ -19165,27 +19163,27 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Dove Street, Bristol, BS2</t>
+          <t>Lewins Mead, Bristol</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -19193,26 +19191,24 @@
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n">
-        <v>21288</v>
-      </c>
+      <c r="N30" s="8" t="n"/>
       <c r="O30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>Airsat Real Estate, Bristol</t>
         </is>
       </c>
       <c r="S30" s="9" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T30" s="12" t="inlineStr">
@@ -19228,7 +19224,7 @@
       <c r="V30" s="7" t="inlineStr"/>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>1bcb0667c3a3efe864816ea971273f0e1ff48f01</t>
+          <t>2d3387df3c55adfe44b18dbc94a6511d536c9187</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19238,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>1</v>
@@ -19257,7 +19253,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Three Queens Lane, Bristol, BS1</t>
+          <t>Caslon Court, Somerset Street, BS1</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -19271,7 +19267,7 @@
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n">
-        <v>20608</v>
+        <v>18424</v>
       </c>
       <c r="O31" s="8" t="n">
         <v>0</v>
@@ -19279,12 +19275,12 @@
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S31" s="9" t="inlineStr">
@@ -19305,7 +19301,7 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>7c9f52e17d949cd3dc79f3eb8c1020a81c729d66</t>
+          <t>f6187d8c2bb085d8ddb57c1f8b8dc96ceada86aa</t>
         </is>
       </c>
     </row>
@@ -19319,13 +19315,13 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>2200</v>
+        <v>1450</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
@@ -19334,32 +19330,36 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Lewins Mead, Bristol</t>
+          <t>Bedminster, Berkeley Place, BS3</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>7685</v>
+      </c>
       <c r="J32" s="8" t="n"/>
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
+      <c r="N32" s="8" t="n">
+        <v>7648</v>
+      </c>
       <c r="O32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Airsat Real Estate, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr">
@@ -19380,7 +19380,7 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>2d3387df3c55adfe44b18dbc94a6511d536c9187</t>
+          <t>4855da62cb452e8973968307d05f937e5ab76b6c</t>
         </is>
       </c>
     </row>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1300</v>
+        <v>2020</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -21686,14 +21686,14 @@
         </is>
       </c>
       <c r="I63" s="8" t="n">
-        <v>405</v>
+        <v>764</v>
       </c>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n">
-        <v>20316</v>
+        <v>20856</v>
       </c>
       <c r="O63" s="8" t="n">
         <v>0</v>
@@ -21701,12 +21701,12 @@
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R63" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S63" s="9" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       <c r="V63" s="7" t="inlineStr"/>
       <c r="W63" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
         </is>
       </c>
     </row>
@@ -21737,7 +21737,7 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>2020</v>
+        <v>2145</v>
       </c>
       <c r="D64" s="8" t="n">
         <v>2</v>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -21761,14 +21761,14 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>764</v>
+        <v>815</v>
       </c>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O64" s="8" t="n">
         <v>0</v>
@@ -21781,7 +21781,7 @@
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S64" s="9" t="inlineStr"/>
@@ -21798,7 +21798,7 @@
       <c r="V64" s="7" t="inlineStr"/>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>6140b74b7d83ae5918fdabb6f9371e2f4b63a9c2</t>
+          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
         </is>
       </c>
     </row>
@@ -21812,13 +21812,13 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>2145</v>
+        <v>1635</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -21836,7 +21836,7 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>815</v>
+        <v>486</v>
       </c>
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
@@ -21856,7 +21856,7 @@
       </c>
       <c r="R65" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S65" s="9" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       <c r="V65" s="7" t="inlineStr"/>
       <c r="W65" s="8" t="inlineStr">
         <is>
-          <t>24009eb3414633bf24b3b69631ba405866a1e5c9</t>
+          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
         </is>
       </c>
     </row>
@@ -21887,13 +21887,13 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>1635</v>
+        <v>1750</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
@@ -21902,23 +21902,23 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>486</v>
+        <v>731</v>
       </c>
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n">
-        <v>21504</v>
+        <v>4680</v>
       </c>
       <c r="O66" s="8" t="n">
         <v>0</v>
@@ -21931,7 +21931,7 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S66" s="9" t="inlineStr"/>
@@ -21948,7 +21948,7 @@
       <c r="V66" s="7" t="inlineStr"/>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>bbf6e42784b6e4b7dae8d6bef9900115d0f3056e</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -21962,13 +21962,13 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -21977,23 +21977,21 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>731</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="n"/>
       <c r="J67" s="8" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n">
-        <v>4680</v>
+        <v>21148</v>
       </c>
       <c r="O67" s="8" t="n">
         <v>0</v>
@@ -22001,12 +21999,12 @@
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S67" s="9" t="inlineStr"/>
@@ -22023,7 +22021,7 @@
       <c r="V67" s="7" t="inlineStr"/>
       <c r="W67" s="8" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -22037,13 +22035,13 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>2100</v>
+        <v>2220</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -22052,7 +22050,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -22060,13 +22058,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I68" s="8" t="n"/>
+      <c r="I68" s="8" t="n">
+        <v>697</v>
+      </c>
       <c r="J68" s="8" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n">
-        <v>21148</v>
+        <v>20820</v>
       </c>
       <c r="O68" s="8" t="n">
         <v>0</v>
@@ -22079,7 +22079,7 @@
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S68" s="9" t="inlineStr"/>
@@ -22096,7 +22096,7 @@
       <c r="V68" s="7" t="inlineStr"/>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -22110,13 +22110,13 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>2220</v>
+        <v>1300</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -22133,15 +22133,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="8" t="n">
-        <v>697</v>
-      </c>
+      <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n">
-        <v>20820</v>
+        <v>21428</v>
       </c>
       <c r="O69" s="8" t="n">
         <v>0</v>
@@ -22149,12 +22147,12 @@
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R69" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S69" s="9" t="inlineStr"/>
@@ -22171,7 +22169,7 @@
       <c r="V69" s="7" t="inlineStr"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22183,7 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D70" s="8" t="n">
         <v>1</v>
@@ -22200,7 +22198,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -22208,13 +22206,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="8" t="n"/>
+      <c r="I70" s="8" t="n">
+        <v>548</v>
+      </c>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n">
-        <v>21428</v>
+        <v>21504</v>
       </c>
       <c r="O70" s="8" t="n">
         <v>0</v>
@@ -22222,12 +22222,12 @@
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S70" s="9" t="inlineStr"/>
@@ -22244,7 +22244,7 @@
       <c r="V70" s="7" t="inlineStr"/>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>317e9ab29cad2381c41672743d877feba2c14e45</t>
+          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22258,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1500</v>
+        <v>1615</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>1</v>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -22282,7 +22282,7 @@
         </is>
       </c>
       <c r="I71" s="8" t="n">
-        <v>548</v>
+        <v>486</v>
       </c>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="R71" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S71" s="9" t="inlineStr"/>
@@ -22319,7 +22319,7 @@
       <c r="V71" s="7" t="inlineStr"/>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>bad1e4584285201ef9995d2b437343fca870009c</t>
+          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
         </is>
       </c>
     </row>
@@ -22333,10 +22333,10 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1615</v>
+        <v>1965</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>1</v>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>486</v>
+        <v>655</v>
       </c>
       <c r="J72" s="8" t="n"/>
       <c r="K72" s="8" t="n"/>
@@ -22372,12 +22372,12 @@
       <c r="P72" s="8" t="n"/>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S72" s="9" t="inlineStr"/>
@@ -22394,7 +22394,7 @@
       <c r="V72" s="7" t="inlineStr"/>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>67ff71428df47b0eb7f7da47600378ffdad1f97c</t>
+          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
         </is>
       </c>
     </row>
@@ -22408,13 +22408,13 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1965</v>
+        <v>2080</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -22432,14 +22432,14 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="J73" s="8" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0</v>
@@ -22452,7 +22452,7 @@
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S73" s="9" t="inlineStr"/>
@@ -22469,7 +22469,7 @@
       <c r="V73" s="7" t="inlineStr"/>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>1a5b509e1606992acea1736489630b2bc57cc717</t>
+          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
         </is>
       </c>
     </row>
@@ -22483,13 +22483,13 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>2080</v>
+        <v>2000</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Welsh Back, Bristol, BS1</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -22507,15 +22507,13 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>705</v>
+        <v>908</v>
       </c>
       <c r="J74" s="8" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
-      <c r="N74" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N74" s="8" t="n"/>
       <c r="O74" s="8" t="n">
         <v>0</v>
       </c>
@@ -22527,7 +22525,7 @@
       </c>
       <c r="R74" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Hello Neighbour, London</t>
         </is>
       </c>
       <c r="S74" s="9" t="inlineStr"/>
@@ -22544,7 +22542,7 @@
       <c r="V74" s="7" t="inlineStr"/>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>0453e07b653a16ada93327f26a41e0b204d289a4</t>
+          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
         </is>
       </c>
     </row>
@@ -22558,13 +22556,13 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>1400</v>
+        <v>2020</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
@@ -22573,7 +22571,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -22581,26 +22579,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I75" s="8" t="n"/>
+      <c r="I75" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J75" s="8" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
-      <c r="N75" s="8" t="n">
-        <v>19484</v>
-      </c>
+      <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="8" t="n"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R75" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S75" s="9" t="inlineStr"/>
@@ -22617,7 +22615,7 @@
       <c r="V75" s="7" t="inlineStr"/>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22635,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
@@ -22646,7 +22644,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol, BS1</t>
+          <t>Eclipse - City Centre</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -22654,9 +22652,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I76" s="8" t="n">
-        <v>908</v>
-      </c>
+      <c r="I76" s="8" t="n"/>
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
@@ -22668,12 +22664,12 @@
       <c r="P76" s="8" t="n"/>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>Hello Neighbour, London</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
@@ -22690,7 +22686,7 @@
       <c r="V76" s="7" t="inlineStr"/>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>65ed2520fdf37e6dde4abe0097cc3edbbbeff957</t>
+          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22700,7 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2020</v>
+        <v>2085</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>2</v>
@@ -22741,7 +22737,7 @@
       <c r="P77" s="8" t="n"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr">
@@ -22763,7 +22759,7 @@
       <c r="V77" s="7" t="inlineStr"/>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>75b3ee81b8ecb4015a80108f6d509e4156f4e8e4</t>
+          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
         </is>
       </c>
     </row>
@@ -22777,13 +22773,13 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>2000</v>
+        <v>1615</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
@@ -22792,7 +22788,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Eclipse - City Centre</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -22800,7 +22796,9 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I78" s="8" t="n"/>
+      <c r="I78" s="8" t="n">
+        <v>487</v>
+      </c>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
@@ -22812,12 +22810,12 @@
       <c r="P78" s="8" t="n"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S78" s="9" t="inlineStr"/>
@@ -22834,7 +22832,7 @@
       <c r="V78" s="7" t="inlineStr"/>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>638ecbe81729048ffda61524ca9b06c4a208ce7b</t>
+          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22846,7 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>2085</v>
+        <v>2065</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>2</v>
@@ -22863,7 +22861,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -22872,7 +22870,7 @@
         </is>
       </c>
       <c r="I79" s="8" t="n">
-        <v>705</v>
+        <v>641</v>
       </c>
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
@@ -22885,12 +22883,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R79" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S79" s="9" t="inlineStr"/>
@@ -22907,7 +22905,7 @@
       <c r="V79" s="7" t="inlineStr"/>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>16c89eb9a4cdeb57ddb3fd1201b7084ea2f3c007</t>
+          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
         </is>
       </c>
     </row>
@@ -22921,13 +22919,13 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>1615</v>
+        <v>2185</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
@@ -22945,7 +22943,7 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>487</v>
+        <v>721</v>
       </c>
       <c r="J80" s="8" t="n"/>
       <c r="K80" s="8" t="n"/>
@@ -22958,7 +22956,7 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="R80" s="8" t="inlineStr">
@@ -22980,7 +22978,7 @@
       <c r="V80" s="7" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>cd57661c8d996d20c5c1c7c34b12787f40073ec9</t>
+          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
         </is>
       </c>
     </row>
@@ -22994,13 +22992,13 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>2065</v>
+        <v>1565</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
@@ -23009,7 +23007,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -23018,7 +23016,7 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>641</v>
+        <v>484</v>
       </c>
       <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n"/>
@@ -23036,7 +23034,7 @@
       </c>
       <c r="R81" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S81" s="9" t="inlineStr"/>
@@ -23053,7 +23051,7 @@
       <c r="V81" s="7" t="inlineStr"/>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>d23eb397c84a723416c257acf4e25973ede40bc5</t>
+          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
         </is>
       </c>
     </row>
@@ -23067,13 +23065,13 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>2185</v>
+        <v>2100</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
@@ -23082,7 +23080,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Three Kings Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -23090,9 +23088,7 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I82" s="8" t="n">
-        <v>721</v>
-      </c>
+      <c r="I82" s="8" t="n"/>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
@@ -23104,12 +23100,12 @@
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S82" s="9" t="inlineStr"/>
@@ -23126,7 +23122,7 @@
       <c r="V82" s="7" t="inlineStr"/>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>6446e0c7d9c4f21f9eb6239caeeeee0599a68101</t>
+          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
         </is>
       </c>
     </row>
@@ -23140,7 +23136,7 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>1565</v>
+        <v>1660</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>1</v>
@@ -23164,20 +23160,22 @@
         </is>
       </c>
       <c r="I83" s="8" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
       <c r="M83" s="8" t="n"/>
-      <c r="N83" s="8" t="n"/>
+      <c r="N83" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O83" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="8" t="n"/>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R83" s="8" t="inlineStr">
@@ -23199,7 +23197,7 @@
       <c r="V83" s="7" t="inlineStr"/>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>34d9877a23c82be120784d9dd55c23c17584c91a</t>
+          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
         </is>
       </c>
     </row>
@@ -23213,13 +23211,13 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>1650</v>
+        <v>2175</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
@@ -23228,7 +23226,7 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -23236,24 +23234,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="8" t="n"/>
+      <c r="I84" s="8" t="n">
+        <v>814</v>
+      </c>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
-      <c r="N84" s="8" t="n"/>
+      <c r="N84" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O84" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="8" t="n"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R84" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S84" s="9" t="inlineStr"/>
@@ -23270,7 +23272,7 @@
       <c r="V84" s="7" t="inlineStr"/>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
         </is>
       </c>
     </row>
@@ -23284,13 +23286,13 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>2100</v>
+        <v>2115</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
@@ -23299,7 +23301,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>The Three Kings Court, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -23307,24 +23309,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I85" s="8" t="n"/>
+      <c r="I85" s="8" t="n">
+        <v>823</v>
+      </c>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
-      <c r="N85" s="8" t="n"/>
+      <c r="N85" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O85" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="8" t="n"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S85" s="9" t="inlineStr"/>
@@ -23341,7 +23347,7 @@
       <c r="V85" s="7" t="inlineStr"/>
       <c r="W85" s="8" t="inlineStr">
         <is>
-          <t>954007c82f6f3a495c465b72c9a1c44c0c84713e</t>
+          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23400,7 @@
       <c r="P86" s="8" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr">
@@ -23416,7 +23422,7 @@
       <c r="V86" s="7" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>c2c660e4e8cefc047b4bc72bf19b48ce9ef7ec99</t>
+          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
         </is>
       </c>
     </row>
@@ -23430,7 +23436,7 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>2175</v>
+        <v>1915</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>2</v>
@@ -23454,14 +23460,14 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>814</v>
+        <v>746</v>
       </c>
       <c r="J87" s="8" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="8" t="n"/>
       <c r="N87" s="8" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O87" s="8" t="n">
         <v>0</v>
@@ -23469,7 +23475,7 @@
       <c r="P87" s="8" t="n"/>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R87" s="8" t="inlineStr">
@@ -23491,7 +23497,7 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="8" t="inlineStr">
         <is>
-          <t>83406f05c9aded812a566cc6806036dda0d45fc0</t>
+          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
         </is>
       </c>
     </row>
@@ -23505,10 +23511,10 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>1500</v>
+        <v>2450</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
         <v>2</v>
@@ -23520,7 +23526,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -23534,7 +23540,7 @@
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="n"/>
       <c r="N88" s="8" t="n">
-        <v>21816</v>
+        <v>21788</v>
       </c>
       <c r="O88" s="8" t="n">
         <v>0</v>
@@ -23542,12 +23548,12 @@
       <c r="P88" s="8" t="n"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S88" s="9" t="inlineStr"/>
@@ -23564,7 +23570,7 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -23578,7 +23584,7 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>2115</v>
+        <v>1700</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>2</v>
@@ -23593,7 +23599,7 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>The Crescent</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -23601,15 +23607,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I89" s="8" t="n">
-        <v>823</v>
-      </c>
+      <c r="I89" s="8" t="n"/>
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="8" t="n">
-        <v>20820</v>
+        <v>16368</v>
       </c>
       <c r="O89" s="8" t="n">
         <v>0</v>
@@ -23617,12 +23621,12 @@
       <c r="P89" s="8" t="n"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R89" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S89" s="9" t="inlineStr"/>
@@ -23639,7 +23643,7 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="8" t="inlineStr">
         <is>
-          <t>0b78c6e29d96ae73c643d0d50d50949797b02893</t>
+          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
         </is>
       </c>
     </row>
@@ -23653,7 +23657,7 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>1660</v>
+        <v>1250</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>1</v>
@@ -23668,7 +23672,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -23676,15 +23680,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I90" s="8" t="n">
-        <v>486</v>
-      </c>
+      <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
       <c r="N90" s="8" t="n">
-        <v>21504</v>
+        <v>21160</v>
       </c>
       <c r="O90" s="8" t="n">
         <v>0</v>
@@ -23692,12 +23694,12 @@
       <c r="P90" s="8" t="n"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S90" s="9" t="inlineStr"/>
@@ -23714,7 +23716,7 @@
       <c r="V90" s="7" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>c798c669d03fa2e42fd418ff0916de022d3380ad</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -23728,13 +23730,13 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>1915</v>
+        <v>1999</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
@@ -23743,7 +23745,7 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -23751,15 +23753,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I91" s="8" t="n">
-        <v>746</v>
-      </c>
+      <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n">
-        <v>21680</v>
+        <v>20800</v>
       </c>
       <c r="O91" s="8" t="n">
         <v>0</v>
@@ -23767,12 +23767,12 @@
       <c r="P91" s="8" t="n"/>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="8" t="inlineStr">
         <is>
-          <t>36797023cff0095f1bf764fa2f176d5595124854</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -23803,7 +23803,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>1150</v>
+        <v>1670</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>1</v>
@@ -23818,21 +23818,23 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I92" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>485</v>
+      </c>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n">
-        <v>6872</v>
+        <v>21504</v>
       </c>
       <c r="O92" s="8" t="n">
         <v>0</v>
@@ -23840,12 +23842,12 @@
       <c r="P92" s="8" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S92" s="9" t="inlineStr"/>
@@ -23862,7 +23864,7 @@
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -23876,13 +23878,13 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>2450</v>
+        <v>1645</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
@@ -23891,7 +23893,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
@@ -23899,13 +23901,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I93" s="8" t="n"/>
+      <c r="I93" s="8" t="n">
+        <v>517</v>
+      </c>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
       <c r="M93" s="8" t="n"/>
       <c r="N93" s="8" t="n">
-        <v>21788</v>
+        <v>20820</v>
       </c>
       <c r="O93" s="8" t="n">
         <v>0</v>
@@ -23913,12 +23917,12 @@
       <c r="P93" s="8" t="n"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S93" s="9" t="inlineStr"/>
@@ -23935,7 +23939,7 @@
       <c r="V93" s="7" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23953,7 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1700</v>
+        <v>2120</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>2</v>
@@ -23964,7 +23968,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>The Crescent</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -23972,13 +23976,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I94" s="8" t="n"/>
+      <c r="I94" s="8" t="n">
+        <v>705</v>
+      </c>
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n">
-        <v>16368</v>
+        <v>20820</v>
       </c>
       <c r="O94" s="8" t="n">
         <v>0</v>
@@ -23986,12 +23992,12 @@
       <c r="P94" s="8" t="n"/>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S94" s="9" t="inlineStr"/>
@@ -24008,7 +24014,7 @@
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>8a8446c119238f7a042580aed1922ef6cfd79ae2</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -24022,7 +24028,7 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>1250</v>
+        <v>1645</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>1</v>
@@ -24037,7 +24043,7 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -24045,13 +24051,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="8" t="n"/>
+      <c r="I95" s="8" t="n">
+        <v>571</v>
+      </c>
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="8" t="n">
-        <v>21160</v>
+        <v>20820</v>
       </c>
       <c r="O95" s="8" t="n">
         <v>0</v>
@@ -24059,12 +24067,12 @@
       <c r="P95" s="8" t="n"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S95" s="9" t="inlineStr"/>
@@ -24081,7 +24089,7 @@
       <c r="V95" s="7" t="inlineStr"/>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
         </is>
       </c>
     </row>
@@ -24095,7 +24103,7 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>1999</v>
+        <v>1600</v>
       </c>
       <c r="D96" s="8" t="n">
         <v>2</v>
@@ -24110,12 +24118,12 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I96" s="8" t="n"/>
@@ -24124,7 +24132,7 @@
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n">
-        <v>20800</v>
+        <v>19576</v>
       </c>
       <c r="O96" s="8" t="n">
         <v>0</v>
@@ -24132,7 +24140,7 @@
       <c r="P96" s="8" t="n"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R96" s="8" t="inlineStr">
@@ -24154,7 +24162,7 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
         </is>
       </c>
     </row>
@@ -24168,13 +24176,13 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>1670</v>
+        <v>1550</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
@@ -24183,7 +24191,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>City Centre, Waverley House, BS1 5LW</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -24192,14 +24200,14 @@
         </is>
       </c>
       <c r="I97" s="8" t="n">
-        <v>485</v>
+        <v>775</v>
       </c>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n">
-        <v>21504</v>
+        <v>17744</v>
       </c>
       <c r="O97" s="8" t="n">
         <v>0</v>
@@ -24207,12 +24215,12 @@
       <c r="P97" s="8" t="n"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R97" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S97" s="9" t="inlineStr"/>
@@ -24229,7 +24237,7 @@
       <c r="V97" s="7" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>ac4ae9e8b18bae38c431398f0f633dd1691dd454</t>
         </is>
       </c>
     </row>
@@ -24243,13 +24251,13 @@
         </is>
       </c>
       <c r="C98" s="17" t="n">
-        <v>1645</v>
+        <v>2125</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
@@ -24267,7 +24275,7 @@
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>517</v>
+        <v>705</v>
       </c>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
@@ -24282,7 +24290,7 @@
       <c r="P98" s="8" t="n"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R98" s="8" t="inlineStr">
@@ -24304,7 +24312,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>4efcb79ae710a68f5f272a2f9030937499117f9d</t>
+          <t>98852e60433cf90995df068fb3ceec727903a8f0</t>
         </is>
       </c>
     </row>
@@ -24318,13 +24326,13 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>2120</v>
+        <v>1580</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
@@ -24333,7 +24341,7 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -24342,14 +24350,14 @@
         </is>
       </c>
       <c r="I99" s="8" t="n">
-        <v>705</v>
+        <v>486</v>
       </c>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O99" s="8" t="n">
         <v>0</v>
@@ -24357,12 +24365,12 @@
       <c r="P99" s="8" t="n"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R99" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S99" s="9" t="inlineStr"/>
@@ -24379,7 +24387,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -24393,7 +24401,7 @@
         </is>
       </c>
       <c r="C100" s="17" t="n">
-        <v>1645</v>
+        <v>1500</v>
       </c>
       <c r="D100" s="8" t="n">
         <v>1</v>
@@ -24408,23 +24416,23 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Bedminster, Regent House, BS3 1FT</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>571</v>
+        <v>527</v>
       </c>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n">
-        <v>20820</v>
+        <v>13548</v>
       </c>
       <c r="O100" s="8" t="n">
         <v>0</v>
@@ -24432,12 +24440,12 @@
       <c r="P100" s="8" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R100" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S100" s="9" t="inlineStr"/>
@@ -24454,7 +24462,7 @@
       <c r="V100" s="7" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>487e67b2d6680ebaabfcc49d4d33e21cb65cca6d</t>
+          <t>b5574d3457f97017e231a45d57df860c0d54fe3d</t>
         </is>
       </c>
     </row>
@@ -24468,10 +24476,10 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>1600</v>
+        <v>1350</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
         <v>1</v>
@@ -24483,21 +24491,23 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Baldwin Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I101" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="n">
+        <v>413</v>
+      </c>
       <c r="J101" s="8" t="n"/>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n">
-        <v>19576</v>
+        <v>21148</v>
       </c>
       <c r="O101" s="8" t="n">
         <v>0</v>
@@ -24505,12 +24515,12 @@
       <c r="P101" s="8" t="n"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R101" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S101" s="9" t="inlineStr"/>
@@ -24527,7 +24537,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>41184aca0a094a13f0cf944554fa6ab5b6f9b761</t>
+          <t>ca58d4891f705dc219b7ca74ef59637a2959afb0</t>
         </is>
       </c>
     </row>
@@ -24541,7 +24551,7 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1555</v>
+        <v>1620</v>
       </c>
       <c r="D102" s="8" t="n">
         <v>1</v>
@@ -24556,21 +24566,23 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Lombard Street, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I102" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="n">
+        <v>494</v>
+      </c>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n">
-        <v>12036</v>
+        <v>20820</v>
       </c>
       <c r="O102" s="8" t="n">
         <v>0</v>
@@ -24578,12 +24590,12 @@
       <c r="P102" s="8" t="n"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R102" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S102" s="9" t="inlineStr"/>
@@ -24600,7 +24612,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
+          <t>b9cdcc0c4daa02ab2447615be3746df090f8a759</t>
         </is>
       </c>
     </row>
@@ -24614,7 +24626,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1550</v>
+        <v>2110</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>2</v>
@@ -24629,7 +24641,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Waverley House, BS1 5LW</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
@@ -24638,15 +24650,13 @@
         </is>
       </c>
       <c r="I103" s="8" t="n">
-        <v>775</v>
+        <v>722</v>
       </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
-      <c r="N103" s="8" t="n">
-        <v>17744</v>
-      </c>
+      <c r="N103" s="8" t="n"/>
       <c r="O103" s="8" t="n">
         <v>0</v>
       </c>
@@ -24658,7 +24668,7 @@
       </c>
       <c r="R103" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S103" s="9" t="inlineStr"/>
@@ -24675,7 +24685,7 @@
       <c r="V103" s="7" t="inlineStr"/>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>ac4ae9e8b18bae38c431398f0f633dd1691dd454</t>
+          <t>1fc314f1a5b51f6a42142e88d789000861f8e441</t>
         </is>
       </c>
     </row>
@@ -24689,13 +24699,13 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>2125</v>
+        <v>1300</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
@@ -24704,7 +24714,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
@@ -24713,14 +24723,14 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>705</v>
+        <v>405</v>
       </c>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n">
-        <v>20820</v>
+        <v>20316</v>
       </c>
       <c r="O104" s="8" t="n">
         <v>0</v>
@@ -24728,12 +24738,12 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24750,7 +24760,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>98852e60433cf90995df068fb3ceec727903a8f0</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24774,7 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1580</v>
+        <v>1400</v>
       </c>
       <c r="D105" s="8" t="n">
         <v>1</v>
@@ -24779,7 +24789,7 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
@@ -24787,15 +24797,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I105" s="8" t="n">
-        <v>486</v>
-      </c>
+      <c r="I105" s="8" t="n"/>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
       <c r="N105" s="8" t="n">
-        <v>21504</v>
+        <v>19484</v>
       </c>
       <c r="O105" s="8" t="n">
         <v>0</v>
@@ -24803,12 +24811,12 @@
       <c r="P105" s="8" t="n"/>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S105" s="9" t="inlineStr"/>
@@ -24825,7 +24833,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -24839,7 +24847,7 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="D106" s="8" t="n">
         <v>1</v>
@@ -24854,36 +24862,32 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Bedminster, Regent House, BS3 1FT</t>
+          <t>Horizon, Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I106" s="8" t="n">
-        <v>527</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="n"/>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n">
-        <v>13548</v>
-      </c>
+      <c r="N106" s="8" t="n"/>
       <c r="O106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24900,7 +24904,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>b5574d3457f97017e231a45d57df860c0d54fe3d</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -24914,13 +24918,13 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -24929,7 +24933,7 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Baldwin Street, Bristol, BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
@@ -24937,15 +24941,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I107" s="8" t="n">
-        <v>413</v>
-      </c>
+      <c r="I107" s="8" t="n"/>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n">
-        <v>21148</v>
+        <v>21816</v>
       </c>
       <c r="O107" s="8" t="n">
         <v>0</v>
@@ -24953,12 +24955,12 @@
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S107" s="9" t="inlineStr"/>
@@ -24975,7 +24977,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>ca58d4891f705dc219b7ca74ef59637a2959afb0</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -24989,7 +24991,7 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>1620</v>
+        <v>1150</v>
       </c>
       <c r="D108" s="8" t="n">
         <v>1</v>
@@ -25004,23 +25006,21 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="n">
-        <v>494</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="n"/>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>20820</v>
+        <v>6872</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -25028,12 +25028,12 @@
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -25050,7 +25050,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>b9cdcc0c4daa02ab2447615be3746df090f8a759</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -25064,13 +25064,13 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>2110</v>
+        <v>1555</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
@@ -25079,34 +25079,34 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Lombard Street, Bristol, BS3</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I109" s="8" t="n">
-        <v>722</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="n"/>
       <c r="J109" s="8" t="n"/>
       <c r="K109" s="8" t="n"/>
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
-      <c r="N109" s="8" t="n"/>
+      <c r="N109" s="8" t="n">
+        <v>12036</v>
+      </c>
       <c r="O109" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="8" t="n"/>
       <c r="Q109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="R109" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S109" s="9" t="inlineStr"/>
@@ -25123,7 +25123,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>1fc314f1a5b51f6a42142e88d789000861f8e441</t>
+          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
         </is>
       </c>
     </row>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'For Sale'!$A$1:$W$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16605,7 +16605,7 @@
   </sheetData>
   <autoFilter ref="A1:W212"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212 U213 U214" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174 U175 U176 U177 U178 U179 U180 U181 U182 U183 U184 U185 U186 U187 U188 U189 U190 U191 U192 U193 U194 U195 U196 U197 U198 U199 U200 U201 U202 U203 U204 U205 U206 U207 U208 U209 U210 U211 U212 U213 U214 U215 U216 U217 U218" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16832,7 +16832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W214"/>
+  <dimension ref="A1:W218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -21170,9 +21170,7 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n">
-        <v>757</v>
-      </c>
+      <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
@@ -24699,13 +24697,13 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1300</v>
+        <v>2075</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
@@ -24714,7 +24712,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>City Centre, Queen Square Apartments, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
@@ -24723,14 +24721,14 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>405</v>
+        <v>673</v>
       </c>
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n">
-        <v>20316</v>
+        <v>20820</v>
       </c>
       <c r="O104" s="8" t="n">
         <v>0</v>
@@ -24738,12 +24736,12 @@
       <c r="P104" s="8" t="n"/>
       <c r="Q104" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R104" s="8" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S104" s="9" t="inlineStr"/>
@@ -24760,7 +24758,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -24774,7 +24772,7 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1400</v>
+        <v>1645</v>
       </c>
       <c r="D105" s="8" t="n">
         <v>1</v>
@@ -24789,7 +24787,7 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
@@ -24797,13 +24795,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I105" s="8" t="n"/>
+      <c r="I105" s="8" t="n">
+        <v>546</v>
+      </c>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
       <c r="N105" s="8" t="n">
-        <v>19484</v>
+        <v>20820</v>
       </c>
       <c r="O105" s="8" t="n">
         <v>0</v>
@@ -24811,12 +24811,12 @@
       <c r="P105" s="8" t="n"/>
       <c r="Q105" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R105" s="8" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S105" s="9" t="inlineStr"/>
@@ -24833,7 +24833,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="8" t="inlineStr">
         <is>
-          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
+          <t>97965ef25d5084c20bb1be86ca100fd603557ea5</t>
         </is>
       </c>
     </row>
@@ -24847,10 +24847,10 @@
         </is>
       </c>
       <c r="C106" s="17" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
         <v>1</v>
@@ -24862,12 +24862,12 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, Bristol, BS1</t>
+          <t>Portland Square, City Centre</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I106" s="8" t="n"/>
@@ -24875,19 +24875,21 @@
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n"/>
+      <c r="N106" s="8" t="n">
+        <v>21392</v>
+      </c>
       <c r="O106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="8" t="n"/>
       <c r="Q106" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R106" s="8" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S106" s="9" t="inlineStr"/>
@@ -24904,7 +24906,7 @@
       <c r="V106" s="7" t="inlineStr"/>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
+          <t>5c6702e019e22ae6a63f958f13da168b2a7871d1</t>
         </is>
       </c>
     </row>
@@ -24918,13 +24920,13 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1500</v>
+        <v>1630</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -24933,7 +24935,7 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>Small Street - City Centre</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
@@ -24941,13 +24943,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I107" s="8" t="n"/>
+      <c r="I107" s="8" t="n">
+        <v>486</v>
+      </c>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n">
-        <v>21816</v>
+        <v>21504</v>
       </c>
       <c r="O107" s="8" t="n">
         <v>0</v>
@@ -24955,12 +24959,12 @@
       <c r="P107" s="8" t="n"/>
       <c r="Q107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R107" s="8" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S107" s="9" t="inlineStr"/>
@@ -24977,7 +24981,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="8" t="inlineStr">
         <is>
-          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -24991,7 +24995,7 @@
         </is>
       </c>
       <c r="C108" s="17" t="n">
-        <v>1150</v>
+        <v>1300</v>
       </c>
       <c r="D108" s="8" t="n">
         <v>1</v>
@@ -25006,21 +25010,23 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>Knowle Road, Bristol</t>
+          <t>City Centre, Queen Square Apartments, BS1</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="n">
+        <v>405</v>
+      </c>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n">
-        <v>6872</v>
+        <v>20316</v>
       </c>
       <c r="O108" s="8" t="n">
         <v>0</v>
@@ -25028,12 +25034,12 @@
       <c r="P108" s="8" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R108" s="8" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S108" s="9" t="inlineStr"/>
@@ -25050,7 +25056,7 @@
       <c r="V108" s="7" t="inlineStr"/>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
+          <t>9ad2c7bc90885b9a9e65b462b952842a964f1d35</t>
         </is>
       </c>
     </row>
@@ -25064,7 +25070,7 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>1555</v>
+        <v>1400</v>
       </c>
       <c r="D109" s="8" t="n">
         <v>1</v>
@@ -25079,12 +25085,12 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Lombard Street, Bristol, BS3</t>
+          <t>Redcliffe Parade West, Flat 3, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I109" s="8" t="n"/>
@@ -25093,7 +25099,7 @@
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
       <c r="N109" s="8" t="n">
-        <v>12036</v>
+        <v>19484</v>
       </c>
       <c r="O109" s="8" t="n">
         <v>0</v>
@@ -25101,12 +25107,12 @@
       <c r="P109" s="8" t="n"/>
       <c r="Q109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R109" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S109" s="9" t="inlineStr"/>
@@ -25123,7 +25129,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="8" t="inlineStr">
         <is>
-          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
+          <t>9b65e5a0fb0bc8fc27d566eae912cddf76828cc9</t>
         </is>
       </c>
     </row>
@@ -25137,13 +25143,13 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>2085</v>
+        <v>1650</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
@@ -25152,7 +25158,7 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Horizon, Broad Weir, Bristol, BS1</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -25160,28 +25166,24 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I110" s="8" t="n">
-        <v>722</v>
-      </c>
+      <c r="I110" s="8" t="n"/>
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
-      <c r="N110" s="8" t="n">
-        <v>21504</v>
-      </c>
+      <c r="N110" s="8" t="n"/>
       <c r="O110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="8" t="n"/>
       <c r="Q110" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R110" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S110" s="9" t="inlineStr"/>
@@ -25198,7 +25200,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
+          <t>aa3cf620ad25601a026424157bd8c0abb746373f</t>
         </is>
       </c>
     </row>
@@ -25212,13 +25214,13 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>1640</v>
+        <v>1500</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
@@ -25227,7 +25229,7 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Small Street - City Centre</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
@@ -25235,15 +25237,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I111" s="8" t="n">
-        <v>570</v>
-      </c>
+      <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n"/>
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
       <c r="N111" s="8" t="n">
-        <v>20820</v>
+        <v>21816</v>
       </c>
       <c r="O111" s="8" t="n">
         <v>0</v>
@@ -25251,12 +25251,12 @@
       <c r="P111" s="8" t="n"/>
       <c r="Q111" s="8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R111" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S111" s="9" t="inlineStr"/>
@@ -25273,7 +25273,7 @@
       <c r="V111" s="7" t="inlineStr"/>
       <c r="W111" s="8" t="inlineStr">
         <is>
-          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
+          <t>cb4b1af676ff54ae12ad7bf4fa94acd8ef94a533</t>
         </is>
       </c>
     </row>
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="C112" s="17" t="n">
-        <v>1595</v>
+        <v>1150</v>
       </c>
       <c r="D112" s="8" t="n">
         <v>1</v>
@@ -25302,34 +25302,34 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Knowle Road, Bristol</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I112" s="8" t="n">
-        <v>499</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="n"/>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
-      <c r="N112" s="8" t="n"/>
+      <c r="N112" s="8" t="n">
+        <v>6872</v>
+      </c>
       <c r="O112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="8" t="n"/>
       <c r="Q112" s="8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R112" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S112" s="9" t="inlineStr"/>
@@ -25346,7 +25346,7 @@
       <c r="V112" s="7" t="inlineStr"/>
       <c r="W112" s="8" t="inlineStr">
         <is>
-          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
+          <t>edac1b499f84e07ce85894b488f82dc5cd104202</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>1625</v>
+        <v>1555</v>
       </c>
       <c r="D113" s="8" t="n">
         <v>1</v>
@@ -25375,34 +25375,34 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Lombard Street, Bristol, BS3</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="n">
-        <v>485</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="n"/>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
-      <c r="N113" s="8" t="n"/>
+      <c r="N113" s="8" t="n">
+        <v>12036</v>
+      </c>
       <c r="O113" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="8" t="n"/>
       <c r="Q113" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="R113" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S113" s="9" t="inlineStr"/>
@@ -25419,7 +25419,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
+          <t>4d3990c67ed2848296e2aa2fa362730e0557bd43</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
         </is>
       </c>
       <c r="C114" s="17" t="n">
-        <v>2175</v>
+        <v>2085</v>
       </c>
       <c r="D114" s="8" t="n">
         <v>2</v>
@@ -25463,14 +25463,16 @@
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
-      <c r="N114" s="8" t="n"/>
+      <c r="N114" s="8" t="n">
+        <v>21504</v>
+      </c>
       <c r="O114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="8" t="n"/>
       <c r="Q114" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R114" s="8" t="inlineStr">
@@ -25492,7 +25494,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
+          <t>12a5f2c4f1be2a8f1a9b2c6cbe66191abf1d7975</t>
         </is>
       </c>
     </row>
@@ -25506,13 +25508,13 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1900</v>
+        <v>1640</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
@@ -25521,7 +25523,7 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
@@ -25529,24 +25531,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I115" s="8" t="n"/>
+      <c r="I115" s="8" t="n">
+        <v>570</v>
+      </c>
       <c r="J115" s="8" t="n"/>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
-      <c r="N115" s="8" t="n"/>
+      <c r="N115" s="8" t="n">
+        <v>20820</v>
+      </c>
       <c r="O115" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="8" t="n"/>
       <c r="Q115" s="8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R115" s="8" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S115" s="9" t="inlineStr"/>
@@ -25563,7 +25569,7 @@
       <c r="V115" s="7" t="inlineStr"/>
       <c r="W115" s="8" t="inlineStr">
         <is>
-          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
+          <t>f7afd1bbb106a22d180a78614dde509c1dbfa8c1</t>
         </is>
       </c>
     </row>
@@ -25577,13 +25583,13 @@
         </is>
       </c>
       <c r="C116" s="17" t="n">
-        <v>2145</v>
+        <v>1595</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
@@ -25592,7 +25598,7 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
@@ -25601,27 +25607,25 @@
         </is>
       </c>
       <c r="I116" s="8" t="n">
-        <v>796</v>
+        <v>499</v>
       </c>
       <c r="J116" s="8" t="n"/>
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
-      <c r="N116" s="8" t="n">
-        <v>20820</v>
-      </c>
+      <c r="N116" s="8" t="n"/>
       <c r="O116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="8" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R116" s="8" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S116" s="9" t="inlineStr"/>
@@ -25638,7 +25642,7 @@
       <c r="V116" s="7" t="inlineStr"/>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>898ba227d5b949e4e7f18b49536b3c908560d145</t>
+          <t>f2f3afa9f34b35c1d7d84b8e8f6c80b9a91340b1</t>
         </is>
       </c>
     </row>
@@ -25652,13 +25656,13 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
@@ -25667,34 +25671,34 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>Ratcliffe Court, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="n">
+        <v>485</v>
+      </c>
       <c r="J117" s="8" t="n"/>
       <c r="K117" s="8" t="n"/>
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
-      <c r="N117" s="8" t="n">
-        <v>20124</v>
-      </c>
+      <c r="N117" s="8" t="n"/>
       <c r="O117" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="8" t="n"/>
       <c r="Q117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R117" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S117" s="9" t="inlineStr"/>
@@ -25711,7 +25715,7 @@
       <c r="V117" s="7" t="inlineStr"/>
       <c r="W117" s="8" t="inlineStr">
         <is>
-          <t>e9219c4f68722ad3bdeee0c4c4cb31134f26af57</t>
+          <t>ea3758a9fd1b4190b4e5ae17519645f00d2e6a8f</t>
         </is>
       </c>
     </row>
@@ -25725,13 +25729,13 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>1600</v>
+        <v>2175</v>
       </c>
       <c r="D118" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
@@ -25740,34 +25744,34 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I118" s="8" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="n">
+        <v>722</v>
+      </c>
       <c r="J118" s="8" t="n"/>
       <c r="K118" s="8" t="n"/>
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
-      <c r="N118" s="8" t="n">
-        <v>19576</v>
-      </c>
+      <c r="N118" s="8" t="n"/>
       <c r="O118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="8" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R118" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S118" s="9" t="inlineStr"/>
@@ -25784,7 +25788,7 @@
       <c r="V118" s="7" t="inlineStr"/>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>2c4d3b36f040dfa0e294ad99ce0d43b5fa15d6c8</t>
+          <t>ab566c9b065047cd166a2ad3ae56e88704bc1358</t>
         </is>
       </c>
     </row>
@@ -25798,13 +25802,13 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>2175</v>
+        <v>1900</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
@@ -25813,7 +25817,7 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>The Granary, Queen Charlotte Street, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -25833,12 +25837,12 @@
       <c r="P119" s="8" t="n"/>
       <c r="Q119" s="8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R119" s="8" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S119" s="9" t="inlineStr"/>
@@ -25855,7 +25859,7 @@
       <c r="V119" s="7" t="inlineStr"/>
       <c r="W119" s="8" t="inlineStr">
         <is>
-          <t>6a00f91534112c4504453102597619449da3a2c1</t>
+          <t>b19bc62dddbc90526344a15be65fbc2e74a96d22</t>
         </is>
       </c>
     </row>
@@ -25869,13 +25873,13 @@
         </is>
       </c>
       <c r="C120" s="17" t="n">
-        <v>1500</v>
+        <v>2145</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
@@ 